--- a/494/initial.xlsx
+++ b/494/initial.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpwillms\Desktop\LocalCode\494\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpwillms\Desktop\494\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4355848B-F6CD-4AB4-A7B1-8D00C827C03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C196EC0-5B4D-45DF-ABF2-C7F23887907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30975" yWindow="2760" windowWidth="21600" windowHeight="11295" xr2:uid="{92F93940-16D1-494E-8DAD-2FEDD2E887ED}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92F93940-16D1-494E-8DAD-2FEDD2E887ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="344">
   <si>
     <t>Source</t>
   </si>
@@ -1038,13 +1038,46 @@
   </si>
   <si>
     <t>JP_d1</t>
+  </si>
+  <si>
+    <t>H7C6X6</t>
+  </si>
+  <si>
+    <t>Enterococcus faecalis</t>
+  </si>
+  <si>
+    <t>SalB</t>
+  </si>
+  <si>
+    <t>SalB domain 1 (long)</t>
+  </si>
+  <si>
+    <t>SalB domain 2 (globular)</t>
+  </si>
+  <si>
+    <t>MKKRLFASVLLCSLTLSAIATPSIALADNVDKKIEEKNQEISSLKAKQGDLASQVSSLEA EVSSVFDESMALREQKQTLKAKSEQLQQEITNLNQRIEKRNEAIKNQARDVQVNGQSTTM LDAVLDADSVADAISRVQAVSTIVSANNDLMQQQKEDKQAVVDKKAENEKKVKQLEATEA ELETKRQDLLSKQSELNVMKASLALEQSSAESSKAGLEKQKAAAEAEQARLAAEQKAAAE KAKQAAAKPAKAEVKAEAPVASSSTTEAQAPASSSSATESSTQQTTETTTPSTDNSATEN TGSSSSEQPVQPTTPSDNGNNGGQTGGGTVTPTPEPTPAPSADPTINALNVLRQSLGLRP VVWDAGLAASATARAAQVEAGGIPNDHWSRGDEVIAIMWAPGNSVIMAWYNETNMVTASG SGHRDWEINPGITRVGFGYSGSTIVGHSA</t>
+  </si>
+  <si>
+    <t>SIALADNVDKKIEEKNQEISSLKAKQGDLASQVSSLEA EVSSVFDESMALREQKQTLKAKSEQLQQEITNLNQRIEKRNEAIKNQARDVQVNGQSTTM LDAVLDADSVADAISRVQAVSTIVSANNDLMQQQKEDKQAVVDKKAENEKKVKQLEATEA ELETKRQDLLSKQSELNVMKASLALEQSSAESSKAGLEKQKAAAEAEQARLAAEQKAAAE KAKQAAAKPA</t>
+  </si>
+  <si>
+    <t>ADPTINALNVLRQSLGLRP VVWDAGLAASATARAAQVEAGGIPNDHWSRGDEVIAIMWAPGNSVIMAWYNETNMVTASG SGHRDWEINPGITRVGFGYSGSTIVGHSA</t>
+  </si>
+  <si>
+    <t>AF-H7C6X6-F1</t>
+  </si>
+  <si>
+    <t>Sal_d1</t>
+  </si>
+  <si>
+    <t>Sal_d2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1087,6 +1120,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Lato"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1155,7 +1195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1193,6 +1233,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3599,35 +3640,83 @@
         <v>331</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-    </row>
-    <row r="82" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
+    <row r="81" spans="1:8" ht="39.75" thickBot="1">
+      <c r="A81" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" t="s">
+        <v>338</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>80</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="39.75" thickBot="1">
+      <c r="A82" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D82" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" t="s">
+        <v>339</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>81</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="39.75" thickBot="1">
+      <c r="A83" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D83" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" t="s">
+        <v>340</v>
+      </c>
+      <c r="F83" s="1">
+        <v>0</v>
+      </c>
+      <c r="G83" s="1">
+        <v>82</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1">
       <c r="A84" s="1"/>
@@ -12035,6 +12124,7 @@
     <hyperlink ref="C78" r:id="rId62" display="https://www.ebi.ac.uk/interpro/protein/reviewed/C0H3T3/" xr:uid="{2FA58E87-4E9F-4DFC-90E7-38A1D6FBC6DF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId63"/>
 </worksheet>
 </file>
 

--- a/494/initial.xlsx
+++ b/494/initial.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpwillms\Desktop\494\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ac4ce512cbdb248/Desktop/FunctionFromSeq/494/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C196EC0-5B4D-45DF-ABF2-C7F23887907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92F93940-16D1-494E-8DAD-2FEDD2E887ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{92F93940-16D1-494E-8DAD-2FEDD2E887ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1570,9 +1570,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E4D86D5-FB97-47E7-8CDB-3D8247ED0B48}">
   <dimension ref="A1:H917"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="27" thickBot="1">
+    <row r="1" spans="1:8" ht="27.6" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="256.5" thickBot="1">
+    <row r="6" spans="1:8" ht="265.2" thickBot="1">
       <c r="A6" s="5" t="s">
         <v>29</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="294.75" thickBot="1">
+    <row r="7" spans="1:8" ht="304.8" thickBot="1">
       <c r="A7" s="1" t="s">
         <v>33</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="396.75" thickBot="1">
+    <row r="8" spans="1:8" ht="409.6" thickBot="1">
       <c r="A8" s="6" t="s">
         <v>36</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="320.25" thickBot="1">
+    <row r="9" spans="1:8" ht="331.2" thickBot="1">
       <c r="A9" s="7" t="s">
         <v>40</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="384" thickBot="1">
+    <row r="10" spans="1:8" ht="397.2" thickBot="1">
       <c r="A10" s="7" t="s">
         <v>44</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="129" thickBot="1">
+    <row r="11" spans="1:8" ht="133.19999999999999" thickBot="1">
       <c r="A11" s="5" t="s">
         <v>48</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="320.25" thickBot="1">
+    <row r="12" spans="1:8" ht="331.2" thickBot="1">
       <c r="A12" s="5" t="s">
         <v>52</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="218.25" thickBot="1">
+    <row r="16" spans="1:8" ht="225.6" thickBot="1">
       <c r="A16" s="7" t="s">
         <v>65</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="103.5" thickBot="1">
+    <row r="17" spans="1:8" ht="106.8" thickBot="1">
       <c r="A17" s="7" t="s">
         <v>69</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="231" thickBot="1">
+    <row r="18" spans="1:8" ht="238.8" thickBot="1">
       <c r="A18" s="6" t="s">
         <v>73</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="154.5" thickBot="1">
+    <row r="19" spans="1:8" ht="172.8" thickBot="1">
       <c r="A19" s="7" t="s">
         <v>76</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="345.75" thickBot="1">
+    <row r="21" spans="1:8" ht="357.6" thickBot="1">
       <c r="A21" s="7" t="s">
         <v>84</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="231" thickBot="1">
+    <row r="22" spans="1:8" ht="225.6" thickBot="1">
       <c r="A22" s="7" t="s">
         <v>88</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="205.5" thickBot="1">
+    <row r="23" spans="1:8" ht="212.4" thickBot="1">
       <c r="A23" s="7" t="s">
         <v>91</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="205.5" thickBot="1">
+    <row r="24" spans="1:8" ht="212.4" thickBot="1">
       <c r="A24" s="7" t="s">
         <v>95</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="384" thickBot="1">
+    <row r="26" spans="1:8" ht="397.2" thickBot="1">
       <c r="A26" s="7" t="s">
         <v>103</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="371.25" thickBot="1">
+    <row r="30" spans="1:8" ht="397.2" thickBot="1">
       <c r="A30" s="7" t="s">
         <v>118</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="282" thickBot="1">
+    <row r="34" spans="1:8" ht="291.60000000000002" thickBot="1">
       <c r="A34" s="5" t="s">
         <v>134</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="243.75" thickBot="1">
+    <row r="35" spans="1:8" ht="252" thickBot="1">
       <c r="A35" s="7" t="s">
         <v>138</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="371.25" thickBot="1">
+    <row r="36" spans="1:8" ht="384" thickBot="1">
       <c r="A36" s="7" t="s">
         <v>141</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="320.25" thickBot="1">
+    <row r="40" spans="1:8" ht="344.4" thickBot="1">
       <c r="A40" s="6" t="s">
         <v>157</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="345.75" thickBot="1">
+    <row r="44" spans="1:8" ht="357.6" thickBot="1">
       <c r="A44" s="5" t="s">
         <v>175</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="294.75" thickBot="1">
+    <row r="45" spans="1:8" ht="304.8" thickBot="1">
       <c r="A45" s="5" t="s">
         <v>179</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="282" thickBot="1">
+    <row r="46" spans="1:8" ht="291.60000000000002" thickBot="1">
       <c r="A46" s="5" t="s">
         <v>184</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="307.5" thickBot="1">
+    <row r="48" spans="1:8" ht="318" thickBot="1">
       <c r="A48" s="6" t="s">
         <v>191</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="384" thickBot="1">
+    <row r="49" spans="1:8" ht="397.2" thickBot="1">
       <c r="A49" s="7" t="s">
         <v>195</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="333" thickBot="1">
+    <row r="55" spans="1:8" ht="344.4" thickBot="1">
       <c r="A55" s="7" t="s">
         <v>218</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="358.5" thickBot="1">
+    <row r="56" spans="1:8" ht="370.8" thickBot="1">
       <c r="A56" s="7" t="s">
         <v>222</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="243.75" thickBot="1">
+    <row r="63" spans="1:8" ht="252" thickBot="1">
       <c r="A63" s="11" t="s">
         <v>251</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="371.25" thickBot="1">
+    <row r="67" spans="1:8" ht="397.2" thickBot="1">
       <c r="A67" s="11" t="s">
         <v>271</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="345.75" thickBot="1">
+    <row r="69" spans="1:8" ht="357.6" thickBot="1">
       <c r="A69" s="7" t="s">
         <v>280</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="358.5" thickBot="1">
+    <row r="70" spans="1:8" ht="370.8" thickBot="1">
       <c r="A70" s="11" t="s">
         <v>285</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="371.25" thickBot="1">
+    <row r="74" spans="1:8" ht="384" thickBot="1">
       <c r="A74" s="11" t="s">
         <v>304</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="358.5" thickBot="1">
+    <row r="75" spans="1:8" ht="370.8" thickBot="1">
       <c r="A75" s="11" t="s">
         <v>309</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="103.5" thickBot="1">
+    <row r="78" spans="1:8" ht="106.8" thickBot="1">
       <c r="A78" s="11" t="s">
         <v>321</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="269.25" thickBot="1">
+    <row r="79" spans="1:8" ht="278.39999999999998" thickBot="1">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="129" thickBot="1">
+    <row r="80" spans="1:8" ht="133.19999999999999" thickBot="1">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="39.75" thickBot="1">
+    <row r="81" spans="1:8" ht="42.6" thickBot="1">
       <c r="A81" s="13" t="s">
         <v>333</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="39.75" thickBot="1">
+    <row r="82" spans="1:8" ht="42.6" thickBot="1">
       <c r="A82" s="13" t="s">
         <v>333</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="39.75" thickBot="1">
+    <row r="83" spans="1:8" ht="42.6" thickBot="1">
       <c r="A83" s="13" t="s">
         <v>333</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.75" thickBot="1">
+    <row r="84" spans="1:8" ht="15" thickBot="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3728,7 +3728,7 @@
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
     </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1">
+    <row r="85" spans="1:8" ht="15" thickBot="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3738,7 +3738,7 @@
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
     </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1">
+    <row r="86" spans="1:8" ht="15" thickBot="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3748,7 +3748,7 @@
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1">
+    <row r="87" spans="1:8" ht="15" thickBot="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3758,7 +3758,7 @@
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
     </row>
-    <row r="88" spans="1:8" ht="15.75" thickBot="1">
+    <row r="88" spans="1:8" ht="15" thickBot="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3768,7 +3768,7 @@
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1">
+    <row r="89" spans="1:8" ht="15" thickBot="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3778,7 +3778,7 @@
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
     </row>
-    <row r="90" spans="1:8" ht="15.75" thickBot="1">
+    <row r="90" spans="1:8" ht="15" thickBot="1">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3788,7 +3788,7 @@
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:8" ht="15.75" thickBot="1">
+    <row r="91" spans="1:8" ht="15" thickBot="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3798,7 +3798,7 @@
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
     </row>
-    <row r="92" spans="1:8" ht="15.75" thickBot="1">
+    <row r="92" spans="1:8" ht="15" thickBot="1">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3808,7 +3808,7 @@
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
     </row>
-    <row r="93" spans="1:8" ht="15.75" thickBot="1">
+    <row r="93" spans="1:8" ht="15" thickBot="1">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3818,7 +3818,7 @@
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:8" ht="15.75" thickBot="1">
+    <row r="94" spans="1:8" ht="15" thickBot="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3828,7 +3828,7 @@
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
     </row>
-    <row r="95" spans="1:8" ht="15.75" thickBot="1">
+    <row r="95" spans="1:8" ht="15" thickBot="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3838,7 +3838,7 @@
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8" ht="15.75" thickBot="1">
+    <row r="96" spans="1:8" ht="15" thickBot="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3848,7 +3848,7 @@
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:8" ht="15.75" thickBot="1">
+    <row r="97" spans="1:8" ht="15" thickBot="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3858,7 +3858,7 @@
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
     </row>
-    <row r="98" spans="1:8" ht="15.75" thickBot="1">
+    <row r="98" spans="1:8" ht="15" thickBot="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3868,7 +3868,7 @@
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:8" ht="15.75" thickBot="1">
+    <row r="99" spans="1:8" ht="15" thickBot="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3878,7 +3878,7 @@
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:8" ht="15.75" thickBot="1">
+    <row r="100" spans="1:8" ht="15" thickBot="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3888,7 +3888,7 @@
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:8" ht="15.75" thickBot="1">
+    <row r="101" spans="1:8" ht="15" thickBot="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3898,7 +3898,7 @@
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:8" ht="15.75" thickBot="1">
+    <row r="102" spans="1:8" ht="15" thickBot="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3908,7 +3908,7 @@
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:8" ht="15.75" thickBot="1">
+    <row r="103" spans="1:8" ht="15" thickBot="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3918,7 +3918,7 @@
       <c r="G103" s="1"/>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:8" ht="15.75" thickBot="1">
+    <row r="104" spans="1:8" ht="15" thickBot="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3928,7 +3928,7 @@
       <c r="G104" s="1"/>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:8" ht="15.75" thickBot="1">
+    <row r="105" spans="1:8" ht="15" thickBot="1">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3938,7 +3938,7 @@
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:8" ht="15.75" thickBot="1">
+    <row r="106" spans="1:8" ht="15" thickBot="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3948,7 +3948,7 @@
       <c r="G106" s="1"/>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:8" ht="15.75" thickBot="1">
+    <row r="107" spans="1:8" ht="15" thickBot="1">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3958,7 +3958,7 @@
       <c r="G107" s="1"/>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:8" ht="15.75" thickBot="1">
+    <row r="108" spans="1:8" ht="15" thickBot="1">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3968,7 +3968,7 @@
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:8" ht="15.75" thickBot="1">
+    <row r="109" spans="1:8" ht="15" thickBot="1">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3978,7 +3978,7 @@
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:8" ht="15.75" thickBot="1">
+    <row r="110" spans="1:8" ht="15" thickBot="1">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3988,7 +3988,7 @@
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:8" ht="15.75" thickBot="1">
+    <row r="111" spans="1:8" ht="15" thickBot="1">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3998,7 +3998,7 @@
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
     </row>
-    <row r="112" spans="1:8" ht="15.75" thickBot="1">
+    <row r="112" spans="1:8" ht="15" thickBot="1">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4008,7 +4008,7 @@
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
     </row>
-    <row r="113" spans="1:8" ht="15.75" thickBot="1">
+    <row r="113" spans="1:8" ht="15" thickBot="1">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4018,7 +4018,7 @@
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
     </row>
-    <row r="114" spans="1:8" ht="15.75" thickBot="1">
+    <row r="114" spans="1:8" ht="15" thickBot="1">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4028,7 +4028,7 @@
       <c r="G114" s="1"/>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8" ht="15.75" thickBot="1">
+    <row r="115" spans="1:8" ht="15" thickBot="1">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4038,7 +4038,7 @@
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8" ht="15.75" thickBot="1">
+    <row r="116" spans="1:8" ht="15" thickBot="1">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4048,7 +4048,7 @@
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8" ht="15.75" thickBot="1">
+    <row r="117" spans="1:8" ht="15" thickBot="1">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4058,7 +4058,7 @@
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8" ht="15.75" thickBot="1">
+    <row r="118" spans="1:8" ht="15" thickBot="1">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4068,7 +4068,7 @@
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8" ht="15.75" thickBot="1">
+    <row r="119" spans="1:8" ht="15" thickBot="1">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4078,7 +4078,7 @@
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8" ht="15.75" thickBot="1">
+    <row r="120" spans="1:8" ht="15" thickBot="1">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4088,7 +4088,7 @@
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8" ht="15.75" thickBot="1">
+    <row r="121" spans="1:8" ht="15" thickBot="1">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4098,7 +4098,7 @@
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:8" ht="15.75" thickBot="1">
+    <row r="122" spans="1:8" ht="15" thickBot="1">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4108,7 +4108,7 @@
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
     </row>
-    <row r="123" spans="1:8" ht="15.75" thickBot="1">
+    <row r="123" spans="1:8" ht="15" thickBot="1">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4118,7 +4118,7 @@
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8" ht="15.75" thickBot="1">
+    <row r="124" spans="1:8" ht="15" thickBot="1">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4128,7 +4128,7 @@
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:8" ht="15.75" thickBot="1">
+    <row r="125" spans="1:8" ht="15" thickBot="1">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4138,7 +4138,7 @@
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
     </row>
-    <row r="126" spans="1:8" ht="15.75" thickBot="1">
+    <row r="126" spans="1:8" ht="15" thickBot="1">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4148,7 +4148,7 @@
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
     </row>
-    <row r="127" spans="1:8" ht="15.75" thickBot="1">
+    <row r="127" spans="1:8" ht="15" thickBot="1">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4158,7 +4158,7 @@
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8" ht="15.75" thickBot="1">
+    <row r="128" spans="1:8" ht="15" thickBot="1">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4168,7 +4168,7 @@
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:8" ht="15.75" thickBot="1">
+    <row r="129" spans="1:8" ht="15" thickBot="1">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4178,7 +4178,7 @@
       <c r="G129" s="1"/>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:8" ht="15.75" thickBot="1">
+    <row r="130" spans="1:8" ht="15" thickBot="1">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4188,7 +4188,7 @@
       <c r="G130" s="1"/>
       <c r="H130" s="1"/>
     </row>
-    <row r="131" spans="1:8" ht="15.75" thickBot="1">
+    <row r="131" spans="1:8" ht="15" thickBot="1">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4198,7 +4198,7 @@
       <c r="G131" s="1"/>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="1:8" ht="15.75" thickBot="1">
+    <row r="132" spans="1:8" ht="15" thickBot="1">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4208,7 +4208,7 @@
       <c r="G132" s="1"/>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:8" ht="15.75" thickBot="1">
+    <row r="133" spans="1:8" ht="15" thickBot="1">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4218,7 +4218,7 @@
       <c r="G133" s="1"/>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:8" ht="15.75" thickBot="1">
+    <row r="134" spans="1:8" ht="15" thickBot="1">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4228,7 +4228,7 @@
       <c r="G134" s="1"/>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:8" ht="15.75" thickBot="1">
+    <row r="135" spans="1:8" ht="15" thickBot="1">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4238,7 +4238,7 @@
       <c r="G135" s="1"/>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:8" ht="15.75" thickBot="1">
+    <row r="136" spans="1:8" ht="15" thickBot="1">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4248,7 +4248,7 @@
       <c r="G136" s="1"/>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:8" ht="15.75" thickBot="1">
+    <row r="137" spans="1:8" ht="15" thickBot="1">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4258,7 +4258,7 @@
       <c r="G137" s="1"/>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:8" ht="15.75" thickBot="1">
+    <row r="138" spans="1:8" ht="15" thickBot="1">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4268,7 +4268,7 @@
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
     </row>
-    <row r="139" spans="1:8" ht="15.75" thickBot="1">
+    <row r="139" spans="1:8" ht="15" thickBot="1">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4278,7 +4278,7 @@
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
     </row>
-    <row r="140" spans="1:8" ht="15.75" thickBot="1">
+    <row r="140" spans="1:8" ht="15" thickBot="1">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4288,7 +4288,7 @@
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
     </row>
-    <row r="141" spans="1:8" ht="15.75" thickBot="1">
+    <row r="141" spans="1:8" ht="15" thickBot="1">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4298,7 +4298,7 @@
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
     </row>
-    <row r="142" spans="1:8" ht="15.75" thickBot="1">
+    <row r="142" spans="1:8" ht="15" thickBot="1">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4308,7 +4308,7 @@
       <c r="G142" s="1"/>
       <c r="H142" s="1"/>
     </row>
-    <row r="143" spans="1:8" ht="15.75" thickBot="1">
+    <row r="143" spans="1:8" ht="15" thickBot="1">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4318,7 +4318,7 @@
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
     </row>
-    <row r="144" spans="1:8" ht="15.75" thickBot="1">
+    <row r="144" spans="1:8" ht="15" thickBot="1">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4328,7 +4328,7 @@
       <c r="G144" s="1"/>
       <c r="H144" s="1"/>
     </row>
-    <row r="145" spans="1:8" ht="15.75" thickBot="1">
+    <row r="145" spans="1:8" ht="15" thickBot="1">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4338,7 +4338,7 @@
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
     </row>
-    <row r="146" spans="1:8" ht="15.75" thickBot="1">
+    <row r="146" spans="1:8" ht="15" thickBot="1">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4348,7 +4348,7 @@
       <c r="G146" s="1"/>
       <c r="H146" s="1"/>
     </row>
-    <row r="147" spans="1:8" ht="15.75" thickBot="1">
+    <row r="147" spans="1:8" ht="15" thickBot="1">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4358,7 +4358,7 @@
       <c r="G147" s="1"/>
       <c r="H147" s="1"/>
     </row>
-    <row r="148" spans="1:8" ht="15.75" thickBot="1">
+    <row r="148" spans="1:8" ht="15" thickBot="1">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4368,7 +4368,7 @@
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
     </row>
-    <row r="149" spans="1:8" ht="15.75" thickBot="1">
+    <row r="149" spans="1:8" ht="15" thickBot="1">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4378,7 +4378,7 @@
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
     </row>
-    <row r="150" spans="1:8" ht="15.75" thickBot="1">
+    <row r="150" spans="1:8" ht="15" thickBot="1">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4388,7 +4388,7 @@
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
     </row>
-    <row r="151" spans="1:8" ht="15.75" thickBot="1">
+    <row r="151" spans="1:8" ht="15" thickBot="1">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4398,7 +4398,7 @@
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
     </row>
-    <row r="152" spans="1:8" ht="15.75" thickBot="1">
+    <row r="152" spans="1:8" ht="15" thickBot="1">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4408,7 +4408,7 @@
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
     </row>
-    <row r="153" spans="1:8" ht="15.75" thickBot="1">
+    <row r="153" spans="1:8" ht="15" thickBot="1">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4418,7 +4418,7 @@
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
     </row>
-    <row r="154" spans="1:8" ht="15.75" thickBot="1">
+    <row r="154" spans="1:8" ht="15" thickBot="1">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4428,7 +4428,7 @@
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
     </row>
-    <row r="155" spans="1:8" ht="15.75" thickBot="1">
+    <row r="155" spans="1:8" ht="15" thickBot="1">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4438,7 +4438,7 @@
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
     </row>
-    <row r="156" spans="1:8" ht="15.75" thickBot="1">
+    <row r="156" spans="1:8" ht="15" thickBot="1">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4448,7 +4448,7 @@
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
     </row>
-    <row r="157" spans="1:8" ht="15.75" thickBot="1">
+    <row r="157" spans="1:8" ht="15" thickBot="1">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4458,7 +4458,7 @@
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
     </row>
-    <row r="158" spans="1:8" ht="15.75" thickBot="1">
+    <row r="158" spans="1:8" ht="15" thickBot="1">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4468,7 +4468,7 @@
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
     </row>
-    <row r="159" spans="1:8" ht="15.75" thickBot="1">
+    <row r="159" spans="1:8" ht="15" thickBot="1">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4478,7 +4478,7 @@
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
     </row>
-    <row r="160" spans="1:8" ht="15.75" thickBot="1">
+    <row r="160" spans="1:8" ht="15" thickBot="1">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4488,7 +4488,7 @@
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
     </row>
-    <row r="161" spans="1:8" ht="15.75" thickBot="1">
+    <row r="161" spans="1:8" ht="15" thickBot="1">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4498,7 +4498,7 @@
       <c r="G161" s="1"/>
       <c r="H161" s="1"/>
     </row>
-    <row r="162" spans="1:8" ht="15.75" thickBot="1">
+    <row r="162" spans="1:8" ht="15" thickBot="1">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4508,7 +4508,7 @@
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
     </row>
-    <row r="163" spans="1:8" ht="15.75" thickBot="1">
+    <row r="163" spans="1:8" ht="15" thickBot="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4518,7 +4518,7 @@
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
     </row>
-    <row r="164" spans="1:8" ht="15.75" thickBot="1">
+    <row r="164" spans="1:8" ht="15" thickBot="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -4528,7 +4528,7 @@
       <c r="G164" s="1"/>
       <c r="H164" s="1"/>
     </row>
-    <row r="165" spans="1:8" ht="15.75" thickBot="1">
+    <row r="165" spans="1:8" ht="15" thickBot="1">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -4538,7 +4538,7 @@
       <c r="G165" s="1"/>
       <c r="H165" s="1"/>
     </row>
-    <row r="166" spans="1:8" ht="15.75" thickBot="1">
+    <row r="166" spans="1:8" ht="15" thickBot="1">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -4548,7 +4548,7 @@
       <c r="G166" s="1"/>
       <c r="H166" s="1"/>
     </row>
-    <row r="167" spans="1:8" ht="15.75" thickBot="1">
+    <row r="167" spans="1:8" ht="15" thickBot="1">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -4558,7 +4558,7 @@
       <c r="G167" s="1"/>
       <c r="H167" s="1"/>
     </row>
-    <row r="168" spans="1:8" ht="15.75" thickBot="1">
+    <row r="168" spans="1:8" ht="15" thickBot="1">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -4568,7 +4568,7 @@
       <c r="G168" s="1"/>
       <c r="H168" s="1"/>
     </row>
-    <row r="169" spans="1:8" ht="15.75" thickBot="1">
+    <row r="169" spans="1:8" ht="15" thickBot="1">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -4578,7 +4578,7 @@
       <c r="G169" s="1"/>
       <c r="H169" s="1"/>
     </row>
-    <row r="170" spans="1:8" ht="15.75" thickBot="1">
+    <row r="170" spans="1:8" ht="15" thickBot="1">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -4588,7 +4588,7 @@
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
     </row>
-    <row r="171" spans="1:8" ht="15.75" thickBot="1">
+    <row r="171" spans="1:8" ht="15" thickBot="1">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -4598,7 +4598,7 @@
       <c r="G171" s="1"/>
       <c r="H171" s="1"/>
     </row>
-    <row r="172" spans="1:8" ht="15.75" thickBot="1">
+    <row r="172" spans="1:8" ht="15" thickBot="1">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -4608,7 +4608,7 @@
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
     </row>
-    <row r="173" spans="1:8" ht="15.75" thickBot="1">
+    <row r="173" spans="1:8" ht="15" thickBot="1">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -4618,7 +4618,7 @@
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
     </row>
-    <row r="174" spans="1:8" ht="15.75" thickBot="1">
+    <row r="174" spans="1:8" ht="15" thickBot="1">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -4628,7 +4628,7 @@
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
     </row>
-    <row r="175" spans="1:8" ht="15.75" thickBot="1">
+    <row r="175" spans="1:8" ht="15" thickBot="1">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -4638,7 +4638,7 @@
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
     </row>
-    <row r="176" spans="1:8" ht="15.75" thickBot="1">
+    <row r="176" spans="1:8" ht="15" thickBot="1">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -4648,7 +4648,7 @@
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="1:8" ht="15.75" thickBot="1">
+    <row r="177" spans="1:8" ht="15" thickBot="1">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -4658,7 +4658,7 @@
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="1:8" ht="15.75" thickBot="1">
+    <row r="178" spans="1:8" ht="15" thickBot="1">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -4668,7 +4668,7 @@
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="1:8" ht="15.75" thickBot="1">
+    <row r="179" spans="1:8" ht="15" thickBot="1">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -4678,7 +4678,7 @@
       <c r="G179" s="1"/>
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="1:8" ht="15.75" thickBot="1">
+    <row r="180" spans="1:8" ht="15" thickBot="1">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -4688,7 +4688,7 @@
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="1:8" ht="15.75" thickBot="1">
+    <row r="181" spans="1:8" ht="15" thickBot="1">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -4698,7 +4698,7 @@
       <c r="G181" s="1"/>
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="1:8" ht="15.75" thickBot="1">
+    <row r="182" spans="1:8" ht="15" thickBot="1">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -4708,7 +4708,7 @@
       <c r="G182" s="1"/>
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="1:8" ht="15.75" thickBot="1">
+    <row r="183" spans="1:8" ht="15" thickBot="1">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -4718,7 +4718,7 @@
       <c r="G183" s="1"/>
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="1:8" ht="15.75" thickBot="1">
+    <row r="184" spans="1:8" ht="15" thickBot="1">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -4728,7 +4728,7 @@
       <c r="G184" s="1"/>
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="1:8" ht="15.75" thickBot="1">
+    <row r="185" spans="1:8" ht="15" thickBot="1">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -4738,7 +4738,7 @@
       <c r="G185" s="1"/>
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="1:8" ht="15.75" thickBot="1">
+    <row r="186" spans="1:8" ht="15" thickBot="1">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -4748,7 +4748,7 @@
       <c r="G186" s="1"/>
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="1:8" ht="15.75" thickBot="1">
+    <row r="187" spans="1:8" ht="15" thickBot="1">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -4758,7 +4758,7 @@
       <c r="G187" s="1"/>
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="1:8" ht="15.75" thickBot="1">
+    <row r="188" spans="1:8" ht="15" thickBot="1">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -4768,7 +4768,7 @@
       <c r="G188" s="1"/>
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="1:8" ht="15.75" thickBot="1">
+    <row r="189" spans="1:8" ht="15" thickBot="1">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -4778,7 +4778,7 @@
       <c r="G189" s="1"/>
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="1:8" ht="15.75" thickBot="1">
+    <row r="190" spans="1:8" ht="15" thickBot="1">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -4788,7 +4788,7 @@
       <c r="G190" s="1"/>
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="1:8" ht="15.75" thickBot="1">
+    <row r="191" spans="1:8" ht="15" thickBot="1">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -4798,7 +4798,7 @@
       <c r="G191" s="1"/>
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="1:8" ht="15.75" thickBot="1">
+    <row r="192" spans="1:8" ht="15" thickBot="1">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -4808,7 +4808,7 @@
       <c r="G192" s="1"/>
       <c r="H192" s="1"/>
     </row>
-    <row r="193" spans="1:8" ht="15.75" thickBot="1">
+    <row r="193" spans="1:8" ht="15" thickBot="1">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -4818,7 +4818,7 @@
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
     </row>
-    <row r="194" spans="1:8" ht="15.75" thickBot="1">
+    <row r="194" spans="1:8" ht="15" thickBot="1">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -4828,7 +4828,7 @@
       <c r="G194" s="1"/>
       <c r="H194" s="1"/>
     </row>
-    <row r="195" spans="1:8" ht="15.75" thickBot="1">
+    <row r="195" spans="1:8" ht="15" thickBot="1">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -4838,7 +4838,7 @@
       <c r="G195" s="1"/>
       <c r="H195" s="1"/>
     </row>
-    <row r="196" spans="1:8" ht="15.75" thickBot="1">
+    <row r="196" spans="1:8" ht="15" thickBot="1">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -4848,7 +4848,7 @@
       <c r="G196" s="1"/>
       <c r="H196" s="1"/>
     </row>
-    <row r="197" spans="1:8" ht="15.75" thickBot="1">
+    <row r="197" spans="1:8" ht="15" thickBot="1">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -4858,7 +4858,7 @@
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
     </row>
-    <row r="198" spans="1:8" ht="15.75" thickBot="1">
+    <row r="198" spans="1:8" ht="15" thickBot="1">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -4868,7 +4868,7 @@
       <c r="G198" s="1"/>
       <c r="H198" s="1"/>
     </row>
-    <row r="199" spans="1:8" ht="15.75" thickBot="1">
+    <row r="199" spans="1:8" ht="15" thickBot="1">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -4878,7 +4878,7 @@
       <c r="G199" s="1"/>
       <c r="H199" s="1"/>
     </row>
-    <row r="200" spans="1:8" ht="15.75" thickBot="1">
+    <row r="200" spans="1:8" ht="15" thickBot="1">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -4888,7 +4888,7 @@
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
     </row>
-    <row r="201" spans="1:8" ht="15.75" thickBot="1">
+    <row r="201" spans="1:8" ht="15" thickBot="1">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -4898,7 +4898,7 @@
       <c r="G201" s="1"/>
       <c r="H201" s="1"/>
     </row>
-    <row r="202" spans="1:8" ht="15.75" thickBot="1">
+    <row r="202" spans="1:8" ht="15" thickBot="1">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -4908,7 +4908,7 @@
       <c r="G202" s="1"/>
       <c r="H202" s="1"/>
     </row>
-    <row r="203" spans="1:8" ht="15.75" thickBot="1">
+    <row r="203" spans="1:8" ht="15" thickBot="1">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -4918,7 +4918,7 @@
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
     </row>
-    <row r="204" spans="1:8" ht="15.75" thickBot="1">
+    <row r="204" spans="1:8" ht="15" thickBot="1">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -4928,7 +4928,7 @@
       <c r="G204" s="1"/>
       <c r="H204" s="1"/>
     </row>
-    <row r="205" spans="1:8" ht="15.75" thickBot="1">
+    <row r="205" spans="1:8" ht="15" thickBot="1">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -4938,7 +4938,7 @@
       <c r="G205" s="1"/>
       <c r="H205" s="1"/>
     </row>
-    <row r="206" spans="1:8" ht="15.75" thickBot="1">
+    <row r="206" spans="1:8" ht="15" thickBot="1">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -4948,7 +4948,7 @@
       <c r="G206" s="1"/>
       <c r="H206" s="1"/>
     </row>
-    <row r="207" spans="1:8" ht="15.75" thickBot="1">
+    <row r="207" spans="1:8" ht="15" thickBot="1">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -4958,7 +4958,7 @@
       <c r="G207" s="1"/>
       <c r="H207" s="1"/>
     </row>
-    <row r="208" spans="1:8" ht="15.75" thickBot="1">
+    <row r="208" spans="1:8" ht="15" thickBot="1">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -4968,7 +4968,7 @@
       <c r="G208" s="1"/>
       <c r="H208" s="1"/>
     </row>
-    <row r="209" spans="1:8" ht="15.75" thickBot="1">
+    <row r="209" spans="1:8" ht="15" thickBot="1">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -4978,7 +4978,7 @@
       <c r="G209" s="1"/>
       <c r="H209" s="1"/>
     </row>
-    <row r="210" spans="1:8" ht="15.75" thickBot="1">
+    <row r="210" spans="1:8" ht="15" thickBot="1">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -4988,7 +4988,7 @@
       <c r="G210" s="1"/>
       <c r="H210" s="1"/>
     </row>
-    <row r="211" spans="1:8" ht="15.75" thickBot="1">
+    <row r="211" spans="1:8" ht="15" thickBot="1">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -4998,7 +4998,7 @@
       <c r="G211" s="1"/>
       <c r="H211" s="1"/>
     </row>
-    <row r="212" spans="1:8" ht="15.75" thickBot="1">
+    <row r="212" spans="1:8" ht="15" thickBot="1">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -5008,7 +5008,7 @@
       <c r="G212" s="1"/>
       <c r="H212" s="1"/>
     </row>
-    <row r="213" spans="1:8" ht="15.75" thickBot="1">
+    <row r="213" spans="1:8" ht="15" thickBot="1">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -5018,7 +5018,7 @@
       <c r="G213" s="1"/>
       <c r="H213" s="1"/>
     </row>
-    <row r="214" spans="1:8" ht="15.75" thickBot="1">
+    <row r="214" spans="1:8" ht="15" thickBot="1">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -5028,7 +5028,7 @@
       <c r="G214" s="1"/>
       <c r="H214" s="1"/>
     </row>
-    <row r="215" spans="1:8" ht="15.75" thickBot="1">
+    <row r="215" spans="1:8" ht="15" thickBot="1">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -5038,7 +5038,7 @@
       <c r="G215" s="1"/>
       <c r="H215" s="1"/>
     </row>
-    <row r="216" spans="1:8" ht="15.75" thickBot="1">
+    <row r="216" spans="1:8" ht="15" thickBot="1">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -5048,7 +5048,7 @@
       <c r="G216" s="1"/>
       <c r="H216" s="1"/>
     </row>
-    <row r="217" spans="1:8" ht="15.75" thickBot="1">
+    <row r="217" spans="1:8" ht="15" thickBot="1">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -5058,7 +5058,7 @@
       <c r="G217" s="1"/>
       <c r="H217" s="1"/>
     </row>
-    <row r="218" spans="1:8" ht="15.75" thickBot="1">
+    <row r="218" spans="1:8" ht="15" thickBot="1">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -5068,7 +5068,7 @@
       <c r="G218" s="1"/>
       <c r="H218" s="1"/>
     </row>
-    <row r="219" spans="1:8" ht="15.75" thickBot="1">
+    <row r="219" spans="1:8" ht="15" thickBot="1">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -5078,7 +5078,7 @@
       <c r="G219" s="1"/>
       <c r="H219" s="1"/>
     </row>
-    <row r="220" spans="1:8" ht="15.75" thickBot="1">
+    <row r="220" spans="1:8" ht="15" thickBot="1">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -5088,7 +5088,7 @@
       <c r="G220" s="1"/>
       <c r="H220" s="1"/>
     </row>
-    <row r="221" spans="1:8" ht="15.75" thickBot="1">
+    <row r="221" spans="1:8" ht="15" thickBot="1">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -5098,7 +5098,7 @@
       <c r="G221" s="1"/>
       <c r="H221" s="1"/>
     </row>
-    <row r="222" spans="1:8" ht="15.75" thickBot="1">
+    <row r="222" spans="1:8" ht="15" thickBot="1">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -5108,7 +5108,7 @@
       <c r="G222" s="1"/>
       <c r="H222" s="1"/>
     </row>
-    <row r="223" spans="1:8" ht="15.75" thickBot="1">
+    <row r="223" spans="1:8" ht="15" thickBot="1">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -5118,7 +5118,7 @@
       <c r="G223" s="1"/>
       <c r="H223" s="1"/>
     </row>
-    <row r="224" spans="1:8" ht="15.75" thickBot="1">
+    <row r="224" spans="1:8" ht="15" thickBot="1">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -5128,7 +5128,7 @@
       <c r="G224" s="1"/>
       <c r="H224" s="1"/>
     </row>
-    <row r="225" spans="1:8" ht="15.75" thickBot="1">
+    <row r="225" spans="1:8" ht="15" thickBot="1">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -5138,7 +5138,7 @@
       <c r="G225" s="1"/>
       <c r="H225" s="1"/>
     </row>
-    <row r="226" spans="1:8" ht="15.75" thickBot="1">
+    <row r="226" spans="1:8" ht="15" thickBot="1">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -5148,7 +5148,7 @@
       <c r="G226" s="1"/>
       <c r="H226" s="1"/>
     </row>
-    <row r="227" spans="1:8" ht="15.75" thickBot="1">
+    <row r="227" spans="1:8" ht="15" thickBot="1">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -5158,7 +5158,7 @@
       <c r="G227" s="1"/>
       <c r="H227" s="1"/>
     </row>
-    <row r="228" spans="1:8" ht="15.75" thickBot="1">
+    <row r="228" spans="1:8" ht="15" thickBot="1">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -5168,7 +5168,7 @@
       <c r="G228" s="1"/>
       <c r="H228" s="1"/>
     </row>
-    <row r="229" spans="1:8" ht="15.75" thickBot="1">
+    <row r="229" spans="1:8" ht="15" thickBot="1">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -5178,7 +5178,7 @@
       <c r="G229" s="1"/>
       <c r="H229" s="1"/>
     </row>
-    <row r="230" spans="1:8" ht="15.75" thickBot="1">
+    <row r="230" spans="1:8" ht="15" thickBot="1">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -5188,7 +5188,7 @@
       <c r="G230" s="1"/>
       <c r="H230" s="1"/>
     </row>
-    <row r="231" spans="1:8" ht="15.75" thickBot="1">
+    <row r="231" spans="1:8" ht="15" thickBot="1">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -5198,7 +5198,7 @@
       <c r="G231" s="1"/>
       <c r="H231" s="1"/>
     </row>
-    <row r="232" spans="1:8" ht="15.75" thickBot="1">
+    <row r="232" spans="1:8" ht="15" thickBot="1">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -5208,7 +5208,7 @@
       <c r="G232" s="1"/>
       <c r="H232" s="1"/>
     </row>
-    <row r="233" spans="1:8" ht="15.75" thickBot="1">
+    <row r="233" spans="1:8" ht="15" thickBot="1">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -5218,7 +5218,7 @@
       <c r="G233" s="1"/>
       <c r="H233" s="1"/>
     </row>
-    <row r="234" spans="1:8" ht="15.75" thickBot="1">
+    <row r="234" spans="1:8" ht="15" thickBot="1">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -5228,7 +5228,7 @@
       <c r="G234" s="1"/>
       <c r="H234" s="1"/>
     </row>
-    <row r="235" spans="1:8" ht="15.75" thickBot="1">
+    <row r="235" spans="1:8" ht="15" thickBot="1">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -5238,7 +5238,7 @@
       <c r="G235" s="1"/>
       <c r="H235" s="1"/>
     </row>
-    <row r="236" spans="1:8" ht="15.75" thickBot="1">
+    <row r="236" spans="1:8" ht="15" thickBot="1">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -5248,7 +5248,7 @@
       <c r="G236" s="1"/>
       <c r="H236" s="1"/>
     </row>
-    <row r="237" spans="1:8" ht="15.75" thickBot="1">
+    <row r="237" spans="1:8" ht="15" thickBot="1">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -5258,7 +5258,7 @@
       <c r="G237" s="1"/>
       <c r="H237" s="1"/>
     </row>
-    <row r="238" spans="1:8" ht="15.75" thickBot="1">
+    <row r="238" spans="1:8" ht="15" thickBot="1">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -5268,7 +5268,7 @@
       <c r="G238" s="1"/>
       <c r="H238" s="1"/>
     </row>
-    <row r="239" spans="1:8" ht="15.75" thickBot="1">
+    <row r="239" spans="1:8" ht="15" thickBot="1">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -5278,7 +5278,7 @@
       <c r="G239" s="1"/>
       <c r="H239" s="1"/>
     </row>
-    <row r="240" spans="1:8" ht="15.75" thickBot="1">
+    <row r="240" spans="1:8" ht="15" thickBot="1">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -5288,7 +5288,7 @@
       <c r="G240" s="1"/>
       <c r="H240" s="1"/>
     </row>
-    <row r="241" spans="1:8" ht="15.75" thickBot="1">
+    <row r="241" spans="1:8" ht="15" thickBot="1">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -5298,7 +5298,7 @@
       <c r="G241" s="1"/>
       <c r="H241" s="1"/>
     </row>
-    <row r="242" spans="1:8" ht="15.75" thickBot="1">
+    <row r="242" spans="1:8" ht="15" thickBot="1">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -5308,7 +5308,7 @@
       <c r="G242" s="1"/>
       <c r="H242" s="1"/>
     </row>
-    <row r="243" spans="1:8" ht="15.75" thickBot="1">
+    <row r="243" spans="1:8" ht="15" thickBot="1">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -5318,7 +5318,7 @@
       <c r="G243" s="1"/>
       <c r="H243" s="1"/>
     </row>
-    <row r="244" spans="1:8" ht="15.75" thickBot="1">
+    <row r="244" spans="1:8" ht="15" thickBot="1">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -5328,7 +5328,7 @@
       <c r="G244" s="1"/>
       <c r="H244" s="1"/>
     </row>
-    <row r="245" spans="1:8" ht="15.75" thickBot="1">
+    <row r="245" spans="1:8" ht="15" thickBot="1">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -5338,7 +5338,7 @@
       <c r="G245" s="1"/>
       <c r="H245" s="1"/>
     </row>
-    <row r="246" spans="1:8" ht="15.75" thickBot="1">
+    <row r="246" spans="1:8" ht="15" thickBot="1">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -5348,7 +5348,7 @@
       <c r="G246" s="1"/>
       <c r="H246" s="1"/>
     </row>
-    <row r="247" spans="1:8" ht="15.75" thickBot="1">
+    <row r="247" spans="1:8" ht="15" thickBot="1">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -5358,7 +5358,7 @@
       <c r="G247" s="1"/>
       <c r="H247" s="1"/>
     </row>
-    <row r="248" spans="1:8" ht="15.75" thickBot="1">
+    <row r="248" spans="1:8" ht="15" thickBot="1">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -5368,7 +5368,7 @@
       <c r="G248" s="1"/>
       <c r="H248" s="1"/>
     </row>
-    <row r="249" spans="1:8" ht="15.75" thickBot="1">
+    <row r="249" spans="1:8" ht="15" thickBot="1">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -5378,7 +5378,7 @@
       <c r="G249" s="1"/>
       <c r="H249" s="1"/>
     </row>
-    <row r="250" spans="1:8" ht="15.75" thickBot="1">
+    <row r="250" spans="1:8" ht="15" thickBot="1">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -5388,7 +5388,7 @@
       <c r="G250" s="1"/>
       <c r="H250" s="1"/>
     </row>
-    <row r="251" spans="1:8" ht="15.75" thickBot="1">
+    <row r="251" spans="1:8" ht="15" thickBot="1">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -5398,7 +5398,7 @@
       <c r="G251" s="1"/>
       <c r="H251" s="1"/>
     </row>
-    <row r="252" spans="1:8" ht="15.75" thickBot="1">
+    <row r="252" spans="1:8" ht="15" thickBot="1">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -5408,7 +5408,7 @@
       <c r="G252" s="1"/>
       <c r="H252" s="1"/>
     </row>
-    <row r="253" spans="1:8" ht="15.75" thickBot="1">
+    <row r="253" spans="1:8" ht="15" thickBot="1">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -5418,7 +5418,7 @@
       <c r="G253" s="1"/>
       <c r="H253" s="1"/>
     </row>
-    <row r="254" spans="1:8" ht="15.75" thickBot="1">
+    <row r="254" spans="1:8" ht="15" thickBot="1">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -5428,7 +5428,7 @@
       <c r="G254" s="1"/>
       <c r="H254" s="1"/>
     </row>
-    <row r="255" spans="1:8" ht="15.75" thickBot="1">
+    <row r="255" spans="1:8" ht="15" thickBot="1">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -5438,7 +5438,7 @@
       <c r="G255" s="1"/>
       <c r="H255" s="1"/>
     </row>
-    <row r="256" spans="1:8" ht="15.75" thickBot="1">
+    <row r="256" spans="1:8" ht="15" thickBot="1">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -5448,7 +5448,7 @@
       <c r="G256" s="1"/>
       <c r="H256" s="1"/>
     </row>
-    <row r="257" spans="1:8" ht="15.75" thickBot="1">
+    <row r="257" spans="1:8" ht="15" thickBot="1">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -5458,7 +5458,7 @@
       <c r="G257" s="1"/>
       <c r="H257" s="1"/>
     </row>
-    <row r="258" spans="1:8" ht="15.75" thickBot="1">
+    <row r="258" spans="1:8" ht="15" thickBot="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -5468,7 +5468,7 @@
       <c r="G258" s="1"/>
       <c r="H258" s="1"/>
     </row>
-    <row r="259" spans="1:8" ht="15.75" thickBot="1">
+    <row r="259" spans="1:8" ht="15" thickBot="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -5478,7 +5478,7 @@
       <c r="G259" s="1"/>
       <c r="H259" s="1"/>
     </row>
-    <row r="260" spans="1:8" ht="15.75" thickBot="1">
+    <row r="260" spans="1:8" ht="15" thickBot="1">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -5488,7 +5488,7 @@
       <c r="G260" s="1"/>
       <c r="H260" s="1"/>
     </row>
-    <row r="261" spans="1:8" ht="15.75" thickBot="1">
+    <row r="261" spans="1:8" ht="15" thickBot="1">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -5498,7 +5498,7 @@
       <c r="G261" s="1"/>
       <c r="H261" s="1"/>
     </row>
-    <row r="262" spans="1:8" ht="15.75" thickBot="1">
+    <row r="262" spans="1:8" ht="15" thickBot="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -5508,7 +5508,7 @@
       <c r="G262" s="1"/>
       <c r="H262" s="1"/>
     </row>
-    <row r="263" spans="1:8" ht="15.75" thickBot="1">
+    <row r="263" spans="1:8" ht="15" thickBot="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -5518,7 +5518,7 @@
       <c r="G263" s="1"/>
       <c r="H263" s="1"/>
     </row>
-    <row r="264" spans="1:8" ht="15.75" thickBot="1">
+    <row r="264" spans="1:8" ht="15" thickBot="1">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -5528,7 +5528,7 @@
       <c r="G264" s="1"/>
       <c r="H264" s="1"/>
     </row>
-    <row r="265" spans="1:8" ht="15.75" thickBot="1">
+    <row r="265" spans="1:8" ht="15" thickBot="1">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -5538,7 +5538,7 @@
       <c r="G265" s="1"/>
       <c r="H265" s="1"/>
     </row>
-    <row r="266" spans="1:8" ht="15.75" thickBot="1">
+    <row r="266" spans="1:8" ht="15" thickBot="1">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -5548,7 +5548,7 @@
       <c r="G266" s="1"/>
       <c r="H266" s="1"/>
     </row>
-    <row r="267" spans="1:8" ht="15.75" thickBot="1">
+    <row r="267" spans="1:8" ht="15" thickBot="1">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -5558,7 +5558,7 @@
       <c r="G267" s="1"/>
       <c r="H267" s="1"/>
     </row>
-    <row r="268" spans="1:8" ht="15.75" thickBot="1">
+    <row r="268" spans="1:8" ht="15" thickBot="1">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -5568,7 +5568,7 @@
       <c r="G268" s="1"/>
       <c r="H268" s="1"/>
     </row>
-    <row r="269" spans="1:8" ht="15.75" thickBot="1">
+    <row r="269" spans="1:8" ht="15" thickBot="1">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -5578,7 +5578,7 @@
       <c r="G269" s="1"/>
       <c r="H269" s="1"/>
     </row>
-    <row r="270" spans="1:8" ht="15.75" thickBot="1">
+    <row r="270" spans="1:8" ht="15" thickBot="1">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -5588,7 +5588,7 @@
       <c r="G270" s="1"/>
       <c r="H270" s="1"/>
     </row>
-    <row r="271" spans="1:8" ht="15.75" thickBot="1">
+    <row r="271" spans="1:8" ht="15" thickBot="1">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -5598,7 +5598,7 @@
       <c r="G271" s="1"/>
       <c r="H271" s="1"/>
     </row>
-    <row r="272" spans="1:8" ht="15.75" thickBot="1">
+    <row r="272" spans="1:8" ht="15" thickBot="1">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -5608,7 +5608,7 @@
       <c r="G272" s="1"/>
       <c r="H272" s="1"/>
     </row>
-    <row r="273" spans="1:8" ht="15.75" thickBot="1">
+    <row r="273" spans="1:8" ht="15" thickBot="1">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -5618,7 +5618,7 @@
       <c r="G273" s="1"/>
       <c r="H273" s="1"/>
     </row>
-    <row r="274" spans="1:8" ht="15.75" thickBot="1">
+    <row r="274" spans="1:8" ht="15" thickBot="1">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -5628,7 +5628,7 @@
       <c r="G274" s="1"/>
       <c r="H274" s="1"/>
     </row>
-    <row r="275" spans="1:8" ht="15.75" thickBot="1">
+    <row r="275" spans="1:8" ht="15" thickBot="1">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -5638,7 +5638,7 @@
       <c r="G275" s="1"/>
       <c r="H275" s="1"/>
     </row>
-    <row r="276" spans="1:8" ht="15.75" thickBot="1">
+    <row r="276" spans="1:8" ht="15" thickBot="1">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -5648,7 +5648,7 @@
       <c r="G276" s="1"/>
       <c r="H276" s="1"/>
     </row>
-    <row r="277" spans="1:8" ht="15.75" thickBot="1">
+    <row r="277" spans="1:8" ht="15" thickBot="1">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -5658,7 +5658,7 @@
       <c r="G277" s="1"/>
       <c r="H277" s="1"/>
     </row>
-    <row r="278" spans="1:8" ht="15.75" thickBot="1">
+    <row r="278" spans="1:8" ht="15" thickBot="1">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -5668,7 +5668,7 @@
       <c r="G278" s="1"/>
       <c r="H278" s="1"/>
     </row>
-    <row r="279" spans="1:8" ht="15.75" thickBot="1">
+    <row r="279" spans="1:8" ht="15" thickBot="1">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -5678,7 +5678,7 @@
       <c r="G279" s="1"/>
       <c r="H279" s="1"/>
     </row>
-    <row r="280" spans="1:8" ht="15.75" thickBot="1">
+    <row r="280" spans="1:8" ht="15" thickBot="1">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -5688,7 +5688,7 @@
       <c r="G280" s="1"/>
       <c r="H280" s="1"/>
     </row>
-    <row r="281" spans="1:8" ht="15.75" thickBot="1">
+    <row r="281" spans="1:8" ht="15" thickBot="1">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -5698,7 +5698,7 @@
       <c r="G281" s="1"/>
       <c r="H281" s="1"/>
     </row>
-    <row r="282" spans="1:8" ht="15.75" thickBot="1">
+    <row r="282" spans="1:8" ht="15" thickBot="1">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -5708,7 +5708,7 @@
       <c r="G282" s="1"/>
       <c r="H282" s="1"/>
     </row>
-    <row r="283" spans="1:8" ht="15.75" thickBot="1">
+    <row r="283" spans="1:8" ht="15" thickBot="1">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -5718,7 +5718,7 @@
       <c r="G283" s="1"/>
       <c r="H283" s="1"/>
     </row>
-    <row r="284" spans="1:8" ht="15.75" thickBot="1">
+    <row r="284" spans="1:8" ht="15" thickBot="1">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -5728,7 +5728,7 @@
       <c r="G284" s="1"/>
       <c r="H284" s="1"/>
     </row>
-    <row r="285" spans="1:8" ht="15.75" thickBot="1">
+    <row r="285" spans="1:8" ht="15" thickBot="1">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -5738,7 +5738,7 @@
       <c r="G285" s="1"/>
       <c r="H285" s="1"/>
     </row>
-    <row r="286" spans="1:8" ht="15.75" thickBot="1">
+    <row r="286" spans="1:8" ht="15" thickBot="1">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -5748,7 +5748,7 @@
       <c r="G286" s="1"/>
       <c r="H286" s="1"/>
     </row>
-    <row r="287" spans="1:8" ht="15.75" thickBot="1">
+    <row r="287" spans="1:8" ht="15" thickBot="1">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -5758,7 +5758,7 @@
       <c r="G287" s="1"/>
       <c r="H287" s="1"/>
     </row>
-    <row r="288" spans="1:8" ht="15.75" thickBot="1">
+    <row r="288" spans="1:8" ht="15" thickBot="1">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -5768,7 +5768,7 @@
       <c r="G288" s="1"/>
       <c r="H288" s="1"/>
     </row>
-    <row r="289" spans="1:8" ht="15.75" thickBot="1">
+    <row r="289" spans="1:8" ht="15" thickBot="1">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -5778,7 +5778,7 @@
       <c r="G289" s="1"/>
       <c r="H289" s="1"/>
     </row>
-    <row r="290" spans="1:8" ht="15.75" thickBot="1">
+    <row r="290" spans="1:8" ht="15" thickBot="1">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -5788,7 +5788,7 @@
       <c r="G290" s="1"/>
       <c r="H290" s="1"/>
     </row>
-    <row r="291" spans="1:8" ht="15.75" thickBot="1">
+    <row r="291" spans="1:8" ht="15" thickBot="1">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -5798,7 +5798,7 @@
       <c r="G291" s="1"/>
       <c r="H291" s="1"/>
     </row>
-    <row r="292" spans="1:8" ht="15.75" thickBot="1">
+    <row r="292" spans="1:8" ht="15" thickBot="1">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -5808,7 +5808,7 @@
       <c r="G292" s="1"/>
       <c r="H292" s="1"/>
     </row>
-    <row r="293" spans="1:8" ht="15.75" thickBot="1">
+    <row r="293" spans="1:8" ht="15" thickBot="1">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -5818,7 +5818,7 @@
       <c r="G293" s="1"/>
       <c r="H293" s="1"/>
     </row>
-    <row r="294" spans="1:8" ht="15.75" thickBot="1">
+    <row r="294" spans="1:8" ht="15" thickBot="1">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -5828,7 +5828,7 @@
       <c r="G294" s="1"/>
       <c r="H294" s="1"/>
     </row>
-    <row r="295" spans="1:8" ht="15.75" thickBot="1">
+    <row r="295" spans="1:8" ht="15" thickBot="1">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -5838,7 +5838,7 @@
       <c r="G295" s="1"/>
       <c r="H295" s="1"/>
     </row>
-    <row r="296" spans="1:8" ht="15.75" thickBot="1">
+    <row r="296" spans="1:8" ht="15" thickBot="1">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -5848,7 +5848,7 @@
       <c r="G296" s="1"/>
       <c r="H296" s="1"/>
     </row>
-    <row r="297" spans="1:8" ht="15.75" thickBot="1">
+    <row r="297" spans="1:8" ht="15" thickBot="1">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -5858,7 +5858,7 @@
       <c r="G297" s="1"/>
       <c r="H297" s="1"/>
     </row>
-    <row r="298" spans="1:8" ht="15.75" thickBot="1">
+    <row r="298" spans="1:8" ht="15" thickBot="1">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -5868,7 +5868,7 @@
       <c r="G298" s="1"/>
       <c r="H298" s="1"/>
     </row>
-    <row r="299" spans="1:8" ht="15.75" thickBot="1">
+    <row r="299" spans="1:8" ht="15" thickBot="1">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -5878,7 +5878,7 @@
       <c r="G299" s="1"/>
       <c r="H299" s="1"/>
     </row>
-    <row r="300" spans="1:8" ht="15.75" thickBot="1">
+    <row r="300" spans="1:8" ht="15" thickBot="1">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -5888,7 +5888,7 @@
       <c r="G300" s="1"/>
       <c r="H300" s="1"/>
     </row>
-    <row r="301" spans="1:8" ht="15.75" thickBot="1">
+    <row r="301" spans="1:8" ht="15" thickBot="1">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -5898,7 +5898,7 @@
       <c r="G301" s="1"/>
       <c r="H301" s="1"/>
     </row>
-    <row r="302" spans="1:8" ht="15.75" thickBot="1">
+    <row r="302" spans="1:8" ht="15" thickBot="1">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -5908,7 +5908,7 @@
       <c r="G302" s="1"/>
       <c r="H302" s="1"/>
     </row>
-    <row r="303" spans="1:8" ht="15.75" thickBot="1">
+    <row r="303" spans="1:8" ht="15" thickBot="1">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -5918,7 +5918,7 @@
       <c r="G303" s="1"/>
       <c r="H303" s="1"/>
     </row>
-    <row r="304" spans="1:8" ht="15.75" thickBot="1">
+    <row r="304" spans="1:8" ht="15" thickBot="1">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -5928,7 +5928,7 @@
       <c r="G304" s="1"/>
       <c r="H304" s="1"/>
     </row>
-    <row r="305" spans="1:8" ht="15.75" thickBot="1">
+    <row r="305" spans="1:8" ht="15" thickBot="1">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -5938,7 +5938,7 @@
       <c r="G305" s="1"/>
       <c r="H305" s="1"/>
     </row>
-    <row r="306" spans="1:8" ht="15.75" thickBot="1">
+    <row r="306" spans="1:8" ht="15" thickBot="1">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -5948,7 +5948,7 @@
       <c r="G306" s="1"/>
       <c r="H306" s="1"/>
     </row>
-    <row r="307" spans="1:8" ht="15.75" thickBot="1">
+    <row r="307" spans="1:8" ht="15" thickBot="1">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -5958,7 +5958,7 @@
       <c r="G307" s="1"/>
       <c r="H307" s="1"/>
     </row>
-    <row r="308" spans="1:8" ht="15.75" thickBot="1">
+    <row r="308" spans="1:8" ht="15" thickBot="1">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -5968,7 +5968,7 @@
       <c r="G308" s="1"/>
       <c r="H308" s="1"/>
     </row>
-    <row r="309" spans="1:8" ht="15.75" thickBot="1">
+    <row r="309" spans="1:8" ht="15" thickBot="1">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -5978,7 +5978,7 @@
       <c r="G309" s="1"/>
       <c r="H309" s="1"/>
     </row>
-    <row r="310" spans="1:8" ht="15.75" thickBot="1">
+    <row r="310" spans="1:8" ht="15" thickBot="1">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -5988,7 +5988,7 @@
       <c r="G310" s="1"/>
       <c r="H310" s="1"/>
     </row>
-    <row r="311" spans="1:8" ht="15.75" thickBot="1">
+    <row r="311" spans="1:8" ht="15" thickBot="1">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -5998,7 +5998,7 @@
       <c r="G311" s="1"/>
       <c r="H311" s="1"/>
     </row>
-    <row r="312" spans="1:8" ht="15.75" thickBot="1">
+    <row r="312" spans="1:8" ht="15" thickBot="1">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -6008,7 +6008,7 @@
       <c r="G312" s="1"/>
       <c r="H312" s="1"/>
     </row>
-    <row r="313" spans="1:8" ht="15.75" thickBot="1">
+    <row r="313" spans="1:8" ht="15" thickBot="1">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -6018,7 +6018,7 @@
       <c r="G313" s="1"/>
       <c r="H313" s="1"/>
     </row>
-    <row r="314" spans="1:8" ht="15.75" thickBot="1">
+    <row r="314" spans="1:8" ht="15" thickBot="1">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -6028,7 +6028,7 @@
       <c r="G314" s="1"/>
       <c r="H314" s="1"/>
     </row>
-    <row r="315" spans="1:8" ht="15.75" thickBot="1">
+    <row r="315" spans="1:8" ht="15" thickBot="1">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -6038,7 +6038,7 @@
       <c r="G315" s="1"/>
       <c r="H315" s="1"/>
     </row>
-    <row r="316" spans="1:8" ht="15.75" thickBot="1">
+    <row r="316" spans="1:8" ht="15" thickBot="1">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -6048,7 +6048,7 @@
       <c r="G316" s="1"/>
       <c r="H316" s="1"/>
     </row>
-    <row r="317" spans="1:8" ht="15.75" thickBot="1">
+    <row r="317" spans="1:8" ht="15" thickBot="1">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -6058,7 +6058,7 @@
       <c r="G317" s="1"/>
       <c r="H317" s="1"/>
     </row>
-    <row r="318" spans="1:8" ht="15.75" thickBot="1">
+    <row r="318" spans="1:8" ht="15" thickBot="1">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -6068,7 +6068,7 @@
       <c r="G318" s="1"/>
       <c r="H318" s="1"/>
     </row>
-    <row r="319" spans="1:8" ht="15.75" thickBot="1">
+    <row r="319" spans="1:8" ht="15" thickBot="1">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -6078,7 +6078,7 @@
       <c r="G319" s="1"/>
       <c r="H319" s="1"/>
     </row>
-    <row r="320" spans="1:8" ht="15.75" thickBot="1">
+    <row r="320" spans="1:8" ht="15" thickBot="1">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -6088,7 +6088,7 @@
       <c r="G320" s="1"/>
       <c r="H320" s="1"/>
     </row>
-    <row r="321" spans="1:8" ht="15.75" thickBot="1">
+    <row r="321" spans="1:8" ht="15" thickBot="1">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -6098,7 +6098,7 @@
       <c r="G321" s="1"/>
       <c r="H321" s="1"/>
     </row>
-    <row r="322" spans="1:8" ht="15.75" thickBot="1">
+    <row r="322" spans="1:8" ht="15" thickBot="1">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -6108,7 +6108,7 @@
       <c r="G322" s="1"/>
       <c r="H322" s="1"/>
     </row>
-    <row r="323" spans="1:8" ht="15.75" thickBot="1">
+    <row r="323" spans="1:8" ht="15" thickBot="1">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -6118,7 +6118,7 @@
       <c r="G323" s="1"/>
       <c r="H323" s="1"/>
     </row>
-    <row r="324" spans="1:8" ht="15.75" thickBot="1">
+    <row r="324" spans="1:8" ht="15" thickBot="1">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -6128,7 +6128,7 @@
       <c r="G324" s="1"/>
       <c r="H324" s="1"/>
     </row>
-    <row r="325" spans="1:8" ht="15.75" thickBot="1">
+    <row r="325" spans="1:8" ht="15" thickBot="1">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -6138,7 +6138,7 @@
       <c r="G325" s="1"/>
       <c r="H325" s="1"/>
     </row>
-    <row r="326" spans="1:8" ht="15.75" thickBot="1">
+    <row r="326" spans="1:8" ht="15" thickBot="1">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -6148,7 +6148,7 @@
       <c r="G326" s="1"/>
       <c r="H326" s="1"/>
     </row>
-    <row r="327" spans="1:8" ht="15.75" thickBot="1">
+    <row r="327" spans="1:8" ht="15" thickBot="1">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -6158,7 +6158,7 @@
       <c r="G327" s="1"/>
       <c r="H327" s="1"/>
     </row>
-    <row r="328" spans="1:8" ht="15.75" thickBot="1">
+    <row r="328" spans="1:8" ht="15" thickBot="1">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -6168,7 +6168,7 @@
       <c r="G328" s="1"/>
       <c r="H328" s="1"/>
     </row>
-    <row r="329" spans="1:8" ht="15.75" thickBot="1">
+    <row r="329" spans="1:8" ht="15" thickBot="1">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -6178,7 +6178,7 @@
       <c r="G329" s="1"/>
       <c r="H329" s="1"/>
     </row>
-    <row r="330" spans="1:8" ht="15.75" thickBot="1">
+    <row r="330" spans="1:8" ht="15" thickBot="1">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -6188,7 +6188,7 @@
       <c r="G330" s="1"/>
       <c r="H330" s="1"/>
     </row>
-    <row r="331" spans="1:8" ht="15.75" thickBot="1">
+    <row r="331" spans="1:8" ht="15" thickBot="1">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -6198,7 +6198,7 @@
       <c r="G331" s="1"/>
       <c r="H331" s="1"/>
     </row>
-    <row r="332" spans="1:8" ht="15.75" thickBot="1">
+    <row r="332" spans="1:8" ht="15" thickBot="1">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -6208,7 +6208,7 @@
       <c r="G332" s="1"/>
       <c r="H332" s="1"/>
     </row>
-    <row r="333" spans="1:8" ht="15.75" thickBot="1">
+    <row r="333" spans="1:8" ht="15" thickBot="1">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -6218,7 +6218,7 @@
       <c r="G333" s="1"/>
       <c r="H333" s="1"/>
     </row>
-    <row r="334" spans="1:8" ht="15.75" thickBot="1">
+    <row r="334" spans="1:8" ht="15" thickBot="1">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -6228,7 +6228,7 @@
       <c r="G334" s="1"/>
       <c r="H334" s="1"/>
     </row>
-    <row r="335" spans="1:8" ht="15.75" thickBot="1">
+    <row r="335" spans="1:8" ht="15" thickBot="1">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -6238,7 +6238,7 @@
       <c r="G335" s="1"/>
       <c r="H335" s="1"/>
     </row>
-    <row r="336" spans="1:8" ht="15.75" thickBot="1">
+    <row r="336" spans="1:8" ht="15" thickBot="1">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -6248,7 +6248,7 @@
       <c r="G336" s="1"/>
       <c r="H336" s="1"/>
     </row>
-    <row r="337" spans="1:8" ht="15.75" thickBot="1">
+    <row r="337" spans="1:8" ht="15" thickBot="1">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -6258,7 +6258,7 @@
       <c r="G337" s="1"/>
       <c r="H337" s="1"/>
     </row>
-    <row r="338" spans="1:8" ht="15.75" thickBot="1">
+    <row r="338" spans="1:8" ht="15" thickBot="1">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -6268,7 +6268,7 @@
       <c r="G338" s="1"/>
       <c r="H338" s="1"/>
     </row>
-    <row r="339" spans="1:8" ht="15.75" thickBot="1">
+    <row r="339" spans="1:8" ht="15" thickBot="1">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -6278,7 +6278,7 @@
       <c r="G339" s="1"/>
       <c r="H339" s="1"/>
     </row>
-    <row r="340" spans="1:8" ht="15.75" thickBot="1">
+    <row r="340" spans="1:8" ht="15" thickBot="1">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -6288,7 +6288,7 @@
       <c r="G340" s="1"/>
       <c r="H340" s="1"/>
     </row>
-    <row r="341" spans="1:8" ht="15.75" thickBot="1">
+    <row r="341" spans="1:8" ht="15" thickBot="1">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -6298,7 +6298,7 @@
       <c r="G341" s="1"/>
       <c r="H341" s="1"/>
     </row>
-    <row r="342" spans="1:8" ht="15.75" thickBot="1">
+    <row r="342" spans="1:8" ht="15" thickBot="1">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -6308,7 +6308,7 @@
       <c r="G342" s="1"/>
       <c r="H342" s="1"/>
     </row>
-    <row r="343" spans="1:8" ht="15.75" thickBot="1">
+    <row r="343" spans="1:8" ht="15" thickBot="1">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -6318,7 +6318,7 @@
       <c r="G343" s="1"/>
       <c r="H343" s="1"/>
     </row>
-    <row r="344" spans="1:8" ht="15.75" thickBot="1">
+    <row r="344" spans="1:8" ht="15" thickBot="1">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -6328,7 +6328,7 @@
       <c r="G344" s="1"/>
       <c r="H344" s="1"/>
     </row>
-    <row r="345" spans="1:8" ht="15.75" thickBot="1">
+    <row r="345" spans="1:8" ht="15" thickBot="1">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -6338,7 +6338,7 @@
       <c r="G345" s="1"/>
       <c r="H345" s="1"/>
     </row>
-    <row r="346" spans="1:8" ht="15.75" thickBot="1">
+    <row r="346" spans="1:8" ht="15" thickBot="1">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -6348,7 +6348,7 @@
       <c r="G346" s="1"/>
       <c r="H346" s="1"/>
     </row>
-    <row r="347" spans="1:8" ht="15.75" thickBot="1">
+    <row r="347" spans="1:8" ht="15" thickBot="1">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -6358,7 +6358,7 @@
       <c r="G347" s="1"/>
       <c r="H347" s="1"/>
     </row>
-    <row r="348" spans="1:8" ht="15.75" thickBot="1">
+    <row r="348" spans="1:8" ht="15" thickBot="1">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -6368,7 +6368,7 @@
       <c r="G348" s="1"/>
       <c r="H348" s="1"/>
     </row>
-    <row r="349" spans="1:8" ht="15.75" thickBot="1">
+    <row r="349" spans="1:8" ht="15" thickBot="1">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -6378,7 +6378,7 @@
       <c r="G349" s="1"/>
       <c r="H349" s="1"/>
     </row>
-    <row r="350" spans="1:8" ht="15.75" thickBot="1">
+    <row r="350" spans="1:8" ht="15" thickBot="1">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -6388,7 +6388,7 @@
       <c r="G350" s="1"/>
       <c r="H350" s="1"/>
     </row>
-    <row r="351" spans="1:8" ht="15.75" thickBot="1">
+    <row r="351" spans="1:8" ht="15" thickBot="1">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -6398,7 +6398,7 @@
       <c r="G351" s="1"/>
       <c r="H351" s="1"/>
     </row>
-    <row r="352" spans="1:8" ht="15.75" thickBot="1">
+    <row r="352" spans="1:8" ht="15" thickBot="1">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -6408,7 +6408,7 @@
       <c r="G352" s="1"/>
       <c r="H352" s="1"/>
     </row>
-    <row r="353" spans="1:8" ht="15.75" thickBot="1">
+    <row r="353" spans="1:8" ht="15" thickBot="1">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -6418,7 +6418,7 @@
       <c r="G353" s="1"/>
       <c r="H353" s="1"/>
     </row>
-    <row r="354" spans="1:8" ht="15.75" thickBot="1">
+    <row r="354" spans="1:8" ht="15" thickBot="1">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -6428,7 +6428,7 @@
       <c r="G354" s="1"/>
       <c r="H354" s="1"/>
     </row>
-    <row r="355" spans="1:8" ht="15.75" thickBot="1">
+    <row r="355" spans="1:8" ht="15" thickBot="1">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -6438,7 +6438,7 @@
       <c r="G355" s="1"/>
       <c r="H355" s="1"/>
     </row>
-    <row r="356" spans="1:8" ht="15.75" thickBot="1">
+    <row r="356" spans="1:8" ht="15" thickBot="1">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -6448,7 +6448,7 @@
       <c r="G356" s="1"/>
       <c r="H356" s="1"/>
     </row>
-    <row r="357" spans="1:8" ht="15.75" thickBot="1">
+    <row r="357" spans="1:8" ht="15" thickBot="1">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -6458,7 +6458,7 @@
       <c r="G357" s="1"/>
       <c r="H357" s="1"/>
     </row>
-    <row r="358" spans="1:8" ht="15.75" thickBot="1">
+    <row r="358" spans="1:8" ht="15" thickBot="1">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -6468,7 +6468,7 @@
       <c r="G358" s="1"/>
       <c r="H358" s="1"/>
     </row>
-    <row r="359" spans="1:8" ht="15.75" thickBot="1">
+    <row r="359" spans="1:8" ht="15" thickBot="1">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -6478,7 +6478,7 @@
       <c r="G359" s="1"/>
       <c r="H359" s="1"/>
     </row>
-    <row r="360" spans="1:8" ht="15.75" thickBot="1">
+    <row r="360" spans="1:8" ht="15" thickBot="1">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -6488,7 +6488,7 @@
       <c r="G360" s="1"/>
       <c r="H360" s="1"/>
     </row>
-    <row r="361" spans="1:8" ht="15.75" thickBot="1">
+    <row r="361" spans="1:8" ht="15" thickBot="1">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -6498,7 +6498,7 @@
       <c r="G361" s="1"/>
       <c r="H361" s="1"/>
     </row>
-    <row r="362" spans="1:8" ht="15.75" thickBot="1">
+    <row r="362" spans="1:8" ht="15" thickBot="1">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -6508,7 +6508,7 @@
       <c r="G362" s="1"/>
       <c r="H362" s="1"/>
     </row>
-    <row r="363" spans="1:8" ht="15.75" thickBot="1">
+    <row r="363" spans="1:8" ht="15" thickBot="1">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -6518,7 +6518,7 @@
       <c r="G363" s="1"/>
       <c r="H363" s="1"/>
     </row>
-    <row r="364" spans="1:8" ht="15.75" thickBot="1">
+    <row r="364" spans="1:8" ht="15" thickBot="1">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -6528,7 +6528,7 @@
       <c r="G364" s="1"/>
       <c r="H364" s="1"/>
     </row>
-    <row r="365" spans="1:8" ht="15.75" thickBot="1">
+    <row r="365" spans="1:8" ht="15" thickBot="1">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -6538,7 +6538,7 @@
       <c r="G365" s="1"/>
       <c r="H365" s="1"/>
     </row>
-    <row r="366" spans="1:8" ht="15.75" thickBot="1">
+    <row r="366" spans="1:8" ht="15" thickBot="1">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -6548,7 +6548,7 @@
       <c r="G366" s="1"/>
       <c r="H366" s="1"/>
     </row>
-    <row r="367" spans="1:8" ht="15.75" thickBot="1">
+    <row r="367" spans="1:8" ht="15" thickBot="1">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -6558,7 +6558,7 @@
       <c r="G367" s="1"/>
       <c r="H367" s="1"/>
     </row>
-    <row r="368" spans="1:8" ht="15.75" thickBot="1">
+    <row r="368" spans="1:8" ht="15" thickBot="1">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -6568,7 +6568,7 @@
       <c r="G368" s="1"/>
       <c r="H368" s="1"/>
     </row>
-    <row r="369" spans="1:8" ht="15.75" thickBot="1">
+    <row r="369" spans="1:8" ht="15" thickBot="1">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -6578,7 +6578,7 @@
       <c r="G369" s="1"/>
       <c r="H369" s="1"/>
     </row>
-    <row r="370" spans="1:8" ht="15.75" thickBot="1">
+    <row r="370" spans="1:8" ht="15" thickBot="1">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -6588,7 +6588,7 @@
       <c r="G370" s="1"/>
       <c r="H370" s="1"/>
     </row>
-    <row r="371" spans="1:8" ht="15.75" thickBot="1">
+    <row r="371" spans="1:8" ht="15" thickBot="1">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -6598,7 +6598,7 @@
       <c r="G371" s="1"/>
       <c r="H371" s="1"/>
     </row>
-    <row r="372" spans="1:8" ht="15.75" thickBot="1">
+    <row r="372" spans="1:8" ht="15" thickBot="1">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -6608,7 +6608,7 @@
       <c r="G372" s="1"/>
       <c r="H372" s="1"/>
     </row>
-    <row r="373" spans="1:8" ht="15.75" thickBot="1">
+    <row r="373" spans="1:8" ht="15" thickBot="1">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -6618,7 +6618,7 @@
       <c r="G373" s="1"/>
       <c r="H373" s="1"/>
     </row>
-    <row r="374" spans="1:8" ht="15.75" thickBot="1">
+    <row r="374" spans="1:8" ht="15" thickBot="1">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -6628,7 +6628,7 @@
       <c r="G374" s="1"/>
       <c r="H374" s="1"/>
     </row>
-    <row r="375" spans="1:8" ht="15.75" thickBot="1">
+    <row r="375" spans="1:8" ht="15" thickBot="1">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -6638,7 +6638,7 @@
       <c r="G375" s="1"/>
       <c r="H375" s="1"/>
     </row>
-    <row r="376" spans="1:8" ht="15.75" thickBot="1">
+    <row r="376" spans="1:8" ht="15" thickBot="1">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -6648,7 +6648,7 @@
       <c r="G376" s="1"/>
       <c r="H376" s="1"/>
     </row>
-    <row r="377" spans="1:8" ht="15.75" thickBot="1">
+    <row r="377" spans="1:8" ht="15" thickBot="1">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -6658,7 +6658,7 @@
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
     </row>
-    <row r="378" spans="1:8" ht="15.75" thickBot="1">
+    <row r="378" spans="1:8" ht="15" thickBot="1">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -6668,7 +6668,7 @@
       <c r="G378" s="1"/>
       <c r="H378" s="1"/>
     </row>
-    <row r="379" spans="1:8" ht="15.75" thickBot="1">
+    <row r="379" spans="1:8" ht="15" thickBot="1">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -6678,7 +6678,7 @@
       <c r="G379" s="1"/>
       <c r="H379" s="1"/>
     </row>
-    <row r="380" spans="1:8" ht="15.75" thickBot="1">
+    <row r="380" spans="1:8" ht="15" thickBot="1">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -6688,7 +6688,7 @@
       <c r="G380" s="1"/>
       <c r="H380" s="1"/>
     </row>
-    <row r="381" spans="1:8" ht="15.75" thickBot="1">
+    <row r="381" spans="1:8" ht="15" thickBot="1">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -6698,7 +6698,7 @@
       <c r="G381" s="1"/>
       <c r="H381" s="1"/>
     </row>
-    <row r="382" spans="1:8" ht="15.75" thickBot="1">
+    <row r="382" spans="1:8" ht="15" thickBot="1">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -6708,7 +6708,7 @@
       <c r="G382" s="1"/>
       <c r="H382" s="1"/>
     </row>
-    <row r="383" spans="1:8" ht="15.75" thickBot="1">
+    <row r="383" spans="1:8" ht="15" thickBot="1">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -6718,7 +6718,7 @@
       <c r="G383" s="1"/>
       <c r="H383" s="1"/>
     </row>
-    <row r="384" spans="1:8" ht="15.75" thickBot="1">
+    <row r="384" spans="1:8" ht="15" thickBot="1">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -6728,7 +6728,7 @@
       <c r="G384" s="1"/>
       <c r="H384" s="1"/>
     </row>
-    <row r="385" spans="1:8" ht="15.75" thickBot="1">
+    <row r="385" spans="1:8" ht="15" thickBot="1">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -6738,7 +6738,7 @@
       <c r="G385" s="1"/>
       <c r="H385" s="1"/>
     </row>
-    <row r="386" spans="1:8" ht="15.75" thickBot="1">
+    <row r="386" spans="1:8" ht="15" thickBot="1">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -6748,7 +6748,7 @@
       <c r="G386" s="1"/>
       <c r="H386" s="1"/>
     </row>
-    <row r="387" spans="1:8" ht="15.75" thickBot="1">
+    <row r="387" spans="1:8" ht="15" thickBot="1">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -6758,7 +6758,7 @@
       <c r="G387" s="1"/>
       <c r="H387" s="1"/>
     </row>
-    <row r="388" spans="1:8" ht="15.75" thickBot="1">
+    <row r="388" spans="1:8" ht="15" thickBot="1">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -6768,7 +6768,7 @@
       <c r="G388" s="1"/>
       <c r="H388" s="1"/>
     </row>
-    <row r="389" spans="1:8" ht="15.75" thickBot="1">
+    <row r="389" spans="1:8" ht="15" thickBot="1">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -6778,7 +6778,7 @@
       <c r="G389" s="1"/>
       <c r="H389" s="1"/>
     </row>
-    <row r="390" spans="1:8" ht="15.75" thickBot="1">
+    <row r="390" spans="1:8" ht="15" thickBot="1">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -6788,7 +6788,7 @@
       <c r="G390" s="1"/>
       <c r="H390" s="1"/>
     </row>
-    <row r="391" spans="1:8" ht="15.75" thickBot="1">
+    <row r="391" spans="1:8" ht="15" thickBot="1">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -6798,7 +6798,7 @@
       <c r="G391" s="1"/>
       <c r="H391" s="1"/>
     </row>
-    <row r="392" spans="1:8" ht="15.75" thickBot="1">
+    <row r="392" spans="1:8" ht="15" thickBot="1">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -6808,7 +6808,7 @@
       <c r="G392" s="1"/>
       <c r="H392" s="1"/>
     </row>
-    <row r="393" spans="1:8" ht="15.75" thickBot="1">
+    <row r="393" spans="1:8" ht="15" thickBot="1">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -6818,7 +6818,7 @@
       <c r="G393" s="1"/>
       <c r="H393" s="1"/>
     </row>
-    <row r="394" spans="1:8" ht="15.75" thickBot="1">
+    <row r="394" spans="1:8" ht="15" thickBot="1">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -6828,7 +6828,7 @@
       <c r="G394" s="1"/>
       <c r="H394" s="1"/>
     </row>
-    <row r="395" spans="1:8" ht="15.75" thickBot="1">
+    <row r="395" spans="1:8" ht="15" thickBot="1">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -6838,7 +6838,7 @@
       <c r="G395" s="1"/>
       <c r="H395" s="1"/>
     </row>
-    <row r="396" spans="1:8" ht="15.75" thickBot="1">
+    <row r="396" spans="1:8" ht="15" thickBot="1">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -6848,7 +6848,7 @@
       <c r="G396" s="1"/>
       <c r="H396" s="1"/>
     </row>
-    <row r="397" spans="1:8" ht="15.75" thickBot="1">
+    <row r="397" spans="1:8" ht="15" thickBot="1">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -6858,7 +6858,7 @@
       <c r="G397" s="1"/>
       <c r="H397" s="1"/>
     </row>
-    <row r="398" spans="1:8" ht="15.75" thickBot="1">
+    <row r="398" spans="1:8" ht="15" thickBot="1">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -6868,7 +6868,7 @@
       <c r="G398" s="1"/>
       <c r="H398" s="1"/>
     </row>
-    <row r="399" spans="1:8" ht="15.75" thickBot="1">
+    <row r="399" spans="1:8" ht="15" thickBot="1">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -6878,7 +6878,7 @@
       <c r="G399" s="1"/>
       <c r="H399" s="1"/>
     </row>
-    <row r="400" spans="1:8" ht="15.75" thickBot="1">
+    <row r="400" spans="1:8" ht="15" thickBot="1">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -6888,7 +6888,7 @@
       <c r="G400" s="1"/>
       <c r="H400" s="1"/>
     </row>
-    <row r="401" spans="1:8" ht="15.75" thickBot="1">
+    <row r="401" spans="1:8" ht="15" thickBot="1">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -6898,7 +6898,7 @@
       <c r="G401" s="1"/>
       <c r="H401" s="1"/>
     </row>
-    <row r="402" spans="1:8" ht="15.75" thickBot="1">
+    <row r="402" spans="1:8" ht="15" thickBot="1">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -6908,7 +6908,7 @@
       <c r="G402" s="1"/>
       <c r="H402" s="1"/>
     </row>
-    <row r="403" spans="1:8" ht="15.75" thickBot="1">
+    <row r="403" spans="1:8" ht="15" thickBot="1">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -6918,7 +6918,7 @@
       <c r="G403" s="1"/>
       <c r="H403" s="1"/>
     </row>
-    <row r="404" spans="1:8" ht="15.75" thickBot="1">
+    <row r="404" spans="1:8" ht="15" thickBot="1">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -6928,7 +6928,7 @@
       <c r="G404" s="1"/>
       <c r="H404" s="1"/>
     </row>
-    <row r="405" spans="1:8" ht="15.75" thickBot="1">
+    <row r="405" spans="1:8" ht="15" thickBot="1">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -6938,7 +6938,7 @@
       <c r="G405" s="1"/>
       <c r="H405" s="1"/>
     </row>
-    <row r="406" spans="1:8" ht="15.75" thickBot="1">
+    <row r="406" spans="1:8" ht="15" thickBot="1">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -6948,7 +6948,7 @@
       <c r="G406" s="1"/>
       <c r="H406" s="1"/>
     </row>
-    <row r="407" spans="1:8" ht="15.75" thickBot="1">
+    <row r="407" spans="1:8" ht="15" thickBot="1">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -6958,7 +6958,7 @@
       <c r="G407" s="1"/>
       <c r="H407" s="1"/>
     </row>
-    <row r="408" spans="1:8" ht="15.75" thickBot="1">
+    <row r="408" spans="1:8" ht="15" thickBot="1">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -6968,7 +6968,7 @@
       <c r="G408" s="1"/>
       <c r="H408" s="1"/>
     </row>
-    <row r="409" spans="1:8" ht="15.75" thickBot="1">
+    <row r="409" spans="1:8" ht="15" thickBot="1">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -6978,7 +6978,7 @@
       <c r="G409" s="1"/>
       <c r="H409" s="1"/>
     </row>
-    <row r="410" spans="1:8" ht="15.75" thickBot="1">
+    <row r="410" spans="1:8" ht="15" thickBot="1">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -6988,7 +6988,7 @@
       <c r="G410" s="1"/>
       <c r="H410" s="1"/>
     </row>
-    <row r="411" spans="1:8" ht="15.75" thickBot="1">
+    <row r="411" spans="1:8" ht="15" thickBot="1">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -6998,7 +6998,7 @@
       <c r="G411" s="1"/>
       <c r="H411" s="1"/>
     </row>
-    <row r="412" spans="1:8" ht="15.75" thickBot="1">
+    <row r="412" spans="1:8" ht="15" thickBot="1">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -7008,7 +7008,7 @@
       <c r="G412" s="1"/>
       <c r="H412" s="1"/>
     </row>
-    <row r="413" spans="1:8" ht="15.75" thickBot="1">
+    <row r="413" spans="1:8" ht="15" thickBot="1">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -7018,7 +7018,7 @@
       <c r="G413" s="1"/>
       <c r="H413" s="1"/>
     </row>
-    <row r="414" spans="1:8" ht="15.75" thickBot="1">
+    <row r="414" spans="1:8" ht="15" thickBot="1">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -7028,7 +7028,7 @@
       <c r="G414" s="1"/>
       <c r="H414" s="1"/>
     </row>
-    <row r="415" spans="1:8" ht="15.75" thickBot="1">
+    <row r="415" spans="1:8" ht="15" thickBot="1">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -7038,7 +7038,7 @@
       <c r="G415" s="1"/>
       <c r="H415" s="1"/>
     </row>
-    <row r="416" spans="1:8" ht="15.75" thickBot="1">
+    <row r="416" spans="1:8" ht="15" thickBot="1">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -7048,7 +7048,7 @@
       <c r="G416" s="1"/>
       <c r="H416" s="1"/>
     </row>
-    <row r="417" spans="1:8" ht="15.75" thickBot="1">
+    <row r="417" spans="1:8" ht="15" thickBot="1">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -7058,7 +7058,7 @@
       <c r="G417" s="1"/>
       <c r="H417" s="1"/>
     </row>
-    <row r="418" spans="1:8" ht="15.75" thickBot="1">
+    <row r="418" spans="1:8" ht="15" thickBot="1">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -7068,7 +7068,7 @@
       <c r="G418" s="1"/>
       <c r="H418" s="1"/>
     </row>
-    <row r="419" spans="1:8" ht="15.75" thickBot="1">
+    <row r="419" spans="1:8" ht="15" thickBot="1">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -7078,7 +7078,7 @@
       <c r="G419" s="1"/>
       <c r="H419" s="1"/>
     </row>
-    <row r="420" spans="1:8" ht="15.75" thickBot="1">
+    <row r="420" spans="1:8" ht="15" thickBot="1">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -7088,7 +7088,7 @@
       <c r="G420" s="1"/>
       <c r="H420" s="1"/>
     </row>
-    <row r="421" spans="1:8" ht="15.75" thickBot="1">
+    <row r="421" spans="1:8" ht="15" thickBot="1">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -7098,7 +7098,7 @@
       <c r="G421" s="1"/>
       <c r="H421" s="1"/>
     </row>
-    <row r="422" spans="1:8" ht="15.75" thickBot="1">
+    <row r="422" spans="1:8" ht="15" thickBot="1">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -7108,7 +7108,7 @@
       <c r="G422" s="1"/>
       <c r="H422" s="1"/>
     </row>
-    <row r="423" spans="1:8" ht="15.75" thickBot="1">
+    <row r="423" spans="1:8" ht="15" thickBot="1">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -7118,7 +7118,7 @@
       <c r="G423" s="1"/>
       <c r="H423" s="1"/>
     </row>
-    <row r="424" spans="1:8" ht="15.75" thickBot="1">
+    <row r="424" spans="1:8" ht="15" thickBot="1">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -7128,7 +7128,7 @@
       <c r="G424" s="1"/>
       <c r="H424" s="1"/>
     </row>
-    <row r="425" spans="1:8" ht="15.75" thickBot="1">
+    <row r="425" spans="1:8" ht="15" thickBot="1">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -7138,7 +7138,7 @@
       <c r="G425" s="1"/>
       <c r="H425" s="1"/>
     </row>
-    <row r="426" spans="1:8" ht="15.75" thickBot="1">
+    <row r="426" spans="1:8" ht="15" thickBot="1">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -7148,7 +7148,7 @@
       <c r="G426" s="1"/>
       <c r="H426" s="1"/>
     </row>
-    <row r="427" spans="1:8" ht="15.75" thickBot="1">
+    <row r="427" spans="1:8" ht="15" thickBot="1">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -7158,7 +7158,7 @@
       <c r="G427" s="1"/>
       <c r="H427" s="1"/>
     </row>
-    <row r="428" spans="1:8" ht="15.75" thickBot="1">
+    <row r="428" spans="1:8" ht="15" thickBot="1">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -7168,7 +7168,7 @@
       <c r="G428" s="1"/>
       <c r="H428" s="1"/>
     </row>
-    <row r="429" spans="1:8" ht="15.75" thickBot="1">
+    <row r="429" spans="1:8" ht="15" thickBot="1">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -7178,7 +7178,7 @@
       <c r="G429" s="1"/>
       <c r="H429" s="1"/>
     </row>
-    <row r="430" spans="1:8" ht="15.75" thickBot="1">
+    <row r="430" spans="1:8" ht="15" thickBot="1">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -7188,7 +7188,7 @@
       <c r="G430" s="1"/>
       <c r="H430" s="1"/>
     </row>
-    <row r="431" spans="1:8" ht="15.75" thickBot="1">
+    <row r="431" spans="1:8" ht="15" thickBot="1">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -7198,7 +7198,7 @@
       <c r="G431" s="1"/>
       <c r="H431" s="1"/>
     </row>
-    <row r="432" spans="1:8" ht="15.75" thickBot="1">
+    <row r="432" spans="1:8" ht="15" thickBot="1">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -7208,7 +7208,7 @@
       <c r="G432" s="1"/>
       <c r="H432" s="1"/>
     </row>
-    <row r="433" spans="1:8" ht="15.75" thickBot="1">
+    <row r="433" spans="1:8" ht="15" thickBot="1">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -7218,7 +7218,7 @@
       <c r="G433" s="1"/>
       <c r="H433" s="1"/>
     </row>
-    <row r="434" spans="1:8" ht="15.75" thickBot="1">
+    <row r="434" spans="1:8" ht="15" thickBot="1">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -7228,7 +7228,7 @@
       <c r="G434" s="1"/>
       <c r="H434" s="1"/>
     </row>
-    <row r="435" spans="1:8" ht="15.75" thickBot="1">
+    <row r="435" spans="1:8" ht="15" thickBot="1">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -7238,7 +7238,7 @@
       <c r="G435" s="1"/>
       <c r="H435" s="1"/>
     </row>
-    <row r="436" spans="1:8" ht="15.75" thickBot="1">
+    <row r="436" spans="1:8" ht="15" thickBot="1">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -7248,7 +7248,7 @@
       <c r="G436" s="1"/>
       <c r="H436" s="1"/>
     </row>
-    <row r="437" spans="1:8" ht="15.75" thickBot="1">
+    <row r="437" spans="1:8" ht="15" thickBot="1">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -7258,7 +7258,7 @@
       <c r="G437" s="1"/>
       <c r="H437" s="1"/>
     </row>
-    <row r="438" spans="1:8" ht="15.75" thickBot="1">
+    <row r="438" spans="1:8" ht="15" thickBot="1">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -7268,7 +7268,7 @@
       <c r="G438" s="1"/>
       <c r="H438" s="1"/>
     </row>
-    <row r="439" spans="1:8" ht="15.75" thickBot="1">
+    <row r="439" spans="1:8" ht="15" thickBot="1">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -7278,7 +7278,7 @@
       <c r="G439" s="1"/>
       <c r="H439" s="1"/>
     </row>
-    <row r="440" spans="1:8" ht="15.75" thickBot="1">
+    <row r="440" spans="1:8" ht="15" thickBot="1">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -7288,7 +7288,7 @@
       <c r="G440" s="1"/>
       <c r="H440" s="1"/>
     </row>
-    <row r="441" spans="1:8" ht="15.75" thickBot="1">
+    <row r="441" spans="1:8" ht="15" thickBot="1">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -7298,7 +7298,7 @@
       <c r="G441" s="1"/>
       <c r="H441" s="1"/>
     </row>
-    <row r="442" spans="1:8" ht="15.75" thickBot="1">
+    <row r="442" spans="1:8" ht="15" thickBot="1">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -7308,7 +7308,7 @@
       <c r="G442" s="1"/>
       <c r="H442" s="1"/>
     </row>
-    <row r="443" spans="1:8" ht="15.75" thickBot="1">
+    <row r="443" spans="1:8" ht="15" thickBot="1">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -7318,7 +7318,7 @@
       <c r="G443" s="1"/>
       <c r="H443" s="1"/>
     </row>
-    <row r="444" spans="1:8" ht="15.75" thickBot="1">
+    <row r="444" spans="1:8" ht="15" thickBot="1">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -7328,7 +7328,7 @@
       <c r="G444" s="1"/>
       <c r="H444" s="1"/>
     </row>
-    <row r="445" spans="1:8" ht="15.75" thickBot="1">
+    <row r="445" spans="1:8" ht="15" thickBot="1">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -7338,7 +7338,7 @@
       <c r="G445" s="1"/>
       <c r="H445" s="1"/>
     </row>
-    <row r="446" spans="1:8" ht="15.75" thickBot="1">
+    <row r="446" spans="1:8" ht="15" thickBot="1">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -7348,7 +7348,7 @@
       <c r="G446" s="1"/>
       <c r="H446" s="1"/>
     </row>
-    <row r="447" spans="1:8" ht="15.75" thickBot="1">
+    <row r="447" spans="1:8" ht="15" thickBot="1">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -7358,7 +7358,7 @@
       <c r="G447" s="1"/>
       <c r="H447" s="1"/>
     </row>
-    <row r="448" spans="1:8" ht="15.75" thickBot="1">
+    <row r="448" spans="1:8" ht="15" thickBot="1">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -7368,7 +7368,7 @@
       <c r="G448" s="1"/>
       <c r="H448" s="1"/>
     </row>
-    <row r="449" spans="1:8" ht="15.75" thickBot="1">
+    <row r="449" spans="1:8" ht="15" thickBot="1">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -7378,7 +7378,7 @@
       <c r="G449" s="1"/>
       <c r="H449" s="1"/>
     </row>
-    <row r="450" spans="1:8" ht="15.75" thickBot="1">
+    <row r="450" spans="1:8" ht="15" thickBot="1">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -7388,7 +7388,7 @@
       <c r="G450" s="1"/>
       <c r="H450" s="1"/>
     </row>
-    <row r="451" spans="1:8" ht="15.75" thickBot="1">
+    <row r="451" spans="1:8" ht="15" thickBot="1">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -7398,7 +7398,7 @@
       <c r="G451" s="1"/>
       <c r="H451" s="1"/>
     </row>
-    <row r="452" spans="1:8" ht="15.75" thickBot="1">
+    <row r="452" spans="1:8" ht="15" thickBot="1">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -7408,7 +7408,7 @@
       <c r="G452" s="1"/>
       <c r="H452" s="1"/>
     </row>
-    <row r="453" spans="1:8" ht="15.75" thickBot="1">
+    <row r="453" spans="1:8" ht="15" thickBot="1">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -7418,7 +7418,7 @@
       <c r="G453" s="1"/>
       <c r="H453" s="1"/>
     </row>
-    <row r="454" spans="1:8" ht="15.75" thickBot="1">
+    <row r="454" spans="1:8" ht="15" thickBot="1">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -7428,7 +7428,7 @@
       <c r="G454" s="1"/>
       <c r="H454" s="1"/>
     </row>
-    <row r="455" spans="1:8" ht="15.75" thickBot="1">
+    <row r="455" spans="1:8" ht="15" thickBot="1">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -7438,7 +7438,7 @@
       <c r="G455" s="1"/>
       <c r="H455" s="1"/>
     </row>
-    <row r="456" spans="1:8" ht="15.75" thickBot="1">
+    <row r="456" spans="1:8" ht="15" thickBot="1">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -7448,7 +7448,7 @@
       <c r="G456" s="1"/>
       <c r="H456" s="1"/>
     </row>
-    <row r="457" spans="1:8" ht="15.75" thickBot="1">
+    <row r="457" spans="1:8" ht="15" thickBot="1">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -7458,7 +7458,7 @@
       <c r="G457" s="1"/>
       <c r="H457" s="1"/>
     </row>
-    <row r="458" spans="1:8" ht="15.75" thickBot="1">
+    <row r="458" spans="1:8" ht="15" thickBot="1">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -7468,7 +7468,7 @@
       <c r="G458" s="1"/>
       <c r="H458" s="1"/>
     </row>
-    <row r="459" spans="1:8" ht="15.75" thickBot="1">
+    <row r="459" spans="1:8" ht="15" thickBot="1">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -7478,7 +7478,7 @@
       <c r="G459" s="1"/>
       <c r="H459" s="1"/>
     </row>
-    <row r="460" spans="1:8" ht="15.75" thickBot="1">
+    <row r="460" spans="1:8" ht="15" thickBot="1">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -7488,7 +7488,7 @@
       <c r="G460" s="1"/>
       <c r="H460" s="1"/>
     </row>
-    <row r="461" spans="1:8" ht="15.75" thickBot="1">
+    <row r="461" spans="1:8" ht="15" thickBot="1">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -7498,7 +7498,7 @@
       <c r="G461" s="1"/>
       <c r="H461" s="1"/>
     </row>
-    <row r="462" spans="1:8" ht="15.75" thickBot="1">
+    <row r="462" spans="1:8" ht="15" thickBot="1">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -7508,7 +7508,7 @@
       <c r="G462" s="1"/>
       <c r="H462" s="1"/>
     </row>
-    <row r="463" spans="1:8" ht="15.75" thickBot="1">
+    <row r="463" spans="1:8" ht="15" thickBot="1">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -7518,7 +7518,7 @@
       <c r="G463" s="1"/>
       <c r="H463" s="1"/>
     </row>
-    <row r="464" spans="1:8" ht="15.75" thickBot="1">
+    <row r="464" spans="1:8" ht="15" thickBot="1">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -7528,7 +7528,7 @@
       <c r="G464" s="1"/>
       <c r="H464" s="1"/>
     </row>
-    <row r="465" spans="1:8" ht="15.75" thickBot="1">
+    <row r="465" spans="1:8" ht="15" thickBot="1">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -7538,7 +7538,7 @@
       <c r="G465" s="1"/>
       <c r="H465" s="1"/>
     </row>
-    <row r="466" spans="1:8" ht="15.75" thickBot="1">
+    <row r="466" spans="1:8" ht="15" thickBot="1">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -7548,7 +7548,7 @@
       <c r="G466" s="1"/>
       <c r="H466" s="1"/>
     </row>
-    <row r="467" spans="1:8" ht="15.75" thickBot="1">
+    <row r="467" spans="1:8" ht="15" thickBot="1">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -7558,7 +7558,7 @@
       <c r="G467" s="1"/>
       <c r="H467" s="1"/>
     </row>
-    <row r="468" spans="1:8" ht="15.75" thickBot="1">
+    <row r="468" spans="1:8" ht="15" thickBot="1">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -7568,7 +7568,7 @@
       <c r="G468" s="1"/>
       <c r="H468" s="1"/>
     </row>
-    <row r="469" spans="1:8" ht="15.75" thickBot="1">
+    <row r="469" spans="1:8" ht="15" thickBot="1">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -7578,7 +7578,7 @@
       <c r="G469" s="1"/>
       <c r="H469" s="1"/>
     </row>
-    <row r="470" spans="1:8" ht="15.75" thickBot="1">
+    <row r="470" spans="1:8" ht="15" thickBot="1">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -7588,7 +7588,7 @@
       <c r="G470" s="1"/>
       <c r="H470" s="1"/>
     </row>
-    <row r="471" spans="1:8" ht="15.75" thickBot="1">
+    <row r="471" spans="1:8" ht="15" thickBot="1">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -7598,7 +7598,7 @@
       <c r="G471" s="1"/>
       <c r="H471" s="1"/>
     </row>
-    <row r="472" spans="1:8" ht="15.75" thickBot="1">
+    <row r="472" spans="1:8" ht="15" thickBot="1">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -7608,7 +7608,7 @@
       <c r="G472" s="1"/>
       <c r="H472" s="1"/>
     </row>
-    <row r="473" spans="1:8" ht="15.75" thickBot="1">
+    <row r="473" spans="1:8" ht="15" thickBot="1">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -7618,7 +7618,7 @@
       <c r="G473" s="1"/>
       <c r="H473" s="1"/>
     </row>
-    <row r="474" spans="1:8" ht="15.75" thickBot="1">
+    <row r="474" spans="1:8" ht="15" thickBot="1">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -7628,7 +7628,7 @@
       <c r="G474" s="1"/>
       <c r="H474" s="1"/>
     </row>
-    <row r="475" spans="1:8" ht="15.75" thickBot="1">
+    <row r="475" spans="1:8" ht="15" thickBot="1">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -7638,7 +7638,7 @@
       <c r="G475" s="1"/>
       <c r="H475" s="1"/>
     </row>
-    <row r="476" spans="1:8" ht="15.75" thickBot="1">
+    <row r="476" spans="1:8" ht="15" thickBot="1">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -7648,7 +7648,7 @@
       <c r="G476" s="1"/>
       <c r="H476" s="1"/>
     </row>
-    <row r="477" spans="1:8" ht="15.75" thickBot="1">
+    <row r="477" spans="1:8" ht="15" thickBot="1">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -7658,7 +7658,7 @@
       <c r="G477" s="1"/>
       <c r="H477" s="1"/>
     </row>
-    <row r="478" spans="1:8" ht="15.75" thickBot="1">
+    <row r="478" spans="1:8" ht="15" thickBot="1">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -7668,7 +7668,7 @@
       <c r="G478" s="1"/>
       <c r="H478" s="1"/>
     </row>
-    <row r="479" spans="1:8" ht="15.75" thickBot="1">
+    <row r="479" spans="1:8" ht="15" thickBot="1">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -7678,7 +7678,7 @@
       <c r="G479" s="1"/>
       <c r="H479" s="1"/>
     </row>
-    <row r="480" spans="1:8" ht="15.75" thickBot="1">
+    <row r="480" spans="1:8" ht="15" thickBot="1">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -7688,7 +7688,7 @@
       <c r="G480" s="1"/>
       <c r="H480" s="1"/>
     </row>
-    <row r="481" spans="1:8" ht="15.75" thickBot="1">
+    <row r="481" spans="1:8" ht="15" thickBot="1">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -7698,7 +7698,7 @@
       <c r="G481" s="1"/>
       <c r="H481" s="1"/>
     </row>
-    <row r="482" spans="1:8" ht="15.75" thickBot="1">
+    <row r="482" spans="1:8" ht="15" thickBot="1">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -7708,7 +7708,7 @@
       <c r="G482" s="1"/>
       <c r="H482" s="1"/>
     </row>
-    <row r="483" spans="1:8" ht="15.75" thickBot="1">
+    <row r="483" spans="1:8" ht="15" thickBot="1">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -7718,7 +7718,7 @@
       <c r="G483" s="1"/>
       <c r="H483" s="1"/>
     </row>
-    <row r="484" spans="1:8" ht="15.75" thickBot="1">
+    <row r="484" spans="1:8" ht="15" thickBot="1">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -7728,7 +7728,7 @@
       <c r="G484" s="1"/>
       <c r="H484" s="1"/>
     </row>
-    <row r="485" spans="1:8" ht="15.75" thickBot="1">
+    <row r="485" spans="1:8" ht="15" thickBot="1">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -7738,7 +7738,7 @@
       <c r="G485" s="1"/>
       <c r="H485" s="1"/>
     </row>
-    <row r="486" spans="1:8" ht="15.75" thickBot="1">
+    <row r="486" spans="1:8" ht="15" thickBot="1">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -7748,7 +7748,7 @@
       <c r="G486" s="1"/>
       <c r="H486" s="1"/>
     </row>
-    <row r="487" spans="1:8" ht="15.75" thickBot="1">
+    <row r="487" spans="1:8" ht="15" thickBot="1">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -7758,7 +7758,7 @@
       <c r="G487" s="1"/>
       <c r="H487" s="1"/>
     </row>
-    <row r="488" spans="1:8" ht="15.75" thickBot="1">
+    <row r="488" spans="1:8" ht="15" thickBot="1">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -7768,7 +7768,7 @@
       <c r="G488" s="1"/>
       <c r="H488" s="1"/>
     </row>
-    <row r="489" spans="1:8" ht="15.75" thickBot="1">
+    <row r="489" spans="1:8" ht="15" thickBot="1">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -7778,7 +7778,7 @@
       <c r="G489" s="1"/>
       <c r="H489" s="1"/>
     </row>
-    <row r="490" spans="1:8" ht="15.75" thickBot="1">
+    <row r="490" spans="1:8" ht="15" thickBot="1">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -7788,7 +7788,7 @@
       <c r="G490" s="1"/>
       <c r="H490" s="1"/>
     </row>
-    <row r="491" spans="1:8" ht="15.75" thickBot="1">
+    <row r="491" spans="1:8" ht="15" thickBot="1">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -7798,7 +7798,7 @@
       <c r="G491" s="1"/>
       <c r="H491" s="1"/>
     </row>
-    <row r="492" spans="1:8" ht="15.75" thickBot="1">
+    <row r="492" spans="1:8" ht="15" thickBot="1">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -7808,7 +7808,7 @@
       <c r="G492" s="1"/>
       <c r="H492" s="1"/>
     </row>
-    <row r="493" spans="1:8" ht="15.75" thickBot="1">
+    <row r="493" spans="1:8" ht="15" thickBot="1">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -7818,7 +7818,7 @@
       <c r="G493" s="1"/>
       <c r="H493" s="1"/>
     </row>
-    <row r="494" spans="1:8" ht="15.75" thickBot="1">
+    <row r="494" spans="1:8" ht="15" thickBot="1">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -7828,7 +7828,7 @@
       <c r="G494" s="1"/>
       <c r="H494" s="1"/>
     </row>
-    <row r="495" spans="1:8" ht="15.75" thickBot="1">
+    <row r="495" spans="1:8" ht="15" thickBot="1">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -7838,7 +7838,7 @@
       <c r="G495" s="1"/>
       <c r="H495" s="1"/>
     </row>
-    <row r="496" spans="1:8" ht="15.75" thickBot="1">
+    <row r="496" spans="1:8" ht="15" thickBot="1">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -7848,7 +7848,7 @@
       <c r="G496" s="1"/>
       <c r="H496" s="1"/>
     </row>
-    <row r="497" spans="1:8" ht="15.75" thickBot="1">
+    <row r="497" spans="1:8" ht="15" thickBot="1">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -7858,7 +7858,7 @@
       <c r="G497" s="1"/>
       <c r="H497" s="1"/>
     </row>
-    <row r="498" spans="1:8" ht="15.75" thickBot="1">
+    <row r="498" spans="1:8" ht="15" thickBot="1">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -7868,7 +7868,7 @@
       <c r="G498" s="1"/>
       <c r="H498" s="1"/>
     </row>
-    <row r="499" spans="1:8" ht="15.75" thickBot="1">
+    <row r="499" spans="1:8" ht="15" thickBot="1">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -7878,7 +7878,7 @@
       <c r="G499" s="1"/>
       <c r="H499" s="1"/>
     </row>
-    <row r="500" spans="1:8" ht="15.75" thickBot="1">
+    <row r="500" spans="1:8" ht="15" thickBot="1">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -7888,7 +7888,7 @@
       <c r="G500" s="1"/>
       <c r="H500" s="1"/>
     </row>
-    <row r="501" spans="1:8" ht="15.75" thickBot="1">
+    <row r="501" spans="1:8" ht="15" thickBot="1">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -7898,7 +7898,7 @@
       <c r="G501" s="1"/>
       <c r="H501" s="1"/>
     </row>
-    <row r="502" spans="1:8" ht="15.75" thickBot="1">
+    <row r="502" spans="1:8" ht="15" thickBot="1">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -7908,7 +7908,7 @@
       <c r="G502" s="1"/>
       <c r="H502" s="1"/>
     </row>
-    <row r="503" spans="1:8" ht="15.75" thickBot="1">
+    <row r="503" spans="1:8" ht="15" thickBot="1">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -7918,7 +7918,7 @@
       <c r="G503" s="1"/>
       <c r="H503" s="1"/>
     </row>
-    <row r="504" spans="1:8" ht="15.75" thickBot="1">
+    <row r="504" spans="1:8" ht="15" thickBot="1">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -7928,7 +7928,7 @@
       <c r="G504" s="1"/>
       <c r="H504" s="1"/>
     </row>
-    <row r="505" spans="1:8" ht="15.75" thickBot="1">
+    <row r="505" spans="1:8" ht="15" thickBot="1">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -7938,7 +7938,7 @@
       <c r="G505" s="1"/>
       <c r="H505" s="1"/>
     </row>
-    <row r="506" spans="1:8" ht="15.75" thickBot="1">
+    <row r="506" spans="1:8" ht="15" thickBot="1">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -7948,7 +7948,7 @@
       <c r="G506" s="1"/>
       <c r="H506" s="1"/>
     </row>
-    <row r="507" spans="1:8" ht="15.75" thickBot="1">
+    <row r="507" spans="1:8" ht="15" thickBot="1">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -7958,7 +7958,7 @@
       <c r="G507" s="1"/>
       <c r="H507" s="1"/>
     </row>
-    <row r="508" spans="1:8" ht="15.75" thickBot="1">
+    <row r="508" spans="1:8" ht="15" thickBot="1">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -7968,7 +7968,7 @@
       <c r="G508" s="1"/>
       <c r="H508" s="1"/>
     </row>
-    <row r="509" spans="1:8" ht="15.75" thickBot="1">
+    <row r="509" spans="1:8" ht="15" thickBot="1">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -7978,7 +7978,7 @@
       <c r="G509" s="1"/>
       <c r="H509" s="1"/>
     </row>
-    <row r="510" spans="1:8" ht="15.75" thickBot="1">
+    <row r="510" spans="1:8" ht="15" thickBot="1">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -7988,7 +7988,7 @@
       <c r="G510" s="1"/>
       <c r="H510" s="1"/>
     </row>
-    <row r="511" spans="1:8" ht="15.75" thickBot="1">
+    <row r="511" spans="1:8" ht="15" thickBot="1">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -7998,7 +7998,7 @@
       <c r="G511" s="1"/>
       <c r="H511" s="1"/>
     </row>
-    <row r="512" spans="1:8" ht="15.75" thickBot="1">
+    <row r="512" spans="1:8" ht="15" thickBot="1">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -8008,7 +8008,7 @@
       <c r="G512" s="1"/>
       <c r="H512" s="1"/>
     </row>
-    <row r="513" spans="1:8" ht="15.75" thickBot="1">
+    <row r="513" spans="1:8" ht="15" thickBot="1">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -8018,7 +8018,7 @@
       <c r="G513" s="1"/>
       <c r="H513" s="1"/>
     </row>
-    <row r="514" spans="1:8" ht="15.75" thickBot="1">
+    <row r="514" spans="1:8" ht="15" thickBot="1">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -8028,7 +8028,7 @@
       <c r="G514" s="1"/>
       <c r="H514" s="1"/>
     </row>
-    <row r="515" spans="1:8" ht="15.75" thickBot="1">
+    <row r="515" spans="1:8" ht="15" thickBot="1">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -8038,7 +8038,7 @@
       <c r="G515" s="1"/>
       <c r="H515" s="1"/>
     </row>
-    <row r="516" spans="1:8" ht="15.75" thickBot="1">
+    <row r="516" spans="1:8" ht="15" thickBot="1">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -8048,7 +8048,7 @@
       <c r="G516" s="1"/>
       <c r="H516" s="1"/>
     </row>
-    <row r="517" spans="1:8" ht="15.75" thickBot="1">
+    <row r="517" spans="1:8" ht="15" thickBot="1">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -8058,7 +8058,7 @@
       <c r="G517" s="1"/>
       <c r="H517" s="1"/>
     </row>
-    <row r="518" spans="1:8" ht="15.75" thickBot="1">
+    <row r="518" spans="1:8" ht="15" thickBot="1">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -8068,7 +8068,7 @@
       <c r="G518" s="1"/>
       <c r="H518" s="1"/>
     </row>
-    <row r="519" spans="1:8" ht="15.75" thickBot="1">
+    <row r="519" spans="1:8" ht="15" thickBot="1">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -8078,7 +8078,7 @@
       <c r="G519" s="1"/>
       <c r="H519" s="1"/>
     </row>
-    <row r="520" spans="1:8" ht="15.75" thickBot="1">
+    <row r="520" spans="1:8" ht="15" thickBot="1">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -8088,7 +8088,7 @@
       <c r="G520" s="1"/>
       <c r="H520" s="1"/>
     </row>
-    <row r="521" spans="1:8" ht="15.75" thickBot="1">
+    <row r="521" spans="1:8" ht="15" thickBot="1">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -8098,7 +8098,7 @@
       <c r="G521" s="1"/>
       <c r="H521" s="1"/>
     </row>
-    <row r="522" spans="1:8" ht="15.75" thickBot="1">
+    <row r="522" spans="1:8" ht="15" thickBot="1">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -8108,7 +8108,7 @@
       <c r="G522" s="1"/>
       <c r="H522" s="1"/>
     </row>
-    <row r="523" spans="1:8" ht="15.75" thickBot="1">
+    <row r="523" spans="1:8" ht="15" thickBot="1">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -8118,7 +8118,7 @@
       <c r="G523" s="1"/>
       <c r="H523" s="1"/>
     </row>
-    <row r="524" spans="1:8" ht="15.75" thickBot="1">
+    <row r="524" spans="1:8" ht="15" thickBot="1">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -8128,7 +8128,7 @@
       <c r="G524" s="1"/>
       <c r="H524" s="1"/>
     </row>
-    <row r="525" spans="1:8" ht="15.75" thickBot="1">
+    <row r="525" spans="1:8" ht="15" thickBot="1">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -8138,7 +8138,7 @@
       <c r="G525" s="1"/>
       <c r="H525" s="1"/>
     </row>
-    <row r="526" spans="1:8" ht="15.75" thickBot="1">
+    <row r="526" spans="1:8" ht="15" thickBot="1">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -8148,7 +8148,7 @@
       <c r="G526" s="1"/>
       <c r="H526" s="1"/>
     </row>
-    <row r="527" spans="1:8" ht="15.75" thickBot="1">
+    <row r="527" spans="1:8" ht="15" thickBot="1">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -8158,7 +8158,7 @@
       <c r="G527" s="1"/>
       <c r="H527" s="1"/>
     </row>
-    <row r="528" spans="1:8" ht="15.75" thickBot="1">
+    <row r="528" spans="1:8" ht="15" thickBot="1">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -8168,7 +8168,7 @@
       <c r="G528" s="1"/>
       <c r="H528" s="1"/>
     </row>
-    <row r="529" spans="1:8" ht="15.75" thickBot="1">
+    <row r="529" spans="1:8" ht="15" thickBot="1">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -8178,7 +8178,7 @@
       <c r="G529" s="1"/>
       <c r="H529" s="1"/>
     </row>
-    <row r="530" spans="1:8" ht="15.75" thickBot="1">
+    <row r="530" spans="1:8" ht="15" thickBot="1">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -8188,7 +8188,7 @@
       <c r="G530" s="1"/>
       <c r="H530" s="1"/>
     </row>
-    <row r="531" spans="1:8" ht="15.75" thickBot="1">
+    <row r="531" spans="1:8" ht="15" thickBot="1">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -8198,7 +8198,7 @@
       <c r="G531" s="1"/>
       <c r="H531" s="1"/>
     </row>
-    <row r="532" spans="1:8" ht="15.75" thickBot="1">
+    <row r="532" spans="1:8" ht="15" thickBot="1">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -8208,7 +8208,7 @@
       <c r="G532" s="1"/>
       <c r="H532" s="1"/>
     </row>
-    <row r="533" spans="1:8" ht="15.75" thickBot="1">
+    <row r="533" spans="1:8" ht="15" thickBot="1">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -8218,7 +8218,7 @@
       <c r="G533" s="1"/>
       <c r="H533" s="1"/>
     </row>
-    <row r="534" spans="1:8" ht="15.75" thickBot="1">
+    <row r="534" spans="1:8" ht="15" thickBot="1">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -8228,7 +8228,7 @@
       <c r="G534" s="1"/>
       <c r="H534" s="1"/>
     </row>
-    <row r="535" spans="1:8" ht="15.75" thickBot="1">
+    <row r="535" spans="1:8" ht="15" thickBot="1">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -8238,7 +8238,7 @@
       <c r="G535" s="1"/>
       <c r="H535" s="1"/>
     </row>
-    <row r="536" spans="1:8" ht="15.75" thickBot="1">
+    <row r="536" spans="1:8" ht="15" thickBot="1">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -8248,7 +8248,7 @@
       <c r="G536" s="1"/>
       <c r="H536" s="1"/>
     </row>
-    <row r="537" spans="1:8" ht="15.75" thickBot="1">
+    <row r="537" spans="1:8" ht="15" thickBot="1">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -8258,7 +8258,7 @@
       <c r="G537" s="1"/>
       <c r="H537" s="1"/>
     </row>
-    <row r="538" spans="1:8" ht="15.75" thickBot="1">
+    <row r="538" spans="1:8" ht="15" thickBot="1">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -8268,7 +8268,7 @@
       <c r="G538" s="1"/>
       <c r="H538" s="1"/>
     </row>
-    <row r="539" spans="1:8" ht="15.75" thickBot="1">
+    <row r="539" spans="1:8" ht="15" thickBot="1">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -8278,7 +8278,7 @@
       <c r="G539" s="1"/>
       <c r="H539" s="1"/>
     </row>
-    <row r="540" spans="1:8" ht="15.75" thickBot="1">
+    <row r="540" spans="1:8" ht="15" thickBot="1">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -8288,7 +8288,7 @@
       <c r="G540" s="1"/>
       <c r="H540" s="1"/>
     </row>
-    <row r="541" spans="1:8" ht="15.75" thickBot="1">
+    <row r="541" spans="1:8" ht="15" thickBot="1">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -8298,7 +8298,7 @@
       <c r="G541" s="1"/>
       <c r="H541" s="1"/>
     </row>
-    <row r="542" spans="1:8" ht="15.75" thickBot="1">
+    <row r="542" spans="1:8" ht="15" thickBot="1">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -8308,7 +8308,7 @@
       <c r="G542" s="1"/>
       <c r="H542" s="1"/>
     </row>
-    <row r="543" spans="1:8" ht="15.75" thickBot="1">
+    <row r="543" spans="1:8" ht="15" thickBot="1">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -8318,7 +8318,7 @@
       <c r="G543" s="1"/>
       <c r="H543" s="1"/>
     </row>
-    <row r="544" spans="1:8" ht="15.75" thickBot="1">
+    <row r="544" spans="1:8" ht="15" thickBot="1">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -8328,7 +8328,7 @@
       <c r="G544" s="1"/>
       <c r="H544" s="1"/>
     </row>
-    <row r="545" spans="1:8" ht="15.75" thickBot="1">
+    <row r="545" spans="1:8" ht="15" thickBot="1">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -8338,7 +8338,7 @@
       <c r="G545" s="1"/>
       <c r="H545" s="1"/>
     </row>
-    <row r="546" spans="1:8" ht="15.75" thickBot="1">
+    <row r="546" spans="1:8" ht="15" thickBot="1">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -8348,7 +8348,7 @@
       <c r="G546" s="1"/>
       <c r="H546" s="1"/>
     </row>
-    <row r="547" spans="1:8" ht="15.75" thickBot="1">
+    <row r="547" spans="1:8" ht="15" thickBot="1">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -8358,7 +8358,7 @@
       <c r="G547" s="1"/>
       <c r="H547" s="1"/>
     </row>
-    <row r="548" spans="1:8" ht="15.75" thickBot="1">
+    <row r="548" spans="1:8" ht="15" thickBot="1">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -8368,7 +8368,7 @@
       <c r="G548" s="1"/>
       <c r="H548" s="1"/>
     </row>
-    <row r="549" spans="1:8" ht="15.75" thickBot="1">
+    <row r="549" spans="1:8" ht="15" thickBot="1">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -8378,7 +8378,7 @@
       <c r="G549" s="1"/>
       <c r="H549" s="1"/>
     </row>
-    <row r="550" spans="1:8" ht="15.75" thickBot="1">
+    <row r="550" spans="1:8" ht="15" thickBot="1">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -8388,7 +8388,7 @@
       <c r="G550" s="1"/>
       <c r="H550" s="1"/>
     </row>
-    <row r="551" spans="1:8" ht="15.75" thickBot="1">
+    <row r="551" spans="1:8" ht="15" thickBot="1">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -8398,7 +8398,7 @@
       <c r="G551" s="1"/>
       <c r="H551" s="1"/>
     </row>
-    <row r="552" spans="1:8" ht="15.75" thickBot="1">
+    <row r="552" spans="1:8" ht="15" thickBot="1">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -8408,7 +8408,7 @@
       <c r="G552" s="1"/>
       <c r="H552" s="1"/>
     </row>
-    <row r="553" spans="1:8" ht="15.75" thickBot="1">
+    <row r="553" spans="1:8" ht="15" thickBot="1">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -8418,7 +8418,7 @@
       <c r="G553" s="1"/>
       <c r="H553" s="1"/>
     </row>
-    <row r="554" spans="1:8" ht="15.75" thickBot="1">
+    <row r="554" spans="1:8" ht="15" thickBot="1">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -8428,7 +8428,7 @@
       <c r="G554" s="1"/>
       <c r="H554" s="1"/>
     </row>
-    <row r="555" spans="1:8" ht="15.75" thickBot="1">
+    <row r="555" spans="1:8" ht="15" thickBot="1">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -8438,7 +8438,7 @@
       <c r="G555" s="1"/>
       <c r="H555" s="1"/>
     </row>
-    <row r="556" spans="1:8" ht="15.75" thickBot="1">
+    <row r="556" spans="1:8" ht="15" thickBot="1">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -8448,7 +8448,7 @@
       <c r="G556" s="1"/>
       <c r="H556" s="1"/>
     </row>
-    <row r="557" spans="1:8" ht="15.75" thickBot="1">
+    <row r="557" spans="1:8" ht="15" thickBot="1">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -8458,7 +8458,7 @@
       <c r="G557" s="1"/>
       <c r="H557" s="1"/>
     </row>
-    <row r="558" spans="1:8" ht="15.75" thickBot="1">
+    <row r="558" spans="1:8" ht="15" thickBot="1">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -8468,7 +8468,7 @@
       <c r="G558" s="1"/>
       <c r="H558" s="1"/>
     </row>
-    <row r="559" spans="1:8" ht="15.75" thickBot="1">
+    <row r="559" spans="1:8" ht="15" thickBot="1">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -8478,7 +8478,7 @@
       <c r="G559" s="1"/>
       <c r="H559" s="1"/>
     </row>
-    <row r="560" spans="1:8" ht="15.75" thickBot="1">
+    <row r="560" spans="1:8" ht="15" thickBot="1">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -8488,7 +8488,7 @@
       <c r="G560" s="1"/>
       <c r="H560" s="1"/>
     </row>
-    <row r="561" spans="1:8" ht="15.75" thickBot="1">
+    <row r="561" spans="1:8" ht="15" thickBot="1">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -8498,7 +8498,7 @@
       <c r="G561" s="1"/>
       <c r="H561" s="1"/>
     </row>
-    <row r="562" spans="1:8" ht="15.75" thickBot="1">
+    <row r="562" spans="1:8" ht="15" thickBot="1">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -8508,7 +8508,7 @@
       <c r="G562" s="1"/>
       <c r="H562" s="1"/>
     </row>
-    <row r="563" spans="1:8" ht="15.75" thickBot="1">
+    <row r="563" spans="1:8" ht="15" thickBot="1">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -8518,7 +8518,7 @@
       <c r="G563" s="1"/>
       <c r="H563" s="1"/>
     </row>
-    <row r="564" spans="1:8" ht="15.75" thickBot="1">
+    <row r="564" spans="1:8" ht="15" thickBot="1">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -8528,7 +8528,7 @@
       <c r="G564" s="1"/>
       <c r="H564" s="1"/>
     </row>
-    <row r="565" spans="1:8" ht="15.75" thickBot="1">
+    <row r="565" spans="1:8" ht="15" thickBot="1">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -8538,7 +8538,7 @@
       <c r="G565" s="1"/>
       <c r="H565" s="1"/>
     </row>
-    <row r="566" spans="1:8" ht="15.75" thickBot="1">
+    <row r="566" spans="1:8" ht="15" thickBot="1">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -8548,7 +8548,7 @@
       <c r="G566" s="1"/>
       <c r="H566" s="1"/>
     </row>
-    <row r="567" spans="1:8" ht="15.75" thickBot="1">
+    <row r="567" spans="1:8" ht="15" thickBot="1">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -8558,7 +8558,7 @@
       <c r="G567" s="1"/>
       <c r="H567" s="1"/>
     </row>
-    <row r="568" spans="1:8" ht="15.75" thickBot="1">
+    <row r="568" spans="1:8" ht="15" thickBot="1">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -8568,7 +8568,7 @@
       <c r="G568" s="1"/>
       <c r="H568" s="1"/>
     </row>
-    <row r="569" spans="1:8" ht="15.75" thickBot="1">
+    <row r="569" spans="1:8" ht="15" thickBot="1">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -8578,7 +8578,7 @@
       <c r="G569" s="1"/>
       <c r="H569" s="1"/>
     </row>
-    <row r="570" spans="1:8" ht="15.75" thickBot="1">
+    <row r="570" spans="1:8" ht="15" thickBot="1">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -8588,7 +8588,7 @@
       <c r="G570" s="1"/>
       <c r="H570" s="1"/>
     </row>
-    <row r="571" spans="1:8" ht="15.75" thickBot="1">
+    <row r="571" spans="1:8" ht="15" thickBot="1">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -8598,7 +8598,7 @@
       <c r="G571" s="1"/>
       <c r="H571" s="1"/>
     </row>
-    <row r="572" spans="1:8" ht="15.75" thickBot="1">
+    <row r="572" spans="1:8" ht="15" thickBot="1">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -8608,7 +8608,7 @@
       <c r="G572" s="1"/>
       <c r="H572" s="1"/>
     </row>
-    <row r="573" spans="1:8" ht="15.75" thickBot="1">
+    <row r="573" spans="1:8" ht="15" thickBot="1">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -8618,7 +8618,7 @@
       <c r="G573" s="1"/>
       <c r="H573" s="1"/>
     </row>
-    <row r="574" spans="1:8" ht="15.75" thickBot="1">
+    <row r="574" spans="1:8" ht="15" thickBot="1">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -8628,7 +8628,7 @@
       <c r="G574" s="1"/>
       <c r="H574" s="1"/>
     </row>
-    <row r="575" spans="1:8" ht="15.75" thickBot="1">
+    <row r="575" spans="1:8" ht="15" thickBot="1">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -8638,7 +8638,7 @@
       <c r="G575" s="1"/>
       <c r="H575" s="1"/>
     </row>
-    <row r="576" spans="1:8" ht="15.75" thickBot="1">
+    <row r="576" spans="1:8" ht="15" thickBot="1">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -8648,7 +8648,7 @@
       <c r="G576" s="1"/>
       <c r="H576" s="1"/>
     </row>
-    <row r="577" spans="1:8" ht="15.75" thickBot="1">
+    <row r="577" spans="1:8" ht="15" thickBot="1">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -8658,7 +8658,7 @@
       <c r="G577" s="1"/>
       <c r="H577" s="1"/>
     </row>
-    <row r="578" spans="1:8" ht="15.75" thickBot="1">
+    <row r="578" spans="1:8" ht="15" thickBot="1">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -8668,7 +8668,7 @@
       <c r="G578" s="1"/>
       <c r="H578" s="1"/>
     </row>
-    <row r="579" spans="1:8" ht="15.75" thickBot="1">
+    <row r="579" spans="1:8" ht="15" thickBot="1">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -8678,7 +8678,7 @@
       <c r="G579" s="1"/>
       <c r="H579" s="1"/>
     </row>
-    <row r="580" spans="1:8" ht="15.75" thickBot="1">
+    <row r="580" spans="1:8" ht="15" thickBot="1">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -8688,7 +8688,7 @@
       <c r="G580" s="1"/>
       <c r="H580" s="1"/>
     </row>
-    <row r="581" spans="1:8" ht="15.75" thickBot="1">
+    <row r="581" spans="1:8" ht="15" thickBot="1">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -8698,7 +8698,7 @@
       <c r="G581" s="1"/>
       <c r="H581" s="1"/>
     </row>
-    <row r="582" spans="1:8" ht="15.75" thickBot="1">
+    <row r="582" spans="1:8" ht="15" thickBot="1">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -8708,7 +8708,7 @@
       <c r="G582" s="1"/>
       <c r="H582" s="1"/>
     </row>
-    <row r="583" spans="1:8" ht="15.75" thickBot="1">
+    <row r="583" spans="1:8" ht="15" thickBot="1">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -8718,7 +8718,7 @@
       <c r="G583" s="1"/>
       <c r="H583" s="1"/>
     </row>
-    <row r="584" spans="1:8" ht="15.75" thickBot="1">
+    <row r="584" spans="1:8" ht="15" thickBot="1">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -8728,7 +8728,7 @@
       <c r="G584" s="1"/>
       <c r="H584" s="1"/>
     </row>
-    <row r="585" spans="1:8" ht="15.75" thickBot="1">
+    <row r="585" spans="1:8" ht="15" thickBot="1">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -8738,7 +8738,7 @@
       <c r="G585" s="1"/>
       <c r="H585" s="1"/>
     </row>
-    <row r="586" spans="1:8" ht="15.75" thickBot="1">
+    <row r="586" spans="1:8" ht="15" thickBot="1">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -8748,7 +8748,7 @@
       <c r="G586" s="1"/>
       <c r="H586" s="1"/>
     </row>
-    <row r="587" spans="1:8" ht="15.75" thickBot="1">
+    <row r="587" spans="1:8" ht="15" thickBot="1">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -8758,7 +8758,7 @@
       <c r="G587" s="1"/>
       <c r="H587" s="1"/>
     </row>
-    <row r="588" spans="1:8" ht="15.75" thickBot="1">
+    <row r="588" spans="1:8" ht="15" thickBot="1">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -8768,7 +8768,7 @@
       <c r="G588" s="1"/>
       <c r="H588" s="1"/>
     </row>
-    <row r="589" spans="1:8" ht="15.75" thickBot="1">
+    <row r="589" spans="1:8" ht="15" thickBot="1">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -8778,7 +8778,7 @@
       <c r="G589" s="1"/>
       <c r="H589" s="1"/>
     </row>
-    <row r="590" spans="1:8" ht="15.75" thickBot="1">
+    <row r="590" spans="1:8" ht="15" thickBot="1">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -8788,7 +8788,7 @@
       <c r="G590" s="1"/>
       <c r="H590" s="1"/>
     </row>
-    <row r="591" spans="1:8" ht="15.75" thickBot="1">
+    <row r="591" spans="1:8" ht="15" thickBot="1">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -8798,7 +8798,7 @@
       <c r="G591" s="1"/>
       <c r="H591" s="1"/>
     </row>
-    <row r="592" spans="1:8" ht="15.75" thickBot="1">
+    <row r="592" spans="1:8" ht="15" thickBot="1">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -8808,7 +8808,7 @@
       <c r="G592" s="1"/>
       <c r="H592" s="1"/>
     </row>
-    <row r="593" spans="1:8" ht="15.75" thickBot="1">
+    <row r="593" spans="1:8" ht="15" thickBot="1">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -8818,7 +8818,7 @@
       <c r="G593" s="1"/>
       <c r="H593" s="1"/>
     </row>
-    <row r="594" spans="1:8" ht="15.75" thickBot="1">
+    <row r="594" spans="1:8" ht="15" thickBot="1">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -8828,7 +8828,7 @@
       <c r="G594" s="1"/>
       <c r="H594" s="1"/>
     </row>
-    <row r="595" spans="1:8" ht="15.75" thickBot="1">
+    <row r="595" spans="1:8" ht="15" thickBot="1">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -8838,7 +8838,7 @@
       <c r="G595" s="1"/>
       <c r="H595" s="1"/>
     </row>
-    <row r="596" spans="1:8" ht="15.75" thickBot="1">
+    <row r="596" spans="1:8" ht="15" thickBot="1">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -8848,7 +8848,7 @@
       <c r="G596" s="1"/>
       <c r="H596" s="1"/>
     </row>
-    <row r="597" spans="1:8" ht="15.75" thickBot="1">
+    <row r="597" spans="1:8" ht="15" thickBot="1">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -8858,7 +8858,7 @@
       <c r="G597" s="1"/>
       <c r="H597" s="1"/>
     </row>
-    <row r="598" spans="1:8" ht="15.75" thickBot="1">
+    <row r="598" spans="1:8" ht="15" thickBot="1">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -8868,7 +8868,7 @@
       <c r="G598" s="1"/>
       <c r="H598" s="1"/>
     </row>
-    <row r="599" spans="1:8" ht="15.75" thickBot="1">
+    <row r="599" spans="1:8" ht="15" thickBot="1">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -8878,7 +8878,7 @@
       <c r="G599" s="1"/>
       <c r="H599" s="1"/>
     </row>
-    <row r="600" spans="1:8" ht="15.75" thickBot="1">
+    <row r="600" spans="1:8" ht="15" thickBot="1">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -8888,7 +8888,7 @@
       <c r="G600" s="1"/>
       <c r="H600" s="1"/>
     </row>
-    <row r="601" spans="1:8" ht="15.75" thickBot="1">
+    <row r="601" spans="1:8" ht="15" thickBot="1">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -8898,7 +8898,7 @@
       <c r="G601" s="1"/>
       <c r="H601" s="1"/>
     </row>
-    <row r="602" spans="1:8" ht="15.75" thickBot="1">
+    <row r="602" spans="1:8" ht="15" thickBot="1">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -8908,7 +8908,7 @@
       <c r="G602" s="1"/>
       <c r="H602" s="1"/>
     </row>
-    <row r="603" spans="1:8" ht="15.75" thickBot="1">
+    <row r="603" spans="1:8" ht="15" thickBot="1">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -8918,7 +8918,7 @@
       <c r="G603" s="1"/>
       <c r="H603" s="1"/>
     </row>
-    <row r="604" spans="1:8" ht="15.75" thickBot="1">
+    <row r="604" spans="1:8" ht="15" thickBot="1">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -8928,7 +8928,7 @@
       <c r="G604" s="1"/>
       <c r="H604" s="1"/>
     </row>
-    <row r="605" spans="1:8" ht="15.75" thickBot="1">
+    <row r="605" spans="1:8" ht="15" thickBot="1">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -8938,7 +8938,7 @@
       <c r="G605" s="1"/>
       <c r="H605" s="1"/>
     </row>
-    <row r="606" spans="1:8" ht="15.75" thickBot="1">
+    <row r="606" spans="1:8" ht="15" thickBot="1">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -8948,7 +8948,7 @@
       <c r="G606" s="1"/>
       <c r="H606" s="1"/>
     </row>
-    <row r="607" spans="1:8" ht="15.75" thickBot="1">
+    <row r="607" spans="1:8" ht="15" thickBot="1">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -8958,7 +8958,7 @@
       <c r="G607" s="1"/>
       <c r="H607" s="1"/>
     </row>
-    <row r="608" spans="1:8" ht="15.75" thickBot="1">
+    <row r="608" spans="1:8" ht="15" thickBot="1">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -8968,7 +8968,7 @@
       <c r="G608" s="1"/>
       <c r="H608" s="1"/>
     </row>
-    <row r="609" spans="1:8" ht="15.75" thickBot="1">
+    <row r="609" spans="1:8" ht="15" thickBot="1">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -8978,7 +8978,7 @@
       <c r="G609" s="1"/>
       <c r="H609" s="1"/>
     </row>
-    <row r="610" spans="1:8" ht="15.75" thickBot="1">
+    <row r="610" spans="1:8" ht="15" thickBot="1">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -8988,7 +8988,7 @@
       <c r="G610" s="1"/>
       <c r="H610" s="1"/>
     </row>
-    <row r="611" spans="1:8" ht="15.75" thickBot="1">
+    <row r="611" spans="1:8" ht="15" thickBot="1">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -8998,7 +8998,7 @@
       <c r="G611" s="1"/>
       <c r="H611" s="1"/>
     </row>
-    <row r="612" spans="1:8" ht="15.75" thickBot="1">
+    <row r="612" spans="1:8" ht="15" thickBot="1">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -9008,7 +9008,7 @@
       <c r="G612" s="1"/>
       <c r="H612" s="1"/>
     </row>
-    <row r="613" spans="1:8" ht="15.75" thickBot="1">
+    <row r="613" spans="1:8" ht="15" thickBot="1">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -9018,7 +9018,7 @@
       <c r="G613" s="1"/>
       <c r="H613" s="1"/>
     </row>
-    <row r="614" spans="1:8" ht="15.75" thickBot="1">
+    <row r="614" spans="1:8" ht="15" thickBot="1">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -9028,7 +9028,7 @@
       <c r="G614" s="1"/>
       <c r="H614" s="1"/>
     </row>
-    <row r="615" spans="1:8" ht="15.75" thickBot="1">
+    <row r="615" spans="1:8" ht="15" thickBot="1">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -9038,7 +9038,7 @@
       <c r="G615" s="1"/>
       <c r="H615" s="1"/>
     </row>
-    <row r="616" spans="1:8" ht="15.75" thickBot="1">
+    <row r="616" spans="1:8" ht="15" thickBot="1">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -9048,7 +9048,7 @@
       <c r="G616" s="1"/>
       <c r="H616" s="1"/>
     </row>
-    <row r="617" spans="1:8" ht="15.75" thickBot="1">
+    <row r="617" spans="1:8" ht="15" thickBot="1">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -9058,7 +9058,7 @@
       <c r="G617" s="1"/>
       <c r="H617" s="1"/>
     </row>
-    <row r="618" spans="1:8" ht="15.75" thickBot="1">
+    <row r="618" spans="1:8" ht="15" thickBot="1">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -9068,7 +9068,7 @@
       <c r="G618" s="1"/>
       <c r="H618" s="1"/>
     </row>
-    <row r="619" spans="1:8" ht="15.75" thickBot="1">
+    <row r="619" spans="1:8" ht="15" thickBot="1">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -9078,7 +9078,7 @@
       <c r="G619" s="1"/>
       <c r="H619" s="1"/>
     </row>
-    <row r="620" spans="1:8" ht="15.75" thickBot="1">
+    <row r="620" spans="1:8" ht="15" thickBot="1">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -9088,7 +9088,7 @@
       <c r="G620" s="1"/>
       <c r="H620" s="1"/>
     </row>
-    <row r="621" spans="1:8" ht="15.75" thickBot="1">
+    <row r="621" spans="1:8" ht="15" thickBot="1">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -9098,7 +9098,7 @@
       <c r="G621" s="1"/>
       <c r="H621" s="1"/>
     </row>
-    <row r="622" spans="1:8" ht="15.75" thickBot="1">
+    <row r="622" spans="1:8" ht="15" thickBot="1">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -9108,7 +9108,7 @@
       <c r="G622" s="1"/>
       <c r="H622" s="1"/>
     </row>
-    <row r="623" spans="1:8" ht="15.75" thickBot="1">
+    <row r="623" spans="1:8" ht="15" thickBot="1">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -9118,7 +9118,7 @@
       <c r="G623" s="1"/>
       <c r="H623" s="1"/>
     </row>
-    <row r="624" spans="1:8" ht="15.75" thickBot="1">
+    <row r="624" spans="1:8" ht="15" thickBot="1">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -9128,7 +9128,7 @@
       <c r="G624" s="1"/>
       <c r="H624" s="1"/>
     </row>
-    <row r="625" spans="1:8" ht="15.75" thickBot="1">
+    <row r="625" spans="1:8" ht="15" thickBot="1">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -9138,7 +9138,7 @@
       <c r="G625" s="1"/>
       <c r="H625" s="1"/>
     </row>
-    <row r="626" spans="1:8" ht="15.75" thickBot="1">
+    <row r="626" spans="1:8" ht="15" thickBot="1">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -9148,7 +9148,7 @@
       <c r="G626" s="1"/>
       <c r="H626" s="1"/>
     </row>
-    <row r="627" spans="1:8" ht="15.75" thickBot="1">
+    <row r="627" spans="1:8" ht="15" thickBot="1">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -9158,7 +9158,7 @@
       <c r="G627" s="1"/>
       <c r="H627" s="1"/>
     </row>
-    <row r="628" spans="1:8" ht="15.75" thickBot="1">
+    <row r="628" spans="1:8" ht="15" thickBot="1">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -9168,7 +9168,7 @@
       <c r="G628" s="1"/>
       <c r="H628" s="1"/>
     </row>
-    <row r="629" spans="1:8" ht="15.75" thickBot="1">
+    <row r="629" spans="1:8" ht="15" thickBot="1">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -9178,7 +9178,7 @@
       <c r="G629" s="1"/>
       <c r="H629" s="1"/>
     </row>
-    <row r="630" spans="1:8" ht="15.75" thickBot="1">
+    <row r="630" spans="1:8" ht="15" thickBot="1">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -9188,7 +9188,7 @@
       <c r="G630" s="1"/>
       <c r="H630" s="1"/>
     </row>
-    <row r="631" spans="1:8" ht="15.75" thickBot="1">
+    <row r="631" spans="1:8" ht="15" thickBot="1">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -9198,7 +9198,7 @@
       <c r="G631" s="1"/>
       <c r="H631" s="1"/>
     </row>
-    <row r="632" spans="1:8" ht="15.75" thickBot="1">
+    <row r="632" spans="1:8" ht="15" thickBot="1">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -9208,7 +9208,7 @@
       <c r="G632" s="1"/>
       <c r="H632" s="1"/>
     </row>
-    <row r="633" spans="1:8" ht="15.75" thickBot="1">
+    <row r="633" spans="1:8" ht="15" thickBot="1">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -9218,7 +9218,7 @@
       <c r="G633" s="1"/>
       <c r="H633" s="1"/>
     </row>
-    <row r="634" spans="1:8" ht="15.75" thickBot="1">
+    <row r="634" spans="1:8" ht="15" thickBot="1">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -9228,7 +9228,7 @@
       <c r="G634" s="1"/>
       <c r="H634" s="1"/>
     </row>
-    <row r="635" spans="1:8" ht="15.75" thickBot="1">
+    <row r="635" spans="1:8" ht="15" thickBot="1">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -9238,7 +9238,7 @@
       <c r="G635" s="1"/>
       <c r="H635" s="1"/>
     </row>
-    <row r="636" spans="1:8" ht="15.75" thickBot="1">
+    <row r="636" spans="1:8" ht="15" thickBot="1">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -9248,7 +9248,7 @@
       <c r="G636" s="1"/>
       <c r="H636" s="1"/>
     </row>
-    <row r="637" spans="1:8" ht="15.75" thickBot="1">
+    <row r="637" spans="1:8" ht="15" thickBot="1">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -9258,7 +9258,7 @@
       <c r="G637" s="1"/>
       <c r="H637" s="1"/>
     </row>
-    <row r="638" spans="1:8" ht="15.75" thickBot="1">
+    <row r="638" spans="1:8" ht="15" thickBot="1">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -9268,7 +9268,7 @@
       <c r="G638" s="1"/>
       <c r="H638" s="1"/>
     </row>
-    <row r="639" spans="1:8" ht="15.75" thickBot="1">
+    <row r="639" spans="1:8" ht="15" thickBot="1">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -9278,7 +9278,7 @@
       <c r="G639" s="1"/>
       <c r="H639" s="1"/>
     </row>
-    <row r="640" spans="1:8" ht="15.75" thickBot="1">
+    <row r="640" spans="1:8" ht="15" thickBot="1">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -9288,7 +9288,7 @@
       <c r="G640" s="1"/>
       <c r="H640" s="1"/>
     </row>
-    <row r="641" spans="1:8" ht="15.75" thickBot="1">
+    <row r="641" spans="1:8" ht="15" thickBot="1">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -9298,7 +9298,7 @@
       <c r="G641" s="1"/>
       <c r="H641" s="1"/>
     </row>
-    <row r="642" spans="1:8" ht="15.75" thickBot="1">
+    <row r="642" spans="1:8" ht="15" thickBot="1">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -9308,7 +9308,7 @@
       <c r="G642" s="1"/>
       <c r="H642" s="1"/>
     </row>
-    <row r="643" spans="1:8" ht="15.75" thickBot="1">
+    <row r="643" spans="1:8" ht="15" thickBot="1">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -9318,7 +9318,7 @@
       <c r="G643" s="1"/>
       <c r="H643" s="1"/>
     </row>
-    <row r="644" spans="1:8" ht="15.75" thickBot="1">
+    <row r="644" spans="1:8" ht="15" thickBot="1">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -9328,7 +9328,7 @@
       <c r="G644" s="1"/>
       <c r="H644" s="1"/>
     </row>
-    <row r="645" spans="1:8" ht="15.75" thickBot="1">
+    <row r="645" spans="1:8" ht="15" thickBot="1">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -9338,7 +9338,7 @@
       <c r="G645" s="1"/>
       <c r="H645" s="1"/>
     </row>
-    <row r="646" spans="1:8" ht="15.75" thickBot="1">
+    <row r="646" spans="1:8" ht="15" thickBot="1">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -9348,7 +9348,7 @@
       <c r="G646" s="1"/>
       <c r="H646" s="1"/>
     </row>
-    <row r="647" spans="1:8" ht="15.75" thickBot="1">
+    <row r="647" spans="1:8" ht="15" thickBot="1">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -9358,7 +9358,7 @@
       <c r="G647" s="1"/>
       <c r="H647" s="1"/>
     </row>
-    <row r="648" spans="1:8" ht="15.75" thickBot="1">
+    <row r="648" spans="1:8" ht="15" thickBot="1">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -9368,7 +9368,7 @@
       <c r="G648" s="1"/>
       <c r="H648" s="1"/>
     </row>
-    <row r="649" spans="1:8" ht="15.75" thickBot="1">
+    <row r="649" spans="1:8" ht="15" thickBot="1">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -9378,7 +9378,7 @@
       <c r="G649" s="1"/>
       <c r="H649" s="1"/>
     </row>
-    <row r="650" spans="1:8" ht="15.75" thickBot="1">
+    <row r="650" spans="1:8" ht="15" thickBot="1">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -9388,7 +9388,7 @@
       <c r="G650" s="1"/>
       <c r="H650" s="1"/>
     </row>
-    <row r="651" spans="1:8" ht="15.75" thickBot="1">
+    <row r="651" spans="1:8" ht="15" thickBot="1">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -9398,7 +9398,7 @@
       <c r="G651" s="1"/>
       <c r="H651" s="1"/>
     </row>
-    <row r="652" spans="1:8" ht="15.75" thickBot="1">
+    <row r="652" spans="1:8" ht="15" thickBot="1">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -9408,7 +9408,7 @@
       <c r="G652" s="1"/>
       <c r="H652" s="1"/>
     </row>
-    <row r="653" spans="1:8" ht="15.75" thickBot="1">
+    <row r="653" spans="1:8" ht="15" thickBot="1">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -9418,7 +9418,7 @@
       <c r="G653" s="1"/>
       <c r="H653" s="1"/>
     </row>
-    <row r="654" spans="1:8" ht="15.75" thickBot="1">
+    <row r="654" spans="1:8" ht="15" thickBot="1">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -9428,7 +9428,7 @@
       <c r="G654" s="1"/>
       <c r="H654" s="1"/>
     </row>
-    <row r="655" spans="1:8" ht="15.75" thickBot="1">
+    <row r="655" spans="1:8" ht="15" thickBot="1">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -9438,7 +9438,7 @@
       <c r="G655" s="1"/>
       <c r="H655" s="1"/>
     </row>
-    <row r="656" spans="1:8" ht="15.75" thickBot="1">
+    <row r="656" spans="1:8" ht="15" thickBot="1">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -9448,7 +9448,7 @@
       <c r="G656" s="1"/>
       <c r="H656" s="1"/>
     </row>
-    <row r="657" spans="1:8" ht="15.75" thickBot="1">
+    <row r="657" spans="1:8" ht="15" thickBot="1">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -9458,7 +9458,7 @@
       <c r="G657" s="1"/>
       <c r="H657" s="1"/>
     </row>
-    <row r="658" spans="1:8" ht="15.75" thickBot="1">
+    <row r="658" spans="1:8" ht="15" thickBot="1">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -9468,7 +9468,7 @@
       <c r="G658" s="1"/>
       <c r="H658" s="1"/>
     </row>
-    <row r="659" spans="1:8" ht="15.75" thickBot="1">
+    <row r="659" spans="1:8" ht="15" thickBot="1">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -9478,7 +9478,7 @@
       <c r="G659" s="1"/>
       <c r="H659" s="1"/>
     </row>
-    <row r="660" spans="1:8" ht="15.75" thickBot="1">
+    <row r="660" spans="1:8" ht="15" thickBot="1">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -9488,7 +9488,7 @@
       <c r="G660" s="1"/>
       <c r="H660" s="1"/>
     </row>
-    <row r="661" spans="1:8" ht="15.75" thickBot="1">
+    <row r="661" spans="1:8" ht="15" thickBot="1">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -9498,7 +9498,7 @@
       <c r="G661" s="1"/>
       <c r="H661" s="1"/>
     </row>
-    <row r="662" spans="1:8" ht="15.75" thickBot="1">
+    <row r="662" spans="1:8" ht="15" thickBot="1">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -9508,7 +9508,7 @@
       <c r="G662" s="1"/>
       <c r="H662" s="1"/>
     </row>
-    <row r="663" spans="1:8" ht="15.75" thickBot="1">
+    <row r="663" spans="1:8" ht="15" thickBot="1">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -9518,7 +9518,7 @@
       <c r="G663" s="1"/>
       <c r="H663" s="1"/>
     </row>
-    <row r="664" spans="1:8" ht="15.75" thickBot="1">
+    <row r="664" spans="1:8" ht="15" thickBot="1">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -9528,7 +9528,7 @@
       <c r="G664" s="1"/>
       <c r="H664" s="1"/>
     </row>
-    <row r="665" spans="1:8" ht="15.75" thickBot="1">
+    <row r="665" spans="1:8" ht="15" thickBot="1">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -9538,7 +9538,7 @@
       <c r="G665" s="1"/>
       <c r="H665" s="1"/>
     </row>
-    <row r="666" spans="1:8" ht="15.75" thickBot="1">
+    <row r="666" spans="1:8" ht="15" thickBot="1">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -9548,7 +9548,7 @@
       <c r="G666" s="1"/>
       <c r="H666" s="1"/>
     </row>
-    <row r="667" spans="1:8" ht="15.75" thickBot="1">
+    <row r="667" spans="1:8" ht="15" thickBot="1">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -9558,7 +9558,7 @@
       <c r="G667" s="1"/>
       <c r="H667" s="1"/>
     </row>
-    <row r="668" spans="1:8" ht="15.75" thickBot="1">
+    <row r="668" spans="1:8" ht="15" thickBot="1">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -9568,7 +9568,7 @@
       <c r="G668" s="1"/>
       <c r="H668" s="1"/>
     </row>
-    <row r="669" spans="1:8" ht="15.75" thickBot="1">
+    <row r="669" spans="1:8" ht="15" thickBot="1">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -9578,7 +9578,7 @@
       <c r="G669" s="1"/>
       <c r="H669" s="1"/>
     </row>
-    <row r="670" spans="1:8" ht="15.75" thickBot="1">
+    <row r="670" spans="1:8" ht="15" thickBot="1">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -9588,7 +9588,7 @@
       <c r="G670" s="1"/>
       <c r="H670" s="1"/>
     </row>
-    <row r="671" spans="1:8" ht="15.75" thickBot="1">
+    <row r="671" spans="1:8" ht="15" thickBot="1">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -9598,7 +9598,7 @@
       <c r="G671" s="1"/>
       <c r="H671" s="1"/>
     </row>
-    <row r="672" spans="1:8" ht="15.75" thickBot="1">
+    <row r="672" spans="1:8" ht="15" thickBot="1">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -9608,7 +9608,7 @@
       <c r="G672" s="1"/>
       <c r="H672" s="1"/>
     </row>
-    <row r="673" spans="1:8" ht="15.75" thickBot="1">
+    <row r="673" spans="1:8" ht="15" thickBot="1">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -9618,7 +9618,7 @@
       <c r="G673" s="1"/>
       <c r="H673" s="1"/>
     </row>
-    <row r="674" spans="1:8" ht="15.75" thickBot="1">
+    <row r="674" spans="1:8" ht="15" thickBot="1">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -9628,7 +9628,7 @@
       <c r="G674" s="1"/>
       <c r="H674" s="1"/>
     </row>
-    <row r="675" spans="1:8" ht="15.75" thickBot="1">
+    <row r="675" spans="1:8" ht="15" thickBot="1">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -9638,7 +9638,7 @@
       <c r="G675" s="1"/>
       <c r="H675" s="1"/>
     </row>
-    <row r="676" spans="1:8" ht="15.75" thickBot="1">
+    <row r="676" spans="1:8" ht="15" thickBot="1">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -9648,7 +9648,7 @@
       <c r="G676" s="1"/>
       <c r="H676" s="1"/>
     </row>
-    <row r="677" spans="1:8" ht="15.75" thickBot="1">
+    <row r="677" spans="1:8" ht="15" thickBot="1">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -9658,7 +9658,7 @@
       <c r="G677" s="1"/>
       <c r="H677" s="1"/>
     </row>
-    <row r="678" spans="1:8" ht="15.75" thickBot="1">
+    <row r="678" spans="1:8" ht="15" thickBot="1">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -9668,7 +9668,7 @@
       <c r="G678" s="1"/>
       <c r="H678" s="1"/>
     </row>
-    <row r="679" spans="1:8" ht="15.75" thickBot="1">
+    <row r="679" spans="1:8" ht="15" thickBot="1">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -9678,7 +9678,7 @@
       <c r="G679" s="1"/>
       <c r="H679" s="1"/>
     </row>
-    <row r="680" spans="1:8" ht="15.75" thickBot="1">
+    <row r="680" spans="1:8" ht="15" thickBot="1">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -9688,7 +9688,7 @@
       <c r="G680" s="1"/>
       <c r="H680" s="1"/>
     </row>
-    <row r="681" spans="1:8" ht="15.75" thickBot="1">
+    <row r="681" spans="1:8" ht="15" thickBot="1">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -9698,7 +9698,7 @@
       <c r="G681" s="1"/>
       <c r="H681" s="1"/>
     </row>
-    <row r="682" spans="1:8" ht="15.75" thickBot="1">
+    <row r="682" spans="1:8" ht="15" thickBot="1">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -9708,7 +9708,7 @@
       <c r="G682" s="1"/>
       <c r="H682" s="1"/>
     </row>
-    <row r="683" spans="1:8" ht="15.75" thickBot="1">
+    <row r="683" spans="1:8" ht="15" thickBot="1">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -9718,7 +9718,7 @@
       <c r="G683" s="1"/>
       <c r="H683" s="1"/>
     </row>
-    <row r="684" spans="1:8" ht="15.75" thickBot="1">
+    <row r="684" spans="1:8" ht="15" thickBot="1">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -9728,7 +9728,7 @@
       <c r="G684" s="1"/>
       <c r="H684" s="1"/>
     </row>
-    <row r="685" spans="1:8" ht="15.75" thickBot="1">
+    <row r="685" spans="1:8" ht="15" thickBot="1">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -9738,7 +9738,7 @@
       <c r="G685" s="1"/>
       <c r="H685" s="1"/>
     </row>
-    <row r="686" spans="1:8" ht="15.75" thickBot="1">
+    <row r="686" spans="1:8" ht="15" thickBot="1">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -9748,7 +9748,7 @@
       <c r="G686" s="1"/>
       <c r="H686" s="1"/>
     </row>
-    <row r="687" spans="1:8" ht="15.75" thickBot="1">
+    <row r="687" spans="1:8" ht="15" thickBot="1">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -9758,7 +9758,7 @@
       <c r="G687" s="1"/>
       <c r="H687" s="1"/>
     </row>
-    <row r="688" spans="1:8" ht="15.75" thickBot="1">
+    <row r="688" spans="1:8" ht="15" thickBot="1">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -9768,7 +9768,7 @@
       <c r="G688" s="1"/>
       <c r="H688" s="1"/>
     </row>
-    <row r="689" spans="1:8" ht="15.75" thickBot="1">
+    <row r="689" spans="1:8" ht="15" thickBot="1">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -9778,7 +9778,7 @@
       <c r="G689" s="1"/>
       <c r="H689" s="1"/>
     </row>
-    <row r="690" spans="1:8" ht="15.75" thickBot="1">
+    <row r="690" spans="1:8" ht="15" thickBot="1">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -9788,7 +9788,7 @@
       <c r="G690" s="1"/>
       <c r="H690" s="1"/>
     </row>
-    <row r="691" spans="1:8" ht="15.75" thickBot="1">
+    <row r="691" spans="1:8" ht="15" thickBot="1">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -9798,7 +9798,7 @@
       <c r="G691" s="1"/>
       <c r="H691" s="1"/>
     </row>
-    <row r="692" spans="1:8" ht="15.75" thickBot="1">
+    <row r="692" spans="1:8" ht="15" thickBot="1">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -9808,7 +9808,7 @@
       <c r="G692" s="1"/>
       <c r="H692" s="1"/>
     </row>
-    <row r="693" spans="1:8" ht="15.75" thickBot="1">
+    <row r="693" spans="1:8" ht="15" thickBot="1">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -9818,7 +9818,7 @@
       <c r="G693" s="1"/>
       <c r="H693" s="1"/>
     </row>
-    <row r="694" spans="1:8" ht="15.75" thickBot="1">
+    <row r="694" spans="1:8" ht="15" thickBot="1">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -9828,7 +9828,7 @@
       <c r="G694" s="1"/>
       <c r="H694" s="1"/>
     </row>
-    <row r="695" spans="1:8" ht="15.75" thickBot="1">
+    <row r="695" spans="1:8" ht="15" thickBot="1">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -9838,7 +9838,7 @@
       <c r="G695" s="1"/>
       <c r="H695" s="1"/>
     </row>
-    <row r="696" spans="1:8" ht="15.75" thickBot="1">
+    <row r="696" spans="1:8" ht="15" thickBot="1">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -9848,7 +9848,7 @@
       <c r="G696" s="1"/>
       <c r="H696" s="1"/>
     </row>
-    <row r="697" spans="1:8" ht="15.75" thickBot="1">
+    <row r="697" spans="1:8" ht="15" thickBot="1">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -9858,7 +9858,7 @@
       <c r="G697" s="1"/>
       <c r="H697" s="1"/>
     </row>
-    <row r="698" spans="1:8" ht="15.75" thickBot="1">
+    <row r="698" spans="1:8" ht="15" thickBot="1">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -9868,7 +9868,7 @@
       <c r="G698" s="1"/>
       <c r="H698" s="1"/>
     </row>
-    <row r="699" spans="1:8" ht="15.75" thickBot="1">
+    <row r="699" spans="1:8" ht="15" thickBot="1">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -9878,7 +9878,7 @@
       <c r="G699" s="1"/>
       <c r="H699" s="1"/>
     </row>
-    <row r="700" spans="1:8" ht="15.75" thickBot="1">
+    <row r="700" spans="1:8" ht="15" thickBot="1">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -9888,7 +9888,7 @@
       <c r="G700" s="1"/>
       <c r="H700" s="1"/>
     </row>
-    <row r="701" spans="1:8" ht="15.75" thickBot="1">
+    <row r="701" spans="1:8" ht="15" thickBot="1">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -9898,7 +9898,7 @@
       <c r="G701" s="1"/>
       <c r="H701" s="1"/>
     </row>
-    <row r="702" spans="1:8" ht="15.75" thickBot="1">
+    <row r="702" spans="1:8" ht="15" thickBot="1">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -9908,7 +9908,7 @@
       <c r="G702" s="1"/>
       <c r="H702" s="1"/>
     </row>
-    <row r="703" spans="1:8" ht="15.75" thickBot="1">
+    <row r="703" spans="1:8" ht="15" thickBot="1">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -9918,7 +9918,7 @@
       <c r="G703" s="1"/>
       <c r="H703" s="1"/>
     </row>
-    <row r="704" spans="1:8" ht="15.75" thickBot="1">
+    <row r="704" spans="1:8" ht="15" thickBot="1">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -9928,7 +9928,7 @@
       <c r="G704" s="1"/>
       <c r="H704" s="1"/>
     </row>
-    <row r="705" spans="1:8" ht="15.75" thickBot="1">
+    <row r="705" spans="1:8" ht="15" thickBot="1">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -9938,7 +9938,7 @@
       <c r="G705" s="1"/>
       <c r="H705" s="1"/>
     </row>
-    <row r="706" spans="1:8" ht="15.75" thickBot="1">
+    <row r="706" spans="1:8" ht="15" thickBot="1">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -9948,7 +9948,7 @@
       <c r="G706" s="1"/>
       <c r="H706" s="1"/>
     </row>
-    <row r="707" spans="1:8" ht="15.75" thickBot="1">
+    <row r="707" spans="1:8" ht="15" thickBot="1">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -9958,7 +9958,7 @@
       <c r="G707" s="1"/>
       <c r="H707" s="1"/>
     </row>
-    <row r="708" spans="1:8" ht="15.75" thickBot="1">
+    <row r="708" spans="1:8" ht="15" thickBot="1">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -9968,7 +9968,7 @@
       <c r="G708" s="1"/>
       <c r="H708" s="1"/>
     </row>
-    <row r="709" spans="1:8" ht="15.75" thickBot="1">
+    <row r="709" spans="1:8" ht="15" thickBot="1">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -9978,7 +9978,7 @@
       <c r="G709" s="1"/>
       <c r="H709" s="1"/>
     </row>
-    <row r="710" spans="1:8" ht="15.75" thickBot="1">
+    <row r="710" spans="1:8" ht="15" thickBot="1">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -9988,7 +9988,7 @@
       <c r="G710" s="1"/>
       <c r="H710" s="1"/>
     </row>
-    <row r="711" spans="1:8" ht="15.75" thickBot="1">
+    <row r="711" spans="1:8" ht="15" thickBot="1">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -9998,7 +9998,7 @@
       <c r="G711" s="1"/>
       <c r="H711" s="1"/>
     </row>
-    <row r="712" spans="1:8" ht="15.75" thickBot="1">
+    <row r="712" spans="1:8" ht="15" thickBot="1">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -10008,7 +10008,7 @@
       <c r="G712" s="1"/>
       <c r="H712" s="1"/>
     </row>
-    <row r="713" spans="1:8" ht="15.75" thickBot="1">
+    <row r="713" spans="1:8" ht="15" thickBot="1">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -10018,7 +10018,7 @@
       <c r="G713" s="1"/>
       <c r="H713" s="1"/>
     </row>
-    <row r="714" spans="1:8" ht="15.75" thickBot="1">
+    <row r="714" spans="1:8" ht="15" thickBot="1">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -10028,7 +10028,7 @@
       <c r="G714" s="1"/>
       <c r="H714" s="1"/>
     </row>
-    <row r="715" spans="1:8" ht="15.75" thickBot="1">
+    <row r="715" spans="1:8" ht="15" thickBot="1">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -10038,7 +10038,7 @@
       <c r="G715" s="1"/>
       <c r="H715" s="1"/>
     </row>
-    <row r="716" spans="1:8" ht="15.75" thickBot="1">
+    <row r="716" spans="1:8" ht="15" thickBot="1">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -10048,7 +10048,7 @@
       <c r="G716" s="1"/>
       <c r="H716" s="1"/>
     </row>
-    <row r="717" spans="1:8" ht="15.75" thickBot="1">
+    <row r="717" spans="1:8" ht="15" thickBot="1">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -10058,7 +10058,7 @@
       <c r="G717" s="1"/>
       <c r="H717" s="1"/>
     </row>
-    <row r="718" spans="1:8" ht="15.75" thickBot="1">
+    <row r="718" spans="1:8" ht="15" thickBot="1">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -10068,7 +10068,7 @@
       <c r="G718" s="1"/>
       <c r="H718" s="1"/>
     </row>
-    <row r="719" spans="1:8" ht="15.75" thickBot="1">
+    <row r="719" spans="1:8" ht="15" thickBot="1">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -10078,7 +10078,7 @@
       <c r="G719" s="1"/>
       <c r="H719" s="1"/>
     </row>
-    <row r="720" spans="1:8" ht="15.75" thickBot="1">
+    <row r="720" spans="1:8" ht="15" thickBot="1">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -10088,7 +10088,7 @@
       <c r="G720" s="1"/>
       <c r="H720" s="1"/>
     </row>
-    <row r="721" spans="1:8" ht="15.75" thickBot="1">
+    <row r="721" spans="1:8" ht="15" thickBot="1">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -10098,7 +10098,7 @@
       <c r="G721" s="1"/>
       <c r="H721" s="1"/>
     </row>
-    <row r="722" spans="1:8" ht="15.75" thickBot="1">
+    <row r="722" spans="1:8" ht="15" thickBot="1">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -10108,7 +10108,7 @@
       <c r="G722" s="1"/>
       <c r="H722" s="1"/>
     </row>
-    <row r="723" spans="1:8" ht="15.75" thickBot="1">
+    <row r="723" spans="1:8" ht="15" thickBot="1">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -10118,7 +10118,7 @@
       <c r="G723" s="1"/>
       <c r="H723" s="1"/>
     </row>
-    <row r="724" spans="1:8" ht="15.75" thickBot="1">
+    <row r="724" spans="1:8" ht="15" thickBot="1">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -10128,7 +10128,7 @@
       <c r="G724" s="1"/>
       <c r="H724" s="1"/>
     </row>
-    <row r="725" spans="1:8" ht="15.75" thickBot="1">
+    <row r="725" spans="1:8" ht="15" thickBot="1">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -10138,7 +10138,7 @@
       <c r="G725" s="1"/>
       <c r="H725" s="1"/>
     </row>
-    <row r="726" spans="1:8" ht="15.75" thickBot="1">
+    <row r="726" spans="1:8" ht="15" thickBot="1">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -10148,7 +10148,7 @@
       <c r="G726" s="1"/>
       <c r="H726" s="1"/>
     </row>
-    <row r="727" spans="1:8" ht="15.75" thickBot="1">
+    <row r="727" spans="1:8" ht="15" thickBot="1">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -10158,7 +10158,7 @@
       <c r="G727" s="1"/>
       <c r="H727" s="1"/>
     </row>
-    <row r="728" spans="1:8" ht="15.75" thickBot="1">
+    <row r="728" spans="1:8" ht="15" thickBot="1">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -10168,7 +10168,7 @@
       <c r="G728" s="1"/>
       <c r="H728" s="1"/>
     </row>
-    <row r="729" spans="1:8" ht="15.75" thickBot="1">
+    <row r="729" spans="1:8" ht="15" thickBot="1">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -10178,7 +10178,7 @@
       <c r="G729" s="1"/>
       <c r="H729" s="1"/>
     </row>
-    <row r="730" spans="1:8" ht="15.75" thickBot="1">
+    <row r="730" spans="1:8" ht="15" thickBot="1">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -10188,7 +10188,7 @@
       <c r="G730" s="1"/>
       <c r="H730" s="1"/>
     </row>
-    <row r="731" spans="1:8" ht="15.75" thickBot="1">
+    <row r="731" spans="1:8" ht="15" thickBot="1">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -10198,7 +10198,7 @@
       <c r="G731" s="1"/>
       <c r="H731" s="1"/>
     </row>
-    <row r="732" spans="1:8" ht="15.75" thickBot="1">
+    <row r="732" spans="1:8" ht="15" thickBot="1">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -10208,7 +10208,7 @@
       <c r="G732" s="1"/>
       <c r="H732" s="1"/>
     </row>
-    <row r="733" spans="1:8" ht="15.75" thickBot="1">
+    <row r="733" spans="1:8" ht="15" thickBot="1">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -10218,7 +10218,7 @@
       <c r="G733" s="1"/>
       <c r="H733" s="1"/>
     </row>
-    <row r="734" spans="1:8" ht="15.75" thickBot="1">
+    <row r="734" spans="1:8" ht="15" thickBot="1">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -10228,7 +10228,7 @@
       <c r="G734" s="1"/>
       <c r="H734" s="1"/>
     </row>
-    <row r="735" spans="1:8" ht="15.75" thickBot="1">
+    <row r="735" spans="1:8" ht="15" thickBot="1">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -10238,7 +10238,7 @@
       <c r="G735" s="1"/>
       <c r="H735" s="1"/>
     </row>
-    <row r="736" spans="1:8" ht="15.75" thickBot="1">
+    <row r="736" spans="1:8" ht="15" thickBot="1">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -10248,7 +10248,7 @@
       <c r="G736" s="1"/>
       <c r="H736" s="1"/>
     </row>
-    <row r="737" spans="1:8" ht="15.75" thickBot="1">
+    <row r="737" spans="1:8" ht="15" thickBot="1">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -10258,7 +10258,7 @@
       <c r="G737" s="1"/>
       <c r="H737" s="1"/>
     </row>
-    <row r="738" spans="1:8" ht="15.75" thickBot="1">
+    <row r="738" spans="1:8" ht="15" thickBot="1">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -10268,7 +10268,7 @@
       <c r="G738" s="1"/>
       <c r="H738" s="1"/>
     </row>
-    <row r="739" spans="1:8" ht="15.75" thickBot="1">
+    <row r="739" spans="1:8" ht="15" thickBot="1">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -10278,7 +10278,7 @@
       <c r="G739" s="1"/>
       <c r="H739" s="1"/>
     </row>
-    <row r="740" spans="1:8" ht="15.75" thickBot="1">
+    <row r="740" spans="1:8" ht="15" thickBot="1">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -10288,7 +10288,7 @@
       <c r="G740" s="1"/>
       <c r="H740" s="1"/>
     </row>
-    <row r="741" spans="1:8" ht="15.75" thickBot="1">
+    <row r="741" spans="1:8" ht="15" thickBot="1">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -10298,7 +10298,7 @@
       <c r="G741" s="1"/>
       <c r="H741" s="1"/>
     </row>
-    <row r="742" spans="1:8" ht="15.75" thickBot="1">
+    <row r="742" spans="1:8" ht="15" thickBot="1">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -10308,7 +10308,7 @@
       <c r="G742" s="1"/>
       <c r="H742" s="1"/>
     </row>
-    <row r="743" spans="1:8" ht="15.75" thickBot="1">
+    <row r="743" spans="1:8" ht="15" thickBot="1">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -10318,7 +10318,7 @@
       <c r="G743" s="1"/>
       <c r="H743" s="1"/>
     </row>
-    <row r="744" spans="1:8" ht="15.75" thickBot="1">
+    <row r="744" spans="1:8" ht="15" thickBot="1">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -10328,7 +10328,7 @@
       <c r="G744" s="1"/>
       <c r="H744" s="1"/>
     </row>
-    <row r="745" spans="1:8" ht="15.75" thickBot="1">
+    <row r="745" spans="1:8" ht="15" thickBot="1">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -10338,7 +10338,7 @@
       <c r="G745" s="1"/>
       <c r="H745" s="1"/>
     </row>
-    <row r="746" spans="1:8" ht="15.75" thickBot="1">
+    <row r="746" spans="1:8" ht="15" thickBot="1">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -10348,7 +10348,7 @@
       <c r="G746" s="1"/>
       <c r="H746" s="1"/>
     </row>
-    <row r="747" spans="1:8" ht="15.75" thickBot="1">
+    <row r="747" spans="1:8" ht="15" thickBot="1">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -10358,7 +10358,7 @@
       <c r="G747" s="1"/>
       <c r="H747" s="1"/>
     </row>
-    <row r="748" spans="1:8" ht="15.75" thickBot="1">
+    <row r="748" spans="1:8" ht="15" thickBot="1">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -10368,7 +10368,7 @@
       <c r="G748" s="1"/>
       <c r="H748" s="1"/>
     </row>
-    <row r="749" spans="1:8" ht="15.75" thickBot="1">
+    <row r="749" spans="1:8" ht="15" thickBot="1">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -10378,7 +10378,7 @@
       <c r="G749" s="1"/>
       <c r="H749" s="1"/>
     </row>
-    <row r="750" spans="1:8" ht="15.75" thickBot="1">
+    <row r="750" spans="1:8" ht="15" thickBot="1">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -10388,7 +10388,7 @@
       <c r="G750" s="1"/>
       <c r="H750" s="1"/>
     </row>
-    <row r="751" spans="1:8" ht="15.75" thickBot="1">
+    <row r="751" spans="1:8" ht="15" thickBot="1">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -10398,7 +10398,7 @@
       <c r="G751" s="1"/>
       <c r="H751" s="1"/>
     </row>
-    <row r="752" spans="1:8" ht="15.75" thickBot="1">
+    <row r="752" spans="1:8" ht="15" thickBot="1">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -10408,7 +10408,7 @@
       <c r="G752" s="1"/>
       <c r="H752" s="1"/>
     </row>
-    <row r="753" spans="1:8" ht="15.75" thickBot="1">
+    <row r="753" spans="1:8" ht="15" thickBot="1">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -10418,7 +10418,7 @@
       <c r="G753" s="1"/>
       <c r="H753" s="1"/>
     </row>
-    <row r="754" spans="1:8" ht="15.75" thickBot="1">
+    <row r="754" spans="1:8" ht="15" thickBot="1">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -10428,7 +10428,7 @@
       <c r="G754" s="1"/>
       <c r="H754" s="1"/>
     </row>
-    <row r="755" spans="1:8" ht="15.75" thickBot="1">
+    <row r="755" spans="1:8" ht="15" thickBot="1">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -10438,7 +10438,7 @@
       <c r="G755" s="1"/>
       <c r="H755" s="1"/>
     </row>
-    <row r="756" spans="1:8" ht="15.75" thickBot="1">
+    <row r="756" spans="1:8" ht="15" thickBot="1">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -10448,7 +10448,7 @@
       <c r="G756" s="1"/>
       <c r="H756" s="1"/>
     </row>
-    <row r="757" spans="1:8" ht="15.75" thickBot="1">
+    <row r="757" spans="1:8" ht="15" thickBot="1">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -10458,7 +10458,7 @@
       <c r="G757" s="1"/>
       <c r="H757" s="1"/>
     </row>
-    <row r="758" spans="1:8" ht="15.75" thickBot="1">
+    <row r="758" spans="1:8" ht="15" thickBot="1">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -10468,7 +10468,7 @@
       <c r="G758" s="1"/>
       <c r="H758" s="1"/>
     </row>
-    <row r="759" spans="1:8" ht="15.75" thickBot="1">
+    <row r="759" spans="1:8" ht="15" thickBot="1">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -10478,7 +10478,7 @@
       <c r="G759" s="1"/>
       <c r="H759" s="1"/>
     </row>
-    <row r="760" spans="1:8" ht="15.75" thickBot="1">
+    <row r="760" spans="1:8" ht="15" thickBot="1">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -10488,7 +10488,7 @@
       <c r="G760" s="1"/>
       <c r="H760" s="1"/>
     </row>
-    <row r="761" spans="1:8" ht="15.75" thickBot="1">
+    <row r="761" spans="1:8" ht="15" thickBot="1">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -10498,7 +10498,7 @@
       <c r="G761" s="1"/>
       <c r="H761" s="1"/>
     </row>
-    <row r="762" spans="1:8" ht="15.75" thickBot="1">
+    <row r="762" spans="1:8" ht="15" thickBot="1">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -10508,7 +10508,7 @@
       <c r="G762" s="1"/>
       <c r="H762" s="1"/>
     </row>
-    <row r="763" spans="1:8" ht="15.75" thickBot="1">
+    <row r="763" spans="1:8" ht="15" thickBot="1">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -10518,7 +10518,7 @@
       <c r="G763" s="1"/>
       <c r="H763" s="1"/>
     </row>
-    <row r="764" spans="1:8" ht="15.75" thickBot="1">
+    <row r="764" spans="1:8" ht="15" thickBot="1">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -10528,7 +10528,7 @@
       <c r="G764" s="1"/>
       <c r="H764" s="1"/>
     </row>
-    <row r="765" spans="1:8" ht="15.75" thickBot="1">
+    <row r="765" spans="1:8" ht="15" thickBot="1">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -10538,7 +10538,7 @@
       <c r="G765" s="1"/>
       <c r="H765" s="1"/>
     </row>
-    <row r="766" spans="1:8" ht="15.75" thickBot="1">
+    <row r="766" spans="1:8" ht="15" thickBot="1">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -10548,7 +10548,7 @@
       <c r="G766" s="1"/>
       <c r="H766" s="1"/>
     </row>
-    <row r="767" spans="1:8" ht="15.75" thickBot="1">
+    <row r="767" spans="1:8" ht="15" thickBot="1">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -10558,7 +10558,7 @@
       <c r="G767" s="1"/>
       <c r="H767" s="1"/>
     </row>
-    <row r="768" spans="1:8" ht="15.75" thickBot="1">
+    <row r="768" spans="1:8" ht="15" thickBot="1">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -10568,7 +10568,7 @@
       <c r="G768" s="1"/>
       <c r="H768" s="1"/>
     </row>
-    <row r="769" spans="1:8" ht="15.75" thickBot="1">
+    <row r="769" spans="1:8" ht="15" thickBot="1">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -10578,7 +10578,7 @@
       <c r="G769" s="1"/>
       <c r="H769" s="1"/>
     </row>
-    <row r="770" spans="1:8" ht="15.75" thickBot="1">
+    <row r="770" spans="1:8" ht="15" thickBot="1">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -10588,7 +10588,7 @@
       <c r="G770" s="1"/>
       <c r="H770" s="1"/>
     </row>
-    <row r="771" spans="1:8" ht="15.75" thickBot="1">
+    <row r="771" spans="1:8" ht="15" thickBot="1">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -10598,7 +10598,7 @@
       <c r="G771" s="1"/>
       <c r="H771" s="1"/>
     </row>
-    <row r="772" spans="1:8" ht="15.75" thickBot="1">
+    <row r="772" spans="1:8" ht="15" thickBot="1">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -10608,7 +10608,7 @@
       <c r="G772" s="1"/>
       <c r="H772" s="1"/>
     </row>
-    <row r="773" spans="1:8" ht="15.75" thickBot="1">
+    <row r="773" spans="1:8" ht="15" thickBot="1">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -10618,7 +10618,7 @@
       <c r="G773" s="1"/>
       <c r="H773" s="1"/>
     </row>
-    <row r="774" spans="1:8" ht="15.75" thickBot="1">
+    <row r="774" spans="1:8" ht="15" thickBot="1">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -10628,7 +10628,7 @@
       <c r="G774" s="1"/>
       <c r="H774" s="1"/>
     </row>
-    <row r="775" spans="1:8" ht="15.75" thickBot="1">
+    <row r="775" spans="1:8" ht="15" thickBot="1">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -10638,7 +10638,7 @@
       <c r="G775" s="1"/>
       <c r="H775" s="1"/>
     </row>
-    <row r="776" spans="1:8" ht="15.75" thickBot="1">
+    <row r="776" spans="1:8" ht="15" thickBot="1">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -10648,7 +10648,7 @@
       <c r="G776" s="1"/>
       <c r="H776" s="1"/>
     </row>
-    <row r="777" spans="1:8" ht="15.75" thickBot="1">
+    <row r="777" spans="1:8" ht="15" thickBot="1">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -10658,7 +10658,7 @@
       <c r="G777" s="1"/>
       <c r="H777" s="1"/>
     </row>
-    <row r="778" spans="1:8" ht="15.75" thickBot="1">
+    <row r="778" spans="1:8" ht="15" thickBot="1">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -10668,7 +10668,7 @@
       <c r="G778" s="1"/>
       <c r="H778" s="1"/>
     </row>
-    <row r="779" spans="1:8" ht="15.75" thickBot="1">
+    <row r="779" spans="1:8" ht="15" thickBot="1">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -10678,7 +10678,7 @@
       <c r="G779" s="1"/>
       <c r="H779" s="1"/>
     </row>
-    <row r="780" spans="1:8" ht="15.75" thickBot="1">
+    <row r="780" spans="1:8" ht="15" thickBot="1">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -10688,7 +10688,7 @@
       <c r="G780" s="1"/>
       <c r="H780" s="1"/>
     </row>
-    <row r="781" spans="1:8" ht="15.75" thickBot="1">
+    <row r="781" spans="1:8" ht="15" thickBot="1">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -10698,7 +10698,7 @@
       <c r="G781" s="1"/>
       <c r="H781" s="1"/>
     </row>
-    <row r="782" spans="1:8" ht="15.75" thickBot="1">
+    <row r="782" spans="1:8" ht="15" thickBot="1">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -10708,7 +10708,7 @@
       <c r="G782" s="1"/>
       <c r="H782" s="1"/>
     </row>
-    <row r="783" spans="1:8" ht="15.75" thickBot="1">
+    <row r="783" spans="1:8" ht="15" thickBot="1">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -10718,7 +10718,7 @@
       <c r="G783" s="1"/>
       <c r="H783" s="1"/>
     </row>
-    <row r="784" spans="1:8" ht="15.75" thickBot="1">
+    <row r="784" spans="1:8" ht="15" thickBot="1">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -10728,7 +10728,7 @@
       <c r="G784" s="1"/>
       <c r="H784" s="1"/>
     </row>
-    <row r="785" spans="1:8" ht="15.75" thickBot="1">
+    <row r="785" spans="1:8" ht="15" thickBot="1">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -10738,7 +10738,7 @@
       <c r="G785" s="1"/>
       <c r="H785" s="1"/>
     </row>
-    <row r="786" spans="1:8" ht="15.75" thickBot="1">
+    <row r="786" spans="1:8" ht="15" thickBot="1">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -10748,7 +10748,7 @@
       <c r="G786" s="1"/>
       <c r="H786" s="1"/>
     </row>
-    <row r="787" spans="1:8" ht="15.75" thickBot="1">
+    <row r="787" spans="1:8" ht="15" thickBot="1">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -10758,7 +10758,7 @@
       <c r="G787" s="1"/>
       <c r="H787" s="1"/>
     </row>
-    <row r="788" spans="1:8" ht="15.75" thickBot="1">
+    <row r="788" spans="1:8" ht="15" thickBot="1">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -10768,7 +10768,7 @@
       <c r="G788" s="1"/>
       <c r="H788" s="1"/>
     </row>
-    <row r="789" spans="1:8" ht="15.75" thickBot="1">
+    <row r="789" spans="1:8" ht="15" thickBot="1">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -10778,7 +10778,7 @@
       <c r="G789" s="1"/>
       <c r="H789" s="1"/>
     </row>
-    <row r="790" spans="1:8" ht="15.75" thickBot="1">
+    <row r="790" spans="1:8" ht="15" thickBot="1">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -10788,7 +10788,7 @@
       <c r="G790" s="1"/>
       <c r="H790" s="1"/>
     </row>
-    <row r="791" spans="1:8" ht="15.75" thickBot="1">
+    <row r="791" spans="1:8" ht="15" thickBot="1">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -10798,7 +10798,7 @@
       <c r="G791" s="1"/>
       <c r="H791" s="1"/>
     </row>
-    <row r="792" spans="1:8" ht="15.75" thickBot="1">
+    <row r="792" spans="1:8" ht="15" thickBot="1">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -10808,7 +10808,7 @@
       <c r="G792" s="1"/>
       <c r="H792" s="1"/>
     </row>
-    <row r="793" spans="1:8" ht="15.75" thickBot="1">
+    <row r="793" spans="1:8" ht="15" thickBot="1">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -10818,7 +10818,7 @@
       <c r="G793" s="1"/>
       <c r="H793" s="1"/>
     </row>
-    <row r="794" spans="1:8" ht="15.75" thickBot="1">
+    <row r="794" spans="1:8" ht="15" thickBot="1">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -10828,7 +10828,7 @@
       <c r="G794" s="1"/>
       <c r="H794" s="1"/>
     </row>
-    <row r="795" spans="1:8" ht="15.75" thickBot="1">
+    <row r="795" spans="1:8" ht="15" thickBot="1">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -10838,7 +10838,7 @@
       <c r="G795" s="1"/>
       <c r="H795" s="1"/>
     </row>
-    <row r="796" spans="1:8" ht="15.75" thickBot="1">
+    <row r="796" spans="1:8" ht="15" thickBot="1">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -10848,7 +10848,7 @@
       <c r="G796" s="1"/>
       <c r="H796" s="1"/>
     </row>
-    <row r="797" spans="1:8" ht="15.75" thickBot="1">
+    <row r="797" spans="1:8" ht="15" thickBot="1">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -10858,7 +10858,7 @@
       <c r="G797" s="1"/>
       <c r="H797" s="1"/>
     </row>
-    <row r="798" spans="1:8" ht="15.75" thickBot="1">
+    <row r="798" spans="1:8" ht="15" thickBot="1">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -10868,7 +10868,7 @@
       <c r="G798" s="1"/>
       <c r="H798" s="1"/>
     </row>
-    <row r="799" spans="1:8" ht="15.75" thickBot="1">
+    <row r="799" spans="1:8" ht="15" thickBot="1">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -10878,7 +10878,7 @@
       <c r="G799" s="1"/>
       <c r="H799" s="1"/>
     </row>
-    <row r="800" spans="1:8" ht="15.75" thickBot="1">
+    <row r="800" spans="1:8" ht="15" thickBot="1">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -10888,7 +10888,7 @@
       <c r="G800" s="1"/>
       <c r="H800" s="1"/>
     </row>
-    <row r="801" spans="1:8" ht="15.75" thickBot="1">
+    <row r="801" spans="1:8" ht="15" thickBot="1">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -10898,7 +10898,7 @@
       <c r="G801" s="1"/>
       <c r="H801" s="1"/>
     </row>
-    <row r="802" spans="1:8" ht="15.75" thickBot="1">
+    <row r="802" spans="1:8" ht="15" thickBot="1">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -10908,7 +10908,7 @@
       <c r="G802" s="1"/>
       <c r="H802" s="1"/>
     </row>
-    <row r="803" spans="1:8" ht="15.75" thickBot="1">
+    <row r="803" spans="1:8" ht="15" thickBot="1">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -10918,7 +10918,7 @@
       <c r="G803" s="1"/>
       <c r="H803" s="1"/>
     </row>
-    <row r="804" spans="1:8" ht="15.75" thickBot="1">
+    <row r="804" spans="1:8" ht="15" thickBot="1">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -10928,7 +10928,7 @@
       <c r="G804" s="1"/>
       <c r="H804" s="1"/>
     </row>
-    <row r="805" spans="1:8" ht="15.75" thickBot="1">
+    <row r="805" spans="1:8" ht="15" thickBot="1">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -10938,7 +10938,7 @@
       <c r="G805" s="1"/>
       <c r="H805" s="1"/>
     </row>
-    <row r="806" spans="1:8" ht="15.75" thickBot="1">
+    <row r="806" spans="1:8" ht="15" thickBot="1">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -10948,7 +10948,7 @@
       <c r="G806" s="1"/>
       <c r="H806" s="1"/>
     </row>
-    <row r="807" spans="1:8" ht="15.75" thickBot="1">
+    <row r="807" spans="1:8" ht="15" thickBot="1">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -10958,7 +10958,7 @@
       <c r="G807" s="1"/>
       <c r="H807" s="1"/>
     </row>
-    <row r="808" spans="1:8" ht="15.75" thickBot="1">
+    <row r="808" spans="1:8" ht="15" thickBot="1">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -10968,7 +10968,7 @@
       <c r="G808" s="1"/>
       <c r="H808" s="1"/>
     </row>
-    <row r="809" spans="1:8" ht="15.75" thickBot="1">
+    <row r="809" spans="1:8" ht="15" thickBot="1">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -10978,7 +10978,7 @@
       <c r="G809" s="1"/>
       <c r="H809" s="1"/>
     </row>
-    <row r="810" spans="1:8" ht="15.75" thickBot="1">
+    <row r="810" spans="1:8" ht="15" thickBot="1">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -10988,7 +10988,7 @@
       <c r="G810" s="1"/>
       <c r="H810" s="1"/>
     </row>
-    <row r="811" spans="1:8" ht="15.75" thickBot="1">
+    <row r="811" spans="1:8" ht="15" thickBot="1">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -10998,7 +10998,7 @@
       <c r="G811" s="1"/>
       <c r="H811" s="1"/>
     </row>
-    <row r="812" spans="1:8" ht="15.75" thickBot="1">
+    <row r="812" spans="1:8" ht="15" thickBot="1">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -11008,7 +11008,7 @@
       <c r="G812" s="1"/>
       <c r="H812" s="1"/>
     </row>
-    <row r="813" spans="1:8" ht="15.75" thickBot="1">
+    <row r="813" spans="1:8" ht="15" thickBot="1">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -11018,7 +11018,7 @@
       <c r="G813" s="1"/>
       <c r="H813" s="1"/>
     </row>
-    <row r="814" spans="1:8" ht="15.75" thickBot="1">
+    <row r="814" spans="1:8" ht="15" thickBot="1">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -11028,7 +11028,7 @@
       <c r="G814" s="1"/>
       <c r="H814" s="1"/>
     </row>
-    <row r="815" spans="1:8" ht="15.75" thickBot="1">
+    <row r="815" spans="1:8" ht="15" thickBot="1">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -11038,7 +11038,7 @@
       <c r="G815" s="1"/>
       <c r="H815" s="1"/>
     </row>
-    <row r="816" spans="1:8" ht="15.75" thickBot="1">
+    <row r="816" spans="1:8" ht="15" thickBot="1">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -11048,7 +11048,7 @@
       <c r="G816" s="1"/>
       <c r="H816" s="1"/>
     </row>
-    <row r="817" spans="1:8" ht="15.75" thickBot="1">
+    <row r="817" spans="1:8" ht="15" thickBot="1">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -11058,7 +11058,7 @@
       <c r="G817" s="1"/>
       <c r="H817" s="1"/>
     </row>
-    <row r="818" spans="1:8" ht="15.75" thickBot="1">
+    <row r="818" spans="1:8" ht="15" thickBot="1">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -11068,7 +11068,7 @@
       <c r="G818" s="1"/>
       <c r="H818" s="1"/>
     </row>
-    <row r="819" spans="1:8" ht="15.75" thickBot="1">
+    <row r="819" spans="1:8" ht="15" thickBot="1">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -11078,7 +11078,7 @@
       <c r="G819" s="1"/>
       <c r="H819" s="1"/>
     </row>
-    <row r="820" spans="1:8" ht="15.75" thickBot="1">
+    <row r="820" spans="1:8" ht="15" thickBot="1">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -11088,7 +11088,7 @@
       <c r="G820" s="1"/>
       <c r="H820" s="1"/>
     </row>
-    <row r="821" spans="1:8" ht="15.75" thickBot="1">
+    <row r="821" spans="1:8" ht="15" thickBot="1">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -11098,7 +11098,7 @@
       <c r="G821" s="1"/>
       <c r="H821" s="1"/>
     </row>
-    <row r="822" spans="1:8" ht="15.75" thickBot="1">
+    <row r="822" spans="1:8" ht="15" thickBot="1">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -11108,7 +11108,7 @@
       <c r="G822" s="1"/>
       <c r="H822" s="1"/>
     </row>
-    <row r="823" spans="1:8" ht="15.75" thickBot="1">
+    <row r="823" spans="1:8" ht="15" thickBot="1">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -11118,7 +11118,7 @@
       <c r="G823" s="1"/>
       <c r="H823" s="1"/>
     </row>
-    <row r="824" spans="1:8" ht="15.75" thickBot="1">
+    <row r="824" spans="1:8" ht="15" thickBot="1">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -11128,7 +11128,7 @@
       <c r="G824" s="1"/>
       <c r="H824" s="1"/>
     </row>
-    <row r="825" spans="1:8" ht="15.75" thickBot="1">
+    <row r="825" spans="1:8" ht="15" thickBot="1">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -11138,7 +11138,7 @@
       <c r="G825" s="1"/>
       <c r="H825" s="1"/>
     </row>
-    <row r="826" spans="1:8" ht="15.75" thickBot="1">
+    <row r="826" spans="1:8" ht="15" thickBot="1">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -11148,7 +11148,7 @@
       <c r="G826" s="1"/>
       <c r="H826" s="1"/>
     </row>
-    <row r="827" spans="1:8" ht="15.75" thickBot="1">
+    <row r="827" spans="1:8" ht="15" thickBot="1">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -11158,7 +11158,7 @@
       <c r="G827" s="1"/>
       <c r="H827" s="1"/>
     </row>
-    <row r="828" spans="1:8" ht="15.75" thickBot="1">
+    <row r="828" spans="1:8" ht="15" thickBot="1">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -11168,7 +11168,7 @@
       <c r="G828" s="1"/>
       <c r="H828" s="1"/>
     </row>
-    <row r="829" spans="1:8" ht="15.75" thickBot="1">
+    <row r="829" spans="1:8" ht="15" thickBot="1">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -11178,7 +11178,7 @@
       <c r="G829" s="1"/>
       <c r="H829" s="1"/>
     </row>
-    <row r="830" spans="1:8" ht="15.75" thickBot="1">
+    <row r="830" spans="1:8" ht="15" thickBot="1">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -11188,7 +11188,7 @@
       <c r="G830" s="1"/>
       <c r="H830" s="1"/>
     </row>
-    <row r="831" spans="1:8" ht="15.75" thickBot="1">
+    <row r="831" spans="1:8" ht="15" thickBot="1">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -11198,7 +11198,7 @@
       <c r="G831" s="1"/>
       <c r="H831" s="1"/>
     </row>
-    <row r="832" spans="1:8" ht="15.75" thickBot="1">
+    <row r="832" spans="1:8" ht="15" thickBot="1">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -11208,7 +11208,7 @@
       <c r="G832" s="1"/>
       <c r="H832" s="1"/>
     </row>
-    <row r="833" spans="1:8" ht="15.75" thickBot="1">
+    <row r="833" spans="1:8" ht="15" thickBot="1">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -11218,7 +11218,7 @@
       <c r="G833" s="1"/>
       <c r="H833" s="1"/>
     </row>
-    <row r="834" spans="1:8" ht="15.75" thickBot="1">
+    <row r="834" spans="1:8" ht="15" thickBot="1">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -11228,7 +11228,7 @@
       <c r="G834" s="1"/>
       <c r="H834" s="1"/>
     </row>
-    <row r="835" spans="1:8" ht="15.75" thickBot="1">
+    <row r="835" spans="1:8" ht="15" thickBot="1">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -11238,7 +11238,7 @@
       <c r="G835" s="1"/>
       <c r="H835" s="1"/>
     </row>
-    <row r="836" spans="1:8" ht="15.75" thickBot="1">
+    <row r="836" spans="1:8" ht="15" thickBot="1">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -11248,7 +11248,7 @@
       <c r="G836" s="1"/>
       <c r="H836" s="1"/>
     </row>
-    <row r="837" spans="1:8" ht="15.75" thickBot="1">
+    <row r="837" spans="1:8" ht="15" thickBot="1">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -11258,7 +11258,7 @@
       <c r="G837" s="1"/>
       <c r="H837" s="1"/>
     </row>
-    <row r="838" spans="1:8" ht="15.75" thickBot="1">
+    <row r="838" spans="1:8" ht="15" thickBot="1">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -11268,7 +11268,7 @@
       <c r="G838" s="1"/>
       <c r="H838" s="1"/>
     </row>
-    <row r="839" spans="1:8" ht="15.75" thickBot="1">
+    <row r="839" spans="1:8" ht="15" thickBot="1">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -11278,7 +11278,7 @@
       <c r="G839" s="1"/>
       <c r="H839" s="1"/>
     </row>
-    <row r="840" spans="1:8" ht="15.75" thickBot="1">
+    <row r="840" spans="1:8" ht="15" thickBot="1">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -11288,7 +11288,7 @@
       <c r="G840" s="1"/>
       <c r="H840" s="1"/>
     </row>
-    <row r="841" spans="1:8" ht="15.75" thickBot="1">
+    <row r="841" spans="1:8" ht="15" thickBot="1">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -11298,7 +11298,7 @@
       <c r="G841" s="1"/>
       <c r="H841" s="1"/>
     </row>
-    <row r="842" spans="1:8" ht="15.75" thickBot="1">
+    <row r="842" spans="1:8" ht="15" thickBot="1">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -11308,7 +11308,7 @@
       <c r="G842" s="1"/>
       <c r="H842" s="1"/>
     </row>
-    <row r="843" spans="1:8" ht="15.75" thickBot="1">
+    <row r="843" spans="1:8" ht="15" thickBot="1">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -11318,7 +11318,7 @@
       <c r="G843" s="1"/>
       <c r="H843" s="1"/>
     </row>
-    <row r="844" spans="1:8" ht="15.75" thickBot="1">
+    <row r="844" spans="1:8" ht="15" thickBot="1">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -11328,7 +11328,7 @@
       <c r="G844" s="1"/>
       <c r="H844" s="1"/>
     </row>
-    <row r="845" spans="1:8" ht="15.75" thickBot="1">
+    <row r="845" spans="1:8" ht="15" thickBot="1">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -11338,7 +11338,7 @@
       <c r="G845" s="1"/>
       <c r="H845" s="1"/>
     </row>
-    <row r="846" spans="1:8" ht="15.75" thickBot="1">
+    <row r="846" spans="1:8" ht="15" thickBot="1">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -11348,7 +11348,7 @@
       <c r="G846" s="1"/>
       <c r="H846" s="1"/>
     </row>
-    <row r="847" spans="1:8" ht="15.75" thickBot="1">
+    <row r="847" spans="1:8" ht="15" thickBot="1">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -11358,7 +11358,7 @@
       <c r="G847" s="1"/>
       <c r="H847" s="1"/>
     </row>
-    <row r="848" spans="1:8" ht="15.75" thickBot="1">
+    <row r="848" spans="1:8" ht="15" thickBot="1">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -11368,7 +11368,7 @@
       <c r="G848" s="1"/>
       <c r="H848" s="1"/>
     </row>
-    <row r="849" spans="1:8" ht="15.75" thickBot="1">
+    <row r="849" spans="1:8" ht="15" thickBot="1">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -11378,7 +11378,7 @@
       <c r="G849" s="1"/>
       <c r="H849" s="1"/>
     </row>
-    <row r="850" spans="1:8" ht="15.75" thickBot="1">
+    <row r="850" spans="1:8" ht="15" thickBot="1">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -11388,7 +11388,7 @@
       <c r="G850" s="1"/>
       <c r="H850" s="1"/>
     </row>
-    <row r="851" spans="1:8" ht="15.75" thickBot="1">
+    <row r="851" spans="1:8" ht="15" thickBot="1">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -11398,7 +11398,7 @@
       <c r="G851" s="1"/>
       <c r="H851" s="1"/>
     </row>
-    <row r="852" spans="1:8" ht="15.75" thickBot="1">
+    <row r="852" spans="1:8" ht="15" thickBot="1">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -11408,7 +11408,7 @@
       <c r="G852" s="1"/>
       <c r="H852" s="1"/>
     </row>
-    <row r="853" spans="1:8" ht="15.75" thickBot="1">
+    <row r="853" spans="1:8" ht="15" thickBot="1">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -11418,7 +11418,7 @@
       <c r="G853" s="1"/>
       <c r="H853" s="1"/>
     </row>
-    <row r="854" spans="1:8" ht="15.75" thickBot="1">
+    <row r="854" spans="1:8" ht="15" thickBot="1">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -11428,7 +11428,7 @@
       <c r="G854" s="1"/>
       <c r="H854" s="1"/>
     </row>
-    <row r="855" spans="1:8" ht="15.75" thickBot="1">
+    <row r="855" spans="1:8" ht="15" thickBot="1">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -11438,7 +11438,7 @@
       <c r="G855" s="1"/>
       <c r="H855" s="1"/>
     </row>
-    <row r="856" spans="1:8" ht="15.75" thickBot="1">
+    <row r="856" spans="1:8" ht="15" thickBot="1">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -11448,7 +11448,7 @@
       <c r="G856" s="1"/>
       <c r="H856" s="1"/>
     </row>
-    <row r="857" spans="1:8" ht="15.75" thickBot="1">
+    <row r="857" spans="1:8" ht="15" thickBot="1">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -11458,7 +11458,7 @@
       <c r="G857" s="1"/>
       <c r="H857" s="1"/>
     </row>
-    <row r="858" spans="1:8" ht="15.75" thickBot="1">
+    <row r="858" spans="1:8" ht="15" thickBot="1">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -11468,7 +11468,7 @@
       <c r="G858" s="1"/>
       <c r="H858" s="1"/>
     </row>
-    <row r="859" spans="1:8" ht="15.75" thickBot="1">
+    <row r="859" spans="1:8" ht="15" thickBot="1">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -11478,7 +11478,7 @@
       <c r="G859" s="1"/>
       <c r="H859" s="1"/>
     </row>
-    <row r="860" spans="1:8" ht="15.75" thickBot="1">
+    <row r="860" spans="1:8" ht="15" thickBot="1">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -11488,7 +11488,7 @@
       <c r="G860" s="1"/>
       <c r="H860" s="1"/>
     </row>
-    <row r="861" spans="1:8" ht="15.75" thickBot="1">
+    <row r="861" spans="1:8" ht="15" thickBot="1">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -11498,7 +11498,7 @@
       <c r="G861" s="1"/>
       <c r="H861" s="1"/>
     </row>
-    <row r="862" spans="1:8" ht="15.75" thickBot="1">
+    <row r="862" spans="1:8" ht="15" thickBot="1">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -11508,7 +11508,7 @@
       <c r="G862" s="1"/>
       <c r="H862" s="1"/>
     </row>
-    <row r="863" spans="1:8" ht="15.75" thickBot="1">
+    <row r="863" spans="1:8" ht="15" thickBot="1">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -11518,7 +11518,7 @@
       <c r="G863" s="1"/>
       <c r="H863" s="1"/>
     </row>
-    <row r="864" spans="1:8" ht="15.75" thickBot="1">
+    <row r="864" spans="1:8" ht="15" thickBot="1">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -11528,7 +11528,7 @@
       <c r="G864" s="1"/>
       <c r="H864" s="1"/>
     </row>
-    <row r="865" spans="1:8" ht="15.75" thickBot="1">
+    <row r="865" spans="1:8" ht="15" thickBot="1">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -11538,7 +11538,7 @@
       <c r="G865" s="1"/>
       <c r="H865" s="1"/>
     </row>
-    <row r="866" spans="1:8" ht="15.75" thickBot="1">
+    <row r="866" spans="1:8" ht="15" thickBot="1">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -11548,7 +11548,7 @@
       <c r="G866" s="1"/>
       <c r="H866" s="1"/>
     </row>
-    <row r="867" spans="1:8" ht="15.75" thickBot="1">
+    <row r="867" spans="1:8" ht="15" thickBot="1">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -11558,7 +11558,7 @@
       <c r="G867" s="1"/>
       <c r="H867" s="1"/>
     </row>
-    <row r="868" spans="1:8" ht="15.75" thickBot="1">
+    <row r="868" spans="1:8" ht="15" thickBot="1">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -11568,7 +11568,7 @@
       <c r="G868" s="1"/>
       <c r="H868" s="1"/>
     </row>
-    <row r="869" spans="1:8" ht="15.75" thickBot="1">
+    <row r="869" spans="1:8" ht="15" thickBot="1">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -11578,7 +11578,7 @@
       <c r="G869" s="1"/>
       <c r="H869" s="1"/>
     </row>
-    <row r="870" spans="1:8" ht="15.75" thickBot="1">
+    <row r="870" spans="1:8" ht="15" thickBot="1">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -11588,7 +11588,7 @@
       <c r="G870" s="1"/>
       <c r="H870" s="1"/>
     </row>
-    <row r="871" spans="1:8" ht="15.75" thickBot="1">
+    <row r="871" spans="1:8" ht="15" thickBot="1">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -11598,7 +11598,7 @@
       <c r="G871" s="1"/>
       <c r="H871" s="1"/>
     </row>
-    <row r="872" spans="1:8" ht="15.75" thickBot="1">
+    <row r="872" spans="1:8" ht="15" thickBot="1">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -11608,7 +11608,7 @@
       <c r="G872" s="1"/>
       <c r="H872" s="1"/>
     </row>
-    <row r="873" spans="1:8" ht="15.75" thickBot="1">
+    <row r="873" spans="1:8" ht="15" thickBot="1">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -11618,7 +11618,7 @@
       <c r="G873" s="1"/>
       <c r="H873" s="1"/>
     </row>
-    <row r="874" spans="1:8" ht="15.75" thickBot="1">
+    <row r="874" spans="1:8" ht="15" thickBot="1">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -11628,7 +11628,7 @@
       <c r="G874" s="1"/>
       <c r="H874" s="1"/>
     </row>
-    <row r="875" spans="1:8" ht="15.75" thickBot="1">
+    <row r="875" spans="1:8" ht="15" thickBot="1">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -11638,7 +11638,7 @@
       <c r="G875" s="1"/>
       <c r="H875" s="1"/>
     </row>
-    <row r="876" spans="1:8" ht="15.75" thickBot="1">
+    <row r="876" spans="1:8" ht="15" thickBot="1">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -11648,7 +11648,7 @@
       <c r="G876" s="1"/>
       <c r="H876" s="1"/>
     </row>
-    <row r="877" spans="1:8" ht="15.75" thickBot="1">
+    <row r="877" spans="1:8" ht="15" thickBot="1">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -11658,7 +11658,7 @@
       <c r="G877" s="1"/>
       <c r="H877" s="1"/>
     </row>
-    <row r="878" spans="1:8" ht="15.75" thickBot="1">
+    <row r="878" spans="1:8" ht="15" thickBot="1">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -11668,7 +11668,7 @@
       <c r="G878" s="1"/>
       <c r="H878" s="1"/>
     </row>
-    <row r="879" spans="1:8" ht="15.75" thickBot="1">
+    <row r="879" spans="1:8" ht="15" thickBot="1">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -11678,7 +11678,7 @@
       <c r="G879" s="1"/>
       <c r="H879" s="1"/>
     </row>
-    <row r="880" spans="1:8" ht="15.75" thickBot="1">
+    <row r="880" spans="1:8" ht="15" thickBot="1">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -11688,7 +11688,7 @@
       <c r="G880" s="1"/>
       <c r="H880" s="1"/>
     </row>
-    <row r="881" spans="1:8" ht="15.75" thickBot="1">
+    <row r="881" spans="1:8" ht="15" thickBot="1">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -11698,7 +11698,7 @@
       <c r="G881" s="1"/>
       <c r="H881" s="1"/>
     </row>
-    <row r="882" spans="1:8" ht="15.75" thickBot="1">
+    <row r="882" spans="1:8" ht="15" thickBot="1">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -11708,7 +11708,7 @@
       <c r="G882" s="1"/>
       <c r="H882" s="1"/>
     </row>
-    <row r="883" spans="1:8" ht="15.75" thickBot="1">
+    <row r="883" spans="1:8" ht="15" thickBot="1">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -11718,7 +11718,7 @@
       <c r="G883" s="1"/>
       <c r="H883" s="1"/>
     </row>
-    <row r="884" spans="1:8" ht="15.75" thickBot="1">
+    <row r="884" spans="1:8" ht="15" thickBot="1">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -11728,7 +11728,7 @@
       <c r="G884" s="1"/>
       <c r="H884" s="1"/>
     </row>
-    <row r="885" spans="1:8" ht="15.75" thickBot="1">
+    <row r="885" spans="1:8" ht="15" thickBot="1">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -11738,7 +11738,7 @@
       <c r="G885" s="1"/>
       <c r="H885" s="1"/>
     </row>
-    <row r="886" spans="1:8" ht="15.75" thickBot="1">
+    <row r="886" spans="1:8" ht="15" thickBot="1">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -11748,7 +11748,7 @@
       <c r="G886" s="1"/>
       <c r="H886" s="1"/>
     </row>
-    <row r="887" spans="1:8" ht="15.75" thickBot="1">
+    <row r="887" spans="1:8" ht="15" thickBot="1">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -11758,7 +11758,7 @@
       <c r="G887" s="1"/>
       <c r="H887" s="1"/>
     </row>
-    <row r="888" spans="1:8" ht="15.75" thickBot="1">
+    <row r="888" spans="1:8" ht="15" thickBot="1">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -11768,7 +11768,7 @@
       <c r="G888" s="1"/>
       <c r="H888" s="1"/>
     </row>
-    <row r="889" spans="1:8" ht="15.75" thickBot="1">
+    <row r="889" spans="1:8" ht="15" thickBot="1">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -11778,7 +11778,7 @@
       <c r="G889" s="1"/>
       <c r="H889" s="1"/>
     </row>
-    <row r="890" spans="1:8" ht="15.75" thickBot="1">
+    <row r="890" spans="1:8" ht="15" thickBot="1">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -11788,7 +11788,7 @@
       <c r="G890" s="1"/>
       <c r="H890" s="1"/>
     </row>
-    <row r="891" spans="1:8" ht="15.75" thickBot="1">
+    <row r="891" spans="1:8" ht="15" thickBot="1">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -11798,7 +11798,7 @@
       <c r="G891" s="1"/>
       <c r="H891" s="1"/>
     </row>
-    <row r="892" spans="1:8" ht="15.75" thickBot="1">
+    <row r="892" spans="1:8" ht="15" thickBot="1">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -11808,7 +11808,7 @@
       <c r="G892" s="1"/>
       <c r="H892" s="1"/>
     </row>
-    <row r="893" spans="1:8" ht="15.75" thickBot="1">
+    <row r="893" spans="1:8" ht="15" thickBot="1">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -11818,7 +11818,7 @@
       <c r="G893" s="1"/>
       <c r="H893" s="1"/>
     </row>
-    <row r="894" spans="1:8" ht="15.75" thickBot="1">
+    <row r="894" spans="1:8" ht="15" thickBot="1">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -11828,7 +11828,7 @@
       <c r="G894" s="1"/>
       <c r="H894" s="1"/>
     </row>
-    <row r="895" spans="1:8" ht="15.75" thickBot="1">
+    <row r="895" spans="1:8" ht="15" thickBot="1">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -11838,7 +11838,7 @@
       <c r="G895" s="1"/>
       <c r="H895" s="1"/>
     </row>
-    <row r="896" spans="1:8" ht="15.75" thickBot="1">
+    <row r="896" spans="1:8" ht="15" thickBot="1">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -11848,7 +11848,7 @@
       <c r="G896" s="1"/>
       <c r="H896" s="1"/>
     </row>
-    <row r="897" spans="1:8" ht="15.75" thickBot="1">
+    <row r="897" spans="1:8" ht="15" thickBot="1">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -11858,7 +11858,7 @@
       <c r="G897" s="1"/>
       <c r="H897" s="1"/>
     </row>
-    <row r="898" spans="1:8" ht="15.75" thickBot="1">
+    <row r="898" spans="1:8" ht="15" thickBot="1">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -11868,7 +11868,7 @@
       <c r="G898" s="1"/>
       <c r="H898" s="1"/>
     </row>
-    <row r="899" spans="1:8" ht="15.75" thickBot="1">
+    <row r="899" spans="1:8" ht="15" thickBot="1">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -11878,7 +11878,7 @@
       <c r="G899" s="1"/>
       <c r="H899" s="1"/>
     </row>
-    <row r="900" spans="1:8" ht="15.75" thickBot="1">
+    <row r="900" spans="1:8" ht="15" thickBot="1">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -11888,7 +11888,7 @@
       <c r="G900" s="1"/>
       <c r="H900" s="1"/>
     </row>
-    <row r="901" spans="1:8" ht="15.75" thickBot="1">
+    <row r="901" spans="1:8" ht="15" thickBot="1">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -11898,7 +11898,7 @@
       <c r="G901" s="1"/>
       <c r="H901" s="1"/>
     </row>
-    <row r="902" spans="1:8" ht="15.75" thickBot="1">
+    <row r="902" spans="1:8" ht="15" thickBot="1">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -11908,7 +11908,7 @@
       <c r="G902" s="1"/>
       <c r="H902" s="1"/>
     </row>
-    <row r="903" spans="1:8" ht="15.75" thickBot="1">
+    <row r="903" spans="1:8" ht="15" thickBot="1">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -11918,7 +11918,7 @@
       <c r="G903" s="1"/>
       <c r="H903" s="1"/>
     </row>
-    <row r="904" spans="1:8" ht="15.75" thickBot="1">
+    <row r="904" spans="1:8" ht="15" thickBot="1">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -11928,7 +11928,7 @@
       <c r="G904" s="1"/>
       <c r="H904" s="1"/>
     </row>
-    <row r="905" spans="1:8" ht="15.75" thickBot="1">
+    <row r="905" spans="1:8" ht="15" thickBot="1">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -11938,7 +11938,7 @@
       <c r="G905" s="1"/>
       <c r="H905" s="1"/>
     </row>
-    <row r="906" spans="1:8" ht="15.75" thickBot="1">
+    <row r="906" spans="1:8" ht="15" thickBot="1">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -11948,7 +11948,7 @@
       <c r="G906" s="1"/>
       <c r="H906" s="1"/>
     </row>
-    <row r="907" spans="1:8" ht="15.75" thickBot="1">
+    <row r="907" spans="1:8" ht="15" thickBot="1">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -11958,7 +11958,7 @@
       <c r="G907" s="1"/>
       <c r="H907" s="1"/>
     </row>
-    <row r="908" spans="1:8" ht="15.75" thickBot="1">
+    <row r="908" spans="1:8" ht="15" thickBot="1">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -11968,7 +11968,7 @@
       <c r="G908" s="1"/>
       <c r="H908" s="1"/>
     </row>
-    <row r="909" spans="1:8" ht="15.75" thickBot="1">
+    <row r="909" spans="1:8" ht="15" thickBot="1">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -11978,7 +11978,7 @@
       <c r="G909" s="1"/>
       <c r="H909" s="1"/>
     </row>
-    <row r="910" spans="1:8" ht="15.75" thickBot="1">
+    <row r="910" spans="1:8" ht="15" thickBot="1">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -11988,7 +11988,7 @@
       <c r="G910" s="1"/>
       <c r="H910" s="1"/>
     </row>
-    <row r="911" spans="1:8" ht="15.75" thickBot="1">
+    <row r="911" spans="1:8" ht="15" thickBot="1">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -11998,7 +11998,7 @@
       <c r="G911" s="1"/>
       <c r="H911" s="1"/>
     </row>
-    <row r="912" spans="1:8" ht="15.75" thickBot="1">
+    <row r="912" spans="1:8" ht="15" thickBot="1">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -12008,7 +12008,7 @@
       <c r="G912" s="1"/>
       <c r="H912" s="1"/>
     </row>
-    <row r="913" spans="1:8" ht="15.75" thickBot="1">
+    <row r="913" spans="1:8" ht="15" thickBot="1">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -12018,7 +12018,7 @@
       <c r="G913" s="1"/>
       <c r="H913" s="1"/>
     </row>
-    <row r="914" spans="1:8" ht="15.75" thickBot="1">
+    <row r="914" spans="1:8" ht="15" thickBot="1">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -12028,7 +12028,7 @@
       <c r="G914" s="1"/>
       <c r="H914" s="1"/>
     </row>
-    <row r="915" spans="1:8" ht="15.75" thickBot="1">
+    <row r="915" spans="1:8" ht="15" thickBot="1">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -12038,7 +12038,7 @@
       <c r="G915" s="1"/>
       <c r="H915" s="1"/>
     </row>
-    <row r="916" spans="1:8" ht="15.75" thickBot="1">
+    <row r="916" spans="1:8" ht="15" thickBot="1">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -12048,7 +12048,7 @@
       <c r="G916" s="1"/>
       <c r="H916" s="1"/>
     </row>
-    <row r="917" spans="1:8" ht="15.75" thickBot="1">
+    <row r="917" spans="1:8" ht="15" thickBot="1">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>

--- a/494/initial.xlsx
+++ b/494/initial.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ac4ce512cbdb248/Desktop/FunctionFromSeq/494/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C196EC0-5B4D-45DF-ABF2-C7F23887907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5C196EC0-5B4D-45DF-ABF2-C7F23887907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68D04ED2-FE96-45A3-B7AA-E8B421A26B5C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{92F93940-16D1-494E-8DAD-2FEDD2E887ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92F93940-16D1-494E-8DAD-2FEDD2E887ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="336">
   <si>
     <t>Source</t>
   </si>
@@ -395,21 +395,9 @@
     <t>CSLPGLSAAADQTIKIGAQSMSESEIIASMLGQLIEHHTDLKTTTIKNLGSNAVQQQALMNGEIDIAATRYTGDALTGTLRMEPEKDPDKALALTQREFKKRYDLKWYDSYGFDNTYAFTVSKELADQYHLETVSDVKKWAPQLKLGVDNYWMKLKGNGYQDFTKTYGMTFGGTYPMQIGLVYDAVKSGKMDIVLAYSTDGRIKSYGLKMLKDDKQFFPPYDCSPVVPEKVLKEHPELEGIIKKMLGKIDTATMQELNYEVDGNLKEPSVVAKEYLEKHRYFES</t>
   </si>
   <si>
-    <t>4ZCQ</t>
-  </si>
-  <si>
-    <t>plasmodium falciparum</t>
-  </si>
-  <si>
-    <t>c-terminal catalytic domain of CTP:phosphochpline cytidyltransferase</t>
-  </si>
-  <si>
     <t>Generic enzyme</t>
   </si>
   <si>
-    <t>GHMAVPDDDDDDDNSNDESEYESSQMDSEKNKGSIKNSKNVVIYADGVYDMLHLGHMKQLEQAKKLFENTTLIVGVTSDNETKLFKGQVVQTLEERTETLKHIRWVDEIISPCPWVVTPEFLEKYKIDYVAHDDIPYANNQKEDIYAWLKRAGKFKATQRTEGVSTTDLIVRILKNYEDY</t>
-  </si>
-  <si>
     <t>4DOJ</t>
   </si>
   <si>
@@ -474,18 +462,6 @@
   </si>
   <si>
     <t>GSHMDYLTGKWKLWYKMLDVNHDGKISIEDVEESRNKFTNLHELLEEKAKGVKVDMENWWTEYIFGQNGPKEISEADFVKRLQTAYETDKAAFVKKMENCFNTIFDVIDTNKDRQIELDEFVLVFKAFGHENEPAVTKFFGLYNAPAGIPIKDIVAYVKFTTSDNSNDTDYVNQSLKLVL</t>
-  </si>
-  <si>
-    <t>5A23</t>
-  </si>
-  <si>
-    <t>pseudomonas aeruginosa</t>
-  </si>
-  <si>
-    <t>SdsA sulfatase</t>
-  </si>
-  <si>
-    <t>MSRLLALLALAPLLAGAAETTAPKPPSAFTVEAQRRVEAELPFADRADFERADRGLIRRPERLLIRNPDGSVAWQLGGYDFLLDGKPRDSINPSLQRQALLNLKYGLFEVAEGIYQVRGFDLANITFIRGDSGWIVVDTLTTPATARAAYELVSRELGERPIRTVIYSHAHADHFGGVRGLVEPQQVASGAVQIIAPAGFMEAAIKENVLAGNAMMRRATYQYGTQLPKGPQGQVDMAIGKGLARGPLSLLAPTRLIEGEGEDLVLDGVPFTFQNTPGTESPAEMNIWLPRQKALLMAENVVGTLHNLYTLRGAEVRDALGWSKYINQALHRFGRQAEVMFAVHNWPRWGNAEIVEVLEKQRDLYGYLHDQTLHLANQGVTIGQVHNRLRLPPSLDQEWYDRGYHGSVSHNARAVLNRYLGYYDGNPATLDPLSPEDSAGRYVEYMGGAERLLEQARASYARGEYRWVVEVVNRLVFAEPDNRAARELQADALEQLGYQAENAGWRNSYLSAAYELRHGVPRDQPTMKAGSADALAAMDTGLLFDYLGVRLDAGAAEGKALSINLRLPDIGENYLLELKNSHLNNLRGVQSEDAGQTVSIDRADLNRLLLKEVSAVRLVFEGKLKSSGNPLLLGQLFGMLGDFDFWFDIVTPAAKSEG</t>
   </si>
   <si>
     <t>1U53</t>
@@ -1250,6 +1226,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1569,10 +1549,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E4D86D5-FB97-47E7-8CDB-3D8247ED0B48}">
-  <dimension ref="A1:H917"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:H915"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.6" thickBot="1">
+    <row r="1" spans="1:8" ht="27" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1702,7 +1682,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="265.2" thickBot="1">
+    <row r="6" spans="1:8" ht="256.5" thickBot="1">
       <c r="A6" s="5" t="s">
         <v>29</v>
       </c>
@@ -1728,7 +1708,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="304.8" thickBot="1">
+    <row r="7" spans="1:8" ht="294.75" thickBot="1">
       <c r="A7" s="1" t="s">
         <v>33</v>
       </c>
@@ -1754,7 +1734,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="409.6" thickBot="1">
+    <row r="8" spans="1:8" ht="396.75" thickBot="1">
       <c r="A8" s="6" t="s">
         <v>36</v>
       </c>
@@ -1780,7 +1760,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="331.2" thickBot="1">
+    <row r="9" spans="1:8" ht="320.25" thickBot="1">
       <c r="A9" s="7" t="s">
         <v>40</v>
       </c>
@@ -1804,7 +1784,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="397.2" thickBot="1">
+    <row r="10" spans="1:8" ht="384" thickBot="1">
       <c r="A10" s="7" t="s">
         <v>44</v>
       </c>
@@ -1830,7 +1810,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="133.19999999999999" thickBot="1">
+    <row r="11" spans="1:8" ht="129" thickBot="1">
       <c r="A11" s="5" t="s">
         <v>48</v>
       </c>
@@ -1856,7 +1836,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="331.2" thickBot="1">
+    <row r="12" spans="1:8" ht="320.25" thickBot="1">
       <c r="A12" s="5" t="s">
         <v>52</v>
       </c>
@@ -1958,7 +1938,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="225.6" thickBot="1">
+    <row r="16" spans="1:8" ht="218.25" thickBot="1">
       <c r="A16" s="7" t="s">
         <v>65</v>
       </c>
@@ -1984,7 +1964,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="106.8" thickBot="1">
+    <row r="17" spans="1:8" ht="103.5" thickBot="1">
       <c r="A17" s="7" t="s">
         <v>69</v>
       </c>
@@ -2010,7 +1990,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="238.8" thickBot="1">
+    <row r="18" spans="1:8" ht="231" thickBot="1">
       <c r="A18" s="6" t="s">
         <v>73</v>
       </c>
@@ -2034,7 +2014,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="172.8" thickBot="1">
+    <row r="19" spans="1:8" ht="154.5" thickBot="1">
       <c r="A19" s="7" t="s">
         <v>76</v>
       </c>
@@ -2086,7 +2066,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="357.6" thickBot="1">
+    <row r="21" spans="1:8" ht="345.75" thickBot="1">
       <c r="A21" s="7" t="s">
         <v>84</v>
       </c>
@@ -2112,7 +2092,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="225.6" thickBot="1">
+    <row r="22" spans="1:8" ht="231" thickBot="1">
       <c r="A22" s="7" t="s">
         <v>88</v>
       </c>
@@ -2136,7 +2116,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="212.4" thickBot="1">
+    <row r="23" spans="1:8" ht="205.5" thickBot="1">
       <c r="A23" s="7" t="s">
         <v>91</v>
       </c>
@@ -2162,7 +2142,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="212.4" thickBot="1">
+    <row r="24" spans="1:8" ht="205.5" thickBot="1">
       <c r="A24" s="7" t="s">
         <v>95</v>
       </c>
@@ -2214,7 +2194,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="397.2" thickBot="1">
+    <row r="26" spans="1:8" ht="384" thickBot="1">
       <c r="A26" s="7" t="s">
         <v>103</v>
       </c>
@@ -2316,13 +2296,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="397.2" thickBot="1">
+    <row r="30" spans="1:8" ht="409.6" thickBot="1">
       <c r="A30" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
         <v>120</v>
       </c>
@@ -2336,22 +2314,24 @@
         <v>1</v>
       </c>
       <c r="G30" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H30" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="409.6" thickBot="1">
+      <c r="A31" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A31" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>126</v>
@@ -2360,50 +2340,50 @@
         <v>1</v>
       </c>
       <c r="G31" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="7" t="s">
         <v>127</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="F32" s="4">
         <v>1</v>
       </c>
       <c r="G32" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:8" ht="282" thickBot="1">
+      <c r="A33" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>132</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>133</v>
@@ -2412,50 +2392,50 @@
         <v>1</v>
       </c>
       <c r="G33" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="291.60000000000002" thickBot="1">
-      <c r="A34" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="243.75" thickBot="1">
+      <c r="A34" s="7" t="s">
         <v>134</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F34" s="4">
         <v>1</v>
       </c>
       <c r="G34" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="252" thickBot="1">
+    <row r="35" spans="1:8" ht="371.25" thickBot="1">
       <c r="A35" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="D35" s="1" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>140</v>
@@ -2464,13 +2444,13 @@
         <v>1</v>
       </c>
       <c r="G35" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="384" thickBot="1">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="409.6" thickBot="1">
       <c r="A36" s="7" t="s">
         <v>141</v>
       </c>
@@ -2481,7 +2461,7 @@
         <v>143</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>125</v>
+        <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>144</v>
@@ -2490,14 +2470,14 @@
         <v>1</v>
       </c>
       <c r="G36" s="4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="7" t="s">
         <v>145</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -2507,7 +2487,7 @@
         <v>147</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>148</v>
@@ -2516,14 +2496,14 @@
         <v>1</v>
       </c>
       <c r="G37" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:8" ht="320.25" thickBot="1">
+      <c r="A38" s="6" t="s">
         <v>149</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -2542,14 +2522,14 @@
         <v>1</v>
       </c>
       <c r="G38" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="8" t="s">
         <v>153</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -2565,128 +2545,128 @@
         <v>156</v>
       </c>
       <c r="F39" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="4">
-        <v>38</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="344.4" thickBot="1">
-      <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>157</v>
       </c>
+    </row>
+    <row r="40" spans="1:8" ht="409.6" thickBot="1">
+      <c r="A40" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="B40" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C40" s="1" t="s">
         <v>159</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>160</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F40" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A41" s="8" t="s">
-        <v>161</v>
+      <c r="A41" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C41" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C41" s="10" t="s">
         <v>163</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F41" s="4">
         <v>0</v>
       </c>
       <c r="G41" s="4">
-        <v>40</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A42" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>166</v>
       </c>
+    </row>
+    <row r="42" spans="1:8" ht="345.75" thickBot="1">
+      <c r="A42" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="B42" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F42" s="4">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4">
+        <v>43</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F42" s="4">
-        <v>0</v>
-      </c>
-      <c r="G42" s="4">
-        <v>41</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A43" s="1" t="s">
+    </row>
+    <row r="43" spans="1:8" ht="294.75" thickBot="1">
+      <c r="A43" s="5" t="s">
         <v>171</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F43" s="4">
+        <v>1</v>
+      </c>
+      <c r="G43" s="4">
+        <v>44</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F43" s="4">
-        <v>0</v>
-      </c>
-      <c r="G43" s="4">
-        <v>42</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="357.6" thickBot="1">
+    </row>
+    <row r="44" spans="1:8" ht="282" thickBot="1">
       <c r="A44" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>27</v>
@@ -2698,14 +2678,14 @@
         <v>1</v>
       </c>
       <c r="G44" s="4">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="304.8" thickBot="1">
-      <c r="A45" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="409.6" thickBot="1">
+      <c r="A45" s="7" t="s">
         <v>179</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -2715,30 +2695,30 @@
         <v>181</v>
       </c>
       <c r="D45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="F45" s="4">
         <v>1</v>
       </c>
       <c r="G45" s="4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="291.60000000000002" thickBot="1">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="1:8" ht="307.5" thickBot="1">
+      <c r="A46" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>27</v>
@@ -2750,13 +2730,13 @@
         <v>1</v>
       </c>
       <c r="G46" s="4">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="409.6" thickBot="1">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="384" thickBot="1">
       <c r="A47" s="7" t="s">
         <v>187</v>
       </c>
@@ -2776,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="G47" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="318" thickBot="1">
+    <row r="48" spans="1:8" ht="409.6" thickBot="1">
       <c r="A48" s="6" t="s">
         <v>191</v>
       </c>
@@ -2793,7 +2773,7 @@
         <v>193</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>194</v>
@@ -2802,13 +2782,13 @@
         <v>1</v>
       </c>
       <c r="G48" s="4">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="397.2" thickBot="1">
+    <row r="49" spans="1:8" ht="409.6" thickBot="1">
       <c r="A49" s="7" t="s">
         <v>195</v>
       </c>
@@ -2828,14 +2808,14 @@
         <v>1</v>
       </c>
       <c r="G49" s="4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="7" t="s">
         <v>199</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -2845,7 +2825,7 @@
         <v>201</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>202</v>
@@ -2854,7 +2834,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="4">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>199</v>
@@ -2865,22 +2845,22 @@
         <v>203</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F51" s="4">
         <v>1</v>
       </c>
       <c r="G51" s="4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>203</v>
@@ -2888,36 +2868,36 @@
     </row>
     <row r="52" spans="1:8" ht="409.6" thickBot="1">
       <c r="A52" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="F52" s="4">
         <v>1</v>
       </c>
       <c r="G52" s="4">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="409.6" thickBot="1">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="333" thickBot="1">
       <c r="A53" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>212</v>
@@ -2932,13 +2912,13 @@
         <v>1</v>
       </c>
       <c r="G53" s="4">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="409.6" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="358.5" thickBot="1">
       <c r="A54" s="7" t="s">
         <v>214</v>
       </c>
@@ -2949,7 +2929,7 @@
         <v>216</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>217</v>
@@ -2958,13 +2938,13 @@
         <v>1</v>
       </c>
       <c r="G54" s="4">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="344.4" thickBot="1">
+    <row r="55" spans="1:8" ht="409.6" thickBot="1">
       <c r="A55" s="7" t="s">
         <v>218</v>
       </c>
@@ -2975,7 +2955,7 @@
         <v>220</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>221</v>
@@ -2984,13 +2964,13 @@
         <v>1</v>
       </c>
       <c r="G55" s="4">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="370.8" thickBot="1">
+    <row r="56" spans="1:8" ht="409.6" thickBot="1">
       <c r="A56" s="7" t="s">
         <v>222</v>
       </c>
@@ -3001,7 +2981,7 @@
         <v>224</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>225</v>
@@ -3010,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="4">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>222</v>
@@ -3021,22 +3001,22 @@
         <v>226</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="F57" s="4">
         <v>1</v>
       </c>
       <c r="G57" s="4">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>226</v>
@@ -3044,458 +3024,458 @@
     </row>
     <row r="58" spans="1:8" ht="409.6" thickBot="1">
       <c r="A58" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="F58" s="4">
         <v>1</v>
       </c>
       <c r="G58" s="4">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>235</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>236</v>
       </c>
       <c r="F59" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="4">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A60" s="7" t="s">
-        <v>237</v>
+      <c r="A60" s="11" t="s">
+        <v>238</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F60" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" s="4">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="409.6" thickBot="1">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="243.75" thickBot="1">
       <c r="A61" s="11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F61" s="4">
         <v>0</v>
       </c>
       <c r="G61" s="4">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="409.6" thickBot="1">
       <c r="A62" s="11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F62" s="4">
         <v>0</v>
       </c>
       <c r="G62" s="4">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="252" thickBot="1">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="409.6" thickBot="1">
       <c r="A63" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F63" s="4">
         <v>0</v>
       </c>
       <c r="G63" s="4">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="409.6" thickBot="1">
       <c r="A64" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F64" s="4">
         <v>0</v>
       </c>
       <c r="G64" s="4">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="409.6" thickBot="1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="371.25" thickBot="1">
       <c r="A65" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F65" s="4">
         <v>0</v>
       </c>
       <c r="G65" s="4">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="409.6" thickBot="1">
       <c r="A66" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>267</v>
+        <v>115</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F66" s="4">
         <v>0</v>
       </c>
       <c r="G66" s="4">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="397.2" thickBot="1">
-      <c r="A67" s="11" t="s">
         <v>271</v>
       </c>
+    </row>
+    <row r="67" spans="1:8" ht="345.75" thickBot="1">
+      <c r="A67" s="7" t="s">
+        <v>272</v>
+      </c>
       <c r="B67" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F67" s="4">
         <v>0</v>
       </c>
       <c r="G67" s="4">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="409.6" thickBot="1">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="358.5" thickBot="1">
       <c r="A68" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>115</v>
+        <v>278</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F68" s="4">
         <v>0</v>
       </c>
       <c r="G68" s="4">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="357.6" thickBot="1">
-      <c r="A69" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="409.6" thickBot="1">
+      <c r="A69" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F69" s="4">
         <v>0</v>
       </c>
       <c r="G69" s="4">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="370.8" thickBot="1">
-      <c r="A70" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="409.6" thickBot="1">
+      <c r="A70" s="12" t="s">
+        <v>287</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>286</v>
+        <v>150</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F70" s="4">
         <v>0</v>
       </c>
       <c r="G70" s="4">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A71" s="1" t="s">
-        <v>290</v>
+      <c r="A71" s="7" t="s">
+        <v>291</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F71" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" s="4">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A72" s="12" t="s">
         <v>295</v>
       </c>
+    </row>
+    <row r="72" spans="1:8" ht="371.25" thickBot="1">
+      <c r="A72" s="11" t="s">
+        <v>296</v>
+      </c>
       <c r="B72" s="1" t="s">
-        <v>158</v>
+        <v>297</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F72" s="4">
         <v>0</v>
       </c>
       <c r="G72" s="4">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A73" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="358.5" thickBot="1">
+      <c r="A73" s="11" t="s">
+        <v>301</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F73" s="4">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4">
+        <v>74</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="409.6" thickBot="1">
+      <c r="A74" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F74" s="4">
         <v>1</v>
       </c>
-      <c r="G73" s="4">
-        <v>72</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="384" thickBot="1">
-      <c r="A74" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="B74" s="1" t="s">
+      <c r="G74" s="4">
+        <v>75</v>
+      </c>
+      <c r="H74" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="F74" s="4">
-        <v>0</v>
-      </c>
-      <c r="G74" s="4">
-        <v>73</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="370.8" thickBot="1">
+    </row>
+    <row r="75" spans="1:8" ht="409.6" thickBot="1">
       <c r="A75" s="11" t="s">
         <v>309</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="D75" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>311</v>
@@ -3504,221 +3484,189 @@
         <v>0</v>
       </c>
       <c r="G75" s="4">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A76" s="5" t="s">
+    <row r="76" spans="1:8" ht="103.5" thickBot="1">
+      <c r="A76" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="10" t="s">
         <v>315</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F76" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="4">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="409.6" thickBot="1">
-      <c r="A77" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C77" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>21</v>
+    </row>
+    <row r="77" spans="1:8" ht="269.25" thickBot="1">
+      <c r="A77" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" t="s">
+        <v>314</v>
+      </c>
+      <c r="C77" t="s">
+        <v>319</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="F77" s="4">
+        <v>320</v>
+      </c>
+      <c r="F77" s="1">
         <v>0</v>
       </c>
-      <c r="G77" s="4">
-        <v>76</v>
+      <c r="G77" s="1">
+        <v>78</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="106.8" thickBot="1">
-      <c r="A78" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="129" thickBot="1">
+      <c r="A78" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" t="s">
+        <v>314</v>
+      </c>
+      <c r="C78" t="s">
         <v>321</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="D78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="F78" s="1">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>79</v>
+      </c>
+      <c r="H78" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E78" s="1" t="s">
+    </row>
+    <row r="79" spans="1:8" ht="42" thickBot="1">
+      <c r="A79" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="F78" s="4">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4">
-        <v>77</v>
-      </c>
-      <c r="H78" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" ht="278.39999999999998" thickBot="1">
-      <c r="A79" t="s">
-        <v>8</v>
-      </c>
-      <c r="B79" t="s">
-        <v>322</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="C79" s="1" t="s">
         <v>327</v>
       </c>
       <c r="D79" t="s">
         <v>11</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>328</v>
+      <c r="E79" t="s">
+        <v>330</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
       </c>
       <c r="G79" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="133.19999999999999" thickBot="1">
-      <c r="A80" t="s">
-        <v>8</v>
-      </c>
-      <c r="B80" t="s">
-        <v>322</v>
-      </c>
-      <c r="C80" t="s">
-        <v>329</v>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="42" thickBot="1">
+      <c r="A80" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="D80" t="s">
         <v>11</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>330</v>
+      <c r="E80" t="s">
+        <v>331</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
       </c>
       <c r="G80" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="42.6" thickBot="1">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="42" thickBot="1">
       <c r="A81" s="13" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
       </c>
       <c r="E81" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
       </c>
       <c r="G81" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="42.6" thickBot="1">
-      <c r="A82" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="D82" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" t="s">
-        <v>339</v>
-      </c>
-      <c r="F82" s="1">
-        <v>0</v>
-      </c>
-      <c r="G82" s="1">
-        <v>81</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="42.6" thickBot="1">
-      <c r="A83" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="D83" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" t="s">
-        <v>340</v>
-      </c>
-      <c r="F83" s="1">
-        <v>0</v>
-      </c>
-      <c r="G83" s="1">
-        <v>82</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="15" thickBot="1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3728,7 +3676,7 @@
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
     </row>
-    <row r="85" spans="1:8" ht="15" thickBot="1">
+    <row r="85" spans="1:8" ht="15.75" thickBot="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3738,7 +3686,7 @@
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
     </row>
-    <row r="86" spans="1:8" ht="15" thickBot="1">
+    <row r="86" spans="1:8" ht="15.75" thickBot="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3748,7 +3696,7 @@
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="1:8" ht="15" thickBot="1">
+    <row r="87" spans="1:8" ht="15.75" thickBot="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3758,7 +3706,7 @@
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
     </row>
-    <row r="88" spans="1:8" ht="15" thickBot="1">
+    <row r="88" spans="1:8" ht="15.75" thickBot="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3768,7 +3716,7 @@
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="1:8" ht="15" thickBot="1">
+    <row r="89" spans="1:8" ht="15.75" thickBot="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3778,7 +3726,7 @@
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
     </row>
-    <row r="90" spans="1:8" ht="15" thickBot="1">
+    <row r="90" spans="1:8" ht="15.75" thickBot="1">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3788,7 +3736,7 @@
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="1:8" ht="15" thickBot="1">
+    <row r="91" spans="1:8" ht="15.75" thickBot="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3798,7 +3746,7 @@
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
     </row>
-    <row r="92" spans="1:8" ht="15" thickBot="1">
+    <row r="92" spans="1:8" ht="15.75" thickBot="1">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3808,7 +3756,7 @@
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
     </row>
-    <row r="93" spans="1:8" ht="15" thickBot="1">
+    <row r="93" spans="1:8" ht="15.75" thickBot="1">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3818,7 +3766,7 @@
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="1:8" ht="15" thickBot="1">
+    <row r="94" spans="1:8" ht="15.75" thickBot="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3828,7 +3776,7 @@
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
     </row>
-    <row r="95" spans="1:8" ht="15" thickBot="1">
+    <row r="95" spans="1:8" ht="15.75" thickBot="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3838,7 +3786,7 @@
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:8" ht="15" thickBot="1">
+    <row r="96" spans="1:8" ht="15.75" thickBot="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3848,7 +3796,7 @@
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:8" ht="15" thickBot="1">
+    <row r="97" spans="1:8" ht="15.75" thickBot="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3858,7 +3806,7 @@
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
     </row>
-    <row r="98" spans="1:8" ht="15" thickBot="1">
+    <row r="98" spans="1:8" ht="15.75" thickBot="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3868,7 +3816,7 @@
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:8" ht="15" thickBot="1">
+    <row r="99" spans="1:8" ht="15.75" thickBot="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3878,7 +3826,7 @@
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:8" ht="15" thickBot="1">
+    <row r="100" spans="1:8" ht="15.75" thickBot="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3888,7 +3836,7 @@
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:8" ht="15" thickBot="1">
+    <row r="101" spans="1:8" ht="15.75" thickBot="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3898,7 +3846,7 @@
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:8" ht="15" thickBot="1">
+    <row r="102" spans="1:8" ht="15.75" thickBot="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3908,7 +3856,7 @@
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:8" ht="15" thickBot="1">
+    <row r="103" spans="1:8" ht="15.75" thickBot="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3918,7 +3866,7 @@
       <c r="G103" s="1"/>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:8" ht="15" thickBot="1">
+    <row r="104" spans="1:8" ht="15.75" thickBot="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3928,7 +3876,7 @@
       <c r="G104" s="1"/>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:8" ht="15" thickBot="1">
+    <row r="105" spans="1:8" ht="15.75" thickBot="1">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3938,7 +3886,7 @@
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:8" ht="15" thickBot="1">
+    <row r="106" spans="1:8" ht="15.75" thickBot="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3948,7 +3896,7 @@
       <c r="G106" s="1"/>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:8" ht="15" thickBot="1">
+    <row r="107" spans="1:8" ht="15.75" thickBot="1">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3958,7 +3906,7 @@
       <c r="G107" s="1"/>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:8" ht="15" thickBot="1">
+    <row r="108" spans="1:8" ht="15.75" thickBot="1">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3968,7 +3916,7 @@
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:8" ht="15" thickBot="1">
+    <row r="109" spans="1:8" ht="15.75" thickBot="1">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3978,7 +3926,7 @@
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:8" ht="15" thickBot="1">
+    <row r="110" spans="1:8" ht="15.75" thickBot="1">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3988,7 +3936,7 @@
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:8" ht="15" thickBot="1">
+    <row r="111" spans="1:8" ht="15.75" thickBot="1">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3998,7 +3946,7 @@
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
     </row>
-    <row r="112" spans="1:8" ht="15" thickBot="1">
+    <row r="112" spans="1:8" ht="15.75" thickBot="1">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4008,7 +3956,7 @@
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
     </row>
-    <row r="113" spans="1:8" ht="15" thickBot="1">
+    <row r="113" spans="1:8" ht="15.75" thickBot="1">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4018,7 +3966,7 @@
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
     </row>
-    <row r="114" spans="1:8" ht="15" thickBot="1">
+    <row r="114" spans="1:8" ht="15.75" thickBot="1">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4028,7 +3976,7 @@
       <c r="G114" s="1"/>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8" ht="15" thickBot="1">
+    <row r="115" spans="1:8" ht="15.75" thickBot="1">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4038,7 +3986,7 @@
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8" ht="15" thickBot="1">
+    <row r="116" spans="1:8" ht="15.75" thickBot="1">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4048,7 +3996,7 @@
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8" ht="15" thickBot="1">
+    <row r="117" spans="1:8" ht="15.75" thickBot="1">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4058,7 +4006,7 @@
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8" ht="15" thickBot="1">
+    <row r="118" spans="1:8" ht="15.75" thickBot="1">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4068,7 +4016,7 @@
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8" ht="15" thickBot="1">
+    <row r="119" spans="1:8" ht="15.75" thickBot="1">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4078,7 +4026,7 @@
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8" ht="15" thickBot="1">
+    <row r="120" spans="1:8" ht="15.75" thickBot="1">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4088,7 +4036,7 @@
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8" ht="15" thickBot="1">
+    <row r="121" spans="1:8" ht="15.75" thickBot="1">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4098,7 +4046,7 @@
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:8" ht="15" thickBot="1">
+    <row r="122" spans="1:8" ht="15.75" thickBot="1">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4108,7 +4056,7 @@
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
     </row>
-    <row r="123" spans="1:8" ht="15" thickBot="1">
+    <row r="123" spans="1:8" ht="15.75" thickBot="1">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4118,7 +4066,7 @@
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8" ht="15" thickBot="1">
+    <row r="124" spans="1:8" ht="15.75" thickBot="1">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4128,7 +4076,7 @@
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:8" ht="15" thickBot="1">
+    <row r="125" spans="1:8" ht="15.75" thickBot="1">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4138,7 +4086,7 @@
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
     </row>
-    <row r="126" spans="1:8" ht="15" thickBot="1">
+    <row r="126" spans="1:8" ht="15.75" thickBot="1">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4148,7 +4096,7 @@
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
     </row>
-    <row r="127" spans="1:8" ht="15" thickBot="1">
+    <row r="127" spans="1:8" ht="15.75" thickBot="1">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4158,7 +4106,7 @@
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8" ht="15" thickBot="1">
+    <row r="128" spans="1:8" ht="15.75" thickBot="1">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4168,7 +4116,7 @@
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:8" ht="15" thickBot="1">
+    <row r="129" spans="1:8" ht="15.75" thickBot="1">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4178,7 +4126,7 @@
       <c r="G129" s="1"/>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:8" ht="15" thickBot="1">
+    <row r="130" spans="1:8" ht="15.75" thickBot="1">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4188,7 +4136,7 @@
       <c r="G130" s="1"/>
       <c r="H130" s="1"/>
     </row>
-    <row r="131" spans="1:8" ht="15" thickBot="1">
+    <row r="131" spans="1:8" ht="15.75" thickBot="1">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4198,7 +4146,7 @@
       <c r="G131" s="1"/>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="1:8" ht="15" thickBot="1">
+    <row r="132" spans="1:8" ht="15.75" thickBot="1">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4208,7 +4156,7 @@
       <c r="G132" s="1"/>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:8" ht="15" thickBot="1">
+    <row r="133" spans="1:8" ht="15.75" thickBot="1">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4218,7 +4166,7 @@
       <c r="G133" s="1"/>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:8" ht="15" thickBot="1">
+    <row r="134" spans="1:8" ht="15.75" thickBot="1">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4228,7 +4176,7 @@
       <c r="G134" s="1"/>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:8" ht="15" thickBot="1">
+    <row r="135" spans="1:8" ht="15.75" thickBot="1">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4238,7 +4186,7 @@
       <c r="G135" s="1"/>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:8" ht="15" thickBot="1">
+    <row r="136" spans="1:8" ht="15.75" thickBot="1">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4248,7 +4196,7 @@
       <c r="G136" s="1"/>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:8" ht="15" thickBot="1">
+    <row r="137" spans="1:8" ht="15.75" thickBot="1">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4258,7 +4206,7 @@
       <c r="G137" s="1"/>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:8" ht="15" thickBot="1">
+    <row r="138" spans="1:8" ht="15.75" thickBot="1">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4268,7 +4216,7 @@
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
     </row>
-    <row r="139" spans="1:8" ht="15" thickBot="1">
+    <row r="139" spans="1:8" ht="15.75" thickBot="1">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4278,7 +4226,7 @@
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
     </row>
-    <row r="140" spans="1:8" ht="15" thickBot="1">
+    <row r="140" spans="1:8" ht="15.75" thickBot="1">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4288,7 +4236,7 @@
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
     </row>
-    <row r="141" spans="1:8" ht="15" thickBot="1">
+    <row r="141" spans="1:8" ht="15.75" thickBot="1">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4298,7 +4246,7 @@
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
     </row>
-    <row r="142" spans="1:8" ht="15" thickBot="1">
+    <row r="142" spans="1:8" ht="15.75" thickBot="1">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4308,7 +4256,7 @@
       <c r="G142" s="1"/>
       <c r="H142" s="1"/>
     </row>
-    <row r="143" spans="1:8" ht="15" thickBot="1">
+    <row r="143" spans="1:8" ht="15.75" thickBot="1">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4318,7 +4266,7 @@
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
     </row>
-    <row r="144" spans="1:8" ht="15" thickBot="1">
+    <row r="144" spans="1:8" ht="15.75" thickBot="1">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4328,7 +4276,7 @@
       <c r="G144" s="1"/>
       <c r="H144" s="1"/>
     </row>
-    <row r="145" spans="1:8" ht="15" thickBot="1">
+    <row r="145" spans="1:8" ht="15.75" thickBot="1">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4338,7 +4286,7 @@
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
     </row>
-    <row r="146" spans="1:8" ht="15" thickBot="1">
+    <row r="146" spans="1:8" ht="15.75" thickBot="1">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4348,7 +4296,7 @@
       <c r="G146" s="1"/>
       <c r="H146" s="1"/>
     </row>
-    <row r="147" spans="1:8" ht="15" thickBot="1">
+    <row r="147" spans="1:8" ht="15.75" thickBot="1">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4358,7 +4306,7 @@
       <c r="G147" s="1"/>
       <c r="H147" s="1"/>
     </row>
-    <row r="148" spans="1:8" ht="15" thickBot="1">
+    <row r="148" spans="1:8" ht="15.75" thickBot="1">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4368,7 +4316,7 @@
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
     </row>
-    <row r="149" spans="1:8" ht="15" thickBot="1">
+    <row r="149" spans="1:8" ht="15.75" thickBot="1">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4378,7 +4326,7 @@
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
     </row>
-    <row r="150" spans="1:8" ht="15" thickBot="1">
+    <row r="150" spans="1:8" ht="15.75" thickBot="1">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4388,7 +4336,7 @@
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
     </row>
-    <row r="151" spans="1:8" ht="15" thickBot="1">
+    <row r="151" spans="1:8" ht="15.75" thickBot="1">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4398,7 +4346,7 @@
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
     </row>
-    <row r="152" spans="1:8" ht="15" thickBot="1">
+    <row r="152" spans="1:8" ht="15.75" thickBot="1">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4408,7 +4356,7 @@
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
     </row>
-    <row r="153" spans="1:8" ht="15" thickBot="1">
+    <row r="153" spans="1:8" ht="15.75" thickBot="1">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4418,7 +4366,7 @@
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
     </row>
-    <row r="154" spans="1:8" ht="15" thickBot="1">
+    <row r="154" spans="1:8" ht="15.75" thickBot="1">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4428,7 +4376,7 @@
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
     </row>
-    <row r="155" spans="1:8" ht="15" thickBot="1">
+    <row r="155" spans="1:8" ht="15.75" thickBot="1">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4438,7 +4386,7 @@
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
     </row>
-    <row r="156" spans="1:8" ht="15" thickBot="1">
+    <row r="156" spans="1:8" ht="15.75" thickBot="1">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4448,7 +4396,7 @@
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
     </row>
-    <row r="157" spans="1:8" ht="15" thickBot="1">
+    <row r="157" spans="1:8" ht="15.75" thickBot="1">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4458,7 +4406,7 @@
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
     </row>
-    <row r="158" spans="1:8" ht="15" thickBot="1">
+    <row r="158" spans="1:8" ht="15.75" thickBot="1">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4468,7 +4416,7 @@
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
     </row>
-    <row r="159" spans="1:8" ht="15" thickBot="1">
+    <row r="159" spans="1:8" ht="15.75" thickBot="1">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4478,7 +4426,7 @@
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
     </row>
-    <row r="160" spans="1:8" ht="15" thickBot="1">
+    <row r="160" spans="1:8" ht="15.75" thickBot="1">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4488,7 +4436,7 @@
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
     </row>
-    <row r="161" spans="1:8" ht="15" thickBot="1">
+    <row r="161" spans="1:8" ht="15.75" thickBot="1">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4498,7 +4446,7 @@
       <c r="G161" s="1"/>
       <c r="H161" s="1"/>
     </row>
-    <row r="162" spans="1:8" ht="15" thickBot="1">
+    <row r="162" spans="1:8" ht="15.75" thickBot="1">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4508,7 +4456,7 @@
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
     </row>
-    <row r="163" spans="1:8" ht="15" thickBot="1">
+    <row r="163" spans="1:8" ht="15.75" thickBot="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4518,7 +4466,7 @@
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
     </row>
-    <row r="164" spans="1:8" ht="15" thickBot="1">
+    <row r="164" spans="1:8" ht="15.75" thickBot="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -4528,7 +4476,7 @@
       <c r="G164" s="1"/>
       <c r="H164" s="1"/>
     </row>
-    <row r="165" spans="1:8" ht="15" thickBot="1">
+    <row r="165" spans="1:8" ht="15.75" thickBot="1">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -4538,7 +4486,7 @@
       <c r="G165" s="1"/>
       <c r="H165" s="1"/>
     </row>
-    <row r="166" spans="1:8" ht="15" thickBot="1">
+    <row r="166" spans="1:8" ht="15.75" thickBot="1">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -4548,7 +4496,7 @@
       <c r="G166" s="1"/>
       <c r="H166" s="1"/>
     </row>
-    <row r="167" spans="1:8" ht="15" thickBot="1">
+    <row r="167" spans="1:8" ht="15.75" thickBot="1">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -4558,7 +4506,7 @@
       <c r="G167" s="1"/>
       <c r="H167" s="1"/>
     </row>
-    <row r="168" spans="1:8" ht="15" thickBot="1">
+    <row r="168" spans="1:8" ht="15.75" thickBot="1">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -4568,7 +4516,7 @@
       <c r="G168" s="1"/>
       <c r="H168" s="1"/>
     </row>
-    <row r="169" spans="1:8" ht="15" thickBot="1">
+    <row r="169" spans="1:8" ht="15.75" thickBot="1">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -4578,7 +4526,7 @@
       <c r="G169" s="1"/>
       <c r="H169" s="1"/>
     </row>
-    <row r="170" spans="1:8" ht="15" thickBot="1">
+    <row r="170" spans="1:8" ht="15.75" thickBot="1">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -4588,7 +4536,7 @@
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
     </row>
-    <row r="171" spans="1:8" ht="15" thickBot="1">
+    <row r="171" spans="1:8" ht="15.75" thickBot="1">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -4598,7 +4546,7 @@
       <c r="G171" s="1"/>
       <c r="H171" s="1"/>
     </row>
-    <row r="172" spans="1:8" ht="15" thickBot="1">
+    <row r="172" spans="1:8" ht="15.75" thickBot="1">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -4608,7 +4556,7 @@
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
     </row>
-    <row r="173" spans="1:8" ht="15" thickBot="1">
+    <row r="173" spans="1:8" ht="15.75" thickBot="1">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -4618,7 +4566,7 @@
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
     </row>
-    <row r="174" spans="1:8" ht="15" thickBot="1">
+    <row r="174" spans="1:8" ht="15.75" thickBot="1">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -4628,7 +4576,7 @@
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
     </row>
-    <row r="175" spans="1:8" ht="15" thickBot="1">
+    <row r="175" spans="1:8" ht="15.75" thickBot="1">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -4638,7 +4586,7 @@
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
     </row>
-    <row r="176" spans="1:8" ht="15" thickBot="1">
+    <row r="176" spans="1:8" ht="15.75" thickBot="1">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -4648,7 +4596,7 @@
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="1:8" ht="15" thickBot="1">
+    <row r="177" spans="1:8" ht="15.75" thickBot="1">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -4658,7 +4606,7 @@
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="1:8" ht="15" thickBot="1">
+    <row r="178" spans="1:8" ht="15.75" thickBot="1">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -4668,7 +4616,7 @@
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="1:8" ht="15" thickBot="1">
+    <row r="179" spans="1:8" ht="15.75" thickBot="1">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -4678,7 +4626,7 @@
       <c r="G179" s="1"/>
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="1:8" ht="15" thickBot="1">
+    <row r="180" spans="1:8" ht="15.75" thickBot="1">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -4688,7 +4636,7 @@
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="1:8" ht="15" thickBot="1">
+    <row r="181" spans="1:8" ht="15.75" thickBot="1">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -4698,7 +4646,7 @@
       <c r="G181" s="1"/>
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="1:8" ht="15" thickBot="1">
+    <row r="182" spans="1:8" ht="15.75" thickBot="1">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -4708,7 +4656,7 @@
       <c r="G182" s="1"/>
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="1:8" ht="15" thickBot="1">
+    <row r="183" spans="1:8" ht="15.75" thickBot="1">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -4718,7 +4666,7 @@
       <c r="G183" s="1"/>
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="1:8" ht="15" thickBot="1">
+    <row r="184" spans="1:8" ht="15.75" thickBot="1">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -4728,7 +4676,7 @@
       <c r="G184" s="1"/>
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="1:8" ht="15" thickBot="1">
+    <row r="185" spans="1:8" ht="15.75" thickBot="1">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -4738,7 +4686,7 @@
       <c r="G185" s="1"/>
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="1:8" ht="15" thickBot="1">
+    <row r="186" spans="1:8" ht="15.75" thickBot="1">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -4748,7 +4696,7 @@
       <c r="G186" s="1"/>
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="1:8" ht="15" thickBot="1">
+    <row r="187" spans="1:8" ht="15.75" thickBot="1">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -4758,7 +4706,7 @@
       <c r="G187" s="1"/>
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="1:8" ht="15" thickBot="1">
+    <row r="188" spans="1:8" ht="15.75" thickBot="1">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -4768,7 +4716,7 @@
       <c r="G188" s="1"/>
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="1:8" ht="15" thickBot="1">
+    <row r="189" spans="1:8" ht="15.75" thickBot="1">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -4778,7 +4726,7 @@
       <c r="G189" s="1"/>
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="1:8" ht="15" thickBot="1">
+    <row r="190" spans="1:8" ht="15.75" thickBot="1">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -4788,7 +4736,7 @@
       <c r="G190" s="1"/>
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="1:8" ht="15" thickBot="1">
+    <row r="191" spans="1:8" ht="15.75" thickBot="1">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -4798,7 +4746,7 @@
       <c r="G191" s="1"/>
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="1:8" ht="15" thickBot="1">
+    <row r="192" spans="1:8" ht="15.75" thickBot="1">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -4808,7 +4756,7 @@
       <c r="G192" s="1"/>
       <c r="H192" s="1"/>
     </row>
-    <row r="193" spans="1:8" ht="15" thickBot="1">
+    <row r="193" spans="1:8" ht="15.75" thickBot="1">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -4818,7 +4766,7 @@
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
     </row>
-    <row r="194" spans="1:8" ht="15" thickBot="1">
+    <row r="194" spans="1:8" ht="15.75" thickBot="1">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -4828,7 +4776,7 @@
       <c r="G194" s="1"/>
       <c r="H194" s="1"/>
     </row>
-    <row r="195" spans="1:8" ht="15" thickBot="1">
+    <row r="195" spans="1:8" ht="15.75" thickBot="1">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -4838,7 +4786,7 @@
       <c r="G195" s="1"/>
       <c r="H195" s="1"/>
     </row>
-    <row r="196" spans="1:8" ht="15" thickBot="1">
+    <row r="196" spans="1:8" ht="15.75" thickBot="1">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -4848,7 +4796,7 @@
       <c r="G196" s="1"/>
       <c r="H196" s="1"/>
     </row>
-    <row r="197" spans="1:8" ht="15" thickBot="1">
+    <row r="197" spans="1:8" ht="15.75" thickBot="1">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -4858,7 +4806,7 @@
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
     </row>
-    <row r="198" spans="1:8" ht="15" thickBot="1">
+    <row r="198" spans="1:8" ht="15.75" thickBot="1">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -4868,7 +4816,7 @@
       <c r="G198" s="1"/>
       <c r="H198" s="1"/>
     </row>
-    <row r="199" spans="1:8" ht="15" thickBot="1">
+    <row r="199" spans="1:8" ht="15.75" thickBot="1">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -4878,7 +4826,7 @@
       <c r="G199" s="1"/>
       <c r="H199" s="1"/>
     </row>
-    <row r="200" spans="1:8" ht="15" thickBot="1">
+    <row r="200" spans="1:8" ht="15.75" thickBot="1">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -4888,7 +4836,7 @@
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
     </row>
-    <row r="201" spans="1:8" ht="15" thickBot="1">
+    <row r="201" spans="1:8" ht="15.75" thickBot="1">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -4898,7 +4846,7 @@
       <c r="G201" s="1"/>
       <c r="H201" s="1"/>
     </row>
-    <row r="202" spans="1:8" ht="15" thickBot="1">
+    <row r="202" spans="1:8" ht="15.75" thickBot="1">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -4908,7 +4856,7 @@
       <c r="G202" s="1"/>
       <c r="H202" s="1"/>
     </row>
-    <row r="203" spans="1:8" ht="15" thickBot="1">
+    <row r="203" spans="1:8" ht="15.75" thickBot="1">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -4918,7 +4866,7 @@
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
     </row>
-    <row r="204" spans="1:8" ht="15" thickBot="1">
+    <row r="204" spans="1:8" ht="15.75" thickBot="1">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -4928,7 +4876,7 @@
       <c r="G204" s="1"/>
       <c r="H204" s="1"/>
     </row>
-    <row r="205" spans="1:8" ht="15" thickBot="1">
+    <row r="205" spans="1:8" ht="15.75" thickBot="1">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -4938,7 +4886,7 @@
       <c r="G205" s="1"/>
       <c r="H205" s="1"/>
     </row>
-    <row r="206" spans="1:8" ht="15" thickBot="1">
+    <row r="206" spans="1:8" ht="15.75" thickBot="1">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -4948,7 +4896,7 @@
       <c r="G206" s="1"/>
       <c r="H206" s="1"/>
     </row>
-    <row r="207" spans="1:8" ht="15" thickBot="1">
+    <row r="207" spans="1:8" ht="15.75" thickBot="1">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -4958,7 +4906,7 @@
       <c r="G207" s="1"/>
       <c r="H207" s="1"/>
     </row>
-    <row r="208" spans="1:8" ht="15" thickBot="1">
+    <row r="208" spans="1:8" ht="15.75" thickBot="1">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -4968,7 +4916,7 @@
       <c r="G208" s="1"/>
       <c r="H208" s="1"/>
     </row>
-    <row r="209" spans="1:8" ht="15" thickBot="1">
+    <row r="209" spans="1:8" ht="15.75" thickBot="1">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -4978,7 +4926,7 @@
       <c r="G209" s="1"/>
       <c r="H209" s="1"/>
     </row>
-    <row r="210" spans="1:8" ht="15" thickBot="1">
+    <row r="210" spans="1:8" ht="15.75" thickBot="1">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -4988,7 +4936,7 @@
       <c r="G210" s="1"/>
       <c r="H210" s="1"/>
     </row>
-    <row r="211" spans="1:8" ht="15" thickBot="1">
+    <row r="211" spans="1:8" ht="15.75" thickBot="1">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -4998,7 +4946,7 @@
       <c r="G211" s="1"/>
       <c r="H211" s="1"/>
     </row>
-    <row r="212" spans="1:8" ht="15" thickBot="1">
+    <row r="212" spans="1:8" ht="15.75" thickBot="1">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -5008,7 +4956,7 @@
       <c r="G212" s="1"/>
       <c r="H212" s="1"/>
     </row>
-    <row r="213" spans="1:8" ht="15" thickBot="1">
+    <row r="213" spans="1:8" ht="15.75" thickBot="1">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -5018,7 +4966,7 @@
       <c r="G213" s="1"/>
       <c r="H213" s="1"/>
     </row>
-    <row r="214" spans="1:8" ht="15" thickBot="1">
+    <row r="214" spans="1:8" ht="15.75" thickBot="1">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -5028,7 +4976,7 @@
       <c r="G214" s="1"/>
       <c r="H214" s="1"/>
     </row>
-    <row r="215" spans="1:8" ht="15" thickBot="1">
+    <row r="215" spans="1:8" ht="15.75" thickBot="1">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -5038,7 +4986,7 @@
       <c r="G215" s="1"/>
       <c r="H215" s="1"/>
     </row>
-    <row r="216" spans="1:8" ht="15" thickBot="1">
+    <row r="216" spans="1:8" ht="15.75" thickBot="1">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -5048,7 +4996,7 @@
       <c r="G216" s="1"/>
       <c r="H216" s="1"/>
     </row>
-    <row r="217" spans="1:8" ht="15" thickBot="1">
+    <row r="217" spans="1:8" ht="15.75" thickBot="1">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -5058,7 +5006,7 @@
       <c r="G217" s="1"/>
       <c r="H217" s="1"/>
     </row>
-    <row r="218" spans="1:8" ht="15" thickBot="1">
+    <row r="218" spans="1:8" ht="15.75" thickBot="1">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -5068,7 +5016,7 @@
       <c r="G218" s="1"/>
       <c r="H218" s="1"/>
     </row>
-    <row r="219" spans="1:8" ht="15" thickBot="1">
+    <row r="219" spans="1:8" ht="15.75" thickBot="1">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -5078,7 +5026,7 @@
       <c r="G219" s="1"/>
       <c r="H219" s="1"/>
     </row>
-    <row r="220" spans="1:8" ht="15" thickBot="1">
+    <row r="220" spans="1:8" ht="15.75" thickBot="1">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -5088,7 +5036,7 @@
       <c r="G220" s="1"/>
       <c r="H220" s="1"/>
     </row>
-    <row r="221" spans="1:8" ht="15" thickBot="1">
+    <row r="221" spans="1:8" ht="15.75" thickBot="1">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -5098,7 +5046,7 @@
       <c r="G221" s="1"/>
       <c r="H221" s="1"/>
     </row>
-    <row r="222" spans="1:8" ht="15" thickBot="1">
+    <row r="222" spans="1:8" ht="15.75" thickBot="1">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -5108,7 +5056,7 @@
       <c r="G222" s="1"/>
       <c r="H222" s="1"/>
     </row>
-    <row r="223" spans="1:8" ht="15" thickBot="1">
+    <row r="223" spans="1:8" ht="15.75" thickBot="1">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -5118,7 +5066,7 @@
       <c r="G223" s="1"/>
       <c r="H223" s="1"/>
     </row>
-    <row r="224" spans="1:8" ht="15" thickBot="1">
+    <row r="224" spans="1:8" ht="15.75" thickBot="1">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -5128,7 +5076,7 @@
       <c r="G224" s="1"/>
       <c r="H224" s="1"/>
     </row>
-    <row r="225" spans="1:8" ht="15" thickBot="1">
+    <row r="225" spans="1:8" ht="15.75" thickBot="1">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -5138,7 +5086,7 @@
       <c r="G225" s="1"/>
       <c r="H225" s="1"/>
     </row>
-    <row r="226" spans="1:8" ht="15" thickBot="1">
+    <row r="226" spans="1:8" ht="15.75" thickBot="1">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -5148,7 +5096,7 @@
       <c r="G226" s="1"/>
       <c r="H226" s="1"/>
     </row>
-    <row r="227" spans="1:8" ht="15" thickBot="1">
+    <row r="227" spans="1:8" ht="15.75" thickBot="1">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -5158,7 +5106,7 @@
       <c r="G227" s="1"/>
       <c r="H227" s="1"/>
     </row>
-    <row r="228" spans="1:8" ht="15" thickBot="1">
+    <row r="228" spans="1:8" ht="15.75" thickBot="1">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -5168,7 +5116,7 @@
       <c r="G228" s="1"/>
       <c r="H228" s="1"/>
     </row>
-    <row r="229" spans="1:8" ht="15" thickBot="1">
+    <row r="229" spans="1:8" ht="15.75" thickBot="1">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -5178,7 +5126,7 @@
       <c r="G229" s="1"/>
       <c r="H229" s="1"/>
     </row>
-    <row r="230" spans="1:8" ht="15" thickBot="1">
+    <row r="230" spans="1:8" ht="15.75" thickBot="1">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -5188,7 +5136,7 @@
       <c r="G230" s="1"/>
       <c r="H230" s="1"/>
     </row>
-    <row r="231" spans="1:8" ht="15" thickBot="1">
+    <row r="231" spans="1:8" ht="15.75" thickBot="1">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -5198,7 +5146,7 @@
       <c r="G231" s="1"/>
       <c r="H231" s="1"/>
     </row>
-    <row r="232" spans="1:8" ht="15" thickBot="1">
+    <row r="232" spans="1:8" ht="15.75" thickBot="1">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -5208,7 +5156,7 @@
       <c r="G232" s="1"/>
       <c r="H232" s="1"/>
     </row>
-    <row r="233" spans="1:8" ht="15" thickBot="1">
+    <row r="233" spans="1:8" ht="15.75" thickBot="1">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -5218,7 +5166,7 @@
       <c r="G233" s="1"/>
       <c r="H233" s="1"/>
     </row>
-    <row r="234" spans="1:8" ht="15" thickBot="1">
+    <row r="234" spans="1:8" ht="15.75" thickBot="1">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -5228,7 +5176,7 @@
       <c r="G234" s="1"/>
       <c r="H234" s="1"/>
     </row>
-    <row r="235" spans="1:8" ht="15" thickBot="1">
+    <row r="235" spans="1:8" ht="15.75" thickBot="1">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -5238,7 +5186,7 @@
       <c r="G235" s="1"/>
       <c r="H235" s="1"/>
     </row>
-    <row r="236" spans="1:8" ht="15" thickBot="1">
+    <row r="236" spans="1:8" ht="15.75" thickBot="1">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -5248,7 +5196,7 @@
       <c r="G236" s="1"/>
       <c r="H236" s="1"/>
     </row>
-    <row r="237" spans="1:8" ht="15" thickBot="1">
+    <row r="237" spans="1:8" ht="15.75" thickBot="1">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -5258,7 +5206,7 @@
       <c r="G237" s="1"/>
       <c r="H237" s="1"/>
     </row>
-    <row r="238" spans="1:8" ht="15" thickBot="1">
+    <row r="238" spans="1:8" ht="15.75" thickBot="1">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -5268,7 +5216,7 @@
       <c r="G238" s="1"/>
       <c r="H238" s="1"/>
     </row>
-    <row r="239" spans="1:8" ht="15" thickBot="1">
+    <row r="239" spans="1:8" ht="15.75" thickBot="1">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -5278,7 +5226,7 @@
       <c r="G239" s="1"/>
       <c r="H239" s="1"/>
     </row>
-    <row r="240" spans="1:8" ht="15" thickBot="1">
+    <row r="240" spans="1:8" ht="15.75" thickBot="1">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -5288,7 +5236,7 @@
       <c r="G240" s="1"/>
       <c r="H240" s="1"/>
     </row>
-    <row r="241" spans="1:8" ht="15" thickBot="1">
+    <row r="241" spans="1:8" ht="15.75" thickBot="1">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -5298,7 +5246,7 @@
       <c r="G241" s="1"/>
       <c r="H241" s="1"/>
     </row>
-    <row r="242" spans="1:8" ht="15" thickBot="1">
+    <row r="242" spans="1:8" ht="15.75" thickBot="1">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -5308,7 +5256,7 @@
       <c r="G242" s="1"/>
       <c r="H242" s="1"/>
     </row>
-    <row r="243" spans="1:8" ht="15" thickBot="1">
+    <row r="243" spans="1:8" ht="15.75" thickBot="1">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -5318,7 +5266,7 @@
       <c r="G243" s="1"/>
       <c r="H243" s="1"/>
     </row>
-    <row r="244" spans="1:8" ht="15" thickBot="1">
+    <row r="244" spans="1:8" ht="15.75" thickBot="1">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -5328,7 +5276,7 @@
       <c r="G244" s="1"/>
       <c r="H244" s="1"/>
     </row>
-    <row r="245" spans="1:8" ht="15" thickBot="1">
+    <row r="245" spans="1:8" ht="15.75" thickBot="1">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -5338,7 +5286,7 @@
       <c r="G245" s="1"/>
       <c r="H245" s="1"/>
     </row>
-    <row r="246" spans="1:8" ht="15" thickBot="1">
+    <row r="246" spans="1:8" ht="15.75" thickBot="1">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -5348,7 +5296,7 @@
       <c r="G246" s="1"/>
       <c r="H246" s="1"/>
     </row>
-    <row r="247" spans="1:8" ht="15" thickBot="1">
+    <row r="247" spans="1:8" ht="15.75" thickBot="1">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -5358,7 +5306,7 @@
       <c r="G247" s="1"/>
       <c r="H247" s="1"/>
     </row>
-    <row r="248" spans="1:8" ht="15" thickBot="1">
+    <row r="248" spans="1:8" ht="15.75" thickBot="1">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -5368,7 +5316,7 @@
       <c r="G248" s="1"/>
       <c r="H248" s="1"/>
     </row>
-    <row r="249" spans="1:8" ht="15" thickBot="1">
+    <row r="249" spans="1:8" ht="15.75" thickBot="1">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -5378,7 +5326,7 @@
       <c r="G249" s="1"/>
       <c r="H249" s="1"/>
     </row>
-    <row r="250" spans="1:8" ht="15" thickBot="1">
+    <row r="250" spans="1:8" ht="15.75" thickBot="1">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -5388,7 +5336,7 @@
       <c r="G250" s="1"/>
       <c r="H250" s="1"/>
     </row>
-    <row r="251" spans="1:8" ht="15" thickBot="1">
+    <row r="251" spans="1:8" ht="15.75" thickBot="1">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -5398,7 +5346,7 @@
       <c r="G251" s="1"/>
       <c r="H251" s="1"/>
     </row>
-    <row r="252" spans="1:8" ht="15" thickBot="1">
+    <row r="252" spans="1:8" ht="15.75" thickBot="1">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -5408,7 +5356,7 @@
       <c r="G252" s="1"/>
       <c r="H252" s="1"/>
     </row>
-    <row r="253" spans="1:8" ht="15" thickBot="1">
+    <row r="253" spans="1:8" ht="15.75" thickBot="1">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -5418,7 +5366,7 @@
       <c r="G253" s="1"/>
       <c r="H253" s="1"/>
     </row>
-    <row r="254" spans="1:8" ht="15" thickBot="1">
+    <row r="254" spans="1:8" ht="15.75" thickBot="1">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -5428,7 +5376,7 @@
       <c r="G254" s="1"/>
       <c r="H254" s="1"/>
     </row>
-    <row r="255" spans="1:8" ht="15" thickBot="1">
+    <row r="255" spans="1:8" ht="15.75" thickBot="1">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -5438,7 +5386,7 @@
       <c r="G255" s="1"/>
       <c r="H255" s="1"/>
     </row>
-    <row r="256" spans="1:8" ht="15" thickBot="1">
+    <row r="256" spans="1:8" ht="15.75" thickBot="1">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -5448,7 +5396,7 @@
       <c r="G256" s="1"/>
       <c r="H256" s="1"/>
     </row>
-    <row r="257" spans="1:8" ht="15" thickBot="1">
+    <row r="257" spans="1:8" ht="15.75" thickBot="1">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -5458,7 +5406,7 @@
       <c r="G257" s="1"/>
       <c r="H257" s="1"/>
     </row>
-    <row r="258" spans="1:8" ht="15" thickBot="1">
+    <row r="258" spans="1:8" ht="15.75" thickBot="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -5468,7 +5416,7 @@
       <c r="G258" s="1"/>
       <c r="H258" s="1"/>
     </row>
-    <row r="259" spans="1:8" ht="15" thickBot="1">
+    <row r="259" spans="1:8" ht="15.75" thickBot="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -5478,7 +5426,7 @@
       <c r="G259" s="1"/>
       <c r="H259" s="1"/>
     </row>
-    <row r="260" spans="1:8" ht="15" thickBot="1">
+    <row r="260" spans="1:8" ht="15.75" thickBot="1">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -5488,7 +5436,7 @@
       <c r="G260" s="1"/>
       <c r="H260" s="1"/>
     </row>
-    <row r="261" spans="1:8" ht="15" thickBot="1">
+    <row r="261" spans="1:8" ht="15.75" thickBot="1">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -5498,7 +5446,7 @@
       <c r="G261" s="1"/>
       <c r="H261" s="1"/>
     </row>
-    <row r="262" spans="1:8" ht="15" thickBot="1">
+    <row r="262" spans="1:8" ht="15.75" thickBot="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -5508,7 +5456,7 @@
       <c r="G262" s="1"/>
       <c r="H262" s="1"/>
     </row>
-    <row r="263" spans="1:8" ht="15" thickBot="1">
+    <row r="263" spans="1:8" ht="15.75" thickBot="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -5518,7 +5466,7 @@
       <c r="G263" s="1"/>
       <c r="H263" s="1"/>
     </row>
-    <row r="264" spans="1:8" ht="15" thickBot="1">
+    <row r="264" spans="1:8" ht="15.75" thickBot="1">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -5528,7 +5476,7 @@
       <c r="G264" s="1"/>
       <c r="H264" s="1"/>
     </row>
-    <row r="265" spans="1:8" ht="15" thickBot="1">
+    <row r="265" spans="1:8" ht="15.75" thickBot="1">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -5538,7 +5486,7 @@
       <c r="G265" s="1"/>
       <c r="H265" s="1"/>
     </row>
-    <row r="266" spans="1:8" ht="15" thickBot="1">
+    <row r="266" spans="1:8" ht="15.75" thickBot="1">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -5548,7 +5496,7 @@
       <c r="G266" s="1"/>
       <c r="H266" s="1"/>
     </row>
-    <row r="267" spans="1:8" ht="15" thickBot="1">
+    <row r="267" spans="1:8" ht="15.75" thickBot="1">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -5558,7 +5506,7 @@
       <c r="G267" s="1"/>
       <c r="H267" s="1"/>
     </row>
-    <row r="268" spans="1:8" ht="15" thickBot="1">
+    <row r="268" spans="1:8" ht="15.75" thickBot="1">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -5568,7 +5516,7 @@
       <c r="G268" s="1"/>
       <c r="H268" s="1"/>
     </row>
-    <row r="269" spans="1:8" ht="15" thickBot="1">
+    <row r="269" spans="1:8" ht="15.75" thickBot="1">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -5578,7 +5526,7 @@
       <c r="G269" s="1"/>
       <c r="H269" s="1"/>
     </row>
-    <row r="270" spans="1:8" ht="15" thickBot="1">
+    <row r="270" spans="1:8" ht="15.75" thickBot="1">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -5588,7 +5536,7 @@
       <c r="G270" s="1"/>
       <c r="H270" s="1"/>
     </row>
-    <row r="271" spans="1:8" ht="15" thickBot="1">
+    <row r="271" spans="1:8" ht="15.75" thickBot="1">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -5598,7 +5546,7 @@
       <c r="G271" s="1"/>
       <c r="H271" s="1"/>
     </row>
-    <row r="272" spans="1:8" ht="15" thickBot="1">
+    <row r="272" spans="1:8" ht="15.75" thickBot="1">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -5608,7 +5556,7 @@
       <c r="G272" s="1"/>
       <c r="H272" s="1"/>
     </row>
-    <row r="273" spans="1:8" ht="15" thickBot="1">
+    <row r="273" spans="1:8" ht="15.75" thickBot="1">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -5618,7 +5566,7 @@
       <c r="G273" s="1"/>
       <c r="H273" s="1"/>
     </row>
-    <row r="274" spans="1:8" ht="15" thickBot="1">
+    <row r="274" spans="1:8" ht="15.75" thickBot="1">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -5628,7 +5576,7 @@
       <c r="G274" s="1"/>
       <c r="H274" s="1"/>
     </row>
-    <row r="275" spans="1:8" ht="15" thickBot="1">
+    <row r="275" spans="1:8" ht="15.75" thickBot="1">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -5638,7 +5586,7 @@
       <c r="G275" s="1"/>
       <c r="H275" s="1"/>
     </row>
-    <row r="276" spans="1:8" ht="15" thickBot="1">
+    <row r="276" spans="1:8" ht="15.75" thickBot="1">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -5648,7 +5596,7 @@
       <c r="G276" s="1"/>
       <c r="H276" s="1"/>
     </row>
-    <row r="277" spans="1:8" ht="15" thickBot="1">
+    <row r="277" spans="1:8" ht="15.75" thickBot="1">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -5658,7 +5606,7 @@
       <c r="G277" s="1"/>
       <c r="H277" s="1"/>
     </row>
-    <row r="278" spans="1:8" ht="15" thickBot="1">
+    <row r="278" spans="1:8" ht="15.75" thickBot="1">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -5668,7 +5616,7 @@
       <c r="G278" s="1"/>
       <c r="H278" s="1"/>
     </row>
-    <row r="279" spans="1:8" ht="15" thickBot="1">
+    <row r="279" spans="1:8" ht="15.75" thickBot="1">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -5678,7 +5626,7 @@
       <c r="G279" s="1"/>
       <c r="H279" s="1"/>
     </row>
-    <row r="280" spans="1:8" ht="15" thickBot="1">
+    <row r="280" spans="1:8" ht="15.75" thickBot="1">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -5688,7 +5636,7 @@
       <c r="G280" s="1"/>
       <c r="H280" s="1"/>
     </row>
-    <row r="281" spans="1:8" ht="15" thickBot="1">
+    <row r="281" spans="1:8" ht="15.75" thickBot="1">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -5698,7 +5646,7 @@
       <c r="G281" s="1"/>
       <c r="H281" s="1"/>
     </row>
-    <row r="282" spans="1:8" ht="15" thickBot="1">
+    <row r="282" spans="1:8" ht="15.75" thickBot="1">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -5708,7 +5656,7 @@
       <c r="G282" s="1"/>
       <c r="H282" s="1"/>
     </row>
-    <row r="283" spans="1:8" ht="15" thickBot="1">
+    <row r="283" spans="1:8" ht="15.75" thickBot="1">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -5718,7 +5666,7 @@
       <c r="G283" s="1"/>
       <c r="H283" s="1"/>
     </row>
-    <row r="284" spans="1:8" ht="15" thickBot="1">
+    <row r="284" spans="1:8" ht="15.75" thickBot="1">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -5728,7 +5676,7 @@
       <c r="G284" s="1"/>
       <c r="H284" s="1"/>
     </row>
-    <row r="285" spans="1:8" ht="15" thickBot="1">
+    <row r="285" spans="1:8" ht="15.75" thickBot="1">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -5738,7 +5686,7 @@
       <c r="G285" s="1"/>
       <c r="H285" s="1"/>
     </row>
-    <row r="286" spans="1:8" ht="15" thickBot="1">
+    <row r="286" spans="1:8" ht="15.75" thickBot="1">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -5748,7 +5696,7 @@
       <c r="G286" s="1"/>
       <c r="H286" s="1"/>
     </row>
-    <row r="287" spans="1:8" ht="15" thickBot="1">
+    <row r="287" spans="1:8" ht="15.75" thickBot="1">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -5758,7 +5706,7 @@
       <c r="G287" s="1"/>
       <c r="H287" s="1"/>
     </row>
-    <row r="288" spans="1:8" ht="15" thickBot="1">
+    <row r="288" spans="1:8" ht="15.75" thickBot="1">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -5768,7 +5716,7 @@
       <c r="G288" s="1"/>
       <c r="H288" s="1"/>
     </row>
-    <row r="289" spans="1:8" ht="15" thickBot="1">
+    <row r="289" spans="1:8" ht="15.75" thickBot="1">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -5778,7 +5726,7 @@
       <c r="G289" s="1"/>
       <c r="H289" s="1"/>
     </row>
-    <row r="290" spans="1:8" ht="15" thickBot="1">
+    <row r="290" spans="1:8" ht="15.75" thickBot="1">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -5788,7 +5736,7 @@
       <c r="G290" s="1"/>
       <c r="H290" s="1"/>
     </row>
-    <row r="291" spans="1:8" ht="15" thickBot="1">
+    <row r="291" spans="1:8" ht="15.75" thickBot="1">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -5798,7 +5746,7 @@
       <c r="G291" s="1"/>
       <c r="H291" s="1"/>
     </row>
-    <row r="292" spans="1:8" ht="15" thickBot="1">
+    <row r="292" spans="1:8" ht="15.75" thickBot="1">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -5808,7 +5756,7 @@
       <c r="G292" s="1"/>
       <c r="H292" s="1"/>
     </row>
-    <row r="293" spans="1:8" ht="15" thickBot="1">
+    <row r="293" spans="1:8" ht="15.75" thickBot="1">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -5818,7 +5766,7 @@
       <c r="G293" s="1"/>
       <c r="H293" s="1"/>
     </row>
-    <row r="294" spans="1:8" ht="15" thickBot="1">
+    <row r="294" spans="1:8" ht="15.75" thickBot="1">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -5828,7 +5776,7 @@
       <c r="G294" s="1"/>
       <c r="H294" s="1"/>
     </row>
-    <row r="295" spans="1:8" ht="15" thickBot="1">
+    <row r="295" spans="1:8" ht="15.75" thickBot="1">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -5838,7 +5786,7 @@
       <c r="G295" s="1"/>
       <c r="H295" s="1"/>
     </row>
-    <row r="296" spans="1:8" ht="15" thickBot="1">
+    <row r="296" spans="1:8" ht="15.75" thickBot="1">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -5848,7 +5796,7 @@
       <c r="G296" s="1"/>
       <c r="H296" s="1"/>
     </row>
-    <row r="297" spans="1:8" ht="15" thickBot="1">
+    <row r="297" spans="1:8" ht="15.75" thickBot="1">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -5858,7 +5806,7 @@
       <c r="G297" s="1"/>
       <c r="H297" s="1"/>
     </row>
-    <row r="298" spans="1:8" ht="15" thickBot="1">
+    <row r="298" spans="1:8" ht="15.75" thickBot="1">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -5868,7 +5816,7 @@
       <c r="G298" s="1"/>
       <c r="H298" s="1"/>
     </row>
-    <row r="299" spans="1:8" ht="15" thickBot="1">
+    <row r="299" spans="1:8" ht="15.75" thickBot="1">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -5878,7 +5826,7 @@
       <c r="G299" s="1"/>
       <c r="H299" s="1"/>
     </row>
-    <row r="300" spans="1:8" ht="15" thickBot="1">
+    <row r="300" spans="1:8" ht="15.75" thickBot="1">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -5888,7 +5836,7 @@
       <c r="G300" s="1"/>
       <c r="H300" s="1"/>
     </row>
-    <row r="301" spans="1:8" ht="15" thickBot="1">
+    <row r="301" spans="1:8" ht="15.75" thickBot="1">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -5898,7 +5846,7 @@
       <c r="G301" s="1"/>
       <c r="H301" s="1"/>
     </row>
-    <row r="302" spans="1:8" ht="15" thickBot="1">
+    <row r="302" spans="1:8" ht="15.75" thickBot="1">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -5908,7 +5856,7 @@
       <c r="G302" s="1"/>
       <c r="H302" s="1"/>
     </row>
-    <row r="303" spans="1:8" ht="15" thickBot="1">
+    <row r="303" spans="1:8" ht="15.75" thickBot="1">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -5918,7 +5866,7 @@
       <c r="G303" s="1"/>
       <c r="H303" s="1"/>
     </row>
-    <row r="304" spans="1:8" ht="15" thickBot="1">
+    <row r="304" spans="1:8" ht="15.75" thickBot="1">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -5928,7 +5876,7 @@
       <c r="G304" s="1"/>
       <c r="H304" s="1"/>
     </row>
-    <row r="305" spans="1:8" ht="15" thickBot="1">
+    <row r="305" spans="1:8" ht="15.75" thickBot="1">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -5938,7 +5886,7 @@
       <c r="G305" s="1"/>
       <c r="H305" s="1"/>
     </row>
-    <row r="306" spans="1:8" ht="15" thickBot="1">
+    <row r="306" spans="1:8" ht="15.75" thickBot="1">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -5948,7 +5896,7 @@
       <c r="G306" s="1"/>
       <c r="H306" s="1"/>
     </row>
-    <row r="307" spans="1:8" ht="15" thickBot="1">
+    <row r="307" spans="1:8" ht="15.75" thickBot="1">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -5958,7 +5906,7 @@
       <c r="G307" s="1"/>
       <c r="H307" s="1"/>
     </row>
-    <row r="308" spans="1:8" ht="15" thickBot="1">
+    <row r="308" spans="1:8" ht="15.75" thickBot="1">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -5968,7 +5916,7 @@
       <c r="G308" s="1"/>
       <c r="H308" s="1"/>
     </row>
-    <row r="309" spans="1:8" ht="15" thickBot="1">
+    <row r="309" spans="1:8" ht="15.75" thickBot="1">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -5978,7 +5926,7 @@
       <c r="G309" s="1"/>
       <c r="H309" s="1"/>
     </row>
-    <row r="310" spans="1:8" ht="15" thickBot="1">
+    <row r="310" spans="1:8" ht="15.75" thickBot="1">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -5988,7 +5936,7 @@
       <c r="G310" s="1"/>
       <c r="H310" s="1"/>
     </row>
-    <row r="311" spans="1:8" ht="15" thickBot="1">
+    <row r="311" spans="1:8" ht="15.75" thickBot="1">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -5998,7 +5946,7 @@
       <c r="G311" s="1"/>
       <c r="H311" s="1"/>
     </row>
-    <row r="312" spans="1:8" ht="15" thickBot="1">
+    <row r="312" spans="1:8" ht="15.75" thickBot="1">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -6008,7 +5956,7 @@
       <c r="G312" s="1"/>
       <c r="H312" s="1"/>
     </row>
-    <row r="313" spans="1:8" ht="15" thickBot="1">
+    <row r="313" spans="1:8" ht="15.75" thickBot="1">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -6018,7 +5966,7 @@
       <c r="G313" s="1"/>
       <c r="H313" s="1"/>
     </row>
-    <row r="314" spans="1:8" ht="15" thickBot="1">
+    <row r="314" spans="1:8" ht="15.75" thickBot="1">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -6028,7 +5976,7 @@
       <c r="G314" s="1"/>
       <c r="H314" s="1"/>
     </row>
-    <row r="315" spans="1:8" ht="15" thickBot="1">
+    <row r="315" spans="1:8" ht="15.75" thickBot="1">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -6038,7 +5986,7 @@
       <c r="G315" s="1"/>
       <c r="H315" s="1"/>
     </row>
-    <row r="316" spans="1:8" ht="15" thickBot="1">
+    <row r="316" spans="1:8" ht="15.75" thickBot="1">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -6048,7 +5996,7 @@
       <c r="G316" s="1"/>
       <c r="H316" s="1"/>
     </row>
-    <row r="317" spans="1:8" ht="15" thickBot="1">
+    <row r="317" spans="1:8" ht="15.75" thickBot="1">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -6058,7 +6006,7 @@
       <c r="G317" s="1"/>
       <c r="H317" s="1"/>
     </row>
-    <row r="318" spans="1:8" ht="15" thickBot="1">
+    <row r="318" spans="1:8" ht="15.75" thickBot="1">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -6068,7 +6016,7 @@
       <c r="G318" s="1"/>
       <c r="H318" s="1"/>
     </row>
-    <row r="319" spans="1:8" ht="15" thickBot="1">
+    <row r="319" spans="1:8" ht="15.75" thickBot="1">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -6078,7 +6026,7 @@
       <c r="G319" s="1"/>
       <c r="H319" s="1"/>
     </row>
-    <row r="320" spans="1:8" ht="15" thickBot="1">
+    <row r="320" spans="1:8" ht="15.75" thickBot="1">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -6088,7 +6036,7 @@
       <c r="G320" s="1"/>
       <c r="H320" s="1"/>
     </row>
-    <row r="321" spans="1:8" ht="15" thickBot="1">
+    <row r="321" spans="1:8" ht="15.75" thickBot="1">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -6098,7 +6046,7 @@
       <c r="G321" s="1"/>
       <c r="H321" s="1"/>
     </row>
-    <row r="322" spans="1:8" ht="15" thickBot="1">
+    <row r="322" spans="1:8" ht="15.75" thickBot="1">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -6108,7 +6056,7 @@
       <c r="G322" s="1"/>
       <c r="H322" s="1"/>
     </row>
-    <row r="323" spans="1:8" ht="15" thickBot="1">
+    <row r="323" spans="1:8" ht="15.75" thickBot="1">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -6118,7 +6066,7 @@
       <c r="G323" s="1"/>
       <c r="H323" s="1"/>
     </row>
-    <row r="324" spans="1:8" ht="15" thickBot="1">
+    <row r="324" spans="1:8" ht="15.75" thickBot="1">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -6128,7 +6076,7 @@
       <c r="G324" s="1"/>
       <c r="H324" s="1"/>
     </row>
-    <row r="325" spans="1:8" ht="15" thickBot="1">
+    <row r="325" spans="1:8" ht="15.75" thickBot="1">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -6138,7 +6086,7 @@
       <c r="G325" s="1"/>
       <c r="H325" s="1"/>
     </row>
-    <row r="326" spans="1:8" ht="15" thickBot="1">
+    <row r="326" spans="1:8" ht="15.75" thickBot="1">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -6148,7 +6096,7 @@
       <c r="G326" s="1"/>
       <c r="H326" s="1"/>
     </row>
-    <row r="327" spans="1:8" ht="15" thickBot="1">
+    <row r="327" spans="1:8" ht="15.75" thickBot="1">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -6158,7 +6106,7 @@
       <c r="G327" s="1"/>
       <c r="H327" s="1"/>
     </row>
-    <row r="328" spans="1:8" ht="15" thickBot="1">
+    <row r="328" spans="1:8" ht="15.75" thickBot="1">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -6168,7 +6116,7 @@
       <c r="G328" s="1"/>
       <c r="H328" s="1"/>
     </row>
-    <row r="329" spans="1:8" ht="15" thickBot="1">
+    <row r="329" spans="1:8" ht="15.75" thickBot="1">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -6178,7 +6126,7 @@
       <c r="G329" s="1"/>
       <c r="H329" s="1"/>
     </row>
-    <row r="330" spans="1:8" ht="15" thickBot="1">
+    <row r="330" spans="1:8" ht="15.75" thickBot="1">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -6188,7 +6136,7 @@
       <c r="G330" s="1"/>
       <c r="H330" s="1"/>
     </row>
-    <row r="331" spans="1:8" ht="15" thickBot="1">
+    <row r="331" spans="1:8" ht="15.75" thickBot="1">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -6198,7 +6146,7 @@
       <c r="G331" s="1"/>
       <c r="H331" s="1"/>
     </row>
-    <row r="332" spans="1:8" ht="15" thickBot="1">
+    <row r="332" spans="1:8" ht="15.75" thickBot="1">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -6208,7 +6156,7 @@
       <c r="G332" s="1"/>
       <c r="H332" s="1"/>
     </row>
-    <row r="333" spans="1:8" ht="15" thickBot="1">
+    <row r="333" spans="1:8" ht="15.75" thickBot="1">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -6218,7 +6166,7 @@
       <c r="G333" s="1"/>
       <c r="H333" s="1"/>
     </row>
-    <row r="334" spans="1:8" ht="15" thickBot="1">
+    <row r="334" spans="1:8" ht="15.75" thickBot="1">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -6228,7 +6176,7 @@
       <c r="G334" s="1"/>
       <c r="H334" s="1"/>
     </row>
-    <row r="335" spans="1:8" ht="15" thickBot="1">
+    <row r="335" spans="1:8" ht="15.75" thickBot="1">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -6238,7 +6186,7 @@
       <c r="G335" s="1"/>
       <c r="H335" s="1"/>
     </row>
-    <row r="336" spans="1:8" ht="15" thickBot="1">
+    <row r="336" spans="1:8" ht="15.75" thickBot="1">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -6248,7 +6196,7 @@
       <c r="G336" s="1"/>
       <c r="H336" s="1"/>
     </row>
-    <row r="337" spans="1:8" ht="15" thickBot="1">
+    <row r="337" spans="1:8" ht="15.75" thickBot="1">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -6258,7 +6206,7 @@
       <c r="G337" s="1"/>
       <c r="H337" s="1"/>
     </row>
-    <row r="338" spans="1:8" ht="15" thickBot="1">
+    <row r="338" spans="1:8" ht="15.75" thickBot="1">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -6268,7 +6216,7 @@
       <c r="G338" s="1"/>
       <c r="H338" s="1"/>
     </row>
-    <row r="339" spans="1:8" ht="15" thickBot="1">
+    <row r="339" spans="1:8" ht="15.75" thickBot="1">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -6278,7 +6226,7 @@
       <c r="G339" s="1"/>
       <c r="H339" s="1"/>
     </row>
-    <row r="340" spans="1:8" ht="15" thickBot="1">
+    <row r="340" spans="1:8" ht="15.75" thickBot="1">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -6288,7 +6236,7 @@
       <c r="G340" s="1"/>
       <c r="H340" s="1"/>
     </row>
-    <row r="341" spans="1:8" ht="15" thickBot="1">
+    <row r="341" spans="1:8" ht="15.75" thickBot="1">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -6298,7 +6246,7 @@
       <c r="G341" s="1"/>
       <c r="H341" s="1"/>
     </row>
-    <row r="342" spans="1:8" ht="15" thickBot="1">
+    <row r="342" spans="1:8" ht="15.75" thickBot="1">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -6308,7 +6256,7 @@
       <c r="G342" s="1"/>
       <c r="H342" s="1"/>
     </row>
-    <row r="343" spans="1:8" ht="15" thickBot="1">
+    <row r="343" spans="1:8" ht="15.75" thickBot="1">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -6318,7 +6266,7 @@
       <c r="G343" s="1"/>
       <c r="H343" s="1"/>
     </row>
-    <row r="344" spans="1:8" ht="15" thickBot="1">
+    <row r="344" spans="1:8" ht="15.75" thickBot="1">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -6328,7 +6276,7 @@
       <c r="G344" s="1"/>
       <c r="H344" s="1"/>
     </row>
-    <row r="345" spans="1:8" ht="15" thickBot="1">
+    <row r="345" spans="1:8" ht="15.75" thickBot="1">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -6338,7 +6286,7 @@
       <c r="G345" s="1"/>
       <c r="H345" s="1"/>
     </row>
-    <row r="346" spans="1:8" ht="15" thickBot="1">
+    <row r="346" spans="1:8" ht="15.75" thickBot="1">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -6348,7 +6296,7 @@
       <c r="G346" s="1"/>
       <c r="H346" s="1"/>
     </row>
-    <row r="347" spans="1:8" ht="15" thickBot="1">
+    <row r="347" spans="1:8" ht="15.75" thickBot="1">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -6358,7 +6306,7 @@
       <c r="G347" s="1"/>
       <c r="H347" s="1"/>
     </row>
-    <row r="348" spans="1:8" ht="15" thickBot="1">
+    <row r="348" spans="1:8" ht="15.75" thickBot="1">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -6368,7 +6316,7 @@
       <c r="G348" s="1"/>
       <c r="H348" s="1"/>
     </row>
-    <row r="349" spans="1:8" ht="15" thickBot="1">
+    <row r="349" spans="1:8" ht="15.75" thickBot="1">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -6378,7 +6326,7 @@
       <c r="G349" s="1"/>
       <c r="H349" s="1"/>
     </row>
-    <row r="350" spans="1:8" ht="15" thickBot="1">
+    <row r="350" spans="1:8" ht="15.75" thickBot="1">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -6388,7 +6336,7 @@
       <c r="G350" s="1"/>
       <c r="H350" s="1"/>
     </row>
-    <row r="351" spans="1:8" ht="15" thickBot="1">
+    <row r="351" spans="1:8" ht="15.75" thickBot="1">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -6398,7 +6346,7 @@
       <c r="G351" s="1"/>
       <c r="H351" s="1"/>
     </row>
-    <row r="352" spans="1:8" ht="15" thickBot="1">
+    <row r="352" spans="1:8" ht="15.75" thickBot="1">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -6408,7 +6356,7 @@
       <c r="G352" s="1"/>
       <c r="H352" s="1"/>
     </row>
-    <row r="353" spans="1:8" ht="15" thickBot="1">
+    <row r="353" spans="1:8" ht="15.75" thickBot="1">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -6418,7 +6366,7 @@
       <c r="G353" s="1"/>
       <c r="H353" s="1"/>
     </row>
-    <row r="354" spans="1:8" ht="15" thickBot="1">
+    <row r="354" spans="1:8" ht="15.75" thickBot="1">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -6428,7 +6376,7 @@
       <c r="G354" s="1"/>
       <c r="H354" s="1"/>
     </row>
-    <row r="355" spans="1:8" ht="15" thickBot="1">
+    <row r="355" spans="1:8" ht="15.75" thickBot="1">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -6438,7 +6386,7 @@
       <c r="G355" s="1"/>
       <c r="H355" s="1"/>
     </row>
-    <row r="356" spans="1:8" ht="15" thickBot="1">
+    <row r="356" spans="1:8" ht="15.75" thickBot="1">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -6448,7 +6396,7 @@
       <c r="G356" s="1"/>
       <c r="H356" s="1"/>
     </row>
-    <row r="357" spans="1:8" ht="15" thickBot="1">
+    <row r="357" spans="1:8" ht="15.75" thickBot="1">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -6458,7 +6406,7 @@
       <c r="G357" s="1"/>
       <c r="H357" s="1"/>
     </row>
-    <row r="358" spans="1:8" ht="15" thickBot="1">
+    <row r="358" spans="1:8" ht="15.75" thickBot="1">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -6468,7 +6416,7 @@
       <c r="G358" s="1"/>
       <c r="H358" s="1"/>
     </row>
-    <row r="359" spans="1:8" ht="15" thickBot="1">
+    <row r="359" spans="1:8" ht="15.75" thickBot="1">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -6478,7 +6426,7 @@
       <c r="G359" s="1"/>
       <c r="H359" s="1"/>
     </row>
-    <row r="360" spans="1:8" ht="15" thickBot="1">
+    <row r="360" spans="1:8" ht="15.75" thickBot="1">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -6488,7 +6436,7 @@
       <c r="G360" s="1"/>
       <c r="H360" s="1"/>
     </row>
-    <row r="361" spans="1:8" ht="15" thickBot="1">
+    <row r="361" spans="1:8" ht="15.75" thickBot="1">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -6498,7 +6446,7 @@
       <c r="G361" s="1"/>
       <c r="H361" s="1"/>
     </row>
-    <row r="362" spans="1:8" ht="15" thickBot="1">
+    <row r="362" spans="1:8" ht="15.75" thickBot="1">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -6508,7 +6456,7 @@
       <c r="G362" s="1"/>
       <c r="H362" s="1"/>
     </row>
-    <row r="363" spans="1:8" ht="15" thickBot="1">
+    <row r="363" spans="1:8" ht="15.75" thickBot="1">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -6518,7 +6466,7 @@
       <c r="G363" s="1"/>
       <c r="H363" s="1"/>
     </row>
-    <row r="364" spans="1:8" ht="15" thickBot="1">
+    <row r="364" spans="1:8" ht="15.75" thickBot="1">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -6528,7 +6476,7 @@
       <c r="G364" s="1"/>
       <c r="H364" s="1"/>
     </row>
-    <row r="365" spans="1:8" ht="15" thickBot="1">
+    <row r="365" spans="1:8" ht="15.75" thickBot="1">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -6538,7 +6486,7 @@
       <c r="G365" s="1"/>
       <c r="H365" s="1"/>
     </row>
-    <row r="366" spans="1:8" ht="15" thickBot="1">
+    <row r="366" spans="1:8" ht="15.75" thickBot="1">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -6548,7 +6496,7 @@
       <c r="G366" s="1"/>
       <c r="H366" s="1"/>
     </row>
-    <row r="367" spans="1:8" ht="15" thickBot="1">
+    <row r="367" spans="1:8" ht="15.75" thickBot="1">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -6558,7 +6506,7 @@
       <c r="G367" s="1"/>
       <c r="H367" s="1"/>
     </row>
-    <row r="368" spans="1:8" ht="15" thickBot="1">
+    <row r="368" spans="1:8" ht="15.75" thickBot="1">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -6568,7 +6516,7 @@
       <c r="G368" s="1"/>
       <c r="H368" s="1"/>
     </row>
-    <row r="369" spans="1:8" ht="15" thickBot="1">
+    <row r="369" spans="1:8" ht="15.75" thickBot="1">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -6578,7 +6526,7 @@
       <c r="G369" s="1"/>
       <c r="H369" s="1"/>
     </row>
-    <row r="370" spans="1:8" ht="15" thickBot="1">
+    <row r="370" spans="1:8" ht="15.75" thickBot="1">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -6588,7 +6536,7 @@
       <c r="G370" s="1"/>
       <c r="H370" s="1"/>
     </row>
-    <row r="371" spans="1:8" ht="15" thickBot="1">
+    <row r="371" spans="1:8" ht="15.75" thickBot="1">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -6598,7 +6546,7 @@
       <c r="G371" s="1"/>
       <c r="H371" s="1"/>
     </row>
-    <row r="372" spans="1:8" ht="15" thickBot="1">
+    <row r="372" spans="1:8" ht="15.75" thickBot="1">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -6608,7 +6556,7 @@
       <c r="G372" s="1"/>
       <c r="H372" s="1"/>
     </row>
-    <row r="373" spans="1:8" ht="15" thickBot="1">
+    <row r="373" spans="1:8" ht="15.75" thickBot="1">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -6618,7 +6566,7 @@
       <c r="G373" s="1"/>
       <c r="H373" s="1"/>
     </row>
-    <row r="374" spans="1:8" ht="15" thickBot="1">
+    <row r="374" spans="1:8" ht="15.75" thickBot="1">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -6628,7 +6576,7 @@
       <c r="G374" s="1"/>
       <c r="H374" s="1"/>
     </row>
-    <row r="375" spans="1:8" ht="15" thickBot="1">
+    <row r="375" spans="1:8" ht="15.75" thickBot="1">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -6638,7 +6586,7 @@
       <c r="G375" s="1"/>
       <c r="H375" s="1"/>
     </row>
-    <row r="376" spans="1:8" ht="15" thickBot="1">
+    <row r="376" spans="1:8" ht="15.75" thickBot="1">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -6648,7 +6596,7 @@
       <c r="G376" s="1"/>
       <c r="H376" s="1"/>
     </row>
-    <row r="377" spans="1:8" ht="15" thickBot="1">
+    <row r="377" spans="1:8" ht="15.75" thickBot="1">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -6658,7 +6606,7 @@
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
     </row>
-    <row r="378" spans="1:8" ht="15" thickBot="1">
+    <row r="378" spans="1:8" ht="15.75" thickBot="1">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -6668,7 +6616,7 @@
       <c r="G378" s="1"/>
       <c r="H378" s="1"/>
     </row>
-    <row r="379" spans="1:8" ht="15" thickBot="1">
+    <row r="379" spans="1:8" ht="15.75" thickBot="1">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -6678,7 +6626,7 @@
       <c r="G379" s="1"/>
       <c r="H379" s="1"/>
     </row>
-    <row r="380" spans="1:8" ht="15" thickBot="1">
+    <row r="380" spans="1:8" ht="15.75" thickBot="1">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -6688,7 +6636,7 @@
       <c r="G380" s="1"/>
       <c r="H380" s="1"/>
     </row>
-    <row r="381" spans="1:8" ht="15" thickBot="1">
+    <row r="381" spans="1:8" ht="15.75" thickBot="1">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -6698,7 +6646,7 @@
       <c r="G381" s="1"/>
       <c r="H381" s="1"/>
     </row>
-    <row r="382" spans="1:8" ht="15" thickBot="1">
+    <row r="382" spans="1:8" ht="15.75" thickBot="1">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -6708,7 +6656,7 @@
       <c r="G382" s="1"/>
       <c r="H382" s="1"/>
     </row>
-    <row r="383" spans="1:8" ht="15" thickBot="1">
+    <row r="383" spans="1:8" ht="15.75" thickBot="1">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -6718,7 +6666,7 @@
       <c r="G383" s="1"/>
       <c r="H383" s="1"/>
     </row>
-    <row r="384" spans="1:8" ht="15" thickBot="1">
+    <row r="384" spans="1:8" ht="15.75" thickBot="1">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -6728,7 +6676,7 @@
       <c r="G384" s="1"/>
       <c r="H384" s="1"/>
     </row>
-    <row r="385" spans="1:8" ht="15" thickBot="1">
+    <row r="385" spans="1:8" ht="15.75" thickBot="1">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -6738,7 +6686,7 @@
       <c r="G385" s="1"/>
       <c r="H385" s="1"/>
     </row>
-    <row r="386" spans="1:8" ht="15" thickBot="1">
+    <row r="386" spans="1:8" ht="15.75" thickBot="1">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -6748,7 +6696,7 @@
       <c r="G386" s="1"/>
       <c r="H386" s="1"/>
     </row>
-    <row r="387" spans="1:8" ht="15" thickBot="1">
+    <row r="387" spans="1:8" ht="15.75" thickBot="1">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -6758,7 +6706,7 @@
       <c r="G387" s="1"/>
       <c r="H387" s="1"/>
     </row>
-    <row r="388" spans="1:8" ht="15" thickBot="1">
+    <row r="388" spans="1:8" ht="15.75" thickBot="1">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -6768,7 +6716,7 @@
       <c r="G388" s="1"/>
       <c r="H388" s="1"/>
     </row>
-    <row r="389" spans="1:8" ht="15" thickBot="1">
+    <row r="389" spans="1:8" ht="15.75" thickBot="1">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -6778,7 +6726,7 @@
       <c r="G389" s="1"/>
       <c r="H389" s="1"/>
     </row>
-    <row r="390" spans="1:8" ht="15" thickBot="1">
+    <row r="390" spans="1:8" ht="15.75" thickBot="1">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -6788,7 +6736,7 @@
       <c r="G390" s="1"/>
       <c r="H390" s="1"/>
     </row>
-    <row r="391" spans="1:8" ht="15" thickBot="1">
+    <row r="391" spans="1:8" ht="15.75" thickBot="1">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -6798,7 +6746,7 @@
       <c r="G391" s="1"/>
       <c r="H391" s="1"/>
     </row>
-    <row r="392" spans="1:8" ht="15" thickBot="1">
+    <row r="392" spans="1:8" ht="15.75" thickBot="1">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -6808,7 +6756,7 @@
       <c r="G392" s="1"/>
       <c r="H392" s="1"/>
     </row>
-    <row r="393" spans="1:8" ht="15" thickBot="1">
+    <row r="393" spans="1:8" ht="15.75" thickBot="1">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -6818,7 +6766,7 @@
       <c r="G393" s="1"/>
       <c r="H393" s="1"/>
     </row>
-    <row r="394" spans="1:8" ht="15" thickBot="1">
+    <row r="394" spans="1:8" ht="15.75" thickBot="1">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -6828,7 +6776,7 @@
       <c r="G394" s="1"/>
       <c r="H394" s="1"/>
     </row>
-    <row r="395" spans="1:8" ht="15" thickBot="1">
+    <row r="395" spans="1:8" ht="15.75" thickBot="1">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -6838,7 +6786,7 @@
       <c r="G395" s="1"/>
       <c r="H395" s="1"/>
     </row>
-    <row r="396" spans="1:8" ht="15" thickBot="1">
+    <row r="396" spans="1:8" ht="15.75" thickBot="1">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -6848,7 +6796,7 @@
       <c r="G396" s="1"/>
       <c r="H396" s="1"/>
     </row>
-    <row r="397" spans="1:8" ht="15" thickBot="1">
+    <row r="397" spans="1:8" ht="15.75" thickBot="1">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -6858,7 +6806,7 @@
       <c r="G397" s="1"/>
       <c r="H397" s="1"/>
     </row>
-    <row r="398" spans="1:8" ht="15" thickBot="1">
+    <row r="398" spans="1:8" ht="15.75" thickBot="1">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -6868,7 +6816,7 @@
       <c r="G398" s="1"/>
       <c r="H398" s="1"/>
     </row>
-    <row r="399" spans="1:8" ht="15" thickBot="1">
+    <row r="399" spans="1:8" ht="15.75" thickBot="1">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -6878,7 +6826,7 @@
       <c r="G399" s="1"/>
       <c r="H399" s="1"/>
     </row>
-    <row r="400" spans="1:8" ht="15" thickBot="1">
+    <row r="400" spans="1:8" ht="15.75" thickBot="1">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -6888,7 +6836,7 @@
       <c r="G400" s="1"/>
       <c r="H400" s="1"/>
     </row>
-    <row r="401" spans="1:8" ht="15" thickBot="1">
+    <row r="401" spans="1:8" ht="15.75" thickBot="1">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -6898,7 +6846,7 @@
       <c r="G401" s="1"/>
       <c r="H401" s="1"/>
     </row>
-    <row r="402" spans="1:8" ht="15" thickBot="1">
+    <row r="402" spans="1:8" ht="15.75" thickBot="1">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -6908,7 +6856,7 @@
       <c r="G402" s="1"/>
       <c r="H402" s="1"/>
     </row>
-    <row r="403" spans="1:8" ht="15" thickBot="1">
+    <row r="403" spans="1:8" ht="15.75" thickBot="1">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -6918,7 +6866,7 @@
       <c r="G403" s="1"/>
       <c r="H403" s="1"/>
     </row>
-    <row r="404" spans="1:8" ht="15" thickBot="1">
+    <row r="404" spans="1:8" ht="15.75" thickBot="1">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -6928,7 +6876,7 @@
       <c r="G404" s="1"/>
       <c r="H404" s="1"/>
     </row>
-    <row r="405" spans="1:8" ht="15" thickBot="1">
+    <row r="405" spans="1:8" ht="15.75" thickBot="1">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -6938,7 +6886,7 @@
       <c r="G405" s="1"/>
       <c r="H405" s="1"/>
     </row>
-    <row r="406" spans="1:8" ht="15" thickBot="1">
+    <row r="406" spans="1:8" ht="15.75" thickBot="1">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -6948,7 +6896,7 @@
       <c r="G406" s="1"/>
       <c r="H406" s="1"/>
     </row>
-    <row r="407" spans="1:8" ht="15" thickBot="1">
+    <row r="407" spans="1:8" ht="15.75" thickBot="1">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -6958,7 +6906,7 @@
       <c r="G407" s="1"/>
       <c r="H407" s="1"/>
     </row>
-    <row r="408" spans="1:8" ht="15" thickBot="1">
+    <row r="408" spans="1:8" ht="15.75" thickBot="1">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -6968,7 +6916,7 @@
       <c r="G408" s="1"/>
       <c r="H408" s="1"/>
     </row>
-    <row r="409" spans="1:8" ht="15" thickBot="1">
+    <row r="409" spans="1:8" ht="15.75" thickBot="1">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -6978,7 +6926,7 @@
       <c r="G409" s="1"/>
       <c r="H409" s="1"/>
     </row>
-    <row r="410" spans="1:8" ht="15" thickBot="1">
+    <row r="410" spans="1:8" ht="15.75" thickBot="1">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -6988,7 +6936,7 @@
       <c r="G410" s="1"/>
       <c r="H410" s="1"/>
     </row>
-    <row r="411" spans="1:8" ht="15" thickBot="1">
+    <row r="411" spans="1:8" ht="15.75" thickBot="1">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -6998,7 +6946,7 @@
       <c r="G411" s="1"/>
       <c r="H411" s="1"/>
     </row>
-    <row r="412" spans="1:8" ht="15" thickBot="1">
+    <row r="412" spans="1:8" ht="15.75" thickBot="1">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -7008,7 +6956,7 @@
       <c r="G412" s="1"/>
       <c r="H412" s="1"/>
     </row>
-    <row r="413" spans="1:8" ht="15" thickBot="1">
+    <row r="413" spans="1:8" ht="15.75" thickBot="1">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -7018,7 +6966,7 @@
       <c r="G413" s="1"/>
       <c r="H413" s="1"/>
     </row>
-    <row r="414" spans="1:8" ht="15" thickBot="1">
+    <row r="414" spans="1:8" ht="15.75" thickBot="1">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -7028,7 +6976,7 @@
       <c r="G414" s="1"/>
       <c r="H414" s="1"/>
     </row>
-    <row r="415" spans="1:8" ht="15" thickBot="1">
+    <row r="415" spans="1:8" ht="15.75" thickBot="1">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -7038,7 +6986,7 @@
       <c r="G415" s="1"/>
       <c r="H415" s="1"/>
     </row>
-    <row r="416" spans="1:8" ht="15" thickBot="1">
+    <row r="416" spans="1:8" ht="15.75" thickBot="1">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -7048,7 +6996,7 @@
       <c r="G416" s="1"/>
       <c r="H416" s="1"/>
     </row>
-    <row r="417" spans="1:8" ht="15" thickBot="1">
+    <row r="417" spans="1:8" ht="15.75" thickBot="1">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -7058,7 +7006,7 @@
       <c r="G417" s="1"/>
       <c r="H417" s="1"/>
     </row>
-    <row r="418" spans="1:8" ht="15" thickBot="1">
+    <row r="418" spans="1:8" ht="15.75" thickBot="1">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -7068,7 +7016,7 @@
       <c r="G418" s="1"/>
       <c r="H418" s="1"/>
     </row>
-    <row r="419" spans="1:8" ht="15" thickBot="1">
+    <row r="419" spans="1:8" ht="15.75" thickBot="1">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -7078,7 +7026,7 @@
       <c r="G419" s="1"/>
       <c r="H419" s="1"/>
     </row>
-    <row r="420" spans="1:8" ht="15" thickBot="1">
+    <row r="420" spans="1:8" ht="15.75" thickBot="1">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -7088,7 +7036,7 @@
       <c r="G420" s="1"/>
       <c r="H420" s="1"/>
     </row>
-    <row r="421" spans="1:8" ht="15" thickBot="1">
+    <row r="421" spans="1:8" ht="15.75" thickBot="1">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -7098,7 +7046,7 @@
       <c r="G421" s="1"/>
       <c r="H421" s="1"/>
     </row>
-    <row r="422" spans="1:8" ht="15" thickBot="1">
+    <row r="422" spans="1:8" ht="15.75" thickBot="1">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -7108,7 +7056,7 @@
       <c r="G422" s="1"/>
       <c r="H422" s="1"/>
     </row>
-    <row r="423" spans="1:8" ht="15" thickBot="1">
+    <row r="423" spans="1:8" ht="15.75" thickBot="1">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -7118,7 +7066,7 @@
       <c r="G423" s="1"/>
       <c r="H423" s="1"/>
     </row>
-    <row r="424" spans="1:8" ht="15" thickBot="1">
+    <row r="424" spans="1:8" ht="15.75" thickBot="1">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -7128,7 +7076,7 @@
       <c r="G424" s="1"/>
       <c r="H424" s="1"/>
     </row>
-    <row r="425" spans="1:8" ht="15" thickBot="1">
+    <row r="425" spans="1:8" ht="15.75" thickBot="1">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -7138,7 +7086,7 @@
       <c r="G425" s="1"/>
       <c r="H425" s="1"/>
     </row>
-    <row r="426" spans="1:8" ht="15" thickBot="1">
+    <row r="426" spans="1:8" ht="15.75" thickBot="1">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -7148,7 +7096,7 @@
       <c r="G426" s="1"/>
       <c r="H426" s="1"/>
     </row>
-    <row r="427" spans="1:8" ht="15" thickBot="1">
+    <row r="427" spans="1:8" ht="15.75" thickBot="1">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -7158,7 +7106,7 @@
       <c r="G427" s="1"/>
       <c r="H427" s="1"/>
     </row>
-    <row r="428" spans="1:8" ht="15" thickBot="1">
+    <row r="428" spans="1:8" ht="15.75" thickBot="1">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -7168,7 +7116,7 @@
       <c r="G428" s="1"/>
       <c r="H428" s="1"/>
     </row>
-    <row r="429" spans="1:8" ht="15" thickBot="1">
+    <row r="429" spans="1:8" ht="15.75" thickBot="1">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -7178,7 +7126,7 @@
       <c r="G429" s="1"/>
       <c r="H429" s="1"/>
     </row>
-    <row r="430" spans="1:8" ht="15" thickBot="1">
+    <row r="430" spans="1:8" ht="15.75" thickBot="1">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -7188,7 +7136,7 @@
       <c r="G430" s="1"/>
       <c r="H430" s="1"/>
     </row>
-    <row r="431" spans="1:8" ht="15" thickBot="1">
+    <row r="431" spans="1:8" ht="15.75" thickBot="1">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -7198,7 +7146,7 @@
       <c r="G431" s="1"/>
       <c r="H431" s="1"/>
     </row>
-    <row r="432" spans="1:8" ht="15" thickBot="1">
+    <row r="432" spans="1:8" ht="15.75" thickBot="1">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -7208,7 +7156,7 @@
       <c r="G432" s="1"/>
       <c r="H432" s="1"/>
     </row>
-    <row r="433" spans="1:8" ht="15" thickBot="1">
+    <row r="433" spans="1:8" ht="15.75" thickBot="1">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -7218,7 +7166,7 @@
       <c r="G433" s="1"/>
       <c r="H433" s="1"/>
     </row>
-    <row r="434" spans="1:8" ht="15" thickBot="1">
+    <row r="434" spans="1:8" ht="15.75" thickBot="1">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -7228,7 +7176,7 @@
       <c r="G434" s="1"/>
       <c r="H434" s="1"/>
     </row>
-    <row r="435" spans="1:8" ht="15" thickBot="1">
+    <row r="435" spans="1:8" ht="15.75" thickBot="1">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -7238,7 +7186,7 @@
       <c r="G435" s="1"/>
       <c r="H435" s="1"/>
     </row>
-    <row r="436" spans="1:8" ht="15" thickBot="1">
+    <row r="436" spans="1:8" ht="15.75" thickBot="1">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -7248,7 +7196,7 @@
       <c r="G436" s="1"/>
       <c r="H436" s="1"/>
     </row>
-    <row r="437" spans="1:8" ht="15" thickBot="1">
+    <row r="437" spans="1:8" ht="15.75" thickBot="1">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -7258,7 +7206,7 @@
       <c r="G437" s="1"/>
       <c r="H437" s="1"/>
     </row>
-    <row r="438" spans="1:8" ht="15" thickBot="1">
+    <row r="438" spans="1:8" ht="15.75" thickBot="1">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -7268,7 +7216,7 @@
       <c r="G438" s="1"/>
       <c r="H438" s="1"/>
     </row>
-    <row r="439" spans="1:8" ht="15" thickBot="1">
+    <row r="439" spans="1:8" ht="15.75" thickBot="1">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -7278,7 +7226,7 @@
       <c r="G439" s="1"/>
       <c r="H439" s="1"/>
     </row>
-    <row r="440" spans="1:8" ht="15" thickBot="1">
+    <row r="440" spans="1:8" ht="15.75" thickBot="1">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -7288,7 +7236,7 @@
       <c r="G440" s="1"/>
       <c r="H440" s="1"/>
     </row>
-    <row r="441" spans="1:8" ht="15" thickBot="1">
+    <row r="441" spans="1:8" ht="15.75" thickBot="1">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -7298,7 +7246,7 @@
       <c r="G441" s="1"/>
       <c r="H441" s="1"/>
     </row>
-    <row r="442" spans="1:8" ht="15" thickBot="1">
+    <row r="442" spans="1:8" ht="15.75" thickBot="1">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -7308,7 +7256,7 @@
       <c r="G442" s="1"/>
       <c r="H442" s="1"/>
     </row>
-    <row r="443" spans="1:8" ht="15" thickBot="1">
+    <row r="443" spans="1:8" ht="15.75" thickBot="1">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -7318,7 +7266,7 @@
       <c r="G443" s="1"/>
       <c r="H443" s="1"/>
     </row>
-    <row r="444" spans="1:8" ht="15" thickBot="1">
+    <row r="444" spans="1:8" ht="15.75" thickBot="1">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -7328,7 +7276,7 @@
       <c r="G444" s="1"/>
       <c r="H444" s="1"/>
     </row>
-    <row r="445" spans="1:8" ht="15" thickBot="1">
+    <row r="445" spans="1:8" ht="15.75" thickBot="1">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -7338,7 +7286,7 @@
       <c r="G445" s="1"/>
       <c r="H445" s="1"/>
     </row>
-    <row r="446" spans="1:8" ht="15" thickBot="1">
+    <row r="446" spans="1:8" ht="15.75" thickBot="1">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -7348,7 +7296,7 @@
       <c r="G446" s="1"/>
       <c r="H446" s="1"/>
     </row>
-    <row r="447" spans="1:8" ht="15" thickBot="1">
+    <row r="447" spans="1:8" ht="15.75" thickBot="1">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -7358,7 +7306,7 @@
       <c r="G447" s="1"/>
       <c r="H447" s="1"/>
     </row>
-    <row r="448" spans="1:8" ht="15" thickBot="1">
+    <row r="448" spans="1:8" ht="15.75" thickBot="1">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -7368,7 +7316,7 @@
       <c r="G448" s="1"/>
       <c r="H448" s="1"/>
     </row>
-    <row r="449" spans="1:8" ht="15" thickBot="1">
+    <row r="449" spans="1:8" ht="15.75" thickBot="1">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -7378,7 +7326,7 @@
       <c r="G449" s="1"/>
       <c r="H449" s="1"/>
     </row>
-    <row r="450" spans="1:8" ht="15" thickBot="1">
+    <row r="450" spans="1:8" ht="15.75" thickBot="1">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -7388,7 +7336,7 @@
       <c r="G450" s="1"/>
       <c r="H450" s="1"/>
     </row>
-    <row r="451" spans="1:8" ht="15" thickBot="1">
+    <row r="451" spans="1:8" ht="15.75" thickBot="1">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -7398,7 +7346,7 @@
       <c r="G451" s="1"/>
       <c r="H451" s="1"/>
     </row>
-    <row r="452" spans="1:8" ht="15" thickBot="1">
+    <row r="452" spans="1:8" ht="15.75" thickBot="1">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -7408,7 +7356,7 @@
       <c r="G452" s="1"/>
       <c r="H452" s="1"/>
     </row>
-    <row r="453" spans="1:8" ht="15" thickBot="1">
+    <row r="453" spans="1:8" ht="15.75" thickBot="1">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -7418,7 +7366,7 @@
       <c r="G453" s="1"/>
       <c r="H453" s="1"/>
     </row>
-    <row r="454" spans="1:8" ht="15" thickBot="1">
+    <row r="454" spans="1:8" ht="15.75" thickBot="1">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -7428,7 +7376,7 @@
       <c r="G454" s="1"/>
       <c r="H454" s="1"/>
     </row>
-    <row r="455" spans="1:8" ht="15" thickBot="1">
+    <row r="455" spans="1:8" ht="15.75" thickBot="1">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -7438,7 +7386,7 @@
       <c r="G455" s="1"/>
       <c r="H455" s="1"/>
     </row>
-    <row r="456" spans="1:8" ht="15" thickBot="1">
+    <row r="456" spans="1:8" ht="15.75" thickBot="1">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -7448,7 +7396,7 @@
       <c r="G456" s="1"/>
       <c r="H456" s="1"/>
     </row>
-    <row r="457" spans="1:8" ht="15" thickBot="1">
+    <row r="457" spans="1:8" ht="15.75" thickBot="1">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -7458,7 +7406,7 @@
       <c r="G457" s="1"/>
       <c r="H457" s="1"/>
     </row>
-    <row r="458" spans="1:8" ht="15" thickBot="1">
+    <row r="458" spans="1:8" ht="15.75" thickBot="1">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -7468,7 +7416,7 @@
       <c r="G458" s="1"/>
       <c r="H458" s="1"/>
     </row>
-    <row r="459" spans="1:8" ht="15" thickBot="1">
+    <row r="459" spans="1:8" ht="15.75" thickBot="1">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -7478,7 +7426,7 @@
       <c r="G459" s="1"/>
       <c r="H459" s="1"/>
     </row>
-    <row r="460" spans="1:8" ht="15" thickBot="1">
+    <row r="460" spans="1:8" ht="15.75" thickBot="1">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -7488,7 +7436,7 @@
       <c r="G460" s="1"/>
       <c r="H460" s="1"/>
     </row>
-    <row r="461" spans="1:8" ht="15" thickBot="1">
+    <row r="461" spans="1:8" ht="15.75" thickBot="1">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -7498,7 +7446,7 @@
       <c r="G461" s="1"/>
       <c r="H461" s="1"/>
     </row>
-    <row r="462" spans="1:8" ht="15" thickBot="1">
+    <row r="462" spans="1:8" ht="15.75" thickBot="1">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -7508,7 +7456,7 @@
       <c r="G462" s="1"/>
       <c r="H462" s="1"/>
     </row>
-    <row r="463" spans="1:8" ht="15" thickBot="1">
+    <row r="463" spans="1:8" ht="15.75" thickBot="1">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -7518,7 +7466,7 @@
       <c r="G463" s="1"/>
       <c r="H463" s="1"/>
     </row>
-    <row r="464" spans="1:8" ht="15" thickBot="1">
+    <row r="464" spans="1:8" ht="15.75" thickBot="1">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -7528,7 +7476,7 @@
       <c r="G464" s="1"/>
       <c r="H464" s="1"/>
     </row>
-    <row r="465" spans="1:8" ht="15" thickBot="1">
+    <row r="465" spans="1:8" ht="15.75" thickBot="1">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -7538,7 +7486,7 @@
       <c r="G465" s="1"/>
       <c r="H465" s="1"/>
     </row>
-    <row r="466" spans="1:8" ht="15" thickBot="1">
+    <row r="466" spans="1:8" ht="15.75" thickBot="1">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -7548,7 +7496,7 @@
       <c r="G466" s="1"/>
       <c r="H466" s="1"/>
     </row>
-    <row r="467" spans="1:8" ht="15" thickBot="1">
+    <row r="467" spans="1:8" ht="15.75" thickBot="1">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -7558,7 +7506,7 @@
       <c r="G467" s="1"/>
       <c r="H467" s="1"/>
     </row>
-    <row r="468" spans="1:8" ht="15" thickBot="1">
+    <row r="468" spans="1:8" ht="15.75" thickBot="1">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -7568,7 +7516,7 @@
       <c r="G468" s="1"/>
       <c r="H468" s="1"/>
     </row>
-    <row r="469" spans="1:8" ht="15" thickBot="1">
+    <row r="469" spans="1:8" ht="15.75" thickBot="1">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -7578,7 +7526,7 @@
       <c r="G469" s="1"/>
       <c r="H469" s="1"/>
     </row>
-    <row r="470" spans="1:8" ht="15" thickBot="1">
+    <row r="470" spans="1:8" ht="15.75" thickBot="1">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -7588,7 +7536,7 @@
       <c r="G470" s="1"/>
       <c r="H470" s="1"/>
     </row>
-    <row r="471" spans="1:8" ht="15" thickBot="1">
+    <row r="471" spans="1:8" ht="15.75" thickBot="1">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -7598,7 +7546,7 @@
       <c r="G471" s="1"/>
       <c r="H471" s="1"/>
     </row>
-    <row r="472" spans="1:8" ht="15" thickBot="1">
+    <row r="472" spans="1:8" ht="15.75" thickBot="1">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -7608,7 +7556,7 @@
       <c r="G472" s="1"/>
       <c r="H472" s="1"/>
     </row>
-    <row r="473" spans="1:8" ht="15" thickBot="1">
+    <row r="473" spans="1:8" ht="15.75" thickBot="1">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -7618,7 +7566,7 @@
       <c r="G473" s="1"/>
       <c r="H473" s="1"/>
     </row>
-    <row r="474" spans="1:8" ht="15" thickBot="1">
+    <row r="474" spans="1:8" ht="15.75" thickBot="1">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -7628,7 +7576,7 @@
       <c r="G474" s="1"/>
       <c r="H474" s="1"/>
     </row>
-    <row r="475" spans="1:8" ht="15" thickBot="1">
+    <row r="475" spans="1:8" ht="15.75" thickBot="1">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -7638,7 +7586,7 @@
       <c r="G475" s="1"/>
       <c r="H475" s="1"/>
     </row>
-    <row r="476" spans="1:8" ht="15" thickBot="1">
+    <row r="476" spans="1:8" ht="15.75" thickBot="1">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -7648,7 +7596,7 @@
       <c r="G476" s="1"/>
       <c r="H476" s="1"/>
     </row>
-    <row r="477" spans="1:8" ht="15" thickBot="1">
+    <row r="477" spans="1:8" ht="15.75" thickBot="1">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -7658,7 +7606,7 @@
       <c r="G477" s="1"/>
       <c r="H477" s="1"/>
     </row>
-    <row r="478" spans="1:8" ht="15" thickBot="1">
+    <row r="478" spans="1:8" ht="15.75" thickBot="1">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -7668,7 +7616,7 @@
       <c r="G478" s="1"/>
       <c r="H478" s="1"/>
     </row>
-    <row r="479" spans="1:8" ht="15" thickBot="1">
+    <row r="479" spans="1:8" ht="15.75" thickBot="1">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -7678,7 +7626,7 @@
       <c r="G479" s="1"/>
       <c r="H479" s="1"/>
     </row>
-    <row r="480" spans="1:8" ht="15" thickBot="1">
+    <row r="480" spans="1:8" ht="15.75" thickBot="1">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -7688,7 +7636,7 @@
       <c r="G480" s="1"/>
       <c r="H480" s="1"/>
     </row>
-    <row r="481" spans="1:8" ht="15" thickBot="1">
+    <row r="481" spans="1:8" ht="15.75" thickBot="1">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -7698,7 +7646,7 @@
       <c r="G481" s="1"/>
       <c r="H481" s="1"/>
     </row>
-    <row r="482" spans="1:8" ht="15" thickBot="1">
+    <row r="482" spans="1:8" ht="15.75" thickBot="1">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -7708,7 +7656,7 @@
       <c r="G482" s="1"/>
       <c r="H482" s="1"/>
     </row>
-    <row r="483" spans="1:8" ht="15" thickBot="1">
+    <row r="483" spans="1:8" ht="15.75" thickBot="1">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -7718,7 +7666,7 @@
       <c r="G483" s="1"/>
       <c r="H483" s="1"/>
     </row>
-    <row r="484" spans="1:8" ht="15" thickBot="1">
+    <row r="484" spans="1:8" ht="15.75" thickBot="1">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -7728,7 +7676,7 @@
       <c r="G484" s="1"/>
       <c r="H484" s="1"/>
     </row>
-    <row r="485" spans="1:8" ht="15" thickBot="1">
+    <row r="485" spans="1:8" ht="15.75" thickBot="1">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -7738,7 +7686,7 @@
       <c r="G485" s="1"/>
       <c r="H485" s="1"/>
     </row>
-    <row r="486" spans="1:8" ht="15" thickBot="1">
+    <row r="486" spans="1:8" ht="15.75" thickBot="1">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -7748,7 +7696,7 @@
       <c r="G486" s="1"/>
       <c r="H486" s="1"/>
     </row>
-    <row r="487" spans="1:8" ht="15" thickBot="1">
+    <row r="487" spans="1:8" ht="15.75" thickBot="1">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -7758,7 +7706,7 @@
       <c r="G487" s="1"/>
       <c r="H487" s="1"/>
     </row>
-    <row r="488" spans="1:8" ht="15" thickBot="1">
+    <row r="488" spans="1:8" ht="15.75" thickBot="1">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -7768,7 +7716,7 @@
       <c r="G488" s="1"/>
       <c r="H488" s="1"/>
     </row>
-    <row r="489" spans="1:8" ht="15" thickBot="1">
+    <row r="489" spans="1:8" ht="15.75" thickBot="1">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -7778,7 +7726,7 @@
       <c r="G489" s="1"/>
       <c r="H489" s="1"/>
     </row>
-    <row r="490" spans="1:8" ht="15" thickBot="1">
+    <row r="490" spans="1:8" ht="15.75" thickBot="1">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -7788,7 +7736,7 @@
       <c r="G490" s="1"/>
       <c r="H490" s="1"/>
     </row>
-    <row r="491" spans="1:8" ht="15" thickBot="1">
+    <row r="491" spans="1:8" ht="15.75" thickBot="1">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -7798,7 +7746,7 @@
       <c r="G491" s="1"/>
       <c r="H491" s="1"/>
     </row>
-    <row r="492" spans="1:8" ht="15" thickBot="1">
+    <row r="492" spans="1:8" ht="15.75" thickBot="1">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -7808,7 +7756,7 @@
       <c r="G492" s="1"/>
       <c r="H492" s="1"/>
     </row>
-    <row r="493" spans="1:8" ht="15" thickBot="1">
+    <row r="493" spans="1:8" ht="15.75" thickBot="1">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -7818,7 +7766,7 @@
       <c r="G493" s="1"/>
       <c r="H493" s="1"/>
     </row>
-    <row r="494" spans="1:8" ht="15" thickBot="1">
+    <row r="494" spans="1:8" ht="15.75" thickBot="1">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -7828,7 +7776,7 @@
       <c r="G494" s="1"/>
       <c r="H494" s="1"/>
     </row>
-    <row r="495" spans="1:8" ht="15" thickBot="1">
+    <row r="495" spans="1:8" ht="15.75" thickBot="1">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -7838,7 +7786,7 @@
       <c r="G495" s="1"/>
       <c r="H495" s="1"/>
     </row>
-    <row r="496" spans="1:8" ht="15" thickBot="1">
+    <row r="496" spans="1:8" ht="15.75" thickBot="1">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -7848,7 +7796,7 @@
       <c r="G496" s="1"/>
       <c r="H496" s="1"/>
     </row>
-    <row r="497" spans="1:8" ht="15" thickBot="1">
+    <row r="497" spans="1:8" ht="15.75" thickBot="1">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -7858,7 +7806,7 @@
       <c r="G497" s="1"/>
       <c r="H497" s="1"/>
     </row>
-    <row r="498" spans="1:8" ht="15" thickBot="1">
+    <row r="498" spans="1:8" ht="15.75" thickBot="1">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -7868,7 +7816,7 @@
       <c r="G498" s="1"/>
       <c r="H498" s="1"/>
     </row>
-    <row r="499" spans="1:8" ht="15" thickBot="1">
+    <row r="499" spans="1:8" ht="15.75" thickBot="1">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -7878,7 +7826,7 @@
       <c r="G499" s="1"/>
       <c r="H499" s="1"/>
     </row>
-    <row r="500" spans="1:8" ht="15" thickBot="1">
+    <row r="500" spans="1:8" ht="15.75" thickBot="1">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -7888,7 +7836,7 @@
       <c r="G500" s="1"/>
       <c r="H500" s="1"/>
     </row>
-    <row r="501" spans="1:8" ht="15" thickBot="1">
+    <row r="501" spans="1:8" ht="15.75" thickBot="1">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -7898,7 +7846,7 @@
       <c r="G501" s="1"/>
       <c r="H501" s="1"/>
     </row>
-    <row r="502" spans="1:8" ht="15" thickBot="1">
+    <row r="502" spans="1:8" ht="15.75" thickBot="1">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -7908,7 +7856,7 @@
       <c r="G502" s="1"/>
       <c r="H502" s="1"/>
     </row>
-    <row r="503" spans="1:8" ht="15" thickBot="1">
+    <row r="503" spans="1:8" ht="15.75" thickBot="1">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -7918,7 +7866,7 @@
       <c r="G503" s="1"/>
       <c r="H503" s="1"/>
     </row>
-    <row r="504" spans="1:8" ht="15" thickBot="1">
+    <row r="504" spans="1:8" ht="15.75" thickBot="1">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -7928,7 +7876,7 @@
       <c r="G504" s="1"/>
       <c r="H504" s="1"/>
     </row>
-    <row r="505" spans="1:8" ht="15" thickBot="1">
+    <row r="505" spans="1:8" ht="15.75" thickBot="1">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -7938,7 +7886,7 @@
       <c r="G505" s="1"/>
       <c r="H505" s="1"/>
     </row>
-    <row r="506" spans="1:8" ht="15" thickBot="1">
+    <row r="506" spans="1:8" ht="15.75" thickBot="1">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -7948,7 +7896,7 @@
       <c r="G506" s="1"/>
       <c r="H506" s="1"/>
     </row>
-    <row r="507" spans="1:8" ht="15" thickBot="1">
+    <row r="507" spans="1:8" ht="15.75" thickBot="1">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -7958,7 +7906,7 @@
       <c r="G507" s="1"/>
       <c r="H507" s="1"/>
     </row>
-    <row r="508" spans="1:8" ht="15" thickBot="1">
+    <row r="508" spans="1:8" ht="15.75" thickBot="1">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -7968,7 +7916,7 @@
       <c r="G508" s="1"/>
       <c r="H508" s="1"/>
     </row>
-    <row r="509" spans="1:8" ht="15" thickBot="1">
+    <row r="509" spans="1:8" ht="15.75" thickBot="1">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -7978,7 +7926,7 @@
       <c r="G509" s="1"/>
       <c r="H509" s="1"/>
     </row>
-    <row r="510" spans="1:8" ht="15" thickBot="1">
+    <row r="510" spans="1:8" ht="15.75" thickBot="1">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -7988,7 +7936,7 @@
       <c r="G510" s="1"/>
       <c r="H510" s="1"/>
     </row>
-    <row r="511" spans="1:8" ht="15" thickBot="1">
+    <row r="511" spans="1:8" ht="15.75" thickBot="1">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -7998,7 +7946,7 @@
       <c r="G511" s="1"/>
       <c r="H511" s="1"/>
     </row>
-    <row r="512" spans="1:8" ht="15" thickBot="1">
+    <row r="512" spans="1:8" ht="15.75" thickBot="1">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -8008,7 +7956,7 @@
       <c r="G512" s="1"/>
       <c r="H512" s="1"/>
     </row>
-    <row r="513" spans="1:8" ht="15" thickBot="1">
+    <row r="513" spans="1:8" ht="15.75" thickBot="1">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -8018,7 +7966,7 @@
       <c r="G513" s="1"/>
       <c r="H513" s="1"/>
     </row>
-    <row r="514" spans="1:8" ht="15" thickBot="1">
+    <row r="514" spans="1:8" ht="15.75" thickBot="1">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -8028,7 +7976,7 @@
       <c r="G514" s="1"/>
       <c r="H514" s="1"/>
     </row>
-    <row r="515" spans="1:8" ht="15" thickBot="1">
+    <row r="515" spans="1:8" ht="15.75" thickBot="1">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -8038,7 +7986,7 @@
       <c r="G515" s="1"/>
       <c r="H515" s="1"/>
     </row>
-    <row r="516" spans="1:8" ht="15" thickBot="1">
+    <row r="516" spans="1:8" ht="15.75" thickBot="1">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -8048,7 +7996,7 @@
       <c r="G516" s="1"/>
       <c r="H516" s="1"/>
     </row>
-    <row r="517" spans="1:8" ht="15" thickBot="1">
+    <row r="517" spans="1:8" ht="15.75" thickBot="1">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -8058,7 +8006,7 @@
       <c r="G517" s="1"/>
       <c r="H517" s="1"/>
     </row>
-    <row r="518" spans="1:8" ht="15" thickBot="1">
+    <row r="518" spans="1:8" ht="15.75" thickBot="1">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -8068,7 +8016,7 @@
       <c r="G518" s="1"/>
       <c r="H518" s="1"/>
     </row>
-    <row r="519" spans="1:8" ht="15" thickBot="1">
+    <row r="519" spans="1:8" ht="15.75" thickBot="1">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -8078,7 +8026,7 @@
       <c r="G519" s="1"/>
       <c r="H519" s="1"/>
     </row>
-    <row r="520" spans="1:8" ht="15" thickBot="1">
+    <row r="520" spans="1:8" ht="15.75" thickBot="1">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -8088,7 +8036,7 @@
       <c r="G520" s="1"/>
       <c r="H520" s="1"/>
     </row>
-    <row r="521" spans="1:8" ht="15" thickBot="1">
+    <row r="521" spans="1:8" ht="15.75" thickBot="1">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -8098,7 +8046,7 @@
       <c r="G521" s="1"/>
       <c r="H521" s="1"/>
     </row>
-    <row r="522" spans="1:8" ht="15" thickBot="1">
+    <row r="522" spans="1:8" ht="15.75" thickBot="1">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -8108,7 +8056,7 @@
       <c r="G522" s="1"/>
       <c r="H522" s="1"/>
     </row>
-    <row r="523" spans="1:8" ht="15" thickBot="1">
+    <row r="523" spans="1:8" ht="15.75" thickBot="1">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -8118,7 +8066,7 @@
       <c r="G523" s="1"/>
       <c r="H523" s="1"/>
     </row>
-    <row r="524" spans="1:8" ht="15" thickBot="1">
+    <row r="524" spans="1:8" ht="15.75" thickBot="1">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -8128,7 +8076,7 @@
       <c r="G524" s="1"/>
       <c r="H524" s="1"/>
     </row>
-    <row r="525" spans="1:8" ht="15" thickBot="1">
+    <row r="525" spans="1:8" ht="15.75" thickBot="1">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -8138,7 +8086,7 @@
       <c r="G525" s="1"/>
       <c r="H525" s="1"/>
     </row>
-    <row r="526" spans="1:8" ht="15" thickBot="1">
+    <row r="526" spans="1:8" ht="15.75" thickBot="1">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -8148,7 +8096,7 @@
       <c r="G526" s="1"/>
       <c r="H526" s="1"/>
     </row>
-    <row r="527" spans="1:8" ht="15" thickBot="1">
+    <row r="527" spans="1:8" ht="15.75" thickBot="1">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -8158,7 +8106,7 @@
       <c r="G527" s="1"/>
       <c r="H527" s="1"/>
     </row>
-    <row r="528" spans="1:8" ht="15" thickBot="1">
+    <row r="528" spans="1:8" ht="15.75" thickBot="1">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -8168,7 +8116,7 @@
       <c r="G528" s="1"/>
       <c r="H528" s="1"/>
     </row>
-    <row r="529" spans="1:8" ht="15" thickBot="1">
+    <row r="529" spans="1:8" ht="15.75" thickBot="1">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -8178,7 +8126,7 @@
       <c r="G529" s="1"/>
       <c r="H529" s="1"/>
     </row>
-    <row r="530" spans="1:8" ht="15" thickBot="1">
+    <row r="530" spans="1:8" ht="15.75" thickBot="1">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -8188,7 +8136,7 @@
       <c r="G530" s="1"/>
       <c r="H530" s="1"/>
     </row>
-    <row r="531" spans="1:8" ht="15" thickBot="1">
+    <row r="531" spans="1:8" ht="15.75" thickBot="1">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -8198,7 +8146,7 @@
       <c r="G531" s="1"/>
       <c r="H531" s="1"/>
     </row>
-    <row r="532" spans="1:8" ht="15" thickBot="1">
+    <row r="532" spans="1:8" ht="15.75" thickBot="1">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -8208,7 +8156,7 @@
       <c r="G532" s="1"/>
       <c r="H532" s="1"/>
     </row>
-    <row r="533" spans="1:8" ht="15" thickBot="1">
+    <row r="533" spans="1:8" ht="15.75" thickBot="1">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -8218,7 +8166,7 @@
       <c r="G533" s="1"/>
       <c r="H533" s="1"/>
     </row>
-    <row r="534" spans="1:8" ht="15" thickBot="1">
+    <row r="534" spans="1:8" ht="15.75" thickBot="1">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -8228,7 +8176,7 @@
       <c r="G534" s="1"/>
       <c r="H534" s="1"/>
     </row>
-    <row r="535" spans="1:8" ht="15" thickBot="1">
+    <row r="535" spans="1:8" ht="15.75" thickBot="1">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -8238,7 +8186,7 @@
       <c r="G535" s="1"/>
       <c r="H535" s="1"/>
     </row>
-    <row r="536" spans="1:8" ht="15" thickBot="1">
+    <row r="536" spans="1:8" ht="15.75" thickBot="1">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -8248,7 +8196,7 @@
       <c r="G536" s="1"/>
       <c r="H536" s="1"/>
     </row>
-    <row r="537" spans="1:8" ht="15" thickBot="1">
+    <row r="537" spans="1:8" ht="15.75" thickBot="1">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -8258,7 +8206,7 @@
       <c r="G537" s="1"/>
       <c r="H537" s="1"/>
     </row>
-    <row r="538" spans="1:8" ht="15" thickBot="1">
+    <row r="538" spans="1:8" ht="15.75" thickBot="1">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -8268,7 +8216,7 @@
       <c r="G538" s="1"/>
       <c r="H538" s="1"/>
     </row>
-    <row r="539" spans="1:8" ht="15" thickBot="1">
+    <row r="539" spans="1:8" ht="15.75" thickBot="1">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -8278,7 +8226,7 @@
       <c r="G539" s="1"/>
       <c r="H539" s="1"/>
     </row>
-    <row r="540" spans="1:8" ht="15" thickBot="1">
+    <row r="540" spans="1:8" ht="15.75" thickBot="1">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -8288,7 +8236,7 @@
       <c r="G540" s="1"/>
       <c r="H540" s="1"/>
     </row>
-    <row r="541" spans="1:8" ht="15" thickBot="1">
+    <row r="541" spans="1:8" ht="15.75" thickBot="1">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -8298,7 +8246,7 @@
       <c r="G541" s="1"/>
       <c r="H541" s="1"/>
     </row>
-    <row r="542" spans="1:8" ht="15" thickBot="1">
+    <row r="542" spans="1:8" ht="15.75" thickBot="1">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -8308,7 +8256,7 @@
       <c r="G542" s="1"/>
       <c r="H542" s="1"/>
     </row>
-    <row r="543" spans="1:8" ht="15" thickBot="1">
+    <row r="543" spans="1:8" ht="15.75" thickBot="1">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -8318,7 +8266,7 @@
       <c r="G543" s="1"/>
       <c r="H543" s="1"/>
     </row>
-    <row r="544" spans="1:8" ht="15" thickBot="1">
+    <row r="544" spans="1:8" ht="15.75" thickBot="1">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -8328,7 +8276,7 @@
       <c r="G544" s="1"/>
       <c r="H544" s="1"/>
     </row>
-    <row r="545" spans="1:8" ht="15" thickBot="1">
+    <row r="545" spans="1:8" ht="15.75" thickBot="1">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -8338,7 +8286,7 @@
       <c r="G545" s="1"/>
       <c r="H545" s="1"/>
     </row>
-    <row r="546" spans="1:8" ht="15" thickBot="1">
+    <row r="546" spans="1:8" ht="15.75" thickBot="1">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -8348,7 +8296,7 @@
       <c r="G546" s="1"/>
       <c r="H546" s="1"/>
     </row>
-    <row r="547" spans="1:8" ht="15" thickBot="1">
+    <row r="547" spans="1:8" ht="15.75" thickBot="1">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -8358,7 +8306,7 @@
       <c r="G547" s="1"/>
       <c r="H547" s="1"/>
     </row>
-    <row r="548" spans="1:8" ht="15" thickBot="1">
+    <row r="548" spans="1:8" ht="15.75" thickBot="1">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -8368,7 +8316,7 @@
       <c r="G548" s="1"/>
       <c r="H548" s="1"/>
     </row>
-    <row r="549" spans="1:8" ht="15" thickBot="1">
+    <row r="549" spans="1:8" ht="15.75" thickBot="1">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -8378,7 +8326,7 @@
       <c r="G549" s="1"/>
       <c r="H549" s="1"/>
     </row>
-    <row r="550" spans="1:8" ht="15" thickBot="1">
+    <row r="550" spans="1:8" ht="15.75" thickBot="1">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -8388,7 +8336,7 @@
       <c r="G550" s="1"/>
       <c r="H550" s="1"/>
     </row>
-    <row r="551" spans="1:8" ht="15" thickBot="1">
+    <row r="551" spans="1:8" ht="15.75" thickBot="1">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -8398,7 +8346,7 @@
       <c r="G551" s="1"/>
       <c r="H551" s="1"/>
     </row>
-    <row r="552" spans="1:8" ht="15" thickBot="1">
+    <row r="552" spans="1:8" ht="15.75" thickBot="1">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -8408,7 +8356,7 @@
       <c r="G552" s="1"/>
       <c r="H552" s="1"/>
     </row>
-    <row r="553" spans="1:8" ht="15" thickBot="1">
+    <row r="553" spans="1:8" ht="15.75" thickBot="1">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -8418,7 +8366,7 @@
       <c r="G553" s="1"/>
       <c r="H553" s="1"/>
     </row>
-    <row r="554" spans="1:8" ht="15" thickBot="1">
+    <row r="554" spans="1:8" ht="15.75" thickBot="1">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -8428,7 +8376,7 @@
       <c r="G554" s="1"/>
       <c r="H554" s="1"/>
     </row>
-    <row r="555" spans="1:8" ht="15" thickBot="1">
+    <row r="555" spans="1:8" ht="15.75" thickBot="1">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -8438,7 +8386,7 @@
       <c r="G555" s="1"/>
       <c r="H555" s="1"/>
     </row>
-    <row r="556" spans="1:8" ht="15" thickBot="1">
+    <row r="556" spans="1:8" ht="15.75" thickBot="1">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -8448,7 +8396,7 @@
       <c r="G556" s="1"/>
       <c r="H556" s="1"/>
     </row>
-    <row r="557" spans="1:8" ht="15" thickBot="1">
+    <row r="557" spans="1:8" ht="15.75" thickBot="1">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -8458,7 +8406,7 @@
       <c r="G557" s="1"/>
       <c r="H557" s="1"/>
     </row>
-    <row r="558" spans="1:8" ht="15" thickBot="1">
+    <row r="558" spans="1:8" ht="15.75" thickBot="1">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -8468,7 +8416,7 @@
       <c r="G558" s="1"/>
       <c r="H558" s="1"/>
     </row>
-    <row r="559" spans="1:8" ht="15" thickBot="1">
+    <row r="559" spans="1:8" ht="15.75" thickBot="1">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -8478,7 +8426,7 @@
       <c r="G559" s="1"/>
       <c r="H559" s="1"/>
     </row>
-    <row r="560" spans="1:8" ht="15" thickBot="1">
+    <row r="560" spans="1:8" ht="15.75" thickBot="1">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -8488,7 +8436,7 @@
       <c r="G560" s="1"/>
       <c r="H560" s="1"/>
     </row>
-    <row r="561" spans="1:8" ht="15" thickBot="1">
+    <row r="561" spans="1:8" ht="15.75" thickBot="1">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -8498,7 +8446,7 @@
       <c r="G561" s="1"/>
       <c r="H561" s="1"/>
     </row>
-    <row r="562" spans="1:8" ht="15" thickBot="1">
+    <row r="562" spans="1:8" ht="15.75" thickBot="1">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -8508,7 +8456,7 @@
       <c r="G562" s="1"/>
       <c r="H562" s="1"/>
     </row>
-    <row r="563" spans="1:8" ht="15" thickBot="1">
+    <row r="563" spans="1:8" ht="15.75" thickBot="1">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -8518,7 +8466,7 @@
       <c r="G563" s="1"/>
       <c r="H563" s="1"/>
     </row>
-    <row r="564" spans="1:8" ht="15" thickBot="1">
+    <row r="564" spans="1:8" ht="15.75" thickBot="1">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -8528,7 +8476,7 @@
       <c r="G564" s="1"/>
       <c r="H564" s="1"/>
     </row>
-    <row r="565" spans="1:8" ht="15" thickBot="1">
+    <row r="565" spans="1:8" ht="15.75" thickBot="1">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -8538,7 +8486,7 @@
       <c r="G565" s="1"/>
       <c r="H565" s="1"/>
     </row>
-    <row r="566" spans="1:8" ht="15" thickBot="1">
+    <row r="566" spans="1:8" ht="15.75" thickBot="1">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -8548,7 +8496,7 @@
       <c r="G566" s="1"/>
       <c r="H566" s="1"/>
     </row>
-    <row r="567" spans="1:8" ht="15" thickBot="1">
+    <row r="567" spans="1:8" ht="15.75" thickBot="1">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -8558,7 +8506,7 @@
       <c r="G567" s="1"/>
       <c r="H567" s="1"/>
     </row>
-    <row r="568" spans="1:8" ht="15" thickBot="1">
+    <row r="568" spans="1:8" ht="15.75" thickBot="1">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -8568,7 +8516,7 @@
       <c r="G568" s="1"/>
       <c r="H568" s="1"/>
     </row>
-    <row r="569" spans="1:8" ht="15" thickBot="1">
+    <row r="569" spans="1:8" ht="15.75" thickBot="1">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -8578,7 +8526,7 @@
       <c r="G569" s="1"/>
       <c r="H569" s="1"/>
     </row>
-    <row r="570" spans="1:8" ht="15" thickBot="1">
+    <row r="570" spans="1:8" ht="15.75" thickBot="1">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -8588,7 +8536,7 @@
       <c r="G570" s="1"/>
       <c r="H570" s="1"/>
     </row>
-    <row r="571" spans="1:8" ht="15" thickBot="1">
+    <row r="571" spans="1:8" ht="15.75" thickBot="1">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -8598,7 +8546,7 @@
       <c r="G571" s="1"/>
       <c r="H571" s="1"/>
     </row>
-    <row r="572" spans="1:8" ht="15" thickBot="1">
+    <row r="572" spans="1:8" ht="15.75" thickBot="1">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -8608,7 +8556,7 @@
       <c r="G572" s="1"/>
       <c r="H572" s="1"/>
     </row>
-    <row r="573" spans="1:8" ht="15" thickBot="1">
+    <row r="573" spans="1:8" ht="15.75" thickBot="1">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -8618,7 +8566,7 @@
       <c r="G573" s="1"/>
       <c r="H573" s="1"/>
     </row>
-    <row r="574" spans="1:8" ht="15" thickBot="1">
+    <row r="574" spans="1:8" ht="15.75" thickBot="1">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -8628,7 +8576,7 @@
       <c r="G574" s="1"/>
       <c r="H574" s="1"/>
     </row>
-    <row r="575" spans="1:8" ht="15" thickBot="1">
+    <row r="575" spans="1:8" ht="15.75" thickBot="1">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -8638,7 +8586,7 @@
       <c r="G575" s="1"/>
       <c r="H575" s="1"/>
     </row>
-    <row r="576" spans="1:8" ht="15" thickBot="1">
+    <row r="576" spans="1:8" ht="15.75" thickBot="1">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -8648,7 +8596,7 @@
       <c r="G576" s="1"/>
       <c r="H576" s="1"/>
     </row>
-    <row r="577" spans="1:8" ht="15" thickBot="1">
+    <row r="577" spans="1:8" ht="15.75" thickBot="1">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -8658,7 +8606,7 @@
       <c r="G577" s="1"/>
       <c r="H577" s="1"/>
     </row>
-    <row r="578" spans="1:8" ht="15" thickBot="1">
+    <row r="578" spans="1:8" ht="15.75" thickBot="1">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -8668,7 +8616,7 @@
       <c r="G578" s="1"/>
       <c r="H578" s="1"/>
     </row>
-    <row r="579" spans="1:8" ht="15" thickBot="1">
+    <row r="579" spans="1:8" ht="15.75" thickBot="1">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -8678,7 +8626,7 @@
       <c r="G579" s="1"/>
       <c r="H579" s="1"/>
     </row>
-    <row r="580" spans="1:8" ht="15" thickBot="1">
+    <row r="580" spans="1:8" ht="15.75" thickBot="1">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -8688,7 +8636,7 @@
       <c r="G580" s="1"/>
       <c r="H580" s="1"/>
     </row>
-    <row r="581" spans="1:8" ht="15" thickBot="1">
+    <row r="581" spans="1:8" ht="15.75" thickBot="1">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -8698,7 +8646,7 @@
       <c r="G581" s="1"/>
       <c r="H581" s="1"/>
     </row>
-    <row r="582" spans="1:8" ht="15" thickBot="1">
+    <row r="582" spans="1:8" ht="15.75" thickBot="1">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -8708,7 +8656,7 @@
       <c r="G582" s="1"/>
       <c r="H582" s="1"/>
     </row>
-    <row r="583" spans="1:8" ht="15" thickBot="1">
+    <row r="583" spans="1:8" ht="15.75" thickBot="1">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -8718,7 +8666,7 @@
       <c r="G583" s="1"/>
       <c r="H583" s="1"/>
     </row>
-    <row r="584" spans="1:8" ht="15" thickBot="1">
+    <row r="584" spans="1:8" ht="15.75" thickBot="1">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -8728,7 +8676,7 @@
       <c r="G584" s="1"/>
       <c r="H584" s="1"/>
     </row>
-    <row r="585" spans="1:8" ht="15" thickBot="1">
+    <row r="585" spans="1:8" ht="15.75" thickBot="1">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -8738,7 +8686,7 @@
       <c r="G585" s="1"/>
       <c r="H585" s="1"/>
     </row>
-    <row r="586" spans="1:8" ht="15" thickBot="1">
+    <row r="586" spans="1:8" ht="15.75" thickBot="1">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -8748,7 +8696,7 @@
       <c r="G586" s="1"/>
       <c r="H586" s="1"/>
     </row>
-    <row r="587" spans="1:8" ht="15" thickBot="1">
+    <row r="587" spans="1:8" ht="15.75" thickBot="1">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -8758,7 +8706,7 @@
       <c r="G587" s="1"/>
       <c r="H587" s="1"/>
     </row>
-    <row r="588" spans="1:8" ht="15" thickBot="1">
+    <row r="588" spans="1:8" ht="15.75" thickBot="1">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -8768,7 +8716,7 @@
       <c r="G588" s="1"/>
       <c r="H588" s="1"/>
     </row>
-    <row r="589" spans="1:8" ht="15" thickBot="1">
+    <row r="589" spans="1:8" ht="15.75" thickBot="1">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -8778,7 +8726,7 @@
       <c r="G589" s="1"/>
       <c r="H589" s="1"/>
     </row>
-    <row r="590" spans="1:8" ht="15" thickBot="1">
+    <row r="590" spans="1:8" ht="15.75" thickBot="1">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -8788,7 +8736,7 @@
       <c r="G590" s="1"/>
       <c r="H590" s="1"/>
     </row>
-    <row r="591" spans="1:8" ht="15" thickBot="1">
+    <row r="591" spans="1:8" ht="15.75" thickBot="1">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -8798,7 +8746,7 @@
       <c r="G591" s="1"/>
       <c r="H591" s="1"/>
     </row>
-    <row r="592" spans="1:8" ht="15" thickBot="1">
+    <row r="592" spans="1:8" ht="15.75" thickBot="1">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -8808,7 +8756,7 @@
       <c r="G592" s="1"/>
       <c r="H592" s="1"/>
     </row>
-    <row r="593" spans="1:8" ht="15" thickBot="1">
+    <row r="593" spans="1:8" ht="15.75" thickBot="1">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -8818,7 +8766,7 @@
       <c r="G593" s="1"/>
       <c r="H593" s="1"/>
     </row>
-    <row r="594" spans="1:8" ht="15" thickBot="1">
+    <row r="594" spans="1:8" ht="15.75" thickBot="1">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -8828,7 +8776,7 @@
       <c r="G594" s="1"/>
       <c r="H594" s="1"/>
     </row>
-    <row r="595" spans="1:8" ht="15" thickBot="1">
+    <row r="595" spans="1:8" ht="15.75" thickBot="1">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -8838,7 +8786,7 @@
       <c r="G595" s="1"/>
       <c r="H595" s="1"/>
     </row>
-    <row r="596" spans="1:8" ht="15" thickBot="1">
+    <row r="596" spans="1:8" ht="15.75" thickBot="1">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -8848,7 +8796,7 @@
       <c r="G596" s="1"/>
       <c r="H596" s="1"/>
     </row>
-    <row r="597" spans="1:8" ht="15" thickBot="1">
+    <row r="597" spans="1:8" ht="15.75" thickBot="1">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -8858,7 +8806,7 @@
       <c r="G597" s="1"/>
       <c r="H597" s="1"/>
     </row>
-    <row r="598" spans="1:8" ht="15" thickBot="1">
+    <row r="598" spans="1:8" ht="15.75" thickBot="1">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -8868,7 +8816,7 @@
       <c r="G598" s="1"/>
       <c r="H598" s="1"/>
     </row>
-    <row r="599" spans="1:8" ht="15" thickBot="1">
+    <row r="599" spans="1:8" ht="15.75" thickBot="1">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -8878,7 +8826,7 @@
       <c r="G599" s="1"/>
       <c r="H599" s="1"/>
     </row>
-    <row r="600" spans="1:8" ht="15" thickBot="1">
+    <row r="600" spans="1:8" ht="15.75" thickBot="1">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -8888,7 +8836,7 @@
       <c r="G600" s="1"/>
       <c r="H600" s="1"/>
     </row>
-    <row r="601" spans="1:8" ht="15" thickBot="1">
+    <row r="601" spans="1:8" ht="15.75" thickBot="1">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -8898,7 +8846,7 @@
       <c r="G601" s="1"/>
       <c r="H601" s="1"/>
     </row>
-    <row r="602" spans="1:8" ht="15" thickBot="1">
+    <row r="602" spans="1:8" ht="15.75" thickBot="1">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -8908,7 +8856,7 @@
       <c r="G602" s="1"/>
       <c r="H602" s="1"/>
     </row>
-    <row r="603" spans="1:8" ht="15" thickBot="1">
+    <row r="603" spans="1:8" ht="15.75" thickBot="1">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -8918,7 +8866,7 @@
       <c r="G603" s="1"/>
       <c r="H603" s="1"/>
     </row>
-    <row r="604" spans="1:8" ht="15" thickBot="1">
+    <row r="604" spans="1:8" ht="15.75" thickBot="1">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -8928,7 +8876,7 @@
       <c r="G604" s="1"/>
       <c r="H604" s="1"/>
     </row>
-    <row r="605" spans="1:8" ht="15" thickBot="1">
+    <row r="605" spans="1:8" ht="15.75" thickBot="1">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -8938,7 +8886,7 @@
       <c r="G605" s="1"/>
       <c r="H605" s="1"/>
     </row>
-    <row r="606" spans="1:8" ht="15" thickBot="1">
+    <row r="606" spans="1:8" ht="15.75" thickBot="1">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -8948,7 +8896,7 @@
       <c r="G606" s="1"/>
       <c r="H606" s="1"/>
     </row>
-    <row r="607" spans="1:8" ht="15" thickBot="1">
+    <row r="607" spans="1:8" ht="15.75" thickBot="1">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -8958,7 +8906,7 @@
       <c r="G607" s="1"/>
       <c r="H607" s="1"/>
     </row>
-    <row r="608" spans="1:8" ht="15" thickBot="1">
+    <row r="608" spans="1:8" ht="15.75" thickBot="1">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -8968,7 +8916,7 @@
       <c r="G608" s="1"/>
       <c r="H608" s="1"/>
     </row>
-    <row r="609" spans="1:8" ht="15" thickBot="1">
+    <row r="609" spans="1:8" ht="15.75" thickBot="1">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -8978,7 +8926,7 @@
       <c r="G609" s="1"/>
       <c r="H609" s="1"/>
     </row>
-    <row r="610" spans="1:8" ht="15" thickBot="1">
+    <row r="610" spans="1:8" ht="15.75" thickBot="1">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -8988,7 +8936,7 @@
       <c r="G610" s="1"/>
       <c r="H610" s="1"/>
     </row>
-    <row r="611" spans="1:8" ht="15" thickBot="1">
+    <row r="611" spans="1:8" ht="15.75" thickBot="1">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -8998,7 +8946,7 @@
       <c r="G611" s="1"/>
       <c r="H611" s="1"/>
     </row>
-    <row r="612" spans="1:8" ht="15" thickBot="1">
+    <row r="612" spans="1:8" ht="15.75" thickBot="1">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -9008,7 +8956,7 @@
       <c r="G612" s="1"/>
       <c r="H612" s="1"/>
     </row>
-    <row r="613" spans="1:8" ht="15" thickBot="1">
+    <row r="613" spans="1:8" ht="15.75" thickBot="1">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -9018,7 +8966,7 @@
       <c r="G613" s="1"/>
       <c r="H613" s="1"/>
     </row>
-    <row r="614" spans="1:8" ht="15" thickBot="1">
+    <row r="614" spans="1:8" ht="15.75" thickBot="1">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -9028,7 +8976,7 @@
       <c r="G614" s="1"/>
       <c r="H614" s="1"/>
     </row>
-    <row r="615" spans="1:8" ht="15" thickBot="1">
+    <row r="615" spans="1:8" ht="15.75" thickBot="1">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -9038,7 +8986,7 @@
       <c r="G615" s="1"/>
       <c r="H615" s="1"/>
     </row>
-    <row r="616" spans="1:8" ht="15" thickBot="1">
+    <row r="616" spans="1:8" ht="15.75" thickBot="1">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -9048,7 +8996,7 @@
       <c r="G616" s="1"/>
       <c r="H616" s="1"/>
     </row>
-    <row r="617" spans="1:8" ht="15" thickBot="1">
+    <row r="617" spans="1:8" ht="15.75" thickBot="1">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -9058,7 +9006,7 @@
       <c r="G617" s="1"/>
       <c r="H617" s="1"/>
     </row>
-    <row r="618" spans="1:8" ht="15" thickBot="1">
+    <row r="618" spans="1:8" ht="15.75" thickBot="1">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -9068,7 +9016,7 @@
       <c r="G618" s="1"/>
       <c r="H618" s="1"/>
     </row>
-    <row r="619" spans="1:8" ht="15" thickBot="1">
+    <row r="619" spans="1:8" ht="15.75" thickBot="1">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -9078,7 +9026,7 @@
       <c r="G619" s="1"/>
       <c r="H619" s="1"/>
     </row>
-    <row r="620" spans="1:8" ht="15" thickBot="1">
+    <row r="620" spans="1:8" ht="15.75" thickBot="1">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -9088,7 +9036,7 @@
       <c r="G620" s="1"/>
       <c r="H620" s="1"/>
     </row>
-    <row r="621" spans="1:8" ht="15" thickBot="1">
+    <row r="621" spans="1:8" ht="15.75" thickBot="1">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -9098,7 +9046,7 @@
       <c r="G621" s="1"/>
       <c r="H621" s="1"/>
     </row>
-    <row r="622" spans="1:8" ht="15" thickBot="1">
+    <row r="622" spans="1:8" ht="15.75" thickBot="1">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -9108,7 +9056,7 @@
       <c r="G622" s="1"/>
       <c r="H622" s="1"/>
     </row>
-    <row r="623" spans="1:8" ht="15" thickBot="1">
+    <row r="623" spans="1:8" ht="15.75" thickBot="1">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -9118,7 +9066,7 @@
       <c r="G623" s="1"/>
       <c r="H623" s="1"/>
     </row>
-    <row r="624" spans="1:8" ht="15" thickBot="1">
+    <row r="624" spans="1:8" ht="15.75" thickBot="1">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -9128,7 +9076,7 @@
       <c r="G624" s="1"/>
       <c r="H624" s="1"/>
     </row>
-    <row r="625" spans="1:8" ht="15" thickBot="1">
+    <row r="625" spans="1:8" ht="15.75" thickBot="1">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -9138,7 +9086,7 @@
       <c r="G625" s="1"/>
       <c r="H625" s="1"/>
     </row>
-    <row r="626" spans="1:8" ht="15" thickBot="1">
+    <row r="626" spans="1:8" ht="15.75" thickBot="1">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -9148,7 +9096,7 @@
       <c r="G626" s="1"/>
       <c r="H626" s="1"/>
     </row>
-    <row r="627" spans="1:8" ht="15" thickBot="1">
+    <row r="627" spans="1:8" ht="15.75" thickBot="1">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -9158,7 +9106,7 @@
       <c r="G627" s="1"/>
       <c r="H627" s="1"/>
     </row>
-    <row r="628" spans="1:8" ht="15" thickBot="1">
+    <row r="628" spans="1:8" ht="15.75" thickBot="1">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -9168,7 +9116,7 @@
       <c r="G628" s="1"/>
       <c r="H628" s="1"/>
     </row>
-    <row r="629" spans="1:8" ht="15" thickBot="1">
+    <row r="629" spans="1:8" ht="15.75" thickBot="1">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -9178,7 +9126,7 @@
       <c r="G629" s="1"/>
       <c r="H629" s="1"/>
     </row>
-    <row r="630" spans="1:8" ht="15" thickBot="1">
+    <row r="630" spans="1:8" ht="15.75" thickBot="1">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -9188,7 +9136,7 @@
       <c r="G630" s="1"/>
       <c r="H630" s="1"/>
     </row>
-    <row r="631" spans="1:8" ht="15" thickBot="1">
+    <row r="631" spans="1:8" ht="15.75" thickBot="1">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -9198,7 +9146,7 @@
       <c r="G631" s="1"/>
       <c r="H631" s="1"/>
     </row>
-    <row r="632" spans="1:8" ht="15" thickBot="1">
+    <row r="632" spans="1:8" ht="15.75" thickBot="1">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -9208,7 +9156,7 @@
       <c r="G632" s="1"/>
       <c r="H632" s="1"/>
     </row>
-    <row r="633" spans="1:8" ht="15" thickBot="1">
+    <row r="633" spans="1:8" ht="15.75" thickBot="1">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -9218,7 +9166,7 @@
       <c r="G633" s="1"/>
       <c r="H633" s="1"/>
     </row>
-    <row r="634" spans="1:8" ht="15" thickBot="1">
+    <row r="634" spans="1:8" ht="15.75" thickBot="1">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -9228,7 +9176,7 @@
       <c r="G634" s="1"/>
       <c r="H634" s="1"/>
     </row>
-    <row r="635" spans="1:8" ht="15" thickBot="1">
+    <row r="635" spans="1:8" ht="15.75" thickBot="1">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -9238,7 +9186,7 @@
       <c r="G635" s="1"/>
       <c r="H635" s="1"/>
     </row>
-    <row r="636" spans="1:8" ht="15" thickBot="1">
+    <row r="636" spans="1:8" ht="15.75" thickBot="1">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -9248,7 +9196,7 @@
       <c r="G636" s="1"/>
       <c r="H636" s="1"/>
     </row>
-    <row r="637" spans="1:8" ht="15" thickBot="1">
+    <row r="637" spans="1:8" ht="15.75" thickBot="1">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -9258,7 +9206,7 @@
       <c r="G637" s="1"/>
       <c r="H637" s="1"/>
     </row>
-    <row r="638" spans="1:8" ht="15" thickBot="1">
+    <row r="638" spans="1:8" ht="15.75" thickBot="1">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -9268,7 +9216,7 @@
       <c r="G638" s="1"/>
       <c r="H638" s="1"/>
     </row>
-    <row r="639" spans="1:8" ht="15" thickBot="1">
+    <row r="639" spans="1:8" ht="15.75" thickBot="1">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -9278,7 +9226,7 @@
       <c r="G639" s="1"/>
       <c r="H639" s="1"/>
     </row>
-    <row r="640" spans="1:8" ht="15" thickBot="1">
+    <row r="640" spans="1:8" ht="15.75" thickBot="1">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -9288,7 +9236,7 @@
       <c r="G640" s="1"/>
       <c r="H640" s="1"/>
     </row>
-    <row r="641" spans="1:8" ht="15" thickBot="1">
+    <row r="641" spans="1:8" ht="15.75" thickBot="1">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -9298,7 +9246,7 @@
       <c r="G641" s="1"/>
       <c r="H641" s="1"/>
     </row>
-    <row r="642" spans="1:8" ht="15" thickBot="1">
+    <row r="642" spans="1:8" ht="15.75" thickBot="1">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -9308,7 +9256,7 @@
       <c r="G642" s="1"/>
       <c r="H642" s="1"/>
     </row>
-    <row r="643" spans="1:8" ht="15" thickBot="1">
+    <row r="643" spans="1:8" ht="15.75" thickBot="1">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -9318,7 +9266,7 @@
       <c r="G643" s="1"/>
       <c r="H643" s="1"/>
     </row>
-    <row r="644" spans="1:8" ht="15" thickBot="1">
+    <row r="644" spans="1:8" ht="15.75" thickBot="1">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -9328,7 +9276,7 @@
       <c r="G644" s="1"/>
       <c r="H644" s="1"/>
     </row>
-    <row r="645" spans="1:8" ht="15" thickBot="1">
+    <row r="645" spans="1:8" ht="15.75" thickBot="1">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -9338,7 +9286,7 @@
       <c r="G645" s="1"/>
       <c r="H645" s="1"/>
     </row>
-    <row r="646" spans="1:8" ht="15" thickBot="1">
+    <row r="646" spans="1:8" ht="15.75" thickBot="1">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -9348,7 +9296,7 @@
       <c r="G646" s="1"/>
       <c r="H646" s="1"/>
     </row>
-    <row r="647" spans="1:8" ht="15" thickBot="1">
+    <row r="647" spans="1:8" ht="15.75" thickBot="1">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -9358,7 +9306,7 @@
       <c r="G647" s="1"/>
       <c r="H647" s="1"/>
     </row>
-    <row r="648" spans="1:8" ht="15" thickBot="1">
+    <row r="648" spans="1:8" ht="15.75" thickBot="1">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -9368,7 +9316,7 @@
       <c r="G648" s="1"/>
       <c r="H648" s="1"/>
     </row>
-    <row r="649" spans="1:8" ht="15" thickBot="1">
+    <row r="649" spans="1:8" ht="15.75" thickBot="1">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -9378,7 +9326,7 @@
       <c r="G649" s="1"/>
       <c r="H649" s="1"/>
     </row>
-    <row r="650" spans="1:8" ht="15" thickBot="1">
+    <row r="650" spans="1:8" ht="15.75" thickBot="1">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -9388,7 +9336,7 @@
       <c r="G650" s="1"/>
       <c r="H650" s="1"/>
     </row>
-    <row r="651" spans="1:8" ht="15" thickBot="1">
+    <row r="651" spans="1:8" ht="15.75" thickBot="1">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -9398,7 +9346,7 @@
       <c r="G651" s="1"/>
       <c r="H651" s="1"/>
     </row>
-    <row r="652" spans="1:8" ht="15" thickBot="1">
+    <row r="652" spans="1:8" ht="15.75" thickBot="1">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -9408,7 +9356,7 @@
       <c r="G652" s="1"/>
       <c r="H652" s="1"/>
     </row>
-    <row r="653" spans="1:8" ht="15" thickBot="1">
+    <row r="653" spans="1:8" ht="15.75" thickBot="1">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -9418,7 +9366,7 @@
       <c r="G653" s="1"/>
       <c r="H653" s="1"/>
     </row>
-    <row r="654" spans="1:8" ht="15" thickBot="1">
+    <row r="654" spans="1:8" ht="15.75" thickBot="1">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -9428,7 +9376,7 @@
       <c r="G654" s="1"/>
       <c r="H654" s="1"/>
     </row>
-    <row r="655" spans="1:8" ht="15" thickBot="1">
+    <row r="655" spans="1:8" ht="15.75" thickBot="1">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -9438,7 +9386,7 @@
       <c r="G655" s="1"/>
       <c r="H655" s="1"/>
     </row>
-    <row r="656" spans="1:8" ht="15" thickBot="1">
+    <row r="656" spans="1:8" ht="15.75" thickBot="1">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -9448,7 +9396,7 @@
       <c r="G656" s="1"/>
       <c r="H656" s="1"/>
     </row>
-    <row r="657" spans="1:8" ht="15" thickBot="1">
+    <row r="657" spans="1:8" ht="15.75" thickBot="1">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -9458,7 +9406,7 @@
       <c r="G657" s="1"/>
       <c r="H657" s="1"/>
     </row>
-    <row r="658" spans="1:8" ht="15" thickBot="1">
+    <row r="658" spans="1:8" ht="15.75" thickBot="1">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -9468,7 +9416,7 @@
       <c r="G658" s="1"/>
       <c r="H658" s="1"/>
     </row>
-    <row r="659" spans="1:8" ht="15" thickBot="1">
+    <row r="659" spans="1:8" ht="15.75" thickBot="1">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -9478,7 +9426,7 @@
       <c r="G659" s="1"/>
       <c r="H659" s="1"/>
     </row>
-    <row r="660" spans="1:8" ht="15" thickBot="1">
+    <row r="660" spans="1:8" ht="15.75" thickBot="1">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -9488,7 +9436,7 @@
       <c r="G660" s="1"/>
       <c r="H660" s="1"/>
     </row>
-    <row r="661" spans="1:8" ht="15" thickBot="1">
+    <row r="661" spans="1:8" ht="15.75" thickBot="1">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -9498,7 +9446,7 @@
       <c r="G661" s="1"/>
       <c r="H661" s="1"/>
     </row>
-    <row r="662" spans="1:8" ht="15" thickBot="1">
+    <row r="662" spans="1:8" ht="15.75" thickBot="1">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -9508,7 +9456,7 @@
       <c r="G662" s="1"/>
       <c r="H662" s="1"/>
     </row>
-    <row r="663" spans="1:8" ht="15" thickBot="1">
+    <row r="663" spans="1:8" ht="15.75" thickBot="1">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -9518,7 +9466,7 @@
       <c r="G663" s="1"/>
       <c r="H663" s="1"/>
     </row>
-    <row r="664" spans="1:8" ht="15" thickBot="1">
+    <row r="664" spans="1:8" ht="15.75" thickBot="1">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -9528,7 +9476,7 @@
       <c r="G664" s="1"/>
       <c r="H664" s="1"/>
     </row>
-    <row r="665" spans="1:8" ht="15" thickBot="1">
+    <row r="665" spans="1:8" ht="15.75" thickBot="1">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -9538,7 +9486,7 @@
       <c r="G665" s="1"/>
       <c r="H665" s="1"/>
     </row>
-    <row r="666" spans="1:8" ht="15" thickBot="1">
+    <row r="666" spans="1:8" ht="15.75" thickBot="1">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -9548,7 +9496,7 @@
       <c r="G666" s="1"/>
       <c r="H666" s="1"/>
     </row>
-    <row r="667" spans="1:8" ht="15" thickBot="1">
+    <row r="667" spans="1:8" ht="15.75" thickBot="1">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -9558,7 +9506,7 @@
       <c r="G667" s="1"/>
       <c r="H667" s="1"/>
     </row>
-    <row r="668" spans="1:8" ht="15" thickBot="1">
+    <row r="668" spans="1:8" ht="15.75" thickBot="1">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -9568,7 +9516,7 @@
       <c r="G668" s="1"/>
       <c r="H668" s="1"/>
     </row>
-    <row r="669" spans="1:8" ht="15" thickBot="1">
+    <row r="669" spans="1:8" ht="15.75" thickBot="1">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -9578,7 +9526,7 @@
       <c r="G669" s="1"/>
       <c r="H669" s="1"/>
     </row>
-    <row r="670" spans="1:8" ht="15" thickBot="1">
+    <row r="670" spans="1:8" ht="15.75" thickBot="1">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -9588,7 +9536,7 @@
       <c r="G670" s="1"/>
       <c r="H670" s="1"/>
     </row>
-    <row r="671" spans="1:8" ht="15" thickBot="1">
+    <row r="671" spans="1:8" ht="15.75" thickBot="1">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -9598,7 +9546,7 @@
       <c r="G671" s="1"/>
       <c r="H671" s="1"/>
     </row>
-    <row r="672" spans="1:8" ht="15" thickBot="1">
+    <row r="672" spans="1:8" ht="15.75" thickBot="1">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -9608,7 +9556,7 @@
       <c r="G672" s="1"/>
       <c r="H672" s="1"/>
     </row>
-    <row r="673" spans="1:8" ht="15" thickBot="1">
+    <row r="673" spans="1:8" ht="15.75" thickBot="1">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -9618,7 +9566,7 @@
       <c r="G673" s="1"/>
       <c r="H673" s="1"/>
     </row>
-    <row r="674" spans="1:8" ht="15" thickBot="1">
+    <row r="674" spans="1:8" ht="15.75" thickBot="1">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -9628,7 +9576,7 @@
       <c r="G674" s="1"/>
       <c r="H674" s="1"/>
     </row>
-    <row r="675" spans="1:8" ht="15" thickBot="1">
+    <row r="675" spans="1:8" ht="15.75" thickBot="1">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -9638,7 +9586,7 @@
       <c r="G675" s="1"/>
       <c r="H675" s="1"/>
     </row>
-    <row r="676" spans="1:8" ht="15" thickBot="1">
+    <row r="676" spans="1:8" ht="15.75" thickBot="1">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -9648,7 +9596,7 @@
       <c r="G676" s="1"/>
       <c r="H676" s="1"/>
     </row>
-    <row r="677" spans="1:8" ht="15" thickBot="1">
+    <row r="677" spans="1:8" ht="15.75" thickBot="1">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -9658,7 +9606,7 @@
       <c r="G677" s="1"/>
       <c r="H677" s="1"/>
     </row>
-    <row r="678" spans="1:8" ht="15" thickBot="1">
+    <row r="678" spans="1:8" ht="15.75" thickBot="1">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -9668,7 +9616,7 @@
       <c r="G678" s="1"/>
       <c r="H678" s="1"/>
     </row>
-    <row r="679" spans="1:8" ht="15" thickBot="1">
+    <row r="679" spans="1:8" ht="15.75" thickBot="1">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -9678,7 +9626,7 @@
       <c r="G679" s="1"/>
       <c r="H679" s="1"/>
     </row>
-    <row r="680" spans="1:8" ht="15" thickBot="1">
+    <row r="680" spans="1:8" ht="15.75" thickBot="1">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -9688,7 +9636,7 @@
       <c r="G680" s="1"/>
       <c r="H680" s="1"/>
     </row>
-    <row r="681" spans="1:8" ht="15" thickBot="1">
+    <row r="681" spans="1:8" ht="15.75" thickBot="1">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -9698,7 +9646,7 @@
       <c r="G681" s="1"/>
       <c r="H681" s="1"/>
     </row>
-    <row r="682" spans="1:8" ht="15" thickBot="1">
+    <row r="682" spans="1:8" ht="15.75" thickBot="1">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -9708,7 +9656,7 @@
       <c r="G682" s="1"/>
       <c r="H682" s="1"/>
     </row>
-    <row r="683" spans="1:8" ht="15" thickBot="1">
+    <row r="683" spans="1:8" ht="15.75" thickBot="1">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -9718,7 +9666,7 @@
       <c r="G683" s="1"/>
       <c r="H683" s="1"/>
     </row>
-    <row r="684" spans="1:8" ht="15" thickBot="1">
+    <row r="684" spans="1:8" ht="15.75" thickBot="1">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -9728,7 +9676,7 @@
       <c r="G684" s="1"/>
       <c r="H684" s="1"/>
     </row>
-    <row r="685" spans="1:8" ht="15" thickBot="1">
+    <row r="685" spans="1:8" ht="15.75" thickBot="1">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -9738,7 +9686,7 @@
       <c r="G685" s="1"/>
       <c r="H685" s="1"/>
     </row>
-    <row r="686" spans="1:8" ht="15" thickBot="1">
+    <row r="686" spans="1:8" ht="15.75" thickBot="1">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -9748,7 +9696,7 @@
       <c r="G686" s="1"/>
       <c r="H686" s="1"/>
     </row>
-    <row r="687" spans="1:8" ht="15" thickBot="1">
+    <row r="687" spans="1:8" ht="15.75" thickBot="1">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -9758,7 +9706,7 @@
       <c r="G687" s="1"/>
       <c r="H687" s="1"/>
     </row>
-    <row r="688" spans="1:8" ht="15" thickBot="1">
+    <row r="688" spans="1:8" ht="15.75" thickBot="1">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -9768,7 +9716,7 @@
       <c r="G688" s="1"/>
       <c r="H688" s="1"/>
     </row>
-    <row r="689" spans="1:8" ht="15" thickBot="1">
+    <row r="689" spans="1:8" ht="15.75" thickBot="1">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -9778,7 +9726,7 @@
       <c r="G689" s="1"/>
       <c r="H689" s="1"/>
     </row>
-    <row r="690" spans="1:8" ht="15" thickBot="1">
+    <row r="690" spans="1:8" ht="15.75" thickBot="1">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -9788,7 +9736,7 @@
       <c r="G690" s="1"/>
       <c r="H690" s="1"/>
     </row>
-    <row r="691" spans="1:8" ht="15" thickBot="1">
+    <row r="691" spans="1:8" ht="15.75" thickBot="1">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -9798,7 +9746,7 @@
       <c r="G691" s="1"/>
       <c r="H691" s="1"/>
     </row>
-    <row r="692" spans="1:8" ht="15" thickBot="1">
+    <row r="692" spans="1:8" ht="15.75" thickBot="1">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -9808,7 +9756,7 @@
       <c r="G692" s="1"/>
       <c r="H692" s="1"/>
     </row>
-    <row r="693" spans="1:8" ht="15" thickBot="1">
+    <row r="693" spans="1:8" ht="15.75" thickBot="1">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -9818,7 +9766,7 @@
       <c r="G693" s="1"/>
       <c r="H693" s="1"/>
     </row>
-    <row r="694" spans="1:8" ht="15" thickBot="1">
+    <row r="694" spans="1:8" ht="15.75" thickBot="1">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -9828,7 +9776,7 @@
       <c r="G694" s="1"/>
       <c r="H694" s="1"/>
     </row>
-    <row r="695" spans="1:8" ht="15" thickBot="1">
+    <row r="695" spans="1:8" ht="15.75" thickBot="1">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -9838,7 +9786,7 @@
       <c r="G695" s="1"/>
       <c r="H695" s="1"/>
     </row>
-    <row r="696" spans="1:8" ht="15" thickBot="1">
+    <row r="696" spans="1:8" ht="15.75" thickBot="1">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -9848,7 +9796,7 @@
       <c r="G696" s="1"/>
       <c r="H696" s="1"/>
     </row>
-    <row r="697" spans="1:8" ht="15" thickBot="1">
+    <row r="697" spans="1:8" ht="15.75" thickBot="1">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -9858,7 +9806,7 @@
       <c r="G697" s="1"/>
       <c r="H697" s="1"/>
     </row>
-    <row r="698" spans="1:8" ht="15" thickBot="1">
+    <row r="698" spans="1:8" ht="15.75" thickBot="1">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -9868,7 +9816,7 @@
       <c r="G698" s="1"/>
       <c r="H698" s="1"/>
     </row>
-    <row r="699" spans="1:8" ht="15" thickBot="1">
+    <row r="699" spans="1:8" ht="15.75" thickBot="1">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -9878,7 +9826,7 @@
       <c r="G699" s="1"/>
       <c r="H699" s="1"/>
     </row>
-    <row r="700" spans="1:8" ht="15" thickBot="1">
+    <row r="700" spans="1:8" ht="15.75" thickBot="1">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -9888,7 +9836,7 @@
       <c r="G700" s="1"/>
       <c r="H700" s="1"/>
     </row>
-    <row r="701" spans="1:8" ht="15" thickBot="1">
+    <row r="701" spans="1:8" ht="15.75" thickBot="1">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -9898,7 +9846,7 @@
       <c r="G701" s="1"/>
       <c r="H701" s="1"/>
     </row>
-    <row r="702" spans="1:8" ht="15" thickBot="1">
+    <row r="702" spans="1:8" ht="15.75" thickBot="1">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -9908,7 +9856,7 @@
       <c r="G702" s="1"/>
       <c r="H702" s="1"/>
     </row>
-    <row r="703" spans="1:8" ht="15" thickBot="1">
+    <row r="703" spans="1:8" ht="15.75" thickBot="1">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -9918,7 +9866,7 @@
       <c r="G703" s="1"/>
       <c r="H703" s="1"/>
     </row>
-    <row r="704" spans="1:8" ht="15" thickBot="1">
+    <row r="704" spans="1:8" ht="15.75" thickBot="1">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -9928,7 +9876,7 @@
       <c r="G704" s="1"/>
       <c r="H704" s="1"/>
     </row>
-    <row r="705" spans="1:8" ht="15" thickBot="1">
+    <row r="705" spans="1:8" ht="15.75" thickBot="1">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -9938,7 +9886,7 @@
       <c r="G705" s="1"/>
       <c r="H705" s="1"/>
     </row>
-    <row r="706" spans="1:8" ht="15" thickBot="1">
+    <row r="706" spans="1:8" ht="15.75" thickBot="1">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -9948,7 +9896,7 @@
       <c r="G706" s="1"/>
       <c r="H706" s="1"/>
     </row>
-    <row r="707" spans="1:8" ht="15" thickBot="1">
+    <row r="707" spans="1:8" ht="15.75" thickBot="1">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -9958,7 +9906,7 @@
       <c r="G707" s="1"/>
       <c r="H707" s="1"/>
     </row>
-    <row r="708" spans="1:8" ht="15" thickBot="1">
+    <row r="708" spans="1:8" ht="15.75" thickBot="1">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -9968,7 +9916,7 @@
       <c r="G708" s="1"/>
       <c r="H708" s="1"/>
     </row>
-    <row r="709" spans="1:8" ht="15" thickBot="1">
+    <row r="709" spans="1:8" ht="15.75" thickBot="1">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -9978,7 +9926,7 @@
       <c r="G709" s="1"/>
       <c r="H709" s="1"/>
     </row>
-    <row r="710" spans="1:8" ht="15" thickBot="1">
+    <row r="710" spans="1:8" ht="15.75" thickBot="1">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -9988,7 +9936,7 @@
       <c r="G710" s="1"/>
       <c r="H710" s="1"/>
     </row>
-    <row r="711" spans="1:8" ht="15" thickBot="1">
+    <row r="711" spans="1:8" ht="15.75" thickBot="1">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -9998,7 +9946,7 @@
       <c r="G711" s="1"/>
       <c r="H711" s="1"/>
     </row>
-    <row r="712" spans="1:8" ht="15" thickBot="1">
+    <row r="712" spans="1:8" ht="15.75" thickBot="1">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -10008,7 +9956,7 @@
       <c r="G712" s="1"/>
       <c r="H712" s="1"/>
     </row>
-    <row r="713" spans="1:8" ht="15" thickBot="1">
+    <row r="713" spans="1:8" ht="15.75" thickBot="1">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -10018,7 +9966,7 @@
       <c r="G713" s="1"/>
       <c r="H713" s="1"/>
     </row>
-    <row r="714" spans="1:8" ht="15" thickBot="1">
+    <row r="714" spans="1:8" ht="15.75" thickBot="1">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -10028,7 +9976,7 @@
       <c r="G714" s="1"/>
       <c r="H714" s="1"/>
     </row>
-    <row r="715" spans="1:8" ht="15" thickBot="1">
+    <row r="715" spans="1:8" ht="15.75" thickBot="1">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -10038,7 +9986,7 @@
       <c r="G715" s="1"/>
       <c r="H715" s="1"/>
     </row>
-    <row r="716" spans="1:8" ht="15" thickBot="1">
+    <row r="716" spans="1:8" ht="15.75" thickBot="1">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -10048,7 +9996,7 @@
       <c r="G716" s="1"/>
       <c r="H716" s="1"/>
     </row>
-    <row r="717" spans="1:8" ht="15" thickBot="1">
+    <row r="717" spans="1:8" ht="15.75" thickBot="1">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -10058,7 +10006,7 @@
       <c r="G717" s="1"/>
       <c r="H717" s="1"/>
     </row>
-    <row r="718" spans="1:8" ht="15" thickBot="1">
+    <row r="718" spans="1:8" ht="15.75" thickBot="1">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -10068,7 +10016,7 @@
       <c r="G718" s="1"/>
       <c r="H718" s="1"/>
     </row>
-    <row r="719" spans="1:8" ht="15" thickBot="1">
+    <row r="719" spans="1:8" ht="15.75" thickBot="1">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -10078,7 +10026,7 @@
       <c r="G719" s="1"/>
       <c r="H719" s="1"/>
     </row>
-    <row r="720" spans="1:8" ht="15" thickBot="1">
+    <row r="720" spans="1:8" ht="15.75" thickBot="1">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -10088,7 +10036,7 @@
       <c r="G720" s="1"/>
       <c r="H720" s="1"/>
     </row>
-    <row r="721" spans="1:8" ht="15" thickBot="1">
+    <row r="721" spans="1:8" ht="15.75" thickBot="1">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -10098,7 +10046,7 @@
       <c r="G721" s="1"/>
       <c r="H721" s="1"/>
     </row>
-    <row r="722" spans="1:8" ht="15" thickBot="1">
+    <row r="722" spans="1:8" ht="15.75" thickBot="1">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -10108,7 +10056,7 @@
       <c r="G722" s="1"/>
       <c r="H722" s="1"/>
     </row>
-    <row r="723" spans="1:8" ht="15" thickBot="1">
+    <row r="723" spans="1:8" ht="15.75" thickBot="1">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -10118,7 +10066,7 @@
       <c r="G723" s="1"/>
       <c r="H723" s="1"/>
     </row>
-    <row r="724" spans="1:8" ht="15" thickBot="1">
+    <row r="724" spans="1:8" ht="15.75" thickBot="1">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -10128,7 +10076,7 @@
       <c r="G724" s="1"/>
       <c r="H724" s="1"/>
     </row>
-    <row r="725" spans="1:8" ht="15" thickBot="1">
+    <row r="725" spans="1:8" ht="15.75" thickBot="1">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -10138,7 +10086,7 @@
       <c r="G725" s="1"/>
       <c r="H725" s="1"/>
     </row>
-    <row r="726" spans="1:8" ht="15" thickBot="1">
+    <row r="726" spans="1:8" ht="15.75" thickBot="1">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -10148,7 +10096,7 @@
       <c r="G726" s="1"/>
       <c r="H726" s="1"/>
     </row>
-    <row r="727" spans="1:8" ht="15" thickBot="1">
+    <row r="727" spans="1:8" ht="15.75" thickBot="1">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -10158,7 +10106,7 @@
       <c r="G727" s="1"/>
       <c r="H727" s="1"/>
     </row>
-    <row r="728" spans="1:8" ht="15" thickBot="1">
+    <row r="728" spans="1:8" ht="15.75" thickBot="1">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -10168,7 +10116,7 @@
       <c r="G728" s="1"/>
       <c r="H728" s="1"/>
     </row>
-    <row r="729" spans="1:8" ht="15" thickBot="1">
+    <row r="729" spans="1:8" ht="15.75" thickBot="1">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -10178,7 +10126,7 @@
       <c r="G729" s="1"/>
       <c r="H729" s="1"/>
     </row>
-    <row r="730" spans="1:8" ht="15" thickBot="1">
+    <row r="730" spans="1:8" ht="15.75" thickBot="1">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -10188,7 +10136,7 @@
       <c r="G730" s="1"/>
       <c r="H730" s="1"/>
     </row>
-    <row r="731" spans="1:8" ht="15" thickBot="1">
+    <row r="731" spans="1:8" ht="15.75" thickBot="1">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -10198,7 +10146,7 @@
       <c r="G731" s="1"/>
       <c r="H731" s="1"/>
     </row>
-    <row r="732" spans="1:8" ht="15" thickBot="1">
+    <row r="732" spans="1:8" ht="15.75" thickBot="1">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -10208,7 +10156,7 @@
       <c r="G732" s="1"/>
       <c r="H732" s="1"/>
     </row>
-    <row r="733" spans="1:8" ht="15" thickBot="1">
+    <row r="733" spans="1:8" ht="15.75" thickBot="1">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -10218,7 +10166,7 @@
       <c r="G733" s="1"/>
       <c r="H733" s="1"/>
     </row>
-    <row r="734" spans="1:8" ht="15" thickBot="1">
+    <row r="734" spans="1:8" ht="15.75" thickBot="1">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -10228,7 +10176,7 @@
       <c r="G734" s="1"/>
       <c r="H734" s="1"/>
     </row>
-    <row r="735" spans="1:8" ht="15" thickBot="1">
+    <row r="735" spans="1:8" ht="15.75" thickBot="1">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -10238,7 +10186,7 @@
       <c r="G735" s="1"/>
       <c r="H735" s="1"/>
     </row>
-    <row r="736" spans="1:8" ht="15" thickBot="1">
+    <row r="736" spans="1:8" ht="15.75" thickBot="1">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -10248,7 +10196,7 @@
       <c r="G736" s="1"/>
       <c r="H736" s="1"/>
     </row>
-    <row r="737" spans="1:8" ht="15" thickBot="1">
+    <row r="737" spans="1:8" ht="15.75" thickBot="1">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -10258,7 +10206,7 @@
       <c r="G737" s="1"/>
       <c r="H737" s="1"/>
     </row>
-    <row r="738" spans="1:8" ht="15" thickBot="1">
+    <row r="738" spans="1:8" ht="15.75" thickBot="1">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -10268,7 +10216,7 @@
       <c r="G738" s="1"/>
       <c r="H738" s="1"/>
     </row>
-    <row r="739" spans="1:8" ht="15" thickBot="1">
+    <row r="739" spans="1:8" ht="15.75" thickBot="1">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -10278,7 +10226,7 @@
       <c r="G739" s="1"/>
       <c r="H739" s="1"/>
     </row>
-    <row r="740" spans="1:8" ht="15" thickBot="1">
+    <row r="740" spans="1:8" ht="15.75" thickBot="1">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -10288,7 +10236,7 @@
       <c r="G740" s="1"/>
       <c r="H740" s="1"/>
     </row>
-    <row r="741" spans="1:8" ht="15" thickBot="1">
+    <row r="741" spans="1:8" ht="15.75" thickBot="1">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -10298,7 +10246,7 @@
       <c r="G741" s="1"/>
       <c r="H741" s="1"/>
     </row>
-    <row r="742" spans="1:8" ht="15" thickBot="1">
+    <row r="742" spans="1:8" ht="15.75" thickBot="1">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -10308,7 +10256,7 @@
       <c r="G742" s="1"/>
       <c r="H742" s="1"/>
     </row>
-    <row r="743" spans="1:8" ht="15" thickBot="1">
+    <row r="743" spans="1:8" ht="15.75" thickBot="1">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -10318,7 +10266,7 @@
       <c r="G743" s="1"/>
       <c r="H743" s="1"/>
     </row>
-    <row r="744" spans="1:8" ht="15" thickBot="1">
+    <row r="744" spans="1:8" ht="15.75" thickBot="1">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -10328,7 +10276,7 @@
       <c r="G744" s="1"/>
       <c r="H744" s="1"/>
     </row>
-    <row r="745" spans="1:8" ht="15" thickBot="1">
+    <row r="745" spans="1:8" ht="15.75" thickBot="1">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -10338,7 +10286,7 @@
       <c r="G745" s="1"/>
       <c r="H745" s="1"/>
     </row>
-    <row r="746" spans="1:8" ht="15" thickBot="1">
+    <row r="746" spans="1:8" ht="15.75" thickBot="1">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -10348,7 +10296,7 @@
       <c r="G746" s="1"/>
       <c r="H746" s="1"/>
     </row>
-    <row r="747" spans="1:8" ht="15" thickBot="1">
+    <row r="747" spans="1:8" ht="15.75" thickBot="1">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -10358,7 +10306,7 @@
       <c r="G747" s="1"/>
       <c r="H747" s="1"/>
     </row>
-    <row r="748" spans="1:8" ht="15" thickBot="1">
+    <row r="748" spans="1:8" ht="15.75" thickBot="1">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -10368,7 +10316,7 @@
       <c r="G748" s="1"/>
       <c r="H748" s="1"/>
     </row>
-    <row r="749" spans="1:8" ht="15" thickBot="1">
+    <row r="749" spans="1:8" ht="15.75" thickBot="1">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -10378,7 +10326,7 @@
       <c r="G749" s="1"/>
       <c r="H749" s="1"/>
     </row>
-    <row r="750" spans="1:8" ht="15" thickBot="1">
+    <row r="750" spans="1:8" ht="15.75" thickBot="1">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -10388,7 +10336,7 @@
       <c r="G750" s="1"/>
       <c r="H750" s="1"/>
     </row>
-    <row r="751" spans="1:8" ht="15" thickBot="1">
+    <row r="751" spans="1:8" ht="15.75" thickBot="1">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -10398,7 +10346,7 @@
       <c r="G751" s="1"/>
       <c r="H751" s="1"/>
     </row>
-    <row r="752" spans="1:8" ht="15" thickBot="1">
+    <row r="752" spans="1:8" ht="15.75" thickBot="1">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -10408,7 +10356,7 @@
       <c r="G752" s="1"/>
       <c r="H752" s="1"/>
     </row>
-    <row r="753" spans="1:8" ht="15" thickBot="1">
+    <row r="753" spans="1:8" ht="15.75" thickBot="1">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -10418,7 +10366,7 @@
       <c r="G753" s="1"/>
       <c r="H753" s="1"/>
     </row>
-    <row r="754" spans="1:8" ht="15" thickBot="1">
+    <row r="754" spans="1:8" ht="15.75" thickBot="1">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -10428,7 +10376,7 @@
       <c r="G754" s="1"/>
       <c r="H754" s="1"/>
     </row>
-    <row r="755" spans="1:8" ht="15" thickBot="1">
+    <row r="755" spans="1:8" ht="15.75" thickBot="1">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -10438,7 +10386,7 @@
       <c r="G755" s="1"/>
       <c r="H755" s="1"/>
     </row>
-    <row r="756" spans="1:8" ht="15" thickBot="1">
+    <row r="756" spans="1:8" ht="15.75" thickBot="1">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -10448,7 +10396,7 @@
       <c r="G756" s="1"/>
       <c r="H756" s="1"/>
     </row>
-    <row r="757" spans="1:8" ht="15" thickBot="1">
+    <row r="757" spans="1:8" ht="15.75" thickBot="1">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -10458,7 +10406,7 @@
       <c r="G757" s="1"/>
       <c r="H757" s="1"/>
     </row>
-    <row r="758" spans="1:8" ht="15" thickBot="1">
+    <row r="758" spans="1:8" ht="15.75" thickBot="1">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -10468,7 +10416,7 @@
       <c r="G758" s="1"/>
       <c r="H758" s="1"/>
     </row>
-    <row r="759" spans="1:8" ht="15" thickBot="1">
+    <row r="759" spans="1:8" ht="15.75" thickBot="1">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -10478,7 +10426,7 @@
       <c r="G759" s="1"/>
       <c r="H759" s="1"/>
     </row>
-    <row r="760" spans="1:8" ht="15" thickBot="1">
+    <row r="760" spans="1:8" ht="15.75" thickBot="1">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -10488,7 +10436,7 @@
       <c r="G760" s="1"/>
       <c r="H760" s="1"/>
     </row>
-    <row r="761" spans="1:8" ht="15" thickBot="1">
+    <row r="761" spans="1:8" ht="15.75" thickBot="1">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -10498,7 +10446,7 @@
       <c r="G761" s="1"/>
       <c r="H761" s="1"/>
     </row>
-    <row r="762" spans="1:8" ht="15" thickBot="1">
+    <row r="762" spans="1:8" ht="15.75" thickBot="1">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -10508,7 +10456,7 @@
       <c r="G762" s="1"/>
       <c r="H762" s="1"/>
     </row>
-    <row r="763" spans="1:8" ht="15" thickBot="1">
+    <row r="763" spans="1:8" ht="15.75" thickBot="1">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -10518,7 +10466,7 @@
       <c r="G763" s="1"/>
       <c r="H763" s="1"/>
     </row>
-    <row r="764" spans="1:8" ht="15" thickBot="1">
+    <row r="764" spans="1:8" ht="15.75" thickBot="1">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -10528,7 +10476,7 @@
       <c r="G764" s="1"/>
       <c r="H764" s="1"/>
     </row>
-    <row r="765" spans="1:8" ht="15" thickBot="1">
+    <row r="765" spans="1:8" ht="15.75" thickBot="1">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -10538,7 +10486,7 @@
       <c r="G765" s="1"/>
       <c r="H765" s="1"/>
     </row>
-    <row r="766" spans="1:8" ht="15" thickBot="1">
+    <row r="766" spans="1:8" ht="15.75" thickBot="1">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -10548,7 +10496,7 @@
       <c r="G766" s="1"/>
       <c r="H766" s="1"/>
     </row>
-    <row r="767" spans="1:8" ht="15" thickBot="1">
+    <row r="767" spans="1:8" ht="15.75" thickBot="1">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -10558,7 +10506,7 @@
       <c r="G767" s="1"/>
       <c r="H767" s="1"/>
     </row>
-    <row r="768" spans="1:8" ht="15" thickBot="1">
+    <row r="768" spans="1:8" ht="15.75" thickBot="1">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -10568,7 +10516,7 @@
       <c r="G768" s="1"/>
       <c r="H768" s="1"/>
     </row>
-    <row r="769" spans="1:8" ht="15" thickBot="1">
+    <row r="769" spans="1:8" ht="15.75" thickBot="1">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -10578,7 +10526,7 @@
       <c r="G769" s="1"/>
       <c r="H769" s="1"/>
     </row>
-    <row r="770" spans="1:8" ht="15" thickBot="1">
+    <row r="770" spans="1:8" ht="15.75" thickBot="1">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -10588,7 +10536,7 @@
       <c r="G770" s="1"/>
       <c r="H770" s="1"/>
     </row>
-    <row r="771" spans="1:8" ht="15" thickBot="1">
+    <row r="771" spans="1:8" ht="15.75" thickBot="1">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -10598,7 +10546,7 @@
       <c r="G771" s="1"/>
       <c r="H771" s="1"/>
     </row>
-    <row r="772" spans="1:8" ht="15" thickBot="1">
+    <row r="772" spans="1:8" ht="15.75" thickBot="1">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -10608,7 +10556,7 @@
       <c r="G772" s="1"/>
       <c r="H772" s="1"/>
     </row>
-    <row r="773" spans="1:8" ht="15" thickBot="1">
+    <row r="773" spans="1:8" ht="15.75" thickBot="1">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -10618,7 +10566,7 @@
       <c r="G773" s="1"/>
       <c r="H773" s="1"/>
     </row>
-    <row r="774" spans="1:8" ht="15" thickBot="1">
+    <row r="774" spans="1:8" ht="15.75" thickBot="1">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -10628,7 +10576,7 @@
       <c r="G774" s="1"/>
       <c r="H774" s="1"/>
     </row>
-    <row r="775" spans="1:8" ht="15" thickBot="1">
+    <row r="775" spans="1:8" ht="15.75" thickBot="1">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -10638,7 +10586,7 @@
       <c r="G775" s="1"/>
       <c r="H775" s="1"/>
     </row>
-    <row r="776" spans="1:8" ht="15" thickBot="1">
+    <row r="776" spans="1:8" ht="15.75" thickBot="1">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -10648,7 +10596,7 @@
       <c r="G776" s="1"/>
       <c r="H776" s="1"/>
     </row>
-    <row r="777" spans="1:8" ht="15" thickBot="1">
+    <row r="777" spans="1:8" ht="15.75" thickBot="1">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -10658,7 +10606,7 @@
       <c r="G777" s="1"/>
       <c r="H777" s="1"/>
     </row>
-    <row r="778" spans="1:8" ht="15" thickBot="1">
+    <row r="778" spans="1:8" ht="15.75" thickBot="1">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -10668,7 +10616,7 @@
       <c r="G778" s="1"/>
       <c r="H778" s="1"/>
     </row>
-    <row r="779" spans="1:8" ht="15" thickBot="1">
+    <row r="779" spans="1:8" ht="15.75" thickBot="1">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -10678,7 +10626,7 @@
       <c r="G779" s="1"/>
       <c r="H779" s="1"/>
     </row>
-    <row r="780" spans="1:8" ht="15" thickBot="1">
+    <row r="780" spans="1:8" ht="15.75" thickBot="1">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -10688,7 +10636,7 @@
       <c r="G780" s="1"/>
       <c r="H780" s="1"/>
     </row>
-    <row r="781" spans="1:8" ht="15" thickBot="1">
+    <row r="781" spans="1:8" ht="15.75" thickBot="1">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -10698,7 +10646,7 @@
       <c r="G781" s="1"/>
       <c r="H781" s="1"/>
     </row>
-    <row r="782" spans="1:8" ht="15" thickBot="1">
+    <row r="782" spans="1:8" ht="15.75" thickBot="1">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -10708,7 +10656,7 @@
       <c r="G782" s="1"/>
       <c r="H782" s="1"/>
     </row>
-    <row r="783" spans="1:8" ht="15" thickBot="1">
+    <row r="783" spans="1:8" ht="15.75" thickBot="1">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -10718,7 +10666,7 @@
       <c r="G783" s="1"/>
       <c r="H783" s="1"/>
     </row>
-    <row r="784" spans="1:8" ht="15" thickBot="1">
+    <row r="784" spans="1:8" ht="15.75" thickBot="1">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -10728,7 +10676,7 @@
       <c r="G784" s="1"/>
       <c r="H784" s="1"/>
     </row>
-    <row r="785" spans="1:8" ht="15" thickBot="1">
+    <row r="785" spans="1:8" ht="15.75" thickBot="1">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -10738,7 +10686,7 @@
       <c r="G785" s="1"/>
       <c r="H785" s="1"/>
     </row>
-    <row r="786" spans="1:8" ht="15" thickBot="1">
+    <row r="786" spans="1:8" ht="15.75" thickBot="1">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -10748,7 +10696,7 @@
       <c r="G786" s="1"/>
       <c r="H786" s="1"/>
     </row>
-    <row r="787" spans="1:8" ht="15" thickBot="1">
+    <row r="787" spans="1:8" ht="15.75" thickBot="1">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -10758,7 +10706,7 @@
       <c r="G787" s="1"/>
       <c r="H787" s="1"/>
     </row>
-    <row r="788" spans="1:8" ht="15" thickBot="1">
+    <row r="788" spans="1:8" ht="15.75" thickBot="1">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -10768,7 +10716,7 @@
       <c r="G788" s="1"/>
       <c r="H788" s="1"/>
     </row>
-    <row r="789" spans="1:8" ht="15" thickBot="1">
+    <row r="789" spans="1:8" ht="15.75" thickBot="1">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -10778,7 +10726,7 @@
       <c r="G789" s="1"/>
       <c r="H789" s="1"/>
     </row>
-    <row r="790" spans="1:8" ht="15" thickBot="1">
+    <row r="790" spans="1:8" ht="15.75" thickBot="1">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -10788,7 +10736,7 @@
       <c r="G790" s="1"/>
       <c r="H790" s="1"/>
     </row>
-    <row r="791" spans="1:8" ht="15" thickBot="1">
+    <row r="791" spans="1:8" ht="15.75" thickBot="1">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -10798,7 +10746,7 @@
       <c r="G791" s="1"/>
       <c r="H791" s="1"/>
     </row>
-    <row r="792" spans="1:8" ht="15" thickBot="1">
+    <row r="792" spans="1:8" ht="15.75" thickBot="1">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -10808,7 +10756,7 @@
       <c r="G792" s="1"/>
       <c r="H792" s="1"/>
     </row>
-    <row r="793" spans="1:8" ht="15" thickBot="1">
+    <row r="793" spans="1:8" ht="15.75" thickBot="1">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -10818,7 +10766,7 @@
       <c r="G793" s="1"/>
       <c r="H793" s="1"/>
     </row>
-    <row r="794" spans="1:8" ht="15" thickBot="1">
+    <row r="794" spans="1:8" ht="15.75" thickBot="1">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -10828,7 +10776,7 @@
       <c r="G794" s="1"/>
       <c r="H794" s="1"/>
     </row>
-    <row r="795" spans="1:8" ht="15" thickBot="1">
+    <row r="795" spans="1:8" ht="15.75" thickBot="1">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -10838,7 +10786,7 @@
       <c r="G795" s="1"/>
       <c r="H795" s="1"/>
     </row>
-    <row r="796" spans="1:8" ht="15" thickBot="1">
+    <row r="796" spans="1:8" ht="15.75" thickBot="1">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -10848,7 +10796,7 @@
       <c r="G796" s="1"/>
       <c r="H796" s="1"/>
     </row>
-    <row r="797" spans="1:8" ht="15" thickBot="1">
+    <row r="797" spans="1:8" ht="15.75" thickBot="1">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -10858,7 +10806,7 @@
       <c r="G797" s="1"/>
       <c r="H797" s="1"/>
     </row>
-    <row r="798" spans="1:8" ht="15" thickBot="1">
+    <row r="798" spans="1:8" ht="15.75" thickBot="1">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -10868,7 +10816,7 @@
       <c r="G798" s="1"/>
       <c r="H798" s="1"/>
     </row>
-    <row r="799" spans="1:8" ht="15" thickBot="1">
+    <row r="799" spans="1:8" ht="15.75" thickBot="1">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -10878,7 +10826,7 @@
       <c r="G799" s="1"/>
       <c r="H799" s="1"/>
     </row>
-    <row r="800" spans="1:8" ht="15" thickBot="1">
+    <row r="800" spans="1:8" ht="15.75" thickBot="1">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -10888,7 +10836,7 @@
       <c r="G800" s="1"/>
       <c r="H800" s="1"/>
     </row>
-    <row r="801" spans="1:8" ht="15" thickBot="1">
+    <row r="801" spans="1:8" ht="15.75" thickBot="1">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -10898,7 +10846,7 @@
       <c r="G801" s="1"/>
       <c r="H801" s="1"/>
     </row>
-    <row r="802" spans="1:8" ht="15" thickBot="1">
+    <row r="802" spans="1:8" ht="15.75" thickBot="1">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -10908,7 +10856,7 @@
       <c r="G802" s="1"/>
       <c r="H802" s="1"/>
     </row>
-    <row r="803" spans="1:8" ht="15" thickBot="1">
+    <row r="803" spans="1:8" ht="15.75" thickBot="1">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -10918,7 +10866,7 @@
       <c r="G803" s="1"/>
       <c r="H803" s="1"/>
     </row>
-    <row r="804" spans="1:8" ht="15" thickBot="1">
+    <row r="804" spans="1:8" ht="15.75" thickBot="1">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -10928,7 +10876,7 @@
       <c r="G804" s="1"/>
       <c r="H804" s="1"/>
     </row>
-    <row r="805" spans="1:8" ht="15" thickBot="1">
+    <row r="805" spans="1:8" ht="15.75" thickBot="1">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -10938,7 +10886,7 @@
       <c r="G805" s="1"/>
       <c r="H805" s="1"/>
     </row>
-    <row r="806" spans="1:8" ht="15" thickBot="1">
+    <row r="806" spans="1:8" ht="15.75" thickBot="1">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -10948,7 +10896,7 @@
       <c r="G806" s="1"/>
       <c r="H806" s="1"/>
     </row>
-    <row r="807" spans="1:8" ht="15" thickBot="1">
+    <row r="807" spans="1:8" ht="15.75" thickBot="1">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -10958,7 +10906,7 @@
       <c r="G807" s="1"/>
       <c r="H807" s="1"/>
     </row>
-    <row r="808" spans="1:8" ht="15" thickBot="1">
+    <row r="808" spans="1:8" ht="15.75" thickBot="1">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -10968,7 +10916,7 @@
       <c r="G808" s="1"/>
       <c r="H808" s="1"/>
     </row>
-    <row r="809" spans="1:8" ht="15" thickBot="1">
+    <row r="809" spans="1:8" ht="15.75" thickBot="1">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -10978,7 +10926,7 @@
       <c r="G809" s="1"/>
       <c r="H809" s="1"/>
     </row>
-    <row r="810" spans="1:8" ht="15" thickBot="1">
+    <row r="810" spans="1:8" ht="15.75" thickBot="1">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -10988,7 +10936,7 @@
       <c r="G810" s="1"/>
       <c r="H810" s="1"/>
     </row>
-    <row r="811" spans="1:8" ht="15" thickBot="1">
+    <row r="811" spans="1:8" ht="15.75" thickBot="1">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -10998,7 +10946,7 @@
       <c r="G811" s="1"/>
       <c r="H811" s="1"/>
     </row>
-    <row r="812" spans="1:8" ht="15" thickBot="1">
+    <row r="812" spans="1:8" ht="15.75" thickBot="1">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -11008,7 +10956,7 @@
       <c r="G812" s="1"/>
       <c r="H812" s="1"/>
     </row>
-    <row r="813" spans="1:8" ht="15" thickBot="1">
+    <row r="813" spans="1:8" ht="15.75" thickBot="1">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -11018,7 +10966,7 @@
       <c r="G813" s="1"/>
       <c r="H813" s="1"/>
     </row>
-    <row r="814" spans="1:8" ht="15" thickBot="1">
+    <row r="814" spans="1:8" ht="15.75" thickBot="1">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -11028,7 +10976,7 @@
       <c r="G814" s="1"/>
       <c r="H814" s="1"/>
     </row>
-    <row r="815" spans="1:8" ht="15" thickBot="1">
+    <row r="815" spans="1:8" ht="15.75" thickBot="1">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -11038,7 +10986,7 @@
       <c r="G815" s="1"/>
       <c r="H815" s="1"/>
     </row>
-    <row r="816" spans="1:8" ht="15" thickBot="1">
+    <row r="816" spans="1:8" ht="15.75" thickBot="1">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -11048,7 +10996,7 @@
       <c r="G816" s="1"/>
       <c r="H816" s="1"/>
     </row>
-    <row r="817" spans="1:8" ht="15" thickBot="1">
+    <row r="817" spans="1:8" ht="15.75" thickBot="1">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -11058,7 +11006,7 @@
       <c r="G817" s="1"/>
       <c r="H817" s="1"/>
     </row>
-    <row r="818" spans="1:8" ht="15" thickBot="1">
+    <row r="818" spans="1:8" ht="15.75" thickBot="1">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -11068,7 +11016,7 @@
       <c r="G818" s="1"/>
       <c r="H818" s="1"/>
     </row>
-    <row r="819" spans="1:8" ht="15" thickBot="1">
+    <row r="819" spans="1:8" ht="15.75" thickBot="1">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -11078,7 +11026,7 @@
       <c r="G819" s="1"/>
       <c r="H819" s="1"/>
     </row>
-    <row r="820" spans="1:8" ht="15" thickBot="1">
+    <row r="820" spans="1:8" ht="15.75" thickBot="1">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -11088,7 +11036,7 @@
       <c r="G820" s="1"/>
       <c r="H820" s="1"/>
     </row>
-    <row r="821" spans="1:8" ht="15" thickBot="1">
+    <row r="821" spans="1:8" ht="15.75" thickBot="1">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -11098,7 +11046,7 @@
       <c r="G821" s="1"/>
       <c r="H821" s="1"/>
     </row>
-    <row r="822" spans="1:8" ht="15" thickBot="1">
+    <row r="822" spans="1:8" ht="15.75" thickBot="1">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -11108,7 +11056,7 @@
       <c r="G822" s="1"/>
       <c r="H822" s="1"/>
     </row>
-    <row r="823" spans="1:8" ht="15" thickBot="1">
+    <row r="823" spans="1:8" ht="15.75" thickBot="1">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -11118,7 +11066,7 @@
       <c r="G823" s="1"/>
       <c r="H823" s="1"/>
     </row>
-    <row r="824" spans="1:8" ht="15" thickBot="1">
+    <row r="824" spans="1:8" ht="15.75" thickBot="1">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -11128,7 +11076,7 @@
       <c r="G824" s="1"/>
       <c r="H824" s="1"/>
     </row>
-    <row r="825" spans="1:8" ht="15" thickBot="1">
+    <row r="825" spans="1:8" ht="15.75" thickBot="1">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -11138,7 +11086,7 @@
       <c r="G825" s="1"/>
       <c r="H825" s="1"/>
     </row>
-    <row r="826" spans="1:8" ht="15" thickBot="1">
+    <row r="826" spans="1:8" ht="15.75" thickBot="1">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -11148,7 +11096,7 @@
       <c r="G826" s="1"/>
       <c r="H826" s="1"/>
     </row>
-    <row r="827" spans="1:8" ht="15" thickBot="1">
+    <row r="827" spans="1:8" ht="15.75" thickBot="1">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -11158,7 +11106,7 @@
       <c r="G827" s="1"/>
       <c r="H827" s="1"/>
     </row>
-    <row r="828" spans="1:8" ht="15" thickBot="1">
+    <row r="828" spans="1:8" ht="15.75" thickBot="1">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -11168,7 +11116,7 @@
       <c r="G828" s="1"/>
       <c r="H828" s="1"/>
     </row>
-    <row r="829" spans="1:8" ht="15" thickBot="1">
+    <row r="829" spans="1:8" ht="15.75" thickBot="1">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -11178,7 +11126,7 @@
       <c r="G829" s="1"/>
       <c r="H829" s="1"/>
     </row>
-    <row r="830" spans="1:8" ht="15" thickBot="1">
+    <row r="830" spans="1:8" ht="15.75" thickBot="1">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -11188,7 +11136,7 @@
       <c r="G830" s="1"/>
       <c r="H830" s="1"/>
     </row>
-    <row r="831" spans="1:8" ht="15" thickBot="1">
+    <row r="831" spans="1:8" ht="15.75" thickBot="1">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -11198,7 +11146,7 @@
       <c r="G831" s="1"/>
       <c r="H831" s="1"/>
     </row>
-    <row r="832" spans="1:8" ht="15" thickBot="1">
+    <row r="832" spans="1:8" ht="15.75" thickBot="1">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -11208,7 +11156,7 @@
       <c r="G832" s="1"/>
       <c r="H832" s="1"/>
     </row>
-    <row r="833" spans="1:8" ht="15" thickBot="1">
+    <row r="833" spans="1:8" ht="15.75" thickBot="1">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -11218,7 +11166,7 @@
       <c r="G833" s="1"/>
       <c r="H833" s="1"/>
     </row>
-    <row r="834" spans="1:8" ht="15" thickBot="1">
+    <row r="834" spans="1:8" ht="15.75" thickBot="1">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -11228,7 +11176,7 @@
       <c r="G834" s="1"/>
       <c r="H834" s="1"/>
     </row>
-    <row r="835" spans="1:8" ht="15" thickBot="1">
+    <row r="835" spans="1:8" ht="15.75" thickBot="1">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -11238,7 +11186,7 @@
       <c r="G835" s="1"/>
       <c r="H835" s="1"/>
     </row>
-    <row r="836" spans="1:8" ht="15" thickBot="1">
+    <row r="836" spans="1:8" ht="15.75" thickBot="1">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -11248,7 +11196,7 @@
       <c r="G836" s="1"/>
       <c r="H836" s="1"/>
     </row>
-    <row r="837" spans="1:8" ht="15" thickBot="1">
+    <row r="837" spans="1:8" ht="15.75" thickBot="1">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -11258,7 +11206,7 @@
       <c r="G837" s="1"/>
       <c r="H837" s="1"/>
     </row>
-    <row r="838" spans="1:8" ht="15" thickBot="1">
+    <row r="838" spans="1:8" ht="15.75" thickBot="1">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -11268,7 +11216,7 @@
       <c r="G838" s="1"/>
       <c r="H838" s="1"/>
     </row>
-    <row r="839" spans="1:8" ht="15" thickBot="1">
+    <row r="839" spans="1:8" ht="15.75" thickBot="1">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -11278,7 +11226,7 @@
       <c r="G839" s="1"/>
       <c r="H839" s="1"/>
     </row>
-    <row r="840" spans="1:8" ht="15" thickBot="1">
+    <row r="840" spans="1:8" ht="15.75" thickBot="1">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -11288,7 +11236,7 @@
       <c r="G840" s="1"/>
       <c r="H840" s="1"/>
     </row>
-    <row r="841" spans="1:8" ht="15" thickBot="1">
+    <row r="841" spans="1:8" ht="15.75" thickBot="1">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -11298,7 +11246,7 @@
       <c r="G841" s="1"/>
       <c r="H841" s="1"/>
     </row>
-    <row r="842" spans="1:8" ht="15" thickBot="1">
+    <row r="842" spans="1:8" ht="15.75" thickBot="1">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -11308,7 +11256,7 @@
       <c r="G842" s="1"/>
       <c r="H842" s="1"/>
     </row>
-    <row r="843" spans="1:8" ht="15" thickBot="1">
+    <row r="843" spans="1:8" ht="15.75" thickBot="1">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -11318,7 +11266,7 @@
       <c r="G843" s="1"/>
       <c r="H843" s="1"/>
     </row>
-    <row r="844" spans="1:8" ht="15" thickBot="1">
+    <row r="844" spans="1:8" ht="15.75" thickBot="1">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -11328,7 +11276,7 @@
       <c r="G844" s="1"/>
       <c r="H844" s="1"/>
     </row>
-    <row r="845" spans="1:8" ht="15" thickBot="1">
+    <row r="845" spans="1:8" ht="15.75" thickBot="1">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -11338,7 +11286,7 @@
       <c r="G845" s="1"/>
       <c r="H845" s="1"/>
     </row>
-    <row r="846" spans="1:8" ht="15" thickBot="1">
+    <row r="846" spans="1:8" ht="15.75" thickBot="1">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -11348,7 +11296,7 @@
       <c r="G846" s="1"/>
       <c r="H846" s="1"/>
     </row>
-    <row r="847" spans="1:8" ht="15" thickBot="1">
+    <row r="847" spans="1:8" ht="15.75" thickBot="1">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -11358,7 +11306,7 @@
       <c r="G847" s="1"/>
       <c r="H847" s="1"/>
     </row>
-    <row r="848" spans="1:8" ht="15" thickBot="1">
+    <row r="848" spans="1:8" ht="15.75" thickBot="1">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -11368,7 +11316,7 @@
       <c r="G848" s="1"/>
       <c r="H848" s="1"/>
     </row>
-    <row r="849" spans="1:8" ht="15" thickBot="1">
+    <row r="849" spans="1:8" ht="15.75" thickBot="1">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -11378,7 +11326,7 @@
       <c r="G849" s="1"/>
       <c r="H849" s="1"/>
     </row>
-    <row r="850" spans="1:8" ht="15" thickBot="1">
+    <row r="850" spans="1:8" ht="15.75" thickBot="1">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -11388,7 +11336,7 @@
       <c r="G850" s="1"/>
       <c r="H850" s="1"/>
     </row>
-    <row r="851" spans="1:8" ht="15" thickBot="1">
+    <row r="851" spans="1:8" ht="15.75" thickBot="1">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -11398,7 +11346,7 @@
       <c r="G851" s="1"/>
       <c r="H851" s="1"/>
     </row>
-    <row r="852" spans="1:8" ht="15" thickBot="1">
+    <row r="852" spans="1:8" ht="15.75" thickBot="1">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -11408,7 +11356,7 @@
       <c r="G852" s="1"/>
       <c r="H852" s="1"/>
     </row>
-    <row r="853" spans="1:8" ht="15" thickBot="1">
+    <row r="853" spans="1:8" ht="15.75" thickBot="1">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -11418,7 +11366,7 @@
       <c r="G853" s="1"/>
       <c r="H853" s="1"/>
     </row>
-    <row r="854" spans="1:8" ht="15" thickBot="1">
+    <row r="854" spans="1:8" ht="15.75" thickBot="1">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -11428,7 +11376,7 @@
       <c r="G854" s="1"/>
       <c r="H854" s="1"/>
     </row>
-    <row r="855" spans="1:8" ht="15" thickBot="1">
+    <row r="855" spans="1:8" ht="15.75" thickBot="1">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -11438,7 +11386,7 @@
       <c r="G855" s="1"/>
       <c r="H855" s="1"/>
     </row>
-    <row r="856" spans="1:8" ht="15" thickBot="1">
+    <row r="856" spans="1:8" ht="15.75" thickBot="1">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -11448,7 +11396,7 @@
       <c r="G856" s="1"/>
       <c r="H856" s="1"/>
     </row>
-    <row r="857" spans="1:8" ht="15" thickBot="1">
+    <row r="857" spans="1:8" ht="15.75" thickBot="1">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -11458,7 +11406,7 @@
       <c r="G857" s="1"/>
       <c r="H857" s="1"/>
     </row>
-    <row r="858" spans="1:8" ht="15" thickBot="1">
+    <row r="858" spans="1:8" ht="15.75" thickBot="1">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -11468,7 +11416,7 @@
       <c r="G858" s="1"/>
       <c r="H858" s="1"/>
     </row>
-    <row r="859" spans="1:8" ht="15" thickBot="1">
+    <row r="859" spans="1:8" ht="15.75" thickBot="1">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -11478,7 +11426,7 @@
       <c r="G859" s="1"/>
       <c r="H859" s="1"/>
     </row>
-    <row r="860" spans="1:8" ht="15" thickBot="1">
+    <row r="860" spans="1:8" ht="15.75" thickBot="1">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -11488,7 +11436,7 @@
       <c r="G860" s="1"/>
       <c r="H860" s="1"/>
     </row>
-    <row r="861" spans="1:8" ht="15" thickBot="1">
+    <row r="861" spans="1:8" ht="15.75" thickBot="1">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -11498,7 +11446,7 @@
       <c r="G861" s="1"/>
       <c r="H861" s="1"/>
     </row>
-    <row r="862" spans="1:8" ht="15" thickBot="1">
+    <row r="862" spans="1:8" ht="15.75" thickBot="1">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -11508,7 +11456,7 @@
       <c r="G862" s="1"/>
       <c r="H862" s="1"/>
     </row>
-    <row r="863" spans="1:8" ht="15" thickBot="1">
+    <row r="863" spans="1:8" ht="15.75" thickBot="1">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -11518,7 +11466,7 @@
       <c r="G863" s="1"/>
       <c r="H863" s="1"/>
     </row>
-    <row r="864" spans="1:8" ht="15" thickBot="1">
+    <row r="864" spans="1:8" ht="15.75" thickBot="1">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -11528,7 +11476,7 @@
       <c r="G864" s="1"/>
       <c r="H864" s="1"/>
     </row>
-    <row r="865" spans="1:8" ht="15" thickBot="1">
+    <row r="865" spans="1:8" ht="15.75" thickBot="1">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -11538,7 +11486,7 @@
       <c r="G865" s="1"/>
       <c r="H865" s="1"/>
     </row>
-    <row r="866" spans="1:8" ht="15" thickBot="1">
+    <row r="866" spans="1:8" ht="15.75" thickBot="1">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -11548,7 +11496,7 @@
       <c r="G866" s="1"/>
       <c r="H866" s="1"/>
     </row>
-    <row r="867" spans="1:8" ht="15" thickBot="1">
+    <row r="867" spans="1:8" ht="15.75" thickBot="1">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -11558,7 +11506,7 @@
       <c r="G867" s="1"/>
       <c r="H867" s="1"/>
     </row>
-    <row r="868" spans="1:8" ht="15" thickBot="1">
+    <row r="868" spans="1:8" ht="15.75" thickBot="1">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -11568,7 +11516,7 @@
       <c r="G868" s="1"/>
       <c r="H868" s="1"/>
     </row>
-    <row r="869" spans="1:8" ht="15" thickBot="1">
+    <row r="869" spans="1:8" ht="15.75" thickBot="1">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -11578,7 +11526,7 @@
       <c r="G869" s="1"/>
       <c r="H869" s="1"/>
     </row>
-    <row r="870" spans="1:8" ht="15" thickBot="1">
+    <row r="870" spans="1:8" ht="15.75" thickBot="1">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -11588,7 +11536,7 @@
       <c r="G870" s="1"/>
       <c r="H870" s="1"/>
     </row>
-    <row r="871" spans="1:8" ht="15" thickBot="1">
+    <row r="871" spans="1:8" ht="15.75" thickBot="1">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -11598,7 +11546,7 @@
       <c r="G871" s="1"/>
       <c r="H871" s="1"/>
     </row>
-    <row r="872" spans="1:8" ht="15" thickBot="1">
+    <row r="872" spans="1:8" ht="15.75" thickBot="1">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -11608,7 +11556,7 @@
       <c r="G872" s="1"/>
       <c r="H872" s="1"/>
     </row>
-    <row r="873" spans="1:8" ht="15" thickBot="1">
+    <row r="873" spans="1:8" ht="15.75" thickBot="1">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -11618,7 +11566,7 @@
       <c r="G873" s="1"/>
       <c r="H873" s="1"/>
     </row>
-    <row r="874" spans="1:8" ht="15" thickBot="1">
+    <row r="874" spans="1:8" ht="15.75" thickBot="1">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -11628,7 +11576,7 @@
       <c r="G874" s="1"/>
       <c r="H874" s="1"/>
     </row>
-    <row r="875" spans="1:8" ht="15" thickBot="1">
+    <row r="875" spans="1:8" ht="15.75" thickBot="1">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -11638,7 +11586,7 @@
       <c r="G875" s="1"/>
       <c r="H875" s="1"/>
     </row>
-    <row r="876" spans="1:8" ht="15" thickBot="1">
+    <row r="876" spans="1:8" ht="15.75" thickBot="1">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -11648,7 +11596,7 @@
       <c r="G876" s="1"/>
       <c r="H876" s="1"/>
     </row>
-    <row r="877" spans="1:8" ht="15" thickBot="1">
+    <row r="877" spans="1:8" ht="15.75" thickBot="1">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -11658,7 +11606,7 @@
       <c r="G877" s="1"/>
       <c r="H877" s="1"/>
     </row>
-    <row r="878" spans="1:8" ht="15" thickBot="1">
+    <row r="878" spans="1:8" ht="15.75" thickBot="1">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -11668,7 +11616,7 @@
       <c r="G878" s="1"/>
       <c r="H878" s="1"/>
     </row>
-    <row r="879" spans="1:8" ht="15" thickBot="1">
+    <row r="879" spans="1:8" ht="15.75" thickBot="1">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -11678,7 +11626,7 @@
       <c r="G879" s="1"/>
       <c r="H879" s="1"/>
     </row>
-    <row r="880" spans="1:8" ht="15" thickBot="1">
+    <row r="880" spans="1:8" ht="15.75" thickBot="1">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -11688,7 +11636,7 @@
       <c r="G880" s="1"/>
       <c r="H880" s="1"/>
     </row>
-    <row r="881" spans="1:8" ht="15" thickBot="1">
+    <row r="881" spans="1:8" ht="15.75" thickBot="1">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -11698,7 +11646,7 @@
       <c r="G881" s="1"/>
       <c r="H881" s="1"/>
     </row>
-    <row r="882" spans="1:8" ht="15" thickBot="1">
+    <row r="882" spans="1:8" ht="15.75" thickBot="1">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -11708,7 +11656,7 @@
       <c r="G882" s="1"/>
       <c r="H882" s="1"/>
     </row>
-    <row r="883" spans="1:8" ht="15" thickBot="1">
+    <row r="883" spans="1:8" ht="15.75" thickBot="1">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -11718,7 +11666,7 @@
       <c r="G883" s="1"/>
       <c r="H883" s="1"/>
     </row>
-    <row r="884" spans="1:8" ht="15" thickBot="1">
+    <row r="884" spans="1:8" ht="15.75" thickBot="1">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -11728,7 +11676,7 @@
       <c r="G884" s="1"/>
       <c r="H884" s="1"/>
     </row>
-    <row r="885" spans="1:8" ht="15" thickBot="1">
+    <row r="885" spans="1:8" ht="15.75" thickBot="1">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -11738,7 +11686,7 @@
       <c r="G885" s="1"/>
       <c r="H885" s="1"/>
     </row>
-    <row r="886" spans="1:8" ht="15" thickBot="1">
+    <row r="886" spans="1:8" ht="15.75" thickBot="1">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -11748,7 +11696,7 @@
       <c r="G886" s="1"/>
       <c r="H886" s="1"/>
     </row>
-    <row r="887" spans="1:8" ht="15" thickBot="1">
+    <row r="887" spans="1:8" ht="15.75" thickBot="1">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -11758,7 +11706,7 @@
       <c r="G887" s="1"/>
       <c r="H887" s="1"/>
     </row>
-    <row r="888" spans="1:8" ht="15" thickBot="1">
+    <row r="888" spans="1:8" ht="15.75" thickBot="1">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -11768,7 +11716,7 @@
       <c r="G888" s="1"/>
       <c r="H888" s="1"/>
     </row>
-    <row r="889" spans="1:8" ht="15" thickBot="1">
+    <row r="889" spans="1:8" ht="15.75" thickBot="1">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -11778,7 +11726,7 @@
       <c r="G889" s="1"/>
       <c r="H889" s="1"/>
     </row>
-    <row r="890" spans="1:8" ht="15" thickBot="1">
+    <row r="890" spans="1:8" ht="15.75" thickBot="1">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -11788,7 +11736,7 @@
       <c r="G890" s="1"/>
       <c r="H890" s="1"/>
     </row>
-    <row r="891" spans="1:8" ht="15" thickBot="1">
+    <row r="891" spans="1:8" ht="15.75" thickBot="1">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -11798,7 +11746,7 @@
       <c r="G891" s="1"/>
       <c r="H891" s="1"/>
     </row>
-    <row r="892" spans="1:8" ht="15" thickBot="1">
+    <row r="892" spans="1:8" ht="15.75" thickBot="1">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -11808,7 +11756,7 @@
       <c r="G892" s="1"/>
       <c r="H892" s="1"/>
     </row>
-    <row r="893" spans="1:8" ht="15" thickBot="1">
+    <row r="893" spans="1:8" ht="15.75" thickBot="1">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -11818,7 +11766,7 @@
       <c r="G893" s="1"/>
       <c r="H893" s="1"/>
     </row>
-    <row r="894" spans="1:8" ht="15" thickBot="1">
+    <row r="894" spans="1:8" ht="15.75" thickBot="1">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -11828,7 +11776,7 @@
       <c r="G894" s="1"/>
       <c r="H894" s="1"/>
     </row>
-    <row r="895" spans="1:8" ht="15" thickBot="1">
+    <row r="895" spans="1:8" ht="15.75" thickBot="1">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -11838,7 +11786,7 @@
       <c r="G895" s="1"/>
       <c r="H895" s="1"/>
     </row>
-    <row r="896" spans="1:8" ht="15" thickBot="1">
+    <row r="896" spans="1:8" ht="15.75" thickBot="1">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -11848,7 +11796,7 @@
       <c r="G896" s="1"/>
       <c r="H896" s="1"/>
     </row>
-    <row r="897" spans="1:8" ht="15" thickBot="1">
+    <row r="897" spans="1:8" ht="15.75" thickBot="1">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -11858,7 +11806,7 @@
       <c r="G897" s="1"/>
       <c r="H897" s="1"/>
     </row>
-    <row r="898" spans="1:8" ht="15" thickBot="1">
+    <row r="898" spans="1:8" ht="15.75" thickBot="1">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -11868,7 +11816,7 @@
       <c r="G898" s="1"/>
       <c r="H898" s="1"/>
     </row>
-    <row r="899" spans="1:8" ht="15" thickBot="1">
+    <row r="899" spans="1:8" ht="15.75" thickBot="1">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -11878,7 +11826,7 @@
       <c r="G899" s="1"/>
       <c r="H899" s="1"/>
     </row>
-    <row r="900" spans="1:8" ht="15" thickBot="1">
+    <row r="900" spans="1:8" ht="15.75" thickBot="1">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -11888,7 +11836,7 @@
       <c r="G900" s="1"/>
       <c r="H900" s="1"/>
     </row>
-    <row r="901" spans="1:8" ht="15" thickBot="1">
+    <row r="901" spans="1:8" ht="15.75" thickBot="1">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -11898,7 +11846,7 @@
       <c r="G901" s="1"/>
       <c r="H901" s="1"/>
     </row>
-    <row r="902" spans="1:8" ht="15" thickBot="1">
+    <row r="902" spans="1:8" ht="15.75" thickBot="1">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -11908,7 +11856,7 @@
       <c r="G902" s="1"/>
       <c r="H902" s="1"/>
     </row>
-    <row r="903" spans="1:8" ht="15" thickBot="1">
+    <row r="903" spans="1:8" ht="15.75" thickBot="1">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -11918,7 +11866,7 @@
       <c r="G903" s="1"/>
       <c r="H903" s="1"/>
     </row>
-    <row r="904" spans="1:8" ht="15" thickBot="1">
+    <row r="904" spans="1:8" ht="15.75" thickBot="1">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -11928,7 +11876,7 @@
       <c r="G904" s="1"/>
       <c r="H904" s="1"/>
     </row>
-    <row r="905" spans="1:8" ht="15" thickBot="1">
+    <row r="905" spans="1:8" ht="15.75" thickBot="1">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -11938,7 +11886,7 @@
       <c r="G905" s="1"/>
       <c r="H905" s="1"/>
     </row>
-    <row r="906" spans="1:8" ht="15" thickBot="1">
+    <row r="906" spans="1:8" ht="15.75" thickBot="1">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -11948,7 +11896,7 @@
       <c r="G906" s="1"/>
       <c r="H906" s="1"/>
     </row>
-    <row r="907" spans="1:8" ht="15" thickBot="1">
+    <row r="907" spans="1:8" ht="15.75" thickBot="1">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -11958,7 +11906,7 @@
       <c r="G907" s="1"/>
       <c r="H907" s="1"/>
     </row>
-    <row r="908" spans="1:8" ht="15" thickBot="1">
+    <row r="908" spans="1:8" ht="15.75" thickBot="1">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -11968,7 +11916,7 @@
       <c r="G908" s="1"/>
       <c r="H908" s="1"/>
     </row>
-    <row r="909" spans="1:8" ht="15" thickBot="1">
+    <row r="909" spans="1:8" ht="15.75" thickBot="1">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -11978,7 +11926,7 @@
       <c r="G909" s="1"/>
       <c r="H909" s="1"/>
     </row>
-    <row r="910" spans="1:8" ht="15" thickBot="1">
+    <row r="910" spans="1:8" ht="15.75" thickBot="1">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -11988,7 +11936,7 @@
       <c r="G910" s="1"/>
       <c r="H910" s="1"/>
     </row>
-    <row r="911" spans="1:8" ht="15" thickBot="1">
+    <row r="911" spans="1:8" ht="15.75" thickBot="1">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -11998,7 +11946,7 @@
       <c r="G911" s="1"/>
       <c r="H911" s="1"/>
     </row>
-    <row r="912" spans="1:8" ht="15" thickBot="1">
+    <row r="912" spans="1:8" ht="15.75" thickBot="1">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -12008,7 +11956,7 @@
       <c r="G912" s="1"/>
       <c r="H912" s="1"/>
     </row>
-    <row r="913" spans="1:8" ht="15" thickBot="1">
+    <row r="913" spans="1:8" ht="15.75" thickBot="1">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -12018,7 +11966,7 @@
       <c r="G913" s="1"/>
       <c r="H913" s="1"/>
     </row>
-    <row r="914" spans="1:8" ht="15" thickBot="1">
+    <row r="914" spans="1:8" ht="15.75" thickBot="1">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -12028,7 +11976,7 @@
       <c r="G914" s="1"/>
       <c r="H914" s="1"/>
     </row>
-    <row r="915" spans="1:8" ht="15" thickBot="1">
+    <row r="915" spans="1:8" ht="15.75" thickBot="1">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -12037,26 +11985,6 @@
       <c r="F915" s="1"/>
       <c r="G915" s="1"/>
       <c r="H915" s="1"/>
-    </row>
-    <row r="916" spans="1:8" ht="15" thickBot="1">
-      <c r="A916" s="1"/>
-      <c r="B916" s="1"/>
-      <c r="C916" s="1"/>
-      <c r="D916" s="1"/>
-      <c r="E916" s="1"/>
-      <c r="F916" s="1"/>
-      <c r="G916" s="1"/>
-      <c r="H916" s="1"/>
-    </row>
-    <row r="917" spans="1:8" ht="15" thickBot="1">
-      <c r="A917" s="1"/>
-      <c r="B917" s="1"/>
-      <c r="C917" s="1"/>
-      <c r="D917" s="1"/>
-      <c r="E917" s="1"/>
-      <c r="F917" s="1"/>
-      <c r="G917" s="1"/>
-      <c r="H917" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -12079,52 +12007,50 @@
     <hyperlink ref="A26" r:id="rId17" display="https://www.rcsb.org/structure/6CWC" xr:uid="{1A4A4F9F-7517-476F-B7C0-98508C1E2D42}"/>
     <hyperlink ref="A27" r:id="rId18" display="https://www.rcsb.org/structure/2VYU" xr:uid="{BB4571DD-C2EF-414D-93BE-708C67B410B8}"/>
     <hyperlink ref="A29" r:id="rId19" display="https://www.rcsb.org/structure/3R6U" xr:uid="{EF0EEBA3-92A2-46F6-8978-BFB597BC1A51}"/>
-    <hyperlink ref="A30" r:id="rId20" display="https://www.rcsb.org/structure/4ZCQ" xr:uid="{FF5E3848-D799-4BB7-81A3-35748893D661}"/>
-    <hyperlink ref="A31" r:id="rId21" display="https://www.rcsb.org/structure/4DOJ" xr:uid="{2250E647-D46C-4BD3-A9B4-99BC88A3F57A}"/>
-    <hyperlink ref="A32" r:id="rId22" display="https://www.rcsb.org/structure/2HV2" xr:uid="{658F781C-395A-43F6-A3A1-B5ECAF5C2AA2}"/>
-    <hyperlink ref="A33" r:id="rId23" display="https://www.rcsb.org/structure/2I00" xr:uid="{C7BC2BA7-E9F3-4113-98CD-FE40F3E89005}"/>
-    <hyperlink ref="A35" r:id="rId24" display="https://www.rcsb.org/structure/1PZ4" xr:uid="{1254DE86-F93E-48DF-A641-632A6868E9AA}"/>
-    <hyperlink ref="A36" r:id="rId25" display="https://www.rcsb.org/structure/9L5M" xr:uid="{46A292EE-B117-433C-8868-56E9E43C739C}"/>
-    <hyperlink ref="A37" r:id="rId26" display="https://www.rcsb.org/structure/5A23" xr:uid="{077B7CFB-34B2-4D74-AC1B-087916D9D579}"/>
-    <hyperlink ref="A38" r:id="rId27" display="https://www.rcsb.org/structure/1U53" xr:uid="{EBF411F8-A255-41AE-B7B2-AFDA52331907}"/>
-    <hyperlink ref="A39" r:id="rId28" display="https://www.rcsb.org/structure/1QNX" xr:uid="{A5C8F691-7B08-42DD-8F92-95FFFAD2ADD8}"/>
-    <hyperlink ref="A40" r:id="rId29" display="https://www.rcsb.org/structure/5ETE" xr:uid="{51C33BAC-3879-4E7D-8672-8E871F8BCA44}"/>
-    <hyperlink ref="C42" r:id="rId30" display="https://www.ebi.ac.uk/interpro/protein/reviewed/A2A5I3/" xr:uid="{4E8BCA6B-5FF0-4D2C-9157-335F9382E810}"/>
-    <hyperlink ref="C43" r:id="rId31" display="https://www.ebi.ac.uk/interpro/protein/reviewed/F8S0Y4/" xr:uid="{1FD524EA-B014-4850-A214-28D0595930A5}"/>
-    <hyperlink ref="A47" r:id="rId32" display="https://www.rcsb.org/structure/3WA5" xr:uid="{9B0B2FB8-F72B-420A-8792-77567E695F8E}"/>
-    <hyperlink ref="A48" r:id="rId33" display="https://www.rcsb.org/structure/8B2E" xr:uid="{3AD389D4-8E45-4797-B549-69ACCBF73BE2}"/>
-    <hyperlink ref="A49" r:id="rId34" display="https://www.rcsb.org/structure/9M3L" xr:uid="{7288A9A6-7997-4857-B4AE-412905AD2394}"/>
-    <hyperlink ref="A50" r:id="rId35" display="https://www.rcsb.org/structure/8B2S" xr:uid="{9C35D557-26F8-4F1B-B4B6-0BBBDEE3D575}"/>
-    <hyperlink ref="A51" r:id="rId36" display="https://www.rcsb.org/structure/6ZM8" xr:uid="{196EEBB3-421A-479B-9545-4337CEE62909}"/>
-    <hyperlink ref="A52" r:id="rId37" display="https://www.rcsb.org/structure/1MT5" xr:uid="{6F593402-5255-47F6-A2E0-EF81D1C513DF}"/>
-    <hyperlink ref="A53" r:id="rId38" display="https://www.rcsb.org/structure/2DC0" xr:uid="{378E57AD-711E-4201-8FBE-5946209F7EF7}"/>
-    <hyperlink ref="A54" r:id="rId39" display="https://www.rcsb.org/structure/1M22" xr:uid="{EBA3F6DC-E5D2-4E7B-B8D4-C17EAFA5A7DD}"/>
-    <hyperlink ref="A55" r:id="rId40" display="https://www.rcsb.org/structure/1YB0" xr:uid="{43331F3E-003B-47D8-9C6C-02608ED9F42D}"/>
-    <hyperlink ref="A56" r:id="rId41" display="https://www.rcsb.org/structure/4R3K" xr:uid="{C39B20E5-70BA-4054-869E-7D3A2BEAE800}"/>
-    <hyperlink ref="A57" r:id="rId42" display="https://www.rcsb.org/structure/2VFC" xr:uid="{622D474D-63B3-41AE-B6A0-2DFA267A1CE7}"/>
-    <hyperlink ref="A58" r:id="rId43" display="https://www.rcsb.org/structure/9M5S" xr:uid="{B2A1D695-843E-4F36-A701-3A2045CDA8AB}"/>
-    <hyperlink ref="A59" r:id="rId44" display="https://www.rcsb.org/structure/4XCM" xr:uid="{066A6BD0-99A3-4918-BFDB-EE4EA948043D}"/>
-    <hyperlink ref="A60" r:id="rId45" display="https://www.rcsb.org/structure/1P3C" xr:uid="{60F367BE-F3E6-4EC3-83D3-C7D3AC802686}"/>
-    <hyperlink ref="A61" r:id="rId46" display="https://www.ebi.ac.uk/interpro/protein/reviewed/A6QLZ7/" xr:uid="{1A7E06D3-A437-4544-A73A-6999A32A6BCE}"/>
-    <hyperlink ref="A62" r:id="rId47" display="https://www.ebi.ac.uk/interpro/protein/reviewed/A6YPK1/" xr:uid="{1CDA67FC-DE33-4E82-8E57-827AEA1FF018}"/>
-    <hyperlink ref="A63" r:id="rId48" display="https://www.ebi.ac.uk/interpro/protein/reviewed/A7X4T8/" xr:uid="{F8A3138B-E4A1-4E3C-8417-72F2C870E400}"/>
-    <hyperlink ref="A64" r:id="rId49" display="https://www.ebi.ac.uk/interpro/protein/reviewed/A8S6B6/" xr:uid="{B3DA1AB5-9235-4693-B529-FAEC0D6E2FBE}"/>
-    <hyperlink ref="A65" r:id="rId50" display="https://www.ebi.ac.uk/interpro/protein/reviewed/B3EWZ8/" xr:uid="{CE290D6E-AAD4-463D-83B4-4B8F1193B724}"/>
-    <hyperlink ref="A66" r:id="rId51" display="https://www.ebi.ac.uk/interpro/protein/reviewed/G2XGR1/" xr:uid="{491E7A35-F62B-4F3C-936C-EEE577BDCD3E}"/>
-    <hyperlink ref="A67" r:id="rId52" display="https://www.ebi.ac.uk/interpro/protein/reviewed/G4N4E9/" xr:uid="{0F6E93CF-7C7D-4E35-864D-D3B7EACAADCC}"/>
-    <hyperlink ref="A68" r:id="rId53" display="https://www.ebi.ac.uk/interpro/protein/reviewed/O34586/" xr:uid="{5DBE5A7C-D26A-407C-9EF8-D9BA3AFF00BA}"/>
-    <hyperlink ref="A69" r:id="rId54" display="https://www.ebi.ac.uk/interpro/protein/reviewed/P04284/" xr:uid="{902428B5-3B5B-4316-A0AA-E8597AAEED78}"/>
-    <hyperlink ref="A70" r:id="rId55" display="https://www.ebi.ac.uk/interpro/protein/reviewed/P07053/" xr:uid="{E9181D28-A7AC-4E98-9627-4BF741C230AB}"/>
-    <hyperlink ref="A72" r:id="rId56" display="https://www.ebi.ac.uk/interpro/protein/reviewed/P47033/" xr:uid="{98D84556-DE69-45A6-9DDA-C6F7E72A6855}"/>
-    <hyperlink ref="A73" r:id="rId57" display="https://www.ebi.ac.uk/interpro/protein/reviewed/P48060/" xr:uid="{391F9303-2E8C-4D96-8D03-93C7888EAA91}"/>
-    <hyperlink ref="A74" r:id="rId58" display="https://www.ebi.ac.uk/interpro/protein/reviewed/Q00008/" xr:uid="{37132AFB-7ECF-4347-86E8-3B8AD51151DC}"/>
-    <hyperlink ref="A75" r:id="rId59" display="https://www.ebi.ac.uk/interpro/protein/reviewed/Q05968/" xr:uid="{BC2160FB-7B03-458E-86E6-239E23D4E347}"/>
-    <hyperlink ref="A77" r:id="rId60" display="https://www.ebi.ac.uk/interpro/protein/reviewed/P39578/" xr:uid="{0350B161-24A2-400F-A564-68D45BF836AF}"/>
-    <hyperlink ref="A78" r:id="rId61" display="https://www.ebi.ac.uk/interpro/protein/reviewed/C0H3T3/" xr:uid="{0866B68F-4B85-4967-AFAA-A69BB12EE122}"/>
-    <hyperlink ref="C78" r:id="rId62" display="https://www.ebi.ac.uk/interpro/protein/reviewed/C0H3T3/" xr:uid="{2FA58E87-4E9F-4DFC-90E7-38A1D6FBC6DF}"/>
+    <hyperlink ref="A30" r:id="rId20" display="https://www.rcsb.org/structure/4DOJ" xr:uid="{2250E647-D46C-4BD3-A9B4-99BC88A3F57A}"/>
+    <hyperlink ref="A31" r:id="rId21" display="https://www.rcsb.org/structure/2HV2" xr:uid="{658F781C-395A-43F6-A3A1-B5ECAF5C2AA2}"/>
+    <hyperlink ref="A32" r:id="rId22" display="https://www.rcsb.org/structure/2I00" xr:uid="{C7BC2BA7-E9F3-4113-98CD-FE40F3E89005}"/>
+    <hyperlink ref="A34" r:id="rId23" display="https://www.rcsb.org/structure/1PZ4" xr:uid="{1254DE86-F93E-48DF-A641-632A6868E9AA}"/>
+    <hyperlink ref="A35" r:id="rId24" display="https://www.rcsb.org/structure/9L5M" xr:uid="{46A292EE-B117-433C-8868-56E9E43C739C}"/>
+    <hyperlink ref="A36" r:id="rId25" display="https://www.rcsb.org/structure/1U53" xr:uid="{EBF411F8-A255-41AE-B7B2-AFDA52331907}"/>
+    <hyperlink ref="A37" r:id="rId26" display="https://www.rcsb.org/structure/1QNX" xr:uid="{A5C8F691-7B08-42DD-8F92-95FFFAD2ADD8}"/>
+    <hyperlink ref="A38" r:id="rId27" display="https://www.rcsb.org/structure/5ETE" xr:uid="{51C33BAC-3879-4E7D-8672-8E871F8BCA44}"/>
+    <hyperlink ref="C40" r:id="rId28" display="https://www.ebi.ac.uk/interpro/protein/reviewed/A2A5I3/" xr:uid="{4E8BCA6B-5FF0-4D2C-9157-335F9382E810}"/>
+    <hyperlink ref="C41" r:id="rId29" display="https://www.ebi.ac.uk/interpro/protein/reviewed/F8S0Y4/" xr:uid="{1FD524EA-B014-4850-A214-28D0595930A5}"/>
+    <hyperlink ref="A45" r:id="rId30" display="https://www.rcsb.org/structure/3WA5" xr:uid="{9B0B2FB8-F72B-420A-8792-77567E695F8E}"/>
+    <hyperlink ref="A46" r:id="rId31" display="https://www.rcsb.org/structure/8B2E" xr:uid="{3AD389D4-8E45-4797-B549-69ACCBF73BE2}"/>
+    <hyperlink ref="A47" r:id="rId32" display="https://www.rcsb.org/structure/9M3L" xr:uid="{7288A9A6-7997-4857-B4AE-412905AD2394}"/>
+    <hyperlink ref="A48" r:id="rId33" display="https://www.rcsb.org/structure/8B2S" xr:uid="{9C35D557-26F8-4F1B-B4B6-0BBBDEE3D575}"/>
+    <hyperlink ref="A49" r:id="rId34" display="https://www.rcsb.org/structure/6ZM8" xr:uid="{196EEBB3-421A-479B-9545-4337CEE62909}"/>
+    <hyperlink ref="A50" r:id="rId35" display="https://www.rcsb.org/structure/1MT5" xr:uid="{6F593402-5255-47F6-A2E0-EF81D1C513DF}"/>
+    <hyperlink ref="A51" r:id="rId36" display="https://www.rcsb.org/structure/2DC0" xr:uid="{378E57AD-711E-4201-8FBE-5946209F7EF7}"/>
+    <hyperlink ref="A52" r:id="rId37" display="https://www.rcsb.org/structure/1M22" xr:uid="{EBA3F6DC-E5D2-4E7B-B8D4-C17EAFA5A7DD}"/>
+    <hyperlink ref="A53" r:id="rId38" display="https://www.rcsb.org/structure/1YB0" xr:uid="{43331F3E-003B-47D8-9C6C-02608ED9F42D}"/>
+    <hyperlink ref="A54" r:id="rId39" display="https://www.rcsb.org/structure/4R3K" xr:uid="{C39B20E5-70BA-4054-869E-7D3A2BEAE800}"/>
+    <hyperlink ref="A55" r:id="rId40" display="https://www.rcsb.org/structure/2VFC" xr:uid="{622D474D-63B3-41AE-B6A0-2DFA267A1CE7}"/>
+    <hyperlink ref="A56" r:id="rId41" display="https://www.rcsb.org/structure/9M5S" xr:uid="{B2A1D695-843E-4F36-A701-3A2045CDA8AB}"/>
+    <hyperlink ref="A57" r:id="rId42" display="https://www.rcsb.org/structure/4XCM" xr:uid="{066A6BD0-99A3-4918-BFDB-EE4EA948043D}"/>
+    <hyperlink ref="A58" r:id="rId43" display="https://www.rcsb.org/structure/1P3C" xr:uid="{60F367BE-F3E6-4EC3-83D3-C7D3AC802686}"/>
+    <hyperlink ref="A59" r:id="rId44" display="https://www.ebi.ac.uk/interpro/protein/reviewed/A6QLZ7/" xr:uid="{1A7E06D3-A437-4544-A73A-6999A32A6BCE}"/>
+    <hyperlink ref="A60" r:id="rId45" display="https://www.ebi.ac.uk/interpro/protein/reviewed/A6YPK1/" xr:uid="{1CDA67FC-DE33-4E82-8E57-827AEA1FF018}"/>
+    <hyperlink ref="A61" r:id="rId46" display="https://www.ebi.ac.uk/interpro/protein/reviewed/A7X4T8/" xr:uid="{F8A3138B-E4A1-4E3C-8417-72F2C870E400}"/>
+    <hyperlink ref="A62" r:id="rId47" display="https://www.ebi.ac.uk/interpro/protein/reviewed/A8S6B6/" xr:uid="{B3DA1AB5-9235-4693-B529-FAEC0D6E2FBE}"/>
+    <hyperlink ref="A63" r:id="rId48" display="https://www.ebi.ac.uk/interpro/protein/reviewed/B3EWZ8/" xr:uid="{CE290D6E-AAD4-463D-83B4-4B8F1193B724}"/>
+    <hyperlink ref="A64" r:id="rId49" display="https://www.ebi.ac.uk/interpro/protein/reviewed/G2XGR1/" xr:uid="{491E7A35-F62B-4F3C-936C-EEE577BDCD3E}"/>
+    <hyperlink ref="A65" r:id="rId50" display="https://www.ebi.ac.uk/interpro/protein/reviewed/G4N4E9/" xr:uid="{0F6E93CF-7C7D-4E35-864D-D3B7EACAADCC}"/>
+    <hyperlink ref="A66" r:id="rId51" display="https://www.ebi.ac.uk/interpro/protein/reviewed/O34586/" xr:uid="{5DBE5A7C-D26A-407C-9EF8-D9BA3AFF00BA}"/>
+    <hyperlink ref="A67" r:id="rId52" display="https://www.ebi.ac.uk/interpro/protein/reviewed/P04284/" xr:uid="{902428B5-3B5B-4316-A0AA-E8597AAEED78}"/>
+    <hyperlink ref="A68" r:id="rId53" display="https://www.ebi.ac.uk/interpro/protein/reviewed/P07053/" xr:uid="{E9181D28-A7AC-4E98-9627-4BF741C230AB}"/>
+    <hyperlink ref="A70" r:id="rId54" display="https://www.ebi.ac.uk/interpro/protein/reviewed/P47033/" xr:uid="{98D84556-DE69-45A6-9DDA-C6F7E72A6855}"/>
+    <hyperlink ref="A71" r:id="rId55" display="https://www.ebi.ac.uk/interpro/protein/reviewed/P48060/" xr:uid="{391F9303-2E8C-4D96-8D03-93C7888EAA91}"/>
+    <hyperlink ref="A72" r:id="rId56" display="https://www.ebi.ac.uk/interpro/protein/reviewed/Q00008/" xr:uid="{37132AFB-7ECF-4347-86E8-3B8AD51151DC}"/>
+    <hyperlink ref="A73" r:id="rId57" display="https://www.ebi.ac.uk/interpro/protein/reviewed/Q05968/" xr:uid="{BC2160FB-7B03-458E-86E6-239E23D4E347}"/>
+    <hyperlink ref="A75" r:id="rId58" display="https://www.ebi.ac.uk/interpro/protein/reviewed/P39578/" xr:uid="{0350B161-24A2-400F-A564-68D45BF836AF}"/>
+    <hyperlink ref="A76" r:id="rId59" display="https://www.ebi.ac.uk/interpro/protein/reviewed/C0H3T3/" xr:uid="{0866B68F-4B85-4967-AFAA-A69BB12EE122}"/>
+    <hyperlink ref="C76" r:id="rId60" display="https://www.ebi.ac.uk/interpro/protein/reviewed/C0H3T3/" xr:uid="{2FA58E87-4E9F-4DFC-90E7-38A1D6FBC6DF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId63"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId61"/>
 </worksheet>
 </file>
 
